--- a/pricing/output/trinity-pricing-text.xlsx
+++ b/pricing/output/trinity-pricing-text.xlsx
@@ -8,7 +8,8 @@
     <sheet name="百炼北京" sheetId="3" r:id="rId3"/>
     <sheet name="AIGC国内站" sheetId="4" r:id="rId4"/>
     <sheet name="AIGC国际站" sheetId="5" r:id="rId5"/>
-    <sheet name="汇总-供应商vs官方" sheetId="6" r:id="rId6"/>
+    <sheet name="火山方舟" sheetId="6" r:id="rId6"/>
+    <sheet name="汇总-供应商vs官方" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -402,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -462,7 +463,7 @@
         <v>claude-opus-4-6</v>
       </c>
       <c r="B2" t="str">
-        <v>claude-opus-4-6</v>
+        <v>Claude Opus 4.6</v>
       </c>
       <c r="C2" t="str">
         <v>Anthropic</v>
@@ -515,7 +516,7 @@
         <v>claude-opus-4-7</v>
       </c>
       <c r="B3" t="str">
-        <v>claude-opus-4-7</v>
+        <v>Claude Opus 4.7</v>
       </c>
       <c r="C3" t="str">
         <v>Anthropic</v>
@@ -568,7 +569,7 @@
         <v>claude-opus-4-8</v>
       </c>
       <c r="B4" t="str">
-        <v>claude-opus-4-8</v>
+        <v>Claude Opus 4.8</v>
       </c>
       <c r="C4" t="str">
         <v>Anthropic</v>
@@ -621,7 +622,7 @@
         <v>claude-sonnet-4-6</v>
       </c>
       <c r="B5" t="str">
-        <v>claude-sonnet-4-6</v>
+        <v>Claude Sonnet 4.6</v>
       </c>
       <c r="C5" t="str">
         <v>Anthropic</v>
@@ -942,10 +943,10 @@
         <v>Gemini 2.5 Flash</v>
       </c>
       <c r="C11" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="D11" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="E11" t="str">
         <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
@@ -960,7 +961,7 @@
         <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="I11" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.033846</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="J11" t="str">
         <v>0%</v>
@@ -969,7 +970,7 @@
         <v>0%</v>
       </c>
       <c r="L11" t="str">
-        <v>+12.8%</v>
+        <v>0%</v>
       </c>
       <c r="M11" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -981,7 +982,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P11" t="str">
-        <v>入✅ 出✅ 缓⚠+12.8%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q11" t="str">
         <v/>
@@ -989,7 +990,7 @@
     </row>
     <row r="12">
       <c r="D12" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="E12" t="str">
         <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
@@ -1004,7 +1005,7 @@
         <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="I12" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.033846</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="J12" t="str">
         <v>-70%</v>
@@ -1013,7 +1014,7 @@
         <v>0%</v>
       </c>
       <c r="L12" t="str">
-        <v>-66.2%</v>
+        <v>-70%</v>
       </c>
       <c r="M12" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1039,7 +1040,7 @@
         <v>Gemini 2.5 Flash Lite</v>
       </c>
       <c r="C13" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="D13" t="str">
         <v>统一价</v>
@@ -1057,7 +1058,7 @@
         <v>入 $0.09999999999999999 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
       <c r="I13" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.011538</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="J13" t="str">
         <v>0%</v>
@@ -1066,7 +1067,7 @@
         <v>0%</v>
       </c>
       <c r="L13" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M13" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1078,7 +1079,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P13" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q13" t="str">
         <v/>
@@ -1092,7 +1093,7 @@
         <v>Gemini 2.5 Flash Lite Preview</v>
       </c>
       <c r="C14" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="D14" t="str">
         <v>统一价</v>
@@ -1110,7 +1111,7 @@
         <v>入 $0.09999999999999999 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
       <c r="I14" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.011538</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="J14" t="str">
         <v>0%</v>
@@ -1119,7 +1120,7 @@
         <v>0%</v>
       </c>
       <c r="L14" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M14" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1131,7 +1132,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P14" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q14" t="str">
         <v>preview 别名，价目同 gemini-2.5-flash-lite</v>
@@ -1145,10 +1146,10 @@
         <v>Gemini 2.5 Pro</v>
       </c>
       <c r="C15" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="D15" t="str">
-        <v>输入&lt;=20万个token</v>
+        <v>输入≤20万个token</v>
       </c>
       <c r="E15" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
@@ -1163,7 +1164,7 @@
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="I15" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.143077</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="J15" t="str">
         <v>0%</v>
@@ -1172,7 +1173,7 @@
         <v>0%</v>
       </c>
       <c r="L15" t="str">
-        <v>+14.5%</v>
+        <v>0%</v>
       </c>
       <c r="M15" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1184,7 +1185,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P15" t="str">
-        <v>入✅ 出✅ 缓⚠+14.5%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q15" t="str">
         <v/>
@@ -1207,7 +1208,7 @@
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="I16" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.287692</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="J16" t="str">
         <v>0%</v>
@@ -1216,7 +1217,7 @@
         <v>0%</v>
       </c>
       <c r="L16" t="str">
-        <v>+15.1%</v>
+        <v>0%</v>
       </c>
       <c r="M16" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1228,7 +1229,7 @@
         <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
       <c r="P16" t="str">
-        <v>入✅ 出✅ 缓⚠+15.1%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q16" t="str">
         <v/>
@@ -1242,10 +1243,10 @@
         <v>Gemini 3 Flash Preview</v>
       </c>
       <c r="C17" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="D17" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="E17" t="str">
         <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
@@ -1260,7 +1261,7 @@
         <v>入 $0.5 · 出 $3 · 缓 $0.049999999999999996</v>
       </c>
       <c r="I17" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.053846</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
       <c r="J17" t="str">
         <v>0%</v>
@@ -1269,7 +1270,7 @@
         <v>0%</v>
       </c>
       <c r="L17" t="str">
-        <v>+7.7%</v>
+        <v>0%</v>
       </c>
       <c r="M17" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1281,7 +1282,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P17" t="str">
-        <v>入✅ 出✅ 缓⚠+7.7%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q17" t="str">
         <v/>
@@ -1289,7 +1290,7 @@
     </row>
     <row r="18">
       <c r="D18" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="E18" t="str">
         <v>入 $1 · 出 $3 · 缓 $0.1</v>
@@ -1304,7 +1305,7 @@
         <v>入 $0.5 · 出 $3 · 缓 $0.049999999999999996</v>
       </c>
       <c r="I18" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.053846</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
       <c r="J18" t="str">
         <v>-50%</v>
@@ -1313,7 +1314,7 @@
         <v>0%</v>
       </c>
       <c r="L18" t="str">
-        <v>-46.2%</v>
+        <v>-50%</v>
       </c>
       <c r="M18" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1339,10 +1340,10 @@
         <v>Gemini 3.1 Flash Lite</v>
       </c>
       <c r="C19" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="D19" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="E19" t="str">
         <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
@@ -1357,7 +1358,7 @@
         <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
       </c>
       <c r="I19" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.027692</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
       <c r="J19" t="str">
         <v>0%</v>
@@ -1366,7 +1367,7 @@
         <v>0%</v>
       </c>
       <c r="L19" t="str">
-        <v>+10.8%</v>
+        <v>0%</v>
       </c>
       <c r="M19" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1378,7 +1379,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P19" t="str">
-        <v>入✅ 出✅ 缓⚠+10.8%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q19" t="str">
         <v/>
@@ -1386,7 +1387,7 @@
     </row>
     <row r="20">
       <c r="D20" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="E20" t="str">
         <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
@@ -1401,7 +1402,7 @@
         <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
       </c>
       <c r="I20" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.027692</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
       <c r="J20" t="str">
         <v>-50%</v>
@@ -1410,7 +1411,7 @@
         <v>0%</v>
       </c>
       <c r="L20" t="str">
-        <v>-44.6%</v>
+        <v>-50%</v>
       </c>
       <c r="M20" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1436,10 +1437,10 @@
         <v>Gemini 3.1 Flash Lite Preview</v>
       </c>
       <c r="C21" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="D21" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="E21" t="str">
         <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
@@ -1454,7 +1455,7 @@
         <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
       </c>
       <c r="I21" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.027692</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
       <c r="J21" t="str">
         <v>0%</v>
@@ -1463,7 +1464,7 @@
         <v>0%</v>
       </c>
       <c r="L21" t="str">
-        <v>+10.8%</v>
+        <v>0%</v>
       </c>
       <c r="M21" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1475,7 +1476,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P21" t="str">
-        <v>入✅ 出✅ 缓⚠+10.8%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q21" t="str">
         <v/>
@@ -1483,7 +1484,7 @@
     </row>
     <row r="22">
       <c r="D22" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="E22" t="str">
         <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
@@ -1498,7 +1499,7 @@
         <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
       </c>
       <c r="I22" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.027692</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
       <c r="J22" t="str">
         <v>-50%</v>
@@ -1507,7 +1508,7 @@
         <v>0%</v>
       </c>
       <c r="L22" t="str">
-        <v>-44.6%</v>
+        <v>-50%</v>
       </c>
       <c r="M22" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1533,10 +1534,10 @@
         <v>Gemini 3.1 Pro Preview</v>
       </c>
       <c r="C23" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="D23" t="str">
-        <v>输入&lt;=20万个token</v>
+        <v>输入≤20万个token</v>
       </c>
       <c r="E23" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
@@ -1551,7 +1552,7 @@
         <v>入 $2 · 出 $12 · 缓 $0.19999999999999998</v>
       </c>
       <c r="I23" t="str">
-        <v>入 $2 · 出 $12 · 缓 $0.230769</v>
+        <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
       <c r="J23" t="str">
         <v>0%</v>
@@ -1560,7 +1561,7 @@
         <v>0%</v>
       </c>
       <c r="L23" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M23" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1572,7 +1573,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P23" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q23" t="str">
         <v/>
@@ -1595,7 +1596,7 @@
         <v>入 $2 · 出 $12 · 缓 $0.19999999999999998</v>
       </c>
       <c r="I24" t="str">
-        <v>入 $4 · 出 $18 · 缓 $0.461538</v>
+        <v>入 $4 · 出 $18 · 缓 $0.4</v>
       </c>
       <c r="J24" t="str">
         <v>0%</v>
@@ -1604,7 +1605,7 @@
         <v>0%</v>
       </c>
       <c r="L24" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M24" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1616,7 +1617,7 @@
         <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
       <c r="P24" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q24" t="str">
         <v/>
@@ -1630,10 +1631,10 @@
         <v>Gemini 3.5 Flash</v>
       </c>
       <c r="C25" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="D25" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="E25" t="str">
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
@@ -1648,7 +1649,7 @@
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="I25" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.173077</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="J25" t="str">
         <v>0%</v>
@@ -1657,7 +1658,7 @@
         <v>0%</v>
       </c>
       <c r="L25" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M25" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1669,7 +1670,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P25" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q25" t="str">
         <v/>
@@ -1677,7 +1678,7 @@
     </row>
     <row r="26">
       <c r="D26" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="E26" t="str">
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
@@ -1692,7 +1693,7 @@
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="I26" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.173077</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="J26" t="str">
         <v>0%</v>
@@ -1701,7 +1702,7 @@
         <v>0%</v>
       </c>
       <c r="L26" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M26" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1736,7 +1737,7 @@
         <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="F27" t="str">
-        <v>入 $0.924 · 出 $3.388 · 缓 $0.231</v>
+        <v>—</v>
       </c>
       <c r="G27" t="str">
         <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
@@ -1745,7 +1746,7 @@
         <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
       </c>
       <c r="I27" t="str">
-        <v>入 $0.923077 · 出 $3.384615 · 缓 $0.154</v>
+        <v>入 $0.923077 · 出 $3.384615 · 缓 $0.230769</v>
       </c>
       <c r="J27" t="str">
         <v>0%</v>
@@ -1754,10 +1755,10 @@
         <v>0%</v>
       </c>
       <c r="L27" t="str">
-        <v>-33.3%</v>
+        <v>0%</v>
       </c>
       <c r="M27" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N27" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1766,7 +1767,7 @@
         <v>入⚠-35% 出⚠-43.3% 缓⚠-48%</v>
       </c>
       <c r="P27" t="str">
-        <v>入✅ 出✅ 缓⚠-33.3%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q27" t="str">
         <v/>
@@ -1780,7 +1781,7 @@
         <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="F28" t="str">
-        <v>入 $0.616 · 出 $2.772 · 缓 $0.154</v>
+        <v>—</v>
       </c>
       <c r="G28" t="str">
         <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
@@ -1789,7 +1790,7 @@
         <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
       </c>
       <c r="I28" t="str">
-        <v>入 $0.615385 · 出 $2.769231 · 缓 $0.231</v>
+        <v>入 $0.615385 · 出 $2.769231 · 缓 $0.153846</v>
       </c>
       <c r="J28" t="str">
         <v>0%</v>
@@ -1798,10 +1799,10 @@
         <v>0%</v>
       </c>
       <c r="L28" t="str">
-        <v>+50.1%</v>
+        <v>0%</v>
       </c>
       <c r="M28" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N28" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1810,39 +1811,30 @@
         <v>入⚠-2.5% 出⚠-30.7% 缓⚠-22%</v>
       </c>
       <c r="P28" t="str">
-        <v>入✅ 出✅ 缓⚠+50.1%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>glm-5-turbo</v>
-      </c>
-      <c r="B29" t="str">
-        <v>GLM 5 Turbo</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Zhipu</v>
-      </c>
       <c r="D29" t="str">
-        <v>输入&gt;=32k</v>
+        <v>输入：≤32K token</v>
       </c>
       <c r="E29" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="F29" t="str">
-        <v>入 $1.078 · 出 $4.004 · 缓 $0.277</v>
+        <v>入 $0.616 · 出 $2.772 · 缓 $0.154</v>
       </c>
       <c r="G29" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>—</v>
       </c>
       <c r="H29" t="str">
-        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
+        <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
       </c>
       <c r="I29" t="str">
-        <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
+        <v>入 $0.615385 · 出 $2.769231 · 缓 $0.153846</v>
       </c>
       <c r="J29" t="str">
         <v>0%</v>
@@ -1857,10 +1849,10 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N29" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O29" t="str">
-        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
+        <v>入⚠-2.5% 出⚠-30.7% 缓⚠-22%</v>
       </c>
       <c r="P29" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1871,22 +1863,22 @@
     </row>
     <row r="30">
       <c r="D30" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>输入：＞32K token</v>
       </c>
       <c r="E30" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="F30" t="str">
-        <v>入 $0.77 · 出 $3.388 · 缓 $0.185</v>
+        <v>入 $0.924 · 出 $3.388 · 缓 $0.231</v>
       </c>
       <c r="G30" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>—</v>
       </c>
       <c r="H30" t="str">
-        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
+        <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
       </c>
       <c r="I30" t="str">
-        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
+        <v>入 $0.923077 · 出 $3.384615 · 缓 $0.230769</v>
       </c>
       <c r="J30" t="str">
         <v>0%</v>
@@ -1901,10 +1893,10 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N30" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O30" t="str">
-        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
+        <v>入⚠-35% 出⚠-43.3% 缓⚠-48%</v>
       </c>
       <c r="P30" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1915,31 +1907,31 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>glm-5.1</v>
+        <v>glm-5-turbo</v>
       </c>
       <c r="B31" t="str">
-        <v>GLM-5.1</v>
+        <v>GLM 5 Turbo</v>
       </c>
       <c r="C31" t="str">
         <v>Zhipu</v>
       </c>
       <c r="D31" t="str">
-        <v>32k&lt;=输入</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="E31" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="F31" t="str">
-        <v>入 $1.232 · 出 $4.312 · 缓 $0.308</v>
+        <v>—</v>
       </c>
       <c r="G31" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="H31" t="str">
-        <v>入 $0.975 · 出 $4.300000000000001</v>
+        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="I31" t="str">
-        <v>入 $1.230769 · 出 $4.307692 · 缓 $0.2</v>
+        <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
       </c>
       <c r="J31" t="str">
         <v>0%</v>
@@ -1948,19 +1940,19 @@
         <v>0%</v>
       </c>
       <c r="L31" t="str">
-        <v>-35%</v>
+        <v>0%</v>
       </c>
       <c r="M31" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N31" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O31" t="str">
-        <v>入⚠-20.8% 出✅</v>
+        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
       </c>
       <c r="P31" t="str">
-        <v>入✅ 出✅ 缓⚠-35%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q31" t="str">
         <v/>
@@ -1971,19 +1963,19 @@
         <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="E32" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="F32" t="str">
-        <v>入 $0.924 · 出 $3.696 · 缓 $0.2</v>
+        <v>—</v>
       </c>
       <c r="G32" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="H32" t="str">
-        <v>入 $0.975 · 出 $4.300000000000001</v>
+        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="I32" t="str">
-        <v>入 $0.923077 · 出 $3.692308 · 缓 $0.308</v>
+        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
       </c>
       <c r="J32" t="str">
         <v>0%</v>
@@ -1992,51 +1984,42 @@
         <v>0%</v>
       </c>
       <c r="L32" t="str">
-        <v>+54%</v>
+        <v>0%</v>
       </c>
       <c r="M32" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N32" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O32" t="str">
-        <v>入⚠+5.6% 出⚠+16.5%</v>
+        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
       </c>
       <c r="P32" t="str">
-        <v>入✅ 出✅ 缓⚠+54%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>glm-5.2</v>
-      </c>
-      <c r="B33" t="str">
-        <v>GLM-5.2</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Zhipu</v>
-      </c>
       <c r="D33" t="str">
-        <v>统一价</v>
+        <v>输入：≤32K token</v>
       </c>
       <c r="E33" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="F33" t="str">
-        <v>—</v>
+        <v>入 $0.77 · 出 $3.388 · 缓 $0.185</v>
       </c>
       <c r="G33" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>—</v>
       </c>
       <c r="H33" t="str">
-        <v>入 $0.9299999999999999 · 出 $3 · 缓 $0.18</v>
+        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="I33" t="str">
-        <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
+        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
       </c>
       <c r="J33" t="str">
         <v>0%</v>
@@ -2048,13 +2031,13 @@
         <v>0%</v>
       </c>
       <c r="M33" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N33" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O33" t="str">
-        <v>入⚠-24.4% 出⚠-30.4% 缓⚠-41.5%</v>
+        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
       </c>
       <c r="P33" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2064,26 +2047,17 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>glm-5v-turbo</v>
-      </c>
-      <c r="B34" t="str">
-        <v>GLM-5V Turbo</v>
-      </c>
-      <c r="C34" t="str">
-        <v>Zhipu</v>
-      </c>
       <c r="D34" t="str">
-        <v>输入&gt;=32k</v>
+        <v>输入：＞32K token</v>
       </c>
       <c r="E34" t="str">
         <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="F34" t="str">
-        <v>—</v>
+        <v>入 $1.078 · 出 $4.004 · 缓 $0.277</v>
       </c>
       <c r="G34" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>—</v>
       </c>
       <c r="H34" t="str">
         <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
@@ -2101,10 +2075,10 @@
         <v>0%</v>
       </c>
       <c r="M34" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N34" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O34" t="str">
         <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
@@ -2113,80 +2087,80 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q34" t="str">
-        <v>多模态 Coding 基座</v>
+        <v/>
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="str">
+        <v>glm-5.1</v>
+      </c>
+      <c r="B35" t="str">
+        <v>GLM-5.1</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Zhipu</v>
+      </c>
       <c r="D35" t="str">
+        <v>32k&lt;=输入</v>
+      </c>
+      <c r="E35" t="str">
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+      </c>
+      <c r="F35" t="str">
+        <v>—</v>
+      </c>
+      <c r="G35" t="str">
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+      </c>
+      <c r="H35" t="str">
+        <v>入 $0.975 · 出 $4.300000000000001</v>
+      </c>
+      <c r="I35" t="str">
+        <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
+      </c>
+      <c r="J35" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K35" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L35" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M35" t="str">
+        <v>—</v>
+      </c>
+      <c r="N35" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="O35" t="str">
+        <v>入⚠-20.8% 出✅</v>
+      </c>
+      <c r="P35" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="Q35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="D36" t="str">
         <v>0&lt;=输入&lt;32k</v>
       </c>
-      <c r="E35" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
-      </c>
-      <c r="F35" t="str">
-        <v>—</v>
-      </c>
-      <c r="G35" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
-      </c>
-      <c r="H35" t="str">
-        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
-      </c>
-      <c r="I35" t="str">
-        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
-      </c>
-      <c r="J35" t="str">
-        <v>0%</v>
-      </c>
-      <c r="K35" t="str">
-        <v>0%</v>
-      </c>
-      <c r="L35" t="str">
-        <v>0%</v>
-      </c>
-      <c r="M35" t="str">
-        <v>—</v>
-      </c>
-      <c r="N35" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="O35" t="str">
-        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
-      </c>
-      <c r="P35" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="Q35" t="str">
-        <v>多模态 Coding 基座</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>gpt-4.1</v>
-      </c>
-      <c r="B36" t="str">
-        <v>gpt-4.1</v>
-      </c>
-      <c r="C36" t="str">
-        <v>OpenAI</v>
-      </c>
-      <c r="D36" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E36" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="F36" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="G36" t="str">
-        <v>—</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="H36" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 $0.975 · 出 $4.300000000000001</v>
       </c>
       <c r="I36" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.576923</v>
+        <v>入 $0.923077 · 出 $3.692308 · 缓 $0.2</v>
       </c>
       <c r="J36" t="str">
         <v>0%</v>
@@ -2195,51 +2169,42 @@
         <v>0%</v>
       </c>
       <c r="L36" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M36" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N36" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O36" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠+5.6% 出⚠+16.5%</v>
       </c>
       <c r="P36" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>gpt-4o</v>
-      </c>
-      <c r="B37" t="str">
-        <v>gpt-4o</v>
-      </c>
-      <c r="C37" t="str">
-        <v>OpenAI</v>
-      </c>
       <c r="D37" t="str">
-        <v>统一价</v>
+        <v>输入：≤32K token</v>
       </c>
       <c r="E37" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="F37" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>入 $0.924 · 出 $3.696 · 缓 $0.2</v>
       </c>
       <c r="G37" t="str">
         <v>—</v>
       </c>
       <c r="H37" t="str">
-        <v>入 $2.5 · 出 $10</v>
+        <v>入 $0.975 · 出 $4.300000000000001</v>
       </c>
       <c r="I37" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.441538</v>
+        <v>入 $0.923077 · 出 $3.692308 · 缓 $0.2</v>
       </c>
       <c r="J37" t="str">
         <v>0%</v>
@@ -2248,7 +2213,7 @@
         <v>0%</v>
       </c>
       <c r="L37" t="str">
-        <v>+15.3%</v>
+        <v>0%</v>
       </c>
       <c r="M37" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2257,42 +2222,33 @@
         <v>—</v>
       </c>
       <c r="O37" t="str">
-        <v>入✅ 出✅</v>
+        <v>入⚠+5.6% 出⚠+16.5%</v>
       </c>
       <c r="P37" t="str">
-        <v>入✅ 出✅ 缓⚠+15.3%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>gpt-5</v>
-      </c>
-      <c r="B38" t="str">
-        <v>gpt-5</v>
-      </c>
-      <c r="C38" t="str">
-        <v>OpenAI</v>
-      </c>
       <c r="D38" t="str">
-        <v>统一价</v>
+        <v>输入：＞32K token</v>
       </c>
       <c r="E38" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="F38" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.232 · 出 $4.312 · 缓 $0.308</v>
       </c>
       <c r="G38" t="str">
         <v>—</v>
       </c>
       <c r="H38" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $0.975 · 出 $4.300000000000001</v>
       </c>
       <c r="I38" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.144231</v>
+        <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
       </c>
       <c r="J38" t="str">
         <v>0%</v>
@@ -2301,7 +2257,7 @@
         <v>0%</v>
       </c>
       <c r="L38" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M38" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2310,10 +2266,10 @@
         <v>—</v>
       </c>
       <c r="O38" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠-20.8% 出✅</v>
       </c>
       <c r="P38" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q38" t="str">
         <v/>
@@ -2321,31 +2277,31 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>gpt-5-nano</v>
+        <v>glm-5.2</v>
       </c>
       <c r="B39" t="str">
-        <v>gpt-5-nano</v>
+        <v>GLM-5.2</v>
       </c>
       <c r="C39" t="str">
-        <v>OpenAI</v>
+        <v>Zhipu</v>
       </c>
       <c r="D39" t="str">
         <v>统一价</v>
       </c>
       <c r="E39" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="F39" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>—</v>
       </c>
       <c r="G39" t="str">
-        <v>—</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="H39" t="str">
-        <v>入 $0.049999999999999996 · 出 $0.39999999999999997 · 缓 $0.01</v>
+        <v>入 $0.9299999999999999 · 出 $3 · 缓 $0.18</v>
       </c>
       <c r="I39" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005769</v>
+        <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
       </c>
       <c r="J39" t="str">
         <v>0%</v>
@@ -2354,19 +2310,19 @@
         <v>0%</v>
       </c>
       <c r="L39" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M39" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N39" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O39" t="str">
-        <v>入✅ 出✅ 缓⚠+100%</v>
+        <v>入⚠-24.4% 出⚠-30.4% 缓⚠-41.5%</v>
       </c>
       <c r="P39" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q39" t="str">
         <v/>
@@ -2374,31 +2330,31 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>gpt-5.1</v>
+        <v>glm-5v-turbo</v>
       </c>
       <c r="B40" t="str">
-        <v>gpt-5.1</v>
+        <v>GLM-5V Turbo</v>
       </c>
       <c r="C40" t="str">
-        <v>OpenAI</v>
+        <v>Zhipu</v>
       </c>
       <c r="D40" t="str">
-        <v>统一价</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="E40" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="F40" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>—</v>
       </c>
       <c r="G40" t="str">
-        <v>—</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="H40" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
+        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="I40" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.144231</v>
+        <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
       </c>
       <c r="J40" t="str">
         <v>0%</v>
@@ -2407,51 +2363,42 @@
         <v>0%</v>
       </c>
       <c r="L40" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M40" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N40" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O40" t="str">
-        <v>入✅ 出✅ 缓⚠+4%</v>
+        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
       </c>
       <c r="P40" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q40" t="str">
-        <v/>
+        <v>多模态 Coding 基座</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>gpt-5.1-chat</v>
-      </c>
-      <c r="B41" t="str">
-        <v>gpt-5.1-chat</v>
-      </c>
-      <c r="C41" t="str">
-        <v>OpenAI</v>
-      </c>
       <c r="D41" t="str">
-        <v>统一价</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="E41" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="F41" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>—</v>
       </c>
       <c r="G41" t="str">
-        <v>—</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="H41" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
+        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="I41" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.144231</v>
+        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
       </c>
       <c r="J41" t="str">
         <v>0%</v>
@@ -2460,30 +2407,30 @@
         <v>0%</v>
       </c>
       <c r="L41" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M41" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N41" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O41" t="str">
-        <v>入✅ 出✅ 缓⚠+4%</v>
+        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
       </c>
       <c r="P41" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q41" t="str">
-        <v>目录名 gpt-5.1-chat</v>
+        <v>多模态 Coding 基座</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>gpt-5.2</v>
+        <v>gpt-4.1</v>
       </c>
       <c r="B42" t="str">
-        <v>gpt-5.2</v>
+        <v>GPT-4.1</v>
       </c>
       <c r="C42" t="str">
         <v>OpenAI</v>
@@ -2492,19 +2439,19 @@
         <v>统一价</v>
       </c>
       <c r="E42" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="F42" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="G42" t="str">
         <v>—</v>
       </c>
       <c r="H42" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="I42" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.201923</v>
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="J42" t="str">
         <v>0%</v>
@@ -2513,7 +2460,7 @@
         <v>0%</v>
       </c>
       <c r="L42" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M42" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2525,7 +2472,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P42" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q42" t="str">
         <v/>
@@ -2533,10 +2480,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>gpt-5.3-codex</v>
+        <v>gpt-4o</v>
       </c>
       <c r="B43" t="str">
-        <v>gpt-5.3-codex</v>
+        <v>GPT-4o</v>
       </c>
       <c r="C43" t="str">
         <v>OpenAI</v>
@@ -2545,40 +2492,40 @@
         <v>统一价</v>
       </c>
       <c r="E43" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="F43" t="str">
-        <v>—</v>
+        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="G43" t="str">
         <v>—</v>
       </c>
       <c r="H43" t="str">
-        <v>—</v>
+        <v>入 $2.5 · 出 $10</v>
       </c>
       <c r="I43" t="str">
-        <v>—</v>
+        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="J43" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="K43" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L43" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M43" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N43" t="str">
         <v>—</v>
       </c>
       <c r="O43" t="str">
-        <v>—</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="P43" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q43" t="str">
         <v/>
@@ -2586,31 +2533,31 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>gpt-5.4</v>
+        <v>gpt-5</v>
       </c>
       <c r="B44" t="str">
-        <v>gpt-5.4</v>
+        <v>GPT-5</v>
       </c>
       <c r="C44" t="str">
         <v>OpenAI</v>
       </c>
       <c r="D44" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>统一价</v>
       </c>
       <c r="E44" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="F44" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G44" t="str">
         <v>—</v>
       </c>
       <c r="H44" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="I44" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.288462</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="J44" t="str">
         <v>0%</v>
@@ -2619,7 +2566,7 @@
         <v>0%</v>
       </c>
       <c r="L44" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M44" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2631,30 +2578,39 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P44" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="str">
+        <v>gpt-5-nano</v>
+      </c>
+      <c r="B45" t="str">
+        <v>GPT-5 Nano</v>
+      </c>
+      <c r="C45" t="str">
+        <v>OpenAI</v>
+      </c>
       <c r="D45" t="str">
-        <v>输入&gt;272K context</v>
+        <v>统一价</v>
       </c>
       <c r="E45" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="F45" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="G45" t="str">
         <v>—</v>
       </c>
       <c r="H45" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $0.049999999999999996 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
       <c r="I45" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.576923</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="J45" t="str">
         <v>0%</v>
@@ -2663,7 +2619,7 @@
         <v>0%</v>
       </c>
       <c r="L45" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M45" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2672,10 +2628,10 @@
         <v>—</v>
       </c>
       <c r="O45" t="str">
-        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
+        <v>入✅ 出✅ 缓⚠+100%</v>
       </c>
       <c r="P45" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q45" t="str">
         <v/>
@@ -2683,10 +2639,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>gpt-5.4-mini</v>
+        <v>gpt-5.1</v>
       </c>
       <c r="B46" t="str">
-        <v>gpt-5.4-mini</v>
+        <v>GPT-5.1</v>
       </c>
       <c r="C46" t="str">
         <v>OpenAI</v>
@@ -2695,19 +2651,19 @@
         <v>统一价</v>
       </c>
       <c r="E46" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="F46" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G46" t="str">
         <v>—</v>
       </c>
       <c r="H46" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
       </c>
       <c r="I46" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.086538</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="J46" t="str">
         <v>0%</v>
@@ -2716,7 +2672,7 @@
         <v>0%</v>
       </c>
       <c r="L46" t="str">
-        <v>+15.4%</v>
+        <v>0%</v>
       </c>
       <c r="M46" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2725,10 +2681,10 @@
         <v>—</v>
       </c>
       <c r="O46" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅ 缓⚠+4%</v>
       </c>
       <c r="P46" t="str">
-        <v>入✅ 出✅ 缓⚠+15.4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q46" t="str">
         <v/>
@@ -2736,31 +2692,31 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>gpt-5.4-pro</v>
+        <v>gpt-5.1-chat</v>
       </c>
       <c r="B47" t="str">
-        <v>gpt-5.4-pro</v>
+        <v>GPT-5.1 Chat</v>
       </c>
       <c r="C47" t="str">
         <v>OpenAI</v>
       </c>
       <c r="D47" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>统一价</v>
       </c>
       <c r="E47" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="F47" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G47" t="str">
         <v>—</v>
       </c>
       <c r="H47" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
       </c>
       <c r="I47" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="J47" t="str">
         <v>0%</v>
@@ -2769,42 +2725,51 @@
         <v>0%</v>
       </c>
       <c r="L47" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M47" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N47" t="str">
         <v>—</v>
       </c>
       <c r="O47" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓⚠+4%</v>
       </c>
       <c r="P47" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q47" t="str">
-        <v/>
+        <v>目录名 gpt-5.1-chat</v>
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="str">
+        <v>gpt-5.2</v>
+      </c>
+      <c r="B48" t="str">
+        <v>GPT-5.2</v>
+      </c>
+      <c r="C48" t="str">
+        <v>OpenAI</v>
+      </c>
       <c r="D48" t="str">
-        <v>输入&gt;272K context</v>
+        <v>统一价</v>
       </c>
       <c r="E48" t="str">
-        <v>入 $60 · 出 $270</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="F48" t="str">
-        <v>入 $60 · 出 $270</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="G48" t="str">
         <v>—</v>
       </c>
       <c r="H48" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="I48" t="str">
-        <v>入 $60 · 出 $270</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="J48" t="str">
         <v>0%</v>
@@ -2813,19 +2778,19 @@
         <v>0%</v>
       </c>
       <c r="L48" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M48" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N48" t="str">
         <v>—</v>
       </c>
       <c r="O48" t="str">
-        <v>入⚠-50% 出⚠-33.3%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P48" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q48" t="str">
         <v/>
@@ -2833,10 +2798,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>gpt-5.5</v>
+        <v>gpt-5.3-codex</v>
       </c>
       <c r="B49" t="str">
-        <v>gpt-5.5</v>
+        <v>GPT-5.3 Codex</v>
       </c>
       <c r="C49" t="str">
         <v>OpenAI</v>
@@ -2845,19 +2810,19 @@
         <v>统一价</v>
       </c>
       <c r="E49" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="F49" t="str">
-        <v>—</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.18</v>
       </c>
       <c r="G49" t="str">
         <v>—</v>
       </c>
       <c r="H49" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="I49" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="J49" t="str">
         <v>0%</v>
@@ -2869,13 +2834,13 @@
         <v>0%</v>
       </c>
       <c r="M49" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓⚠+2.9%</v>
       </c>
       <c r="N49" t="str">
         <v>—</v>
       </c>
       <c r="O49" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P49" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2886,31 +2851,31 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>hunyuan-role-latest</v>
+        <v>gpt-5.4</v>
       </c>
       <c r="B50" t="str">
-        <v>Hy-Role Latest</v>
+        <v>GPT-5.4</v>
       </c>
       <c r="C50" t="str">
-        <v>Tencent</v>
+        <v>OpenAI</v>
       </c>
       <c r="D50" t="str">
-        <v>统一价</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="E50" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="F50" t="str">
-        <v>—</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="G50" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>—</v>
       </c>
       <c r="H50" t="str">
-        <v>—</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="I50" t="str">
-        <v>入 $0.369231 · 出 $1.476923</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="J50" t="str">
         <v>0%</v>
@@ -2919,51 +2884,42 @@
         <v>0%</v>
       </c>
       <c r="L50" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M50" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N50" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="O50" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P50" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q50" t="str">
-        <v>Hy-Role-Latest</v>
+        <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str">
-        <v>hy-mt2-lite</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Hy-MT2 Lite</v>
-      </c>
-      <c r="C51" t="str">
-        <v>Tencent</v>
-      </c>
       <c r="D51" t="str">
-        <v>统一价</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="E51" t="str">
-        <v>入 ¥0.3 · 出 ¥1.2</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="F51" t="str">
-        <v>—</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="G51" t="str">
-        <v>入 ¥0.3 · 出 ¥1.2</v>
+        <v>—</v>
       </c>
       <c r="H51" t="str">
-        <v>—</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="I51" t="str">
-        <v>入 $0.046154 · 出 $0.184615</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="J51" t="str">
         <v>0%</v>
@@ -2972,19 +2928,19 @@
         <v>0%</v>
       </c>
       <c r="L51" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M51" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N51" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="O51" t="str">
-        <v>—</v>
+        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
       <c r="P51" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q51" t="str">
         <v/>
@@ -2992,31 +2948,31 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>hy-mt2-plus</v>
+        <v>gpt-5.4-mini</v>
       </c>
       <c r="B52" t="str">
-        <v>Hy-MT2 Plus</v>
+        <v>GPT-5.4 Mini</v>
       </c>
       <c r="C52" t="str">
-        <v>Tencent</v>
+        <v>OpenAI</v>
       </c>
       <c r="D52" t="str">
         <v>统一价</v>
       </c>
       <c r="E52" t="str">
-        <v>入 ¥0.5 · 出 ¥2</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="F52" t="str">
-        <v>—</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="G52" t="str">
-        <v>入 ¥0.5 · 出 ¥2</v>
+        <v>—</v>
       </c>
       <c r="H52" t="str">
-        <v>—</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="I52" t="str">
-        <v>入 $0.076923 · 出 $0.307692</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="J52" t="str">
         <v>0%</v>
@@ -3025,19 +2981,19 @@
         <v>0%</v>
       </c>
       <c r="L52" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M52" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N52" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="O52" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P52" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q52" t="str">
         <v/>
@@ -3045,31 +3001,31 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>hy-mt2-pro</v>
+        <v>gpt-5.4-pro</v>
       </c>
       <c r="B53" t="str">
-        <v>Hy-MT2 Pro</v>
+        <v>GPT-5.4 Pro</v>
       </c>
       <c r="C53" t="str">
-        <v>Tencent</v>
+        <v>OpenAI</v>
       </c>
       <c r="D53" t="str">
-        <v>统一价</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="E53" t="str">
-        <v>入 ¥0.5 · 出 ¥2</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="F53" t="str">
-        <v>—</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="G53" t="str">
-        <v>入 ¥0.5 · 出 ¥2</v>
+        <v>—</v>
       </c>
       <c r="H53" t="str">
-        <v>—</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="I53" t="str">
-        <v>入 $0.076923 · 出 $0.307692</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="J53" t="str">
         <v>0%</v>
@@ -3081,13 +3037,13 @@
         <v>—</v>
       </c>
       <c r="M53" t="str">
-        <v>—</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="N53" t="str">
+        <v>—</v>
+      </c>
+      <c r="O53" t="str">
         <v>入✅ 出✅</v>
-      </c>
-      <c r="O53" t="str">
-        <v>—</v>
       </c>
       <c r="P53" t="str">
         <v>入✅ 出✅</v>
@@ -3097,32 +3053,23 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="str">
-        <v>hy-role</v>
-      </c>
-      <c r="B54" t="str">
-        <v>Hy-Role</v>
-      </c>
-      <c r="C54" t="str">
-        <v>Tencent</v>
-      </c>
       <c r="D54" t="str">
-        <v>统一价</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="E54" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="F54" t="str">
-        <v>—</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="G54" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>—</v>
       </c>
       <c r="H54" t="str">
-        <v>—</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="I54" t="str">
-        <v>入 $0.369231 · 出 $1.476923</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="J54" t="str">
         <v>0%</v>
@@ -3134,13 +3081,13 @@
         <v>—</v>
       </c>
       <c r="M54" t="str">
-        <v>—</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="N54" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="O54" t="str">
-        <v>—</v>
+        <v>入⚠-50% 出⚠-33.3%</v>
       </c>
       <c r="P54" t="str">
         <v>入✅ 出✅</v>
@@ -3151,84 +3098,75 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>hy-vision-2.0-instruct</v>
+        <v>gpt-5.5</v>
       </c>
       <c r="B55" t="str">
-        <v>Hy-Vision 2.0 Instruct</v>
+        <v>GPT-5.5</v>
       </c>
       <c r="C55" t="str">
-        <v>Tencent</v>
+        <v>OpenAI</v>
       </c>
       <c r="D55" t="str">
-        <v>统一价</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="E55" t="str">
-        <v>入 ¥7.5 · 出 ¥17.5</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="F55" t="str">
-        <v>—</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="G55" t="str">
         <v>—</v>
       </c>
       <c r="H55" t="str">
-        <v>—</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="I55" t="str">
-        <v>入 $1.034483 · 出 $2.413793</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="J55" t="str">
-        <v>-10.3%</v>
+        <v>0%</v>
       </c>
       <c r="K55" t="str">
-        <v>-10.3%</v>
+        <v>0%</v>
       </c>
       <c r="L55" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M55" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N55" t="str">
         <v>—</v>
       </c>
       <c r="O55" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P55" t="str">
-        <v>入⚠-10.3% 出⚠-10.3%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q55" t="str">
-        <v>多模态视觉理解 · 按 token 计费</v>
+        <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="str">
-        <v>hy3-preview</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Hy3 Preview</v>
-      </c>
-      <c r="C56" t="str">
-        <v>Tencent</v>
-      </c>
       <c r="D56" t="str">
-        <v>输入&lt;16k</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="E56" t="str">
-        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="F56" t="str">
-        <v>—</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="G56" t="str">
-        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+        <v>—</v>
       </c>
       <c r="H56" t="str">
-        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="I56" t="str">
-        <v>入 $0.184615 · 出 $0.615385 · 缓 $0.061538</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="J56" t="str">
         <v>0%</v>
@@ -3240,13 +3178,13 @@
         <v>0%</v>
       </c>
       <c r="M56" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N56" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O56" t="str">
-        <v>入⚠-65.9% 出⚠-65.9% 缓⚠-65.9%</v>
+        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
       <c r="P56" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -3256,23 +3194,32 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="str">
+        <v>hunyuan-role-latest</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Hy-Role Latest</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Tencent</v>
+      </c>
       <c r="D57" t="str">
-        <v>16k&lt;=输入&lt;32k</v>
+        <v>统一价</v>
       </c>
       <c r="E57" t="str">
-        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="F57" t="str">
         <v>—</v>
       </c>
       <c r="G57" t="str">
-        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="H57" t="str">
-        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I57" t="str">
-        <v>入 $0.246154 · 出 $0.984615 · 缓 $0.092308</v>
+        <v>入 $0.369231 · 出 $1.476923</v>
       </c>
       <c r="J57" t="str">
         <v>0%</v>
@@ -3281,42 +3228,51 @@
         <v>0%</v>
       </c>
       <c r="L57" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M57" t="str">
         <v>—</v>
       </c>
       <c r="N57" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="O57" t="str">
-        <v>入⚠-74.4% 出⚠-78.7% 缓⚠-77.2%</v>
+        <v>—</v>
       </c>
       <c r="P57" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="Q57" t="str">
-        <v/>
+        <v>Hy-Role-Latest</v>
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="str">
+        <v>hy-mt2-lite</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Hy-MT2 Lite</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Tencent</v>
+      </c>
       <c r="D58" t="str">
-        <v>输入&gt;=32k</v>
+        <v>统一价</v>
       </c>
       <c r="E58" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
+        <v>入 ¥0.3 · 出 ¥1.2</v>
       </c>
       <c r="F58" t="str">
         <v>—</v>
       </c>
       <c r="G58" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
+        <v>入 ¥0.3 · 出 ¥1.2</v>
       </c>
       <c r="H58" t="str">
-        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I58" t="str">
-        <v>入 $0.307692 · 出 $1.230769 · 缓 $0.123077</v>
+        <v>入 $0.046154 · 出 $0.184615</v>
       </c>
       <c r="J58" t="str">
         <v>0%</v>
@@ -3325,19 +3281,19 @@
         <v>0%</v>
       </c>
       <c r="L58" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M58" t="str">
         <v>—</v>
       </c>
       <c r="N58" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="O58" t="str">
-        <v>入⚠-79.5% 出⚠-82.9% 缓⚠-82.9%</v>
+        <v>—</v>
       </c>
       <c r="P58" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="Q58" t="str">
         <v/>
@@ -3345,31 +3301,31 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>kimi-k2.5</v>
+        <v>hy-mt2-plus</v>
       </c>
       <c r="B59" t="str">
-        <v>Kimi K2.5</v>
+        <v>Hy-MT2 Plus</v>
       </c>
       <c r="C59" t="str">
-        <v>Tongyi</v>
+        <v>Tencent</v>
       </c>
       <c r="D59" t="str">
         <v>统一价</v>
       </c>
       <c r="E59" t="str">
-        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+        <v>入 ¥0.5 · 出 ¥2</v>
       </c>
       <c r="F59" t="str">
-        <v>入 $0.616 · 出 $3.234 · 缓 $0.108</v>
+        <v>—</v>
       </c>
       <c r="G59" t="str">
-        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+        <v>入 ¥0.5 · 出 ¥2</v>
       </c>
       <c r="H59" t="str">
-        <v>入 $0.375 · 出 $2.025</v>
+        <v>—</v>
       </c>
       <c r="I59" t="str">
-        <v>入 $0.615385 · 出 $3.230769 · 缓 $0.107692</v>
+        <v>入 $0.076923 · 出 $0.307692</v>
       </c>
       <c r="J59" t="str">
         <v>0%</v>
@@ -3378,19 +3334,19 @@
         <v>0%</v>
       </c>
       <c r="L59" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M59" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N59" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="O59" t="str">
-        <v>入⚠-39.1% 出⚠-37.3%</v>
+        <v>—</v>
       </c>
       <c r="P59" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="Q59" t="str">
         <v/>
@@ -3398,31 +3354,31 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>kimi-k2.6</v>
+        <v>hy-mt2-pro</v>
       </c>
       <c r="B60" t="str">
-        <v>Kimi K2.6</v>
+        <v>Hy-MT2 Pro</v>
       </c>
       <c r="C60" t="str">
-        <v>Tongyi</v>
+        <v>Tencent</v>
       </c>
       <c r="D60" t="str">
         <v>统一价</v>
       </c>
       <c r="E60" t="str">
-        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
+        <v>入 ¥0.5 · 出 ¥2</v>
       </c>
       <c r="F60" t="str">
         <v>—</v>
       </c>
       <c r="G60" t="str">
-        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
+        <v>入 ¥0.5 · 出 ¥2</v>
       </c>
       <c r="H60" t="str">
-        <v>入 $0.55 · 出 $3.1999999999999997 · 缓 $0.11</v>
+        <v>—</v>
       </c>
       <c r="I60" t="str">
-        <v>入 $1 · 出 $4.153846 · 缓 $0.169231</v>
+        <v>入 $0.076923 · 出 $0.307692</v>
       </c>
       <c r="J60" t="str">
         <v>0%</v>
@@ -3431,19 +3387,19 @@
         <v>0%</v>
       </c>
       <c r="L60" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M60" t="str">
         <v>—</v>
       </c>
       <c r="N60" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="O60" t="str">
-        <v>入⚠-45% 出⚠-23% 缓⚠-35%</v>
+        <v>—</v>
       </c>
       <c r="P60" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="Q60" t="str">
         <v/>
@@ -3451,31 +3407,31 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>kimi-k2.7-code</v>
+        <v>hy-role</v>
       </c>
       <c r="B61" t="str">
-        <v>Kimi K2.7 Code</v>
+        <v>Hy-Role</v>
       </c>
       <c r="C61" t="str">
-        <v>Tongyi</v>
+        <v>Tencent</v>
       </c>
       <c r="D61" t="str">
         <v>统一价</v>
       </c>
       <c r="E61" t="str">
-        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="F61" t="str">
         <v>—</v>
       </c>
       <c r="G61" t="str">
-        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="H61" t="str">
-        <v>入 $0.74 · 出 $3.5 · 缓 $0.15</v>
+        <v>—</v>
       </c>
       <c r="I61" t="str">
-        <v>入 $1 · 出 $4.153846</v>
+        <v>入 $0.369231 · 出 $1.476923</v>
       </c>
       <c r="J61" t="str">
         <v>0%</v>
@@ -3490,10 +3446,10 @@
         <v>—</v>
       </c>
       <c r="N61" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="O61" t="str">
-        <v>入⚠-26% 出⚠-15.7% 缓⚠-25%</v>
+        <v>—</v>
       </c>
       <c r="P61" t="str">
         <v>入✅ 出✅</v>
@@ -3504,31 +3460,31 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>kimi-k2.7-code-highspeed</v>
+        <v>hy-vision-2.0-instruct</v>
       </c>
       <c r="B62" t="str">
-        <v>Kimi K2.7 Code HighSpeed</v>
+        <v>Hy-Vision 2.0 Instruct</v>
       </c>
       <c r="C62" t="str">
-        <v>Moonshot AI</v>
+        <v>Tencent</v>
       </c>
       <c r="D62" t="str">
         <v>统一价</v>
       </c>
       <c r="E62" t="str">
-        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
+        <v>入 ¥7.5 · 出 ¥17.5</v>
       </c>
       <c r="F62" t="str">
         <v>—</v>
       </c>
       <c r="G62" t="str">
-        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
+        <v>—</v>
       </c>
       <c r="H62" t="str">
         <v>—</v>
       </c>
       <c r="I62" t="str">
-        <v>入 $2 · 出 $8.307692 · 缓 $0.4</v>
+        <v>入 $1.153846 · 出 $2.692308</v>
       </c>
       <c r="J62" t="str">
         <v>0%</v>
@@ -3537,51 +3493,51 @@
         <v>0%</v>
       </c>
       <c r="L62" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M62" t="str">
         <v>—</v>
       </c>
       <c r="N62" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O62" t="str">
         <v>—</v>
       </c>
       <c r="P62" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="Q62" t="str">
-        <v>K2.7 Code 高速版</v>
+        <v>多模态视觉理解 · 按 token 计费</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>minimax-m2.5</v>
+        <v>hy3-preview</v>
       </c>
       <c r="B63" t="str">
-        <v>MiniMax M2.5</v>
+        <v>Hy3 Preview</v>
       </c>
       <c r="C63" t="str">
-        <v>MiniMax</v>
+        <v>Tencent</v>
       </c>
       <c r="D63" t="str">
-        <v>统一价</v>
+        <v>输入&lt;16k</v>
       </c>
       <c r="E63" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
       </c>
       <c r="F63" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.03</v>
+        <v>—</v>
       </c>
       <c r="G63" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
       </c>
       <c r="H63" t="str">
-        <v>入 $0.12 · 出 $0.48</v>
+        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
       <c r="I63" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.032308</v>
+        <v>入 $0.184615 · 出 $0.615385 · 缓 $0.061538</v>
       </c>
       <c r="J63" t="str">
         <v>0%</v>
@@ -3593,13 +3549,13 @@
         <v>0%</v>
       </c>
       <c r="M63" t="str">
-        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
+        <v>—</v>
       </c>
       <c r="N63" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O63" t="str">
-        <v>入⚠-62.9% 出⚠-62.9%</v>
+        <v>入⚠-65.9% 出⚠-65.9% 缓⚠-65.9%</v>
       </c>
       <c r="P63" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -3609,32 +3565,23 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="str">
-        <v>minimax-m2.7</v>
-      </c>
-      <c r="B64" t="str">
-        <v>MiniMax M2.7</v>
-      </c>
-      <c r="C64" t="str">
-        <v>MiniMax</v>
-      </c>
       <c r="D64" t="str">
-        <v>统一价</v>
+        <v>16k&lt;=输入&lt;32k</v>
       </c>
       <c r="E64" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
       <c r="F64" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
+        <v>—</v>
       </c>
       <c r="G64" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
       <c r="H64" t="str">
-        <v>入 $0.18 · 出 $0.72</v>
+        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
       <c r="I64" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
+        <v>入 $0.246154 · 出 $0.984615 · 缓 $0.092308</v>
       </c>
       <c r="J64" t="str">
         <v>0%</v>
@@ -3646,13 +3593,13 @@
         <v>0%</v>
       </c>
       <c r="M64" t="str">
-        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
+        <v>—</v>
       </c>
       <c r="N64" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O64" t="str">
-        <v>入⚠-44.3% 出⚠-44.3%</v>
+        <v>入⚠-74.4% 出⚠-78.7% 缓⚠-77.2%</v>
       </c>
       <c r="P64" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -3662,32 +3609,23 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="str">
-        <v>minimax-m3</v>
-      </c>
-      <c r="B65" t="str">
-        <v>MiniMax M3</v>
-      </c>
-      <c r="C65" t="str">
-        <v>MiniMax</v>
-      </c>
       <c r="D65" t="str">
-        <v>输入&lt;=512k</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="E65" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="F65" t="str">
         <v>—</v>
       </c>
       <c r="G65" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="H65" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
+        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
       <c r="I65" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
+        <v>入 $0.307692 · 出 $1.230769 · 缓 $0.123077</v>
       </c>
       <c r="J65" t="str">
         <v>0%</v>
@@ -3705,33 +3643,33 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O65" t="str">
-        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
+        <v>入⚠-79.5% 出⚠-82.9% 缓⚠-82.9%</v>
       </c>
       <c r="P65" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q65" t="str">
-        <v>512k 以上输入档仍在内测开放中</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="D66" t="str">
-        <v>512k&lt;输入</v>
+        <v>输入长度（0, 16k）</v>
       </c>
       <c r="E66" t="str">
-        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
       </c>
       <c r="F66" t="str">
         <v>—</v>
       </c>
       <c r="G66" t="str">
-        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
+        <v>—</v>
       </c>
       <c r="H66" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
+        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
       <c r="I66" t="str">
-        <v>入 $0.646154 · 出 $2.584615 · 缓 $0.129231</v>
+        <v>入 $0.184615 · 出 $0.615385 · 缓 $0.061538</v>
       </c>
       <c r="J66" t="str">
         <v>0%</v>
@@ -3746,45 +3684,45 @@
         <v>—</v>
       </c>
       <c r="N66" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O66" t="str">
-        <v>入⚠-53.6% 出⚠-53.6% 缓⚠-53.6%</v>
+        <v>入⚠-65.9% 出⚠-65.9% 缓⚠-65.9%</v>
       </c>
       <c r="P66" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q66" t="str">
-        <v>512k 以上输入档仍在内测开放中</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>qwen-flash</v>
+        <v>kimi-k2.5</v>
       </c>
       <c r="B67" t="str">
-        <v>Qwen Flash</v>
+        <v>Kimi K2.5</v>
       </c>
       <c r="C67" t="str">
-        <v>Tongyi</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="D67" t="str">
-        <v>0&lt;Token≤128K</v>
+        <v>统一价</v>
       </c>
       <c r="E67" t="str">
-        <v>入 ¥0.15 · 出 ¥1.5 · 缓 ¥0.03</v>
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
       </c>
       <c r="F67" t="str">
-        <v>—</v>
+        <v>入 $0.616 · 出 $3.234 · 缓 $0.108</v>
       </c>
       <c r="G67" t="str">
-        <v>—</v>
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
       </c>
       <c r="H67" t="str">
-        <v>—</v>
+        <v>入 $0.375 · 出 $2.025</v>
       </c>
       <c r="I67" t="str">
-        <v>入 $0.023077 · 出 $0.230769 · 缓 $0.004615</v>
+        <v>入 $0.615385 · 出 $3.230769 · 缓 $0.107692</v>
       </c>
       <c r="J67" t="str">
         <v>0%</v>
@@ -3796,13 +3734,13 @@
         <v>0%</v>
       </c>
       <c r="M67" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N67" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O67" t="str">
-        <v>—</v>
+        <v>入⚠-39.1% 出⚠-37.3%</v>
       </c>
       <c r="P67" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -3812,73 +3750,91 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="str">
+        <v>kimi-k2.6</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Kimi K2.6</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Moonshot AI</v>
+      </c>
       <c r="D68" t="str">
-        <v>128K&lt;Token≤256K</v>
+        <v>统一价</v>
       </c>
       <c r="E68" t="str">
-        <v>入 ¥0.6 · 出 ¥6 · 缓 ¥0.12</v>
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
       </c>
       <c r="F68" t="str">
         <v>—</v>
       </c>
       <c r="G68" t="str">
-        <v>—</v>
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
       </c>
       <c r="H68" t="str">
-        <v>—</v>
+        <v>入 $0.55 · 出 $3.1999999999999997 · 缓 $0.11</v>
       </c>
       <c r="I68" t="str">
-        <v>—</v>
+        <v>入 $1 · 出 $4.153846 · 缓 $0.169231</v>
       </c>
       <c r="J68" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="K68" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L68" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M68" t="str">
         <v>—</v>
       </c>
       <c r="N68" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O68" t="str">
-        <v>—</v>
+        <v>入⚠-45% 出⚠-23% 缓⚠-35%</v>
       </c>
       <c r="P68" t="str">
-        <v>ℹ 线上无同档</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="str">
+        <v>kimi-k2.7-code</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Kimi K2.7 Code</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Moonshot AI</v>
+      </c>
       <c r="D69" t="str">
-        <v>256K&lt;Token≤1M</v>
+        <v>统一价</v>
       </c>
       <c r="E69" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
       </c>
       <c r="F69" t="str">
         <v>—</v>
       </c>
       <c r="G69" t="str">
-        <v>—</v>
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
       </c>
       <c r="H69" t="str">
-        <v>—</v>
+        <v>入 $0.74 · 出 $3.5 · 缓 $0.15</v>
       </c>
       <c r="I69" t="str">
-        <v>—</v>
+        <v>入 $1 · 出 $4.153846</v>
       </c>
       <c r="J69" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="K69" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L69" t="str">
         <v>—</v>
@@ -3887,13 +3843,13 @@
         <v>—</v>
       </c>
       <c r="N69" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O69" t="str">
-        <v>—</v>
+        <v>入⚠-26% 出⚠-15.7% 缓⚠-25%</v>
       </c>
       <c r="P69" t="str">
-        <v>ℹ 线上无同档</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="Q69" t="str">
         <v/>
@@ -3901,31 +3857,31 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>qwen-max</v>
+        <v>kimi-k2.7-code-highspeed</v>
       </c>
       <c r="B70" t="str">
-        <v>Qwen Max</v>
+        <v>Kimi K2.7 Code HighSpeed</v>
       </c>
       <c r="C70" t="str">
-        <v>Tongyi</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="D70" t="str">
-        <v>无阶梯计价</v>
+        <v>统一价</v>
       </c>
       <c r="E70" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
       </c>
       <c r="F70" t="str">
         <v>—</v>
       </c>
       <c r="G70" t="str">
-        <v>—</v>
+        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
       </c>
       <c r="H70" t="str">
         <v>—</v>
       </c>
       <c r="I70" t="str">
-        <v>入 $0.369231 · 出 $1.476923 · 缓 $0.082759</v>
+        <v>入 $2 · 出 $8.307692 · 缓 $0.4</v>
       </c>
       <c r="J70" t="str">
         <v>0%</v>
@@ -3934,51 +3890,51 @@
         <v>0%</v>
       </c>
       <c r="L70" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M70" t="str">
         <v>—</v>
       </c>
       <c r="N70" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O70" t="str">
         <v>—</v>
       </c>
       <c r="P70" t="str">
-        <v>入✅ 出✅ 缓—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q70" t="str">
-        <v/>
+        <v>K2.7 Code 高速版</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>qwen-plus</v>
+        <v>minimax-m2.5</v>
       </c>
       <c r="B71" t="str">
-        <v>Qwen Plus</v>
+        <v>MiniMax M2.5</v>
       </c>
       <c r="C71" t="str">
-        <v>Tongyi</v>
+        <v>MiniMax</v>
       </c>
       <c r="D71" t="str">
-        <v>0&lt;Token≤128K</v>
+        <v>统一价</v>
       </c>
       <c r="E71" t="str">
-        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
       </c>
       <c r="F71" t="str">
-        <v>—</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.03</v>
       </c>
       <c r="G71" t="str">
-        <v>—</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
       </c>
       <c r="H71" t="str">
-        <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
+        <v>入 $0.12 · 出 $0.48</v>
       </c>
       <c r="I71" t="str">
-        <v>入 $0.123077 · 出 $0.307692 · 缓 $0.024615</v>
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.032308</v>
       </c>
       <c r="J71" t="str">
         <v>0%</v>
@@ -3990,13 +3946,13 @@
         <v>0%</v>
       </c>
       <c r="M71" t="str">
-        <v>—</v>
+        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
       <c r="N71" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O71" t="str">
-        <v>入⚠+111.3% 出⚠+153.5% 缓⚠+111.3%</v>
+        <v>入⚠-62.9% 出⚠-62.9%</v>
       </c>
       <c r="P71" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -4007,31 +3963,31 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>qwen-turbo</v>
+        <v>minimax-m2.7</v>
       </c>
       <c r="B72" t="str">
-        <v>Qwen Turbo</v>
+        <v>MiniMax M2.7</v>
       </c>
       <c r="C72" t="str">
-        <v>Tongyi</v>
+        <v>MiniMax</v>
       </c>
       <c r="D72" t="str">
         <v>统一价</v>
       </c>
       <c r="E72" t="str">
-        <v>入 ¥0.3 · 出 ¥0.6</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="F72" t="str">
-        <v>—</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="G72" t="str">
-        <v>—</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="H72" t="str">
-        <v>—</v>
+        <v>入 $0.18 · 出 $0.72</v>
       </c>
       <c r="I72" t="str">
-        <v>入 $0.046154 · 出 $0.092308 · 缓 $0.010345</v>
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
       <c r="J72" t="str">
         <v>0%</v>
@@ -4040,19 +3996,19 @@
         <v>0%</v>
       </c>
       <c r="L72" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M72" t="str">
-        <v>—</v>
+        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
       <c r="N72" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O72" t="str">
-        <v>—</v>
+        <v>入⚠-44.3% 出⚠-44.3%</v>
       </c>
       <c r="P72" t="str">
-        <v>入✅ 出✅ 缓—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q72" t="str">
         <v/>
@@ -4060,31 +4016,31 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>qwen3.5-flash</v>
+        <v>minimax-m3</v>
       </c>
       <c r="B73" t="str">
-        <v>Qwen3.5 Flash</v>
+        <v>MiniMax M3</v>
       </c>
       <c r="C73" t="str">
-        <v>Tongyi</v>
+        <v>MiniMax</v>
       </c>
       <c r="D73" t="str">
-        <v>0&lt;输入&lt;=128k</v>
+        <v>输入&lt;=512k</v>
       </c>
       <c r="E73" t="str">
-        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="F73" t="str">
         <v>—</v>
       </c>
       <c r="G73" t="str">
-        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="H73" t="str">
-        <v>入 $0.065 · 出 $0.26</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="I73" t="str">
-        <v>入 $0.030769 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
       <c r="J73" t="str">
         <v>0%</v>
@@ -4102,42 +4058,42 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O73" t="str">
-        <v>入⚠+111.3% 出⚠-15.5%</v>
+        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
       <c r="P73" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q73" t="str">
-        <v/>
+        <v>512k 以上输入档仍在内测开放中</v>
       </c>
     </row>
     <row r="74">
       <c r="D74" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>512k&lt;输入</v>
       </c>
       <c r="E74" t="str">
-        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
+        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="F74" t="str">
         <v>—</v>
       </c>
       <c r="G74" t="str">
-        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
+        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="H74" t="str">
-        <v>入 $0.065 · 出 $0.26</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="I74" t="str">
-        <v>—</v>
+        <v>入 $0.646154 · 出 $2.584615 · 缓 $0.129231</v>
       </c>
       <c r="J74" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="K74" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L74" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M74" t="str">
         <v>—</v>
@@ -4146,107 +4102,107 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O74" t="str">
-        <v>入⚠-47.2% 出⚠-78.9%</v>
+        <v>入⚠-53.6% 出⚠-53.6% 缓⚠-53.6%</v>
       </c>
       <c r="P74" t="str">
-        <v>ℹ 线上无同档</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q74" t="str">
-        <v/>
+        <v>512k 以上输入档仍在内测开放中</v>
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="str">
+        <v>qwen-flash</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Qwen Flash</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="D75" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>0&lt;Token≤128K</v>
       </c>
       <c r="E75" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
+        <v>入 ¥0.15 · 出 ¥1.5 · 缓 ¥0.03</v>
       </c>
       <c r="F75" t="str">
         <v>—</v>
       </c>
       <c r="G75" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
+        <v>—</v>
       </c>
       <c r="H75" t="str">
-        <v>入 $0.065 · 出 $0.26</v>
+        <v>—</v>
       </c>
       <c r="I75" t="str">
-        <v>—</v>
+        <v>入 $0.023077 · 出 $0.230769 · 缓 $0.004615</v>
       </c>
       <c r="J75" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="K75" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L75" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M75" t="str">
         <v>—</v>
       </c>
       <c r="N75" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O75" t="str">
-        <v>入⚠-64.8% 出⚠-85.9%</v>
+        <v>—</v>
       </c>
       <c r="P75" t="str">
-        <v>ℹ 线上无同档</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="str">
-        <v>qwen3.5-plus</v>
-      </c>
-      <c r="B76" t="str">
-        <v>Qwen3.5 Plus</v>
-      </c>
-      <c r="C76" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="D76" t="str">
-        <v>输入&lt;=128k</v>
+        <v>128K&lt;Token≤256K</v>
       </c>
       <c r="E76" t="str">
-        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+        <v>入 ¥0.6 · 出 ¥6 · 缓 ¥0.12</v>
       </c>
       <c r="F76" t="str">
         <v>—</v>
       </c>
       <c r="G76" t="str">
-        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+        <v>—</v>
       </c>
       <c r="H76" t="str">
-        <v>入 $0.3 · 出 $1.7999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I76" t="str">
-        <v>入 $0.123077 · 出 $0.738462 · 缓 $0.012308</v>
+        <v>—</v>
       </c>
       <c r="J76" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K76" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L76" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M76" t="str">
         <v>—</v>
       </c>
       <c r="N76" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O76" t="str">
-        <v>入⚠+143.7% 出⚠+143.7%</v>
+        <v>—</v>
       </c>
       <c r="P76" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>ℹ 线上无同档</v>
       </c>
       <c r="Q76" t="str">
         <v/>
@@ -4254,19 +4210,19 @@
     </row>
     <row r="77">
       <c r="D77" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>256K&lt;Token≤1M</v>
       </c>
       <c r="E77" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
       </c>
       <c r="F77" t="str">
         <v>—</v>
       </c>
       <c r="G77" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+        <v>—</v>
       </c>
       <c r="H77" t="str">
-        <v>入 $0.3 · 出 $1.7999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I77" t="str">
         <v>—</v>
@@ -4284,10 +4240,10 @@
         <v>—</v>
       </c>
       <c r="N77" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O77" t="str">
-        <v>入⚠-2.5% 出⚠-2.5%</v>
+        <v>—</v>
       </c>
       <c r="P77" t="str">
         <v>ℹ 线上无同档</v>
@@ -4297,29 +4253,38 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="str">
+        <v>qwen-max</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Qwen Max</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="D78" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>无阶梯计价</v>
       </c>
       <c r="E78" t="str">
-        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="F78" t="str">
         <v>—</v>
       </c>
       <c r="G78" t="str">
-        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
+        <v>—</v>
       </c>
       <c r="H78" t="str">
-        <v>入 $0.3 · 出 $1.7999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I78" t="str">
-        <v>—</v>
+        <v>入 $0.369231 · 出 $1.476923 · 缓 $0.082759</v>
       </c>
       <c r="J78" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="K78" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L78" t="str">
         <v>—</v>
@@ -4328,13 +4293,13 @@
         <v>—</v>
       </c>
       <c r="N78" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O78" t="str">
-        <v>入⚠-51.3% 出⚠-51.3%</v>
+        <v>—</v>
       </c>
       <c r="P78" t="str">
-        <v>ℹ 线上无同档</v>
+        <v>入✅ 出✅ 缓—</v>
       </c>
       <c r="Q78" t="str">
         <v/>
@@ -4342,19 +4307,19 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>qwen3.6-flash</v>
+        <v>qwen-plus</v>
       </c>
       <c r="B79" t="str">
-        <v>Qwen3.6 Flash</v>
+        <v>Qwen Plus</v>
       </c>
       <c r="C79" t="str">
         <v>Tongyi</v>
       </c>
       <c r="D79" t="str">
-        <v>256K&lt;Token≤1M</v>
+        <v>0&lt;Token≤128K</v>
       </c>
       <c r="E79" t="str">
-        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
       </c>
       <c r="F79" t="str">
         <v>—</v>
@@ -4363,19 +4328,19 @@
         <v>—</v>
       </c>
       <c r="H79" t="str">
-        <v>入 $0.1875 · 出 $1.125</v>
+        <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
       </c>
       <c r="I79" t="str">
-        <v>—</v>
+        <v>入 $0.123077 · 出 $0.307692 · 缓 $0.024615</v>
       </c>
       <c r="J79" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="K79" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L79" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M79" t="str">
         <v>—</v>
@@ -4384,21 +4349,30 @@
         <v>—</v>
       </c>
       <c r="O79" t="str">
-        <v>入⚠-74.6% 出⚠-74.6%</v>
+        <v>入⚠+111.3% 出⚠+153.5% 缓⚠+111.3%</v>
       </c>
       <c r="P79" t="str">
-        <v>ℹ 线上无同档</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="str">
+        <v>qwen-turbo</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Qwen Turbo</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="D80" t="str">
-        <v>0&lt;Token≤256K</v>
+        <v>统一价</v>
       </c>
       <c r="E80" t="str">
-        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
+        <v>入 ¥0.3 · 出 ¥0.6</v>
       </c>
       <c r="F80" t="str">
         <v>—</v>
@@ -4407,10 +4381,10 @@
         <v>—</v>
       </c>
       <c r="H80" t="str">
-        <v>入 $0.1875 · 出 $1.125</v>
+        <v>—</v>
       </c>
       <c r="I80" t="str">
-        <v>入 $0.184615 · 出 $1.107692 · 缓 $0.036923</v>
+        <v>入 $0.046154 · 出 $0.092308 · 缓 $0.010345</v>
       </c>
       <c r="J80" t="str">
         <v>0%</v>
@@ -4419,7 +4393,7 @@
         <v>0%</v>
       </c>
       <c r="L80" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M80" t="str">
         <v>—</v>
@@ -4428,10 +4402,10 @@
         <v>—</v>
       </c>
       <c r="O80" t="str">
-        <v>入⚠+1.6% 出⚠+1.6%</v>
+        <v>—</v>
       </c>
       <c r="P80" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅ 缓—</v>
       </c>
       <c r="Q80" t="str">
         <v/>
@@ -4439,31 +4413,31 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>qwen3.6-plus</v>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="B81" t="str">
-        <v>Qwen3.6 Plus</v>
+        <v>Qwen3.5 Flash</v>
       </c>
       <c r="C81" t="str">
         <v>Tongyi</v>
       </c>
       <c r="D81" t="str">
-        <v>0&lt;Token≤256K</v>
+        <v>0&lt;输入&lt;=128k</v>
       </c>
       <c r="E81" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="F81" t="str">
         <v>—</v>
       </c>
       <c r="G81" t="str">
-        <v>—</v>
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="H81" t="str">
-        <v>入 $0.325 · 出 $1.95</v>
+        <v>入 $0.065 · 出 $0.26</v>
       </c>
       <c r="I81" t="str">
-        <v>入 $0.307692 · 出 $1.846154 · 缓 $0.061538</v>
+        <v>入 $0.030769 · 出 $0.307692 · 缓 $0.003077</v>
       </c>
       <c r="J81" t="str">
         <v>0%</v>
@@ -4478,10 +4452,10 @@
         <v>—</v>
       </c>
       <c r="N81" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O81" t="str">
-        <v>入⚠+5.6% 出⚠+5.6%</v>
+        <v>入⚠+111.3% 出⚠-15.5%</v>
       </c>
       <c r="P81" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -4491,113 +4465,492 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="str">
-        <v>qwen3.7-max</v>
-      </c>
-      <c r="B82" t="str">
-        <v>Qwen3.7 Max</v>
-      </c>
-      <c r="C82" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="D82" t="str">
-        <v>0&lt;Token≤1M</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E82" t="str">
-        <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
+        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
       </c>
       <c r="F82" t="str">
         <v>—</v>
       </c>
       <c r="G82" t="str">
-        <v>—</v>
+        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
       </c>
       <c r="H82" t="str">
-        <v>入 $1.25 · 出 $3.75 · 缓 $0.25</v>
+        <v>入 $0.065 · 出 $0.26</v>
       </c>
       <c r="I82" t="str">
-        <v>入 $1.846154 · 出 $5.538462 · 缓 $0.369231</v>
+        <v>—</v>
       </c>
       <c r="J82" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K82" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L82" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M82" t="str">
         <v>—</v>
       </c>
       <c r="N82" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O82" t="str">
-        <v>入⚠-32.3% 出⚠-32.3% 缓⚠-32.3%</v>
+        <v>入⚠-47.2% 出⚠-78.9%</v>
       </c>
       <c r="P82" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>ℹ 线上无同档</v>
       </c>
       <c r="Q82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="str">
-        <v>qwen3.7-plus</v>
-      </c>
-      <c r="B83" t="str">
-        <v>Qwen3.7 Plus</v>
-      </c>
-      <c r="C83" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="D83" t="str">
-        <v>0&lt;Token≤256K</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="E83" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
       </c>
       <c r="F83" t="str">
         <v>—</v>
       </c>
       <c r="G83" t="str">
-        <v>—</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
       </c>
       <c r="H83" t="str">
-        <v>入 $0.32 · 出 $1.28 · 缓 $0.064</v>
+        <v>入 $0.065 · 出 $0.26</v>
       </c>
       <c r="I83" t="str">
-        <v>入 $0.307692 · 出 $1.230769 · 缓 $0.061538</v>
+        <v>—</v>
       </c>
       <c r="J83" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K83" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L83" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M83" t="str">
         <v>—</v>
       </c>
       <c r="N83" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O83" t="str">
-        <v>入⚠+4% 出⚠+4% 缓⚠+4%</v>
+        <v>入⚠-64.8% 出⚠-85.9%</v>
       </c>
       <c r="P83" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>ℹ 线上无同档</v>
       </c>
       <c r="Q83" t="str">
         <v/>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>qwen3.5-plus</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Qwen3.5 Plus</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="D84" t="str">
+        <v>输入&lt;=128k</v>
+      </c>
+      <c r="E84" t="str">
+        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+      </c>
+      <c r="F84" t="str">
+        <v>—</v>
+      </c>
+      <c r="G84" t="str">
+        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+      </c>
+      <c r="H84" t="str">
+        <v>入 $0.3 · 出 $1.7999999999999998</v>
+      </c>
+      <c r="I84" t="str">
+        <v>入 $0.123077 · 出 $0.738462 · 缓 $0.012308</v>
+      </c>
+      <c r="J84" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K84" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L84" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M84" t="str">
+        <v>—</v>
+      </c>
+      <c r="N84" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="O84" t="str">
+        <v>入⚠+143.7% 出⚠+143.7%</v>
+      </c>
+      <c r="P84" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="D85" t="str">
+        <v>128k&lt;输入&lt;=256k</v>
+      </c>
+      <c r="E85" t="str">
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+      </c>
+      <c r="F85" t="str">
+        <v>—</v>
+      </c>
+      <c r="G85" t="str">
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+      </c>
+      <c r="H85" t="str">
+        <v>入 $0.3 · 出 $1.7999999999999998</v>
+      </c>
+      <c r="I85" t="str">
+        <v>—</v>
+      </c>
+      <c r="J85" t="str">
+        <v>—</v>
+      </c>
+      <c r="K85" t="str">
+        <v>—</v>
+      </c>
+      <c r="L85" t="str">
+        <v>—</v>
+      </c>
+      <c r="M85" t="str">
+        <v>—</v>
+      </c>
+      <c r="N85" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="O85" t="str">
+        <v>入⚠-2.5% 出⚠-2.5%</v>
+      </c>
+      <c r="P85" t="str">
+        <v>ℹ 线上无同档</v>
+      </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="D86" t="str">
+        <v>256k&lt;输入&lt;=1M</v>
+      </c>
+      <c r="E86" t="str">
+        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
+      </c>
+      <c r="F86" t="str">
+        <v>—</v>
+      </c>
+      <c r="G86" t="str">
+        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
+      </c>
+      <c r="H86" t="str">
+        <v>入 $0.3 · 出 $1.7999999999999998</v>
+      </c>
+      <c r="I86" t="str">
+        <v>—</v>
+      </c>
+      <c r="J86" t="str">
+        <v>—</v>
+      </c>
+      <c r="K86" t="str">
+        <v>—</v>
+      </c>
+      <c r="L86" t="str">
+        <v>—</v>
+      </c>
+      <c r="M86" t="str">
+        <v>—</v>
+      </c>
+      <c r="N86" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="O86" t="str">
+        <v>入⚠-51.3% 出⚠-51.3%</v>
+      </c>
+      <c r="P86" t="str">
+        <v>ℹ 线上无同档</v>
+      </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>qwen3.6-flash</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Qwen3.6 Flash</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="D87" t="str">
+        <v>256K&lt;Token≤1M</v>
+      </c>
+      <c r="E87" t="str">
+        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
+      </c>
+      <c r="F87" t="str">
+        <v>—</v>
+      </c>
+      <c r="G87" t="str">
+        <v>—</v>
+      </c>
+      <c r="H87" t="str">
+        <v>入 $0.1875 · 出 $1.125</v>
+      </c>
+      <c r="I87" t="str">
+        <v>—</v>
+      </c>
+      <c r="J87" t="str">
+        <v>—</v>
+      </c>
+      <c r="K87" t="str">
+        <v>—</v>
+      </c>
+      <c r="L87" t="str">
+        <v>—</v>
+      </c>
+      <c r="M87" t="str">
+        <v>—</v>
+      </c>
+      <c r="N87" t="str">
+        <v>—</v>
+      </c>
+      <c r="O87" t="str">
+        <v>入⚠-74.6% 出⚠-74.6%</v>
+      </c>
+      <c r="P87" t="str">
+        <v>ℹ 线上无同档</v>
+      </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="D88" t="str">
+        <v>0&lt;Token≤256K</v>
+      </c>
+      <c r="E88" t="str">
+        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
+      </c>
+      <c r="F88" t="str">
+        <v>—</v>
+      </c>
+      <c r="G88" t="str">
+        <v>—</v>
+      </c>
+      <c r="H88" t="str">
+        <v>入 $0.1875 · 出 $1.125</v>
+      </c>
+      <c r="I88" t="str">
+        <v>入 $0.184615 · 出 $1.107692 · 缓 $0.036923</v>
+      </c>
+      <c r="J88" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K88" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L88" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M88" t="str">
+        <v>—</v>
+      </c>
+      <c r="N88" t="str">
+        <v>—</v>
+      </c>
+      <c r="O88" t="str">
+        <v>入⚠+1.6% 出⚠+1.6%</v>
+      </c>
+      <c r="P88" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>qwen3.6-plus</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Qwen3.6 Plus</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="D89" t="str">
+        <v>0&lt;Token≤256K</v>
+      </c>
+      <c r="E89" t="str">
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
+      </c>
+      <c r="F89" t="str">
+        <v>—</v>
+      </c>
+      <c r="G89" t="str">
+        <v>—</v>
+      </c>
+      <c r="H89" t="str">
+        <v>入 $0.325 · 出 $1.95</v>
+      </c>
+      <c r="I89" t="str">
+        <v>入 $0.307692 · 出 $1.846154 · 缓 $0.061538</v>
+      </c>
+      <c r="J89" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K89" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L89" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M89" t="str">
+        <v>—</v>
+      </c>
+      <c r="N89" t="str">
+        <v>—</v>
+      </c>
+      <c r="O89" t="str">
+        <v>入⚠+5.6% 出⚠+5.6%</v>
+      </c>
+      <c r="P89" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>qwen3.7-max</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Qwen3.7 Max</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="D90" t="str">
+        <v>0&lt;Token≤1M</v>
+      </c>
+      <c r="E90" t="str">
+        <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
+      </c>
+      <c r="F90" t="str">
+        <v>—</v>
+      </c>
+      <c r="G90" t="str">
+        <v>—</v>
+      </c>
+      <c r="H90" t="str">
+        <v>入 $1.25 · 出 $3.75 · 缓 $0.25</v>
+      </c>
+      <c r="I90" t="str">
+        <v>入 $1.846154 · 出 $5.538462 · 缓 $0.369231</v>
+      </c>
+      <c r="J90" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K90" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L90" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M90" t="str">
+        <v>—</v>
+      </c>
+      <c r="N90" t="str">
+        <v>—</v>
+      </c>
+      <c r="O90" t="str">
+        <v>入⚠-32.3% 出⚠-32.3% 缓⚠-32.3%</v>
+      </c>
+      <c r="P90" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>qwen3.7-plus</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Qwen3.7 Plus</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="D91" t="str">
+        <v>0&lt;Token≤256K</v>
+      </c>
+      <c r="E91" t="str">
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
+      </c>
+      <c r="F91" t="str">
+        <v>—</v>
+      </c>
+      <c r="G91" t="str">
+        <v>—</v>
+      </c>
+      <c r="H91" t="str">
+        <v>入 $0.32 · 出 $1.28 · 缓 $0.064</v>
+      </c>
+      <c r="I91" t="str">
+        <v>入 $0.307692 · 出 $1.230769 · 缓 $0.061538</v>
+      </c>
+      <c r="J91" t="str">
+        <v>0%</v>
+      </c>
+      <c r="K91" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L91" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M91" t="str">
+        <v>—</v>
+      </c>
+      <c r="N91" t="str">
+        <v>—</v>
+      </c>
+      <c r="O91" t="str">
+        <v>入⚠+4% 出⚠+4% 缓⚠+4%</v>
+      </c>
+      <c r="P91" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="60">
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
@@ -4619,45 +4972,48 @@
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="C67:C69"/>
-    <mergeCell ref="A73:A75"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="A76:A78"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="C35:C38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="B63:B66"/>
+    <mergeCell ref="C63:C66"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="A75:A77"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="C75:C77"/>
+    <mergeCell ref="A81:A83"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="C81:C83"/>
+    <mergeCell ref="A84:A86"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q91"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5428,7 +5784,7 @@
         <v>Kimi K2.5</v>
       </c>
       <c r="D24" t="str">
-        <v>Tongyi</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="E24" t="str">
         <v>统一价</v>
@@ -5463,7 +5819,7 @@
         <v>Kimi K2.6</v>
       </c>
       <c r="D25" t="str">
-        <v>Tongyi</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="E25" t="str">
         <v>统一价</v>
@@ -5498,7 +5854,7 @@
         <v>Kimi K2.7 Code</v>
       </c>
       <c r="D26" t="str">
-        <v>Tongyi</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="E26" t="str">
         <v>统一价</v>
@@ -6207,7 +6563,7 @@
         <v>Kimi K2.5</v>
       </c>
       <c r="D10" t="str">
-        <v>Tongyi</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="E10" t="str">
         <v>统一价</v>
@@ -6242,7 +6598,7 @@
         <v>Kimi K2.6</v>
       </c>
       <c r="D11" t="str">
-        <v>Tongyi</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="E11" t="str">
         <v>统一价</v>
@@ -6277,7 +6633,7 @@
         <v>Kimi K2.7 Code</v>
       </c>
       <c r="D12" t="str">
-        <v>Tongyi</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="E12" t="str">
         <v>统一价</v>
@@ -6897,7 +7253,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7050,10 +7406,10 @@
         <v>Gemini 2.5 Flash</v>
       </c>
       <c r="D5" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E5" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="F5" t="str">
         <v>2.5-flash</v>
@@ -7079,7 +7435,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="F6" t="str">
         <v>2.5-flash</v>
@@ -7111,7 +7467,7 @@
         <v>Gemini 2.5 Flash Lite</v>
       </c>
       <c r="D7" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E7" t="str">
         <v>统一价</v>
@@ -7146,7 +7502,7 @@
         <v>Gemini 2.5 Flash Lite Preview</v>
       </c>
       <c r="D8" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E8" t="str">
         <v>统一价</v>
@@ -7181,10 +7537,10 @@
         <v>Gemini 2.5 Pro</v>
       </c>
       <c r="D9" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E9" t="str">
-        <v>输入&lt;=20万个token</v>
+        <v>输入≤20万个token</v>
       </c>
       <c r="F9" t="str">
         <v>2.5-pro</v>
@@ -7242,10 +7598,10 @@
         <v>Gemini 3 Flash Preview</v>
       </c>
       <c r="D11" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E11" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="F11" t="str">
         <v>3.0-flash</v>
@@ -7271,7 +7627,7 @@
         <v>11</v>
       </c>
       <c r="E12" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="F12" t="str">
         <v>3.0-flash</v>
@@ -7303,13 +7659,13 @@
         <v>Gemini 3.1 Flash Lite</v>
       </c>
       <c r="D13" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E13" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="F13" t="str">
-        <v>3.1-flash-lite (new)</v>
+        <v>3.1-flash-lite（new）</v>
       </c>
       <c r="G13" t="str">
         <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
@@ -7332,10 +7688,10 @@
         <v>13</v>
       </c>
       <c r="E14" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="F14" t="str">
-        <v>3.1-flash-lite (new)</v>
+        <v>3.1-flash-lite（new）</v>
       </c>
       <c r="G14" t="str">
         <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
@@ -7364,10 +7720,10 @@
         <v>Gemini 3.1 Flash Lite Preview</v>
       </c>
       <c r="D15" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E15" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="F15" t="str">
         <v>3.1-flash-lite-preview</v>
@@ -7393,7 +7749,7 @@
         <v>15</v>
       </c>
       <c r="E16" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="F16" t="str">
         <v>3.1-flash-lite-preview</v>
@@ -7425,10 +7781,10 @@
         <v>Gemini 3.1 Pro Preview</v>
       </c>
       <c r="D17" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E17" t="str">
-        <v>输入&lt;=20万个token</v>
+        <v>输入≤20万个token</v>
       </c>
       <c r="F17" t="str">
         <v>3.1-pro</v>
@@ -7486,13 +7842,13 @@
         <v>Gemini 3.5 Flash</v>
       </c>
       <c r="D19" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E19" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="F19" t="str">
-        <v>3.5-flash (new)</v>
+        <v>3.5-flash（new）</v>
       </c>
       <c r="G19" t="str">
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
@@ -7515,10 +7871,10 @@
         <v>19</v>
       </c>
       <c r="E20" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="F20" t="str">
-        <v>3.5-flash (new)</v>
+        <v>3.5-flash（new）</v>
       </c>
       <c r="G20" t="str">
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
@@ -7550,16 +7906,16 @@
         <v>Zhipu</v>
       </c>
       <c r="E21" t="str">
-        <v>32k&lt;=输入</v>
+        <v>输入：≤32K token</v>
       </c>
       <c r="F21" t="str">
         <v>5</v>
       </c>
       <c r="G21" t="str">
-        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="H21" t="str">
-        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="I21" t="str">
         <v>✅ 一致</v>
@@ -7576,16 +7932,16 @@
         <v>21</v>
       </c>
       <c r="E22" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>输入：＞32K token</v>
       </c>
       <c r="F22" t="str">
         <v>5</v>
       </c>
       <c r="G22" t="str">
-        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="H22" t="str">
-        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="I22" t="str">
         <v>✅ 一致</v>
@@ -7611,16 +7967,16 @@
         <v>Zhipu</v>
       </c>
       <c r="E23" t="str">
-        <v>输入&gt;=32k</v>
+        <v>输入：≤32K token</v>
       </c>
       <c r="F23" t="str">
         <v>5-Turbo</v>
       </c>
       <c r="G23" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="H23" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="I23" t="str">
         <v>✅ 一致</v>
@@ -7637,16 +7993,16 @@
         <v>23</v>
       </c>
       <c r="E24" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>输入：＞32K token</v>
       </c>
       <c r="F24" t="str">
         <v>5-Turbo</v>
       </c>
       <c r="G24" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="H24" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="I24" t="str">
         <v>✅ 一致</v>
@@ -7672,16 +8028,16 @@
         <v>Zhipu</v>
       </c>
       <c r="E25" t="str">
-        <v>32k&lt;=输入</v>
+        <v>输入：≤32K token</v>
       </c>
       <c r="F25" t="str">
-        <v>5.1 (new)</v>
+        <v>5.1（new）</v>
       </c>
       <c r="G25" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="H25" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="I25" t="str">
         <v>✅ 一致</v>
@@ -7698,16 +8054,16 @@
         <v>25</v>
       </c>
       <c r="E26" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>输入：＞32K token</v>
       </c>
       <c r="F26" t="str">
-        <v>5.1 (new)</v>
+        <v>5.1（new）</v>
       </c>
       <c r="G26" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="H26" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="I26" t="str">
         <v>✅ 一致</v>
@@ -7727,7 +8083,7 @@
         <v>gpt-4.1</v>
       </c>
       <c r="C27" t="str">
-        <v>gpt-4.1</v>
+        <v>GPT-4.1</v>
       </c>
       <c r="D27" t="str">
         <v>OpenAI</v>
@@ -7736,7 +8092,7 @@
         <v>统一价</v>
       </c>
       <c r="F27" t="str">
-        <v>gpt-4.1 (new)</v>
+        <v>4.1（new）</v>
       </c>
       <c r="G27" t="str">
         <v>入 $2 · 出 $8 · 缓 $0.5</v>
@@ -7762,7 +8118,7 @@
         <v>gpt-4o</v>
       </c>
       <c r="C28" t="str">
-        <v>gpt-4o</v>
+        <v>GPT-4o</v>
       </c>
       <c r="D28" t="str">
         <v>OpenAI</v>
@@ -7771,7 +8127,7 @@
         <v>统一价</v>
       </c>
       <c r="F28" t="str">
-        <v>gpt-4o</v>
+        <v>4o</v>
       </c>
       <c r="G28" t="str">
         <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
@@ -7797,7 +8153,7 @@
         <v>gpt-5</v>
       </c>
       <c r="C29" t="str">
-        <v>gpt-5</v>
+        <v>GPT-5</v>
       </c>
       <c r="D29" t="str">
         <v>OpenAI</v>
@@ -7806,16 +8162,16 @@
         <v>统一价</v>
       </c>
       <c r="F29" t="str">
-        <v>5-chat-latest</v>
+        <v>5</v>
       </c>
       <c r="G29" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="H29" t="str">
-        <v>入 ¥9.375 · 出 ¥75 · 缓 ¥0.9375</v>
+        <v>入 ¥9.37 · 出 ¥75 · 缓 ¥0.93</v>
       </c>
       <c r="I29" t="str">
-        <v>✅ 一致(÷7.5)</v>
+        <v>⚠ 缓-0.7%</v>
       </c>
       <c r="J29" t="str">
         <v>待填</v>
@@ -7832,7 +8188,7 @@
         <v>gpt-5-nano</v>
       </c>
       <c r="C30" t="str">
-        <v>gpt-5-nano</v>
+        <v>GPT-5 Nano</v>
       </c>
       <c r="D30" t="str">
         <v>OpenAI</v>
@@ -7847,10 +8203,10 @@
         <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="H30" t="str">
-        <v>入 ¥0.375 · 出 ¥3 · 缓 ¥0.0375</v>
+        <v>入 ¥0.37 · 出 ¥3 · 缓 ¥0.03</v>
       </c>
       <c r="I30" t="str">
-        <v>✅ 一致(÷7.5)</v>
+        <v>⚠ 入+13.8% 出+15.4% 缓-7.7%</v>
       </c>
       <c r="J30" t="str">
         <v>待填</v>
@@ -7867,7 +8223,7 @@
         <v>gpt-5.1</v>
       </c>
       <c r="C31" t="str">
-        <v>gpt-5.1</v>
+        <v>GPT-5.1</v>
       </c>
       <c r="D31" t="str">
         <v>OpenAI</v>
@@ -7882,10 +8238,10 @@
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="H31" t="str">
-        <v>入 ¥9.375 · 出 ¥75 · 缓 ¥0.9375</v>
+        <v>入 ¥8.75 · 出 ¥70 · 缓 ¥0.87</v>
       </c>
       <c r="I31" t="str">
-        <v>✅ 一致(÷7.5)</v>
+        <v>⚠ 缓-0.6%</v>
       </c>
       <c r="J31" t="str">
         <v>待填</v>
@@ -7902,7 +8258,7 @@
         <v>gpt-5.1-chat</v>
       </c>
       <c r="C32" t="str">
-        <v>gpt-5.1-chat</v>
+        <v>GPT-5.1 Chat</v>
       </c>
       <c r="D32" t="str">
         <v>OpenAI</v>
@@ -7911,16 +8267,16 @@
         <v>统一价</v>
       </c>
       <c r="F32" t="str">
-        <v>5.1-chat</v>
+        <v>5.1-chat-latest（new）</v>
       </c>
       <c r="G32" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="H32" t="str">
-        <v>入 ¥9.375 · 出 ¥75 · 缓 ¥0.9375</v>
+        <v>入 ¥9.37 · 出 ¥75 · 缓 ¥0.93</v>
       </c>
       <c r="I32" t="str">
-        <v>✅ 一致(÷7.5)</v>
+        <v>⚠ 缓-0.7%</v>
       </c>
       <c r="J32" t="str">
         <v>待填</v>
@@ -7937,7 +8293,7 @@
         <v>gpt-5.2</v>
       </c>
       <c r="C33" t="str">
-        <v>gpt-5.2</v>
+        <v>GPT-5.2</v>
       </c>
       <c r="D33" t="str">
         <v>OpenAI</v>
@@ -7952,10 +8308,10 @@
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="H33" t="str">
-        <v>入 ¥13.125 · 出 ¥105 · 缓 ¥1.3125</v>
+        <v>入 ¥12.25 · 出 ¥98 · 缓 ¥1.22</v>
       </c>
       <c r="I33" t="str">
-        <v>✅ 一致(÷7.5)</v>
+        <v>✅ 一致(÷隐含)</v>
       </c>
       <c r="J33" t="str">
         <v>待填</v>
@@ -7969,28 +8325,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>gpt-5.4</v>
+        <v>gpt-5.3-codex</v>
       </c>
       <c r="C34" t="str">
-        <v>gpt-5.4</v>
+        <v>GPT-5.3 Codex</v>
       </c>
       <c r="D34" t="str">
         <v>OpenAI</v>
       </c>
       <c r="E34" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>统一价</v>
       </c>
       <c r="F34" t="str">
-        <v>5.4</v>
+        <v>5.3-codex</v>
       </c>
       <c r="G34" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="H34" t="str">
-        <v>入 ¥18.75 · 出 ¥112.5 · 缓 ¥1.875</v>
+        <v>入 ¥13.13 · 出 ¥105 · 缓 ¥1.35</v>
       </c>
       <c r="I34" t="str">
-        <v>✅ 一致(÷7.5)</v>
+        <v>⚠ 缓+2.8%</v>
       </c>
       <c r="J34" t="str">
         <v>待填</v>
@@ -8003,17 +8359,26 @@
       <c r="A35">
         <v>34</v>
       </c>
+      <c r="B35" t="str">
+        <v>gpt-5.4</v>
+      </c>
+      <c r="C35" t="str">
+        <v>GPT-5.4</v>
+      </c>
+      <c r="D35" t="str">
+        <v>OpenAI</v>
+      </c>
       <c r="E35" t="str">
-        <v>输入&gt;272K context</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="F35" t="str">
         <v>5.4</v>
       </c>
       <c r="G35" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="H35" t="str">
-        <v>入 ¥37.5 · 出 ¥168.75 · 缓 ¥3.75</v>
+        <v>入 ¥18.75 · 出 ¥112.5 · 缓 ¥1.88</v>
       </c>
       <c r="I35" t="str">
         <v>✅ 一致(÷7.5)</v>
@@ -8029,26 +8394,17 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="str">
-        <v>gpt-5.4-mini</v>
-      </c>
-      <c r="C36" t="str">
-        <v>gpt-5.4-mini</v>
-      </c>
-      <c r="D36" t="str">
-        <v>OpenAI</v>
-      </c>
       <c r="E36" t="str">
-        <v>统一价</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="F36" t="str">
-        <v>5.4-mini</v>
+        <v>5.4</v>
       </c>
       <c r="G36" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="H36" t="str">
-        <v>入 ¥5.625 · 出 ¥33.75 · 缓 ¥0.5625</v>
+        <v>入 ¥37.5 · 出 ¥168.75 · 缓 ¥3.75</v>
       </c>
       <c r="I36" t="str">
         <v>✅ 一致(÷7.5)</v>
@@ -8065,25 +8421,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>gpt-5.4-pro</v>
+        <v>gpt-5.4-mini</v>
       </c>
       <c r="C37" t="str">
-        <v>gpt-5.4-pro</v>
+        <v>GPT-5.4 Mini</v>
       </c>
       <c r="D37" t="str">
         <v>OpenAI</v>
       </c>
       <c r="E37" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>统一价</v>
       </c>
       <c r="F37" t="str">
-        <v>5.4-pro</v>
+        <v>5.4-mini</v>
       </c>
       <c r="G37" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="H37" t="str">
-        <v>入 ¥225 · 出 ¥1350</v>
+        <v>入 ¥5.63 · 出 ¥33.75 · 缓 ¥0.56</v>
       </c>
       <c r="I37" t="str">
         <v>✅ 一致(÷7.5)</v>
@@ -8099,17 +8455,26 @@
       <c r="A38">
         <v>37</v>
       </c>
+      <c r="B38" t="str">
+        <v>gpt-5.4-pro</v>
+      </c>
+      <c r="C38" t="str">
+        <v>GPT-5.4 Pro</v>
+      </c>
+      <c r="D38" t="str">
+        <v>OpenAI</v>
+      </c>
       <c r="E38" t="str">
-        <v>输入&gt;272K context</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="F38" t="str">
         <v>5.4-pro</v>
       </c>
       <c r="G38" t="str">
-        <v>入 $60 · 出 $270</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="H38" t="str">
-        <v>入 ¥450 · 出 ¥2025</v>
+        <v>入 ¥225 · 出 ¥1350</v>
       </c>
       <c r="I38" t="str">
         <v>✅ 一致(÷7.5)</v>
@@ -8125,29 +8490,20 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="str">
-        <v>hy3-preview</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Hy3 Preview</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Tencent</v>
-      </c>
       <c r="E39" t="str">
-        <v>输入&lt;16k</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="F39" t="str">
-        <v>3-preview</v>
+        <v>5.4-pro</v>
       </c>
       <c r="G39" t="str">
-        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="H39" t="str">
-        <v>入 ¥1.2 · 出 ¥4.8 · 缓 ¥0.6</v>
+        <v>入 ¥450 · 出 ¥2025</v>
       </c>
       <c r="I39" t="str">
-        <v>⚠ 出+20% 缓+50%</v>
+        <v>✅ 一致(÷7.5)</v>
       </c>
       <c r="J39" t="str">
         <v>待填</v>
@@ -8160,20 +8516,29 @@
       <c r="A40">
         <v>39</v>
       </c>
+      <c r="B40" t="str">
+        <v>gpt-5.5</v>
+      </c>
+      <c r="C40" t="str">
+        <v>GPT-5.5</v>
+      </c>
+      <c r="D40" t="str">
+        <v>OpenAI</v>
+      </c>
       <c r="E40" t="str">
-        <v>16k&lt;=输入&lt;32k</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="F40" t="str">
-        <v>3-preview</v>
+        <v>5.5（new）</v>
       </c>
       <c r="G40" t="str">
-        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="H40" t="str">
-        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.8</v>
+        <v>入 ¥37.5 · 出 ¥225 · 缓 ¥3.75</v>
       </c>
       <c r="I40" t="str">
-        <v>⚠ 缓+33.3%</v>
+        <v>✅ 一致(÷7.5)</v>
       </c>
       <c r="J40" t="str">
         <v>待填</v>
@@ -8187,19 +8552,19 @@
         <v>40</v>
       </c>
       <c r="E41" t="str">
-        <v>输入&gt;=32k</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="F41" t="str">
-        <v>3-preview</v>
+        <v>5.5（new）</v>
       </c>
       <c r="G41" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="H41" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥1</v>
+        <v>入 ¥75 · 出 ¥337.5 · 缓 ¥7.5</v>
       </c>
       <c r="I41" t="str">
-        <v>⚠ 缓+25%</v>
+        <v>✅ 一致(÷7.5)</v>
       </c>
       <c r="J41" t="str">
         <v>待填</v>
@@ -8213,25 +8578,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>kimi-k2.5</v>
+        <v>hy3-preview</v>
       </c>
       <c r="C42" t="str">
-        <v>Kimi K2.5</v>
+        <v>Hy3 Preview</v>
       </c>
       <c r="D42" t="str">
-        <v>Tongyi</v>
+        <v>Tencent</v>
       </c>
       <c r="E42" t="str">
-        <v>统一价</v>
+        <v>16k&lt;=输入&lt;32k</v>
       </c>
       <c r="F42" t="str">
-        <v>k1.5 (普通搜索)</v>
+        <v>3-preview</v>
       </c>
       <c r="G42" t="str">
-        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
       <c r="H42" t="str">
-        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
       <c r="I42" t="str">
         <v>✅ 一致</v>
@@ -8247,26 +8612,17 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="str">
-        <v>minimax-m2.5</v>
-      </c>
-      <c r="C43" t="str">
-        <v>MiniMax M2.5</v>
-      </c>
-      <c r="D43" t="str">
-        <v>MiniMax</v>
-      </c>
       <c r="E43" t="str">
-        <v>统一价</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="F43" t="str">
-        <v>M2.5</v>
+        <v>3-preview</v>
       </c>
       <c r="G43" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="H43" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="I43" t="str">
         <v>✅ 一致</v>
@@ -8282,39 +8638,135 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="str">
+      <c r="E44" t="str">
+        <v>输入长度（0, 16k）</v>
+      </c>
+      <c r="F44" t="str">
+        <v>3-preview</v>
+      </c>
+      <c r="G44" t="str">
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+      </c>
+      <c r="H44" t="str">
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+      </c>
+      <c r="I44" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J44" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K44" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>kimi-k2.5</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Kimi K2.5</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Moonshot AI</v>
+      </c>
+      <c r="E45" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="F45" t="str">
+        <v>k1.5 (普通搜索)</v>
+      </c>
+      <c r="G45" t="str">
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+      </c>
+      <c r="H45" t="str">
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+      </c>
+      <c r="I45" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J45" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K45" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>minimax-m2.5</v>
+      </c>
+      <c r="C46" t="str">
+        <v>MiniMax M2.5</v>
+      </c>
+      <c r="D46" t="str">
+        <v>MiniMax</v>
+      </c>
+      <c r="E46" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="F46" t="str">
+        <v>M2.5</v>
+      </c>
+      <c r="G46" t="str">
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+      </c>
+      <c r="H46" t="str">
+        <v>入 ¥2.1 · 出 ¥8.4</v>
+      </c>
+      <c r="I46" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J46" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K46" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
         <v>minimax-m2.7</v>
       </c>
-      <c r="C44" t="str">
+      <c r="C47" t="str">
         <v>MiniMax M2.7</v>
       </c>
-      <c r="D44" t="str">
+      <c r="D47" t="str">
         <v>MiniMax</v>
       </c>
-      <c r="E44" t="str">
+      <c r="E47" t="str">
         <v>统一价</v>
       </c>
-      <c r="F44" t="str">
+      <c r="F47" t="str">
         <v>M2.7</v>
       </c>
-      <c r="G44" t="str">
+      <c r="G47" t="str">
         <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
-      <c r="H44" t="str">
+      <c r="H47" t="str">
         <v>入 ¥2.1 · 出 ¥8.4</v>
       </c>
-      <c r="I44" t="str">
-        <v>✅ 一致</v>
-      </c>
-      <c r="J44" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K44" t="str">
+      <c r="I47" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J47" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K47" t="str">
         <v>待填</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="42">
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
@@ -8345,25 +8797,28 @@
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="D25:D26"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K47"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8408,7 +8863,7 @@
         <v>claude-opus-4-6</v>
       </c>
       <c r="C2" t="str">
-        <v>claude-opus-4-6</v>
+        <v>Claude Opus 4.6</v>
       </c>
       <c r="D2" t="str">
         <v>Anthropic</v>
@@ -8443,7 +8898,7 @@
         <v>claude-opus-4-7</v>
       </c>
       <c r="C3" t="str">
-        <v>claude-opus-4-7</v>
+        <v>Claude Opus 4.7</v>
       </c>
       <c r="D3" t="str">
         <v>Anthropic</v>
@@ -8478,7 +8933,7 @@
         <v>claude-opus-4-8</v>
       </c>
       <c r="C4" t="str">
-        <v>claude-opus-4-8</v>
+        <v>Claude Opus 4.8</v>
       </c>
       <c r="D4" t="str">
         <v>Anthropic</v>
@@ -8513,7 +8968,7 @@
         <v>claude-sonnet-4-6</v>
       </c>
       <c r="C5" t="str">
-        <v>claude-sonnet-4-6</v>
+        <v>Claude Sonnet 4.6</v>
       </c>
       <c r="D5" t="str">
         <v>Anthropic</v>
@@ -8656,10 +9111,10 @@
         <v>Gemini 2.5 Flash</v>
       </c>
       <c r="D9" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E9" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="F9" t="str">
         <v>2.5-flash</v>
@@ -8685,7 +9140,7 @@
         <v>9</v>
       </c>
       <c r="E10" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="F10" t="str">
         <v>2.5-flash</v>
@@ -8717,7 +9172,7 @@
         <v>Gemini 2.5 Flash Lite</v>
       </c>
       <c r="D11" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E11" t="str">
         <v>统一价</v>
@@ -8752,7 +9207,7 @@
         <v>Gemini 2.5 Flash Lite Preview</v>
       </c>
       <c r="D12" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E12" t="str">
         <v>统一价</v>
@@ -8787,10 +9242,10 @@
         <v>Gemini 2.5 Pro</v>
       </c>
       <c r="D13" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E13" t="str">
-        <v>输入&lt;=20万个token</v>
+        <v>输入≤20万个token</v>
       </c>
       <c r="F13" t="str">
         <v>2.5-pro</v>
@@ -8848,10 +9303,10 @@
         <v>Gemini 3 Flash Preview</v>
       </c>
       <c r="D15" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E15" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="F15" t="str">
         <v>3.0-flash</v>
@@ -8877,7 +9332,7 @@
         <v>15</v>
       </c>
       <c r="E16" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="F16" t="str">
         <v>3.0-flash</v>
@@ -8909,13 +9364,13 @@
         <v>Gemini 3.1 Flash Lite</v>
       </c>
       <c r="D17" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E17" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="F17" t="str">
-        <v>3.1-flash-lite (new)</v>
+        <v>3.1-flash-lite（new）</v>
       </c>
       <c r="G17" t="str">
         <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
@@ -8938,10 +9393,10 @@
         <v>17</v>
       </c>
       <c r="E18" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="F18" t="str">
-        <v>3.1-flash-lite (new)</v>
+        <v>3.1-flash-lite（new）</v>
       </c>
       <c r="G18" t="str">
         <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
@@ -8970,10 +9425,10 @@
         <v>Gemini 3.1 Flash Lite Preview</v>
       </c>
       <c r="D19" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E19" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="F19" t="str">
         <v>3.1-flash-lite-preview</v>
@@ -8999,7 +9454,7 @@
         <v>19</v>
       </c>
       <c r="E20" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="F20" t="str">
         <v>3.1-flash-lite-preview</v>
@@ -9031,10 +9486,10 @@
         <v>Gemini 3.1 Pro Preview</v>
       </c>
       <c r="D21" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E21" t="str">
-        <v>输入&lt;=20万个token</v>
+        <v>输入≤20万个token</v>
       </c>
       <c r="F21" t="str">
         <v>3.1-pro</v>
@@ -9092,13 +9547,13 @@
         <v>Gemini 3.5 Flash</v>
       </c>
       <c r="D23" t="str">
-        <v>Google</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E23" t="str">
-        <v>输入:文本/图片/视频</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="F23" t="str">
-        <v>3.5-flash (new)</v>
+        <v>3.5-flash（new）</v>
       </c>
       <c r="G23" t="str">
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
@@ -9121,10 +9576,10 @@
         <v>23</v>
       </c>
       <c r="E24" t="str">
-        <v>输入:音频</v>
+        <v>输入：音频</v>
       </c>
       <c r="F24" t="str">
-        <v>3.5-flash (new)</v>
+        <v>3.5-flash（new）</v>
       </c>
       <c r="G24" t="str">
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
@@ -9156,16 +9611,16 @@
         <v>Zhipu</v>
       </c>
       <c r="E25" t="str">
-        <v>32k&lt;=输入</v>
+        <v>输入：≤32K token</v>
       </c>
       <c r="F25" t="str">
         <v>5</v>
       </c>
       <c r="G25" t="str">
-        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="H25" t="str">
-        <v>入 $0.924 · 出 $3.388 · 缓 $0.231</v>
+        <v>入 $0.616 · 出 $2.772 · 缓 $0.154</v>
       </c>
       <c r="I25" t="str">
         <v>✅ 一致(÷6.5)</v>
@@ -9182,16 +9637,16 @@
         <v>25</v>
       </c>
       <c r="E26" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>输入：＞32K token</v>
       </c>
       <c r="F26" t="str">
         <v>5</v>
       </c>
       <c r="G26" t="str">
-        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="H26" t="str">
-        <v>入 $0.616 · 出 $2.772 · 缓 $0.154</v>
+        <v>入 $0.924 · 出 $3.388 · 缓 $0.231</v>
       </c>
       <c r="I26" t="str">
         <v>✅ 一致(÷6.5)</v>
@@ -9217,16 +9672,16 @@
         <v>Zhipu</v>
       </c>
       <c r="E27" t="str">
-        <v>输入&gt;=32k</v>
+        <v>输入：≤32K token</v>
       </c>
       <c r="F27" t="str">
         <v>5-Turbo</v>
       </c>
       <c r="G27" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="H27" t="str">
-        <v>入 $1.078 · 出 $4.004 · 缓 $0.277</v>
+        <v>入 $0.77 · 出 $3.388 · 缓 $0.185</v>
       </c>
       <c r="I27" t="str">
         <v>✅ 一致(÷6.5)</v>
@@ -9243,16 +9698,16 @@
         <v>27</v>
       </c>
       <c r="E28" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>输入：＞32K token</v>
       </c>
       <c r="F28" t="str">
         <v>5-Turbo</v>
       </c>
       <c r="G28" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="H28" t="str">
-        <v>入 $0.77 · 出 $3.388 · 缓 $0.185</v>
+        <v>入 $1.078 · 出 $4.004 · 缓 $0.277</v>
       </c>
       <c r="I28" t="str">
         <v>✅ 一致(÷6.5)</v>
@@ -9278,16 +9733,16 @@
         <v>Zhipu</v>
       </c>
       <c r="E29" t="str">
-        <v>32k&lt;=输入</v>
+        <v>输入：≤32K token</v>
       </c>
       <c r="F29" t="str">
-        <v>5.1 (new)</v>
+        <v>5.1（new）</v>
       </c>
       <c r="G29" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="H29" t="str">
-        <v>入 $1.232 · 出 $4.312 · 缓 $0.308</v>
+        <v>入 $0.924 · 出 $3.696 · 缓 $0.2</v>
       </c>
       <c r="I29" t="str">
         <v>✅ 一致(÷6.5)</v>
@@ -9304,16 +9759,16 @@
         <v>29</v>
       </c>
       <c r="E30" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>输入：＞32K token</v>
       </c>
       <c r="F30" t="str">
-        <v>5.1 (new)</v>
+        <v>5.1（new）</v>
       </c>
       <c r="G30" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="H30" t="str">
-        <v>入 $0.924 · 出 $3.696 · 缓 $0.2</v>
+        <v>入 $1.232 · 出 $4.312 · 缓 $0.308</v>
       </c>
       <c r="I30" t="str">
         <v>✅ 一致(÷6.5)</v>
@@ -9333,7 +9788,7 @@
         <v>gpt-4.1</v>
       </c>
       <c r="C31" t="str">
-        <v>gpt-4.1</v>
+        <v>GPT-4.1</v>
       </c>
       <c r="D31" t="str">
         <v>OpenAI</v>
@@ -9342,7 +9797,7 @@
         <v>统一价</v>
       </c>
       <c r="F31" t="str">
-        <v>gpt-4.1 (new)</v>
+        <v>4.1（new）</v>
       </c>
       <c r="G31" t="str">
         <v>入 $2 · 出 $8 · 缓 $0.5</v>
@@ -9368,7 +9823,7 @@
         <v>gpt-4o</v>
       </c>
       <c r="C32" t="str">
-        <v>gpt-4o</v>
+        <v>GPT-4o</v>
       </c>
       <c r="D32" t="str">
         <v>OpenAI</v>
@@ -9377,7 +9832,7 @@
         <v>统一价</v>
       </c>
       <c r="F32" t="str">
-        <v>gpt-4o</v>
+        <v>4o</v>
       </c>
       <c r="G32" t="str">
         <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
@@ -9403,7 +9858,7 @@
         <v>gpt-5</v>
       </c>
       <c r="C33" t="str">
-        <v>gpt-5</v>
+        <v>GPT-5</v>
       </c>
       <c r="D33" t="str">
         <v>OpenAI</v>
@@ -9412,7 +9867,7 @@
         <v>统一价</v>
       </c>
       <c r="F33" t="str">
-        <v>5-chat-latest</v>
+        <v>5</v>
       </c>
       <c r="G33" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
@@ -9438,7 +9893,7 @@
         <v>gpt-5-nano</v>
       </c>
       <c r="C34" t="str">
-        <v>gpt-5-nano</v>
+        <v>GPT-5 Nano</v>
       </c>
       <c r="D34" t="str">
         <v>OpenAI</v>
@@ -9473,7 +9928,7 @@
         <v>gpt-5.1</v>
       </c>
       <c r="C35" t="str">
-        <v>gpt-5.1</v>
+        <v>GPT-5.1</v>
       </c>
       <c r="D35" t="str">
         <v>OpenAI</v>
@@ -9508,7 +9963,7 @@
         <v>gpt-5.1-chat</v>
       </c>
       <c r="C36" t="str">
-        <v>gpt-5.1-chat</v>
+        <v>GPT-5.1 Chat</v>
       </c>
       <c r="D36" t="str">
         <v>OpenAI</v>
@@ -9517,7 +9972,7 @@
         <v>统一价</v>
       </c>
       <c r="F36" t="str">
-        <v>5.1-chat</v>
+        <v>5.1-chat-latest（new）</v>
       </c>
       <c r="G36" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
@@ -9543,7 +9998,7 @@
         <v>gpt-5.2</v>
       </c>
       <c r="C37" t="str">
-        <v>gpt-5.2</v>
+        <v>GPT-5.2</v>
       </c>
       <c r="D37" t="str">
         <v>OpenAI</v>
@@ -9575,28 +10030,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>gpt-5.4</v>
+        <v>gpt-5.3-codex</v>
       </c>
       <c r="C38" t="str">
-        <v>gpt-5.4</v>
+        <v>GPT-5.3 Codex</v>
       </c>
       <c r="D38" t="str">
         <v>OpenAI</v>
       </c>
       <c r="E38" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>统一价</v>
       </c>
       <c r="F38" t="str">
-        <v>5.4</v>
+        <v>5.3-codex</v>
       </c>
       <c r="G38" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="H38" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.18</v>
       </c>
       <c r="I38" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 缓+2.9%</v>
       </c>
       <c r="J38" t="str">
         <v>待填</v>
@@ -9609,17 +10064,26 @@
       <c r="A39">
         <v>38</v>
       </c>
+      <c r="B39" t="str">
+        <v>gpt-5.4</v>
+      </c>
+      <c r="C39" t="str">
+        <v>GPT-5.4</v>
+      </c>
+      <c r="D39" t="str">
+        <v>OpenAI</v>
+      </c>
       <c r="E39" t="str">
-        <v>输入&gt;272K context</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="F39" t="str">
         <v>5.4</v>
       </c>
       <c r="G39" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="H39" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="I39" t="str">
         <v>✅ 一致</v>
@@ -9635,26 +10099,17 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="str">
-        <v>gpt-5.4-mini</v>
-      </c>
-      <c r="C40" t="str">
-        <v>gpt-5.4-mini</v>
-      </c>
-      <c r="D40" t="str">
-        <v>OpenAI</v>
-      </c>
       <c r="E40" t="str">
-        <v>统一价</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="F40" t="str">
-        <v>5.4-mini</v>
+        <v>5.4</v>
       </c>
       <c r="G40" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="H40" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="I40" t="str">
         <v>✅ 一致</v>
@@ -9671,25 +10126,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>gpt-5.4-pro</v>
+        <v>gpt-5.4-mini</v>
       </c>
       <c r="C41" t="str">
-        <v>gpt-5.4-pro</v>
+        <v>GPT-5.4 Mini</v>
       </c>
       <c r="D41" t="str">
         <v>OpenAI</v>
       </c>
       <c r="E41" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>统一价</v>
       </c>
       <c r="F41" t="str">
-        <v>5.4-pro</v>
+        <v>5.4-mini</v>
       </c>
       <c r="G41" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="H41" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="I41" t="str">
         <v>✅ 一致</v>
@@ -9705,17 +10160,26 @@
       <c r="A42">
         <v>41</v>
       </c>
+      <c r="B42" t="str">
+        <v>gpt-5.4-pro</v>
+      </c>
+      <c r="C42" t="str">
+        <v>GPT-5.4 Pro</v>
+      </c>
+      <c r="D42" t="str">
+        <v>OpenAI</v>
+      </c>
       <c r="E42" t="str">
-        <v>输入&gt;272K context</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="F42" t="str">
         <v>5.4-pro</v>
       </c>
       <c r="G42" t="str">
-        <v>入 $60 · 出 $270</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="H42" t="str">
-        <v>入 $60 · 出 $270</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="I42" t="str">
         <v>✅ 一致</v>
@@ -9731,29 +10195,20 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="str">
-        <v>kimi-k2.5</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Kimi K2.5</v>
-      </c>
-      <c r="D43" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="E43" t="str">
-        <v>统一价</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="F43" t="str">
-        <v>k1.5 (普通搜索)</v>
+        <v>5.4-pro</v>
       </c>
       <c r="G43" t="str">
-        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="H43" t="str">
-        <v>入 $0.616 · 出 $3.234 · 缓 $0.108</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="I43" t="str">
-        <v>✅ 一致(÷6.5)</v>
+        <v>✅ 一致</v>
       </c>
       <c r="J43" t="str">
         <v>待填</v>
@@ -9767,28 +10222,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>minimax-m2.5</v>
+        <v>gpt-5.5</v>
       </c>
       <c r="C44" t="str">
-        <v>MiniMax M2.5</v>
+        <v>GPT-5.5</v>
       </c>
       <c r="D44" t="str">
-        <v>MiniMax</v>
+        <v>OpenAI</v>
       </c>
       <c r="E44" t="str">
-        <v>统一价</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="F44" t="str">
-        <v>M2.5</v>
+        <v>5.5（new）</v>
       </c>
       <c r="G44" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="H44" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.03</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="I44" t="str">
-        <v>⚠ 入-7.1% 出-7.1% 缓-7.1%</v>
+        <v>✅ 一致</v>
       </c>
       <c r="J44" t="str">
         <v>待填</v>
@@ -9801,39 +10256,135 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="str">
+      <c r="E45" t="str">
+        <v>输入&gt;272K context</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5.5（new）</v>
+      </c>
+      <c r="G45" t="str">
+        <v>入 $10 · 出 $45 · 缓 $1</v>
+      </c>
+      <c r="H45" t="str">
+        <v>入 $10 · 出 $45 · 缓 $1</v>
+      </c>
+      <c r="I45" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J45" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K45" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>kimi-k2.5</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Kimi K2.5</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Moonshot AI</v>
+      </c>
+      <c r="E46" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="F46" t="str">
+        <v>k1.5 (普通搜索)</v>
+      </c>
+      <c r="G46" t="str">
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+      </c>
+      <c r="H46" t="str">
+        <v>入 $0.616 · 出 $3.234 · 缓 $0.108</v>
+      </c>
+      <c r="I46" t="str">
+        <v>✅ 一致(÷6.5)</v>
+      </c>
+      <c r="J46" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K46" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>minimax-m2.5</v>
+      </c>
+      <c r="C47" t="str">
+        <v>MiniMax M2.5</v>
+      </c>
+      <c r="D47" t="str">
+        <v>MiniMax</v>
+      </c>
+      <c r="E47" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="F47" t="str">
+        <v>M2.5</v>
+      </c>
+      <c r="G47" t="str">
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+      </c>
+      <c r="H47" t="str">
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.03</v>
+      </c>
+      <c r="I47" t="str">
+        <v>⚠ 入-7.1% 出-7.1% 缓-7.1%</v>
+      </c>
+      <c r="J47" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K47" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
         <v>minimax-m2.7</v>
       </c>
-      <c r="C45" t="str">
+      <c r="C48" t="str">
         <v>MiniMax M2.7</v>
       </c>
-      <c r="D45" t="str">
+      <c r="D48" t="str">
         <v>MiniMax</v>
       </c>
-      <c r="E45" t="str">
+      <c r="E48" t="str">
         <v>统一价</v>
       </c>
-      <c r="F45" t="str">
+      <c r="F48" t="str">
         <v>M2.7</v>
       </c>
-      <c r="G45" t="str">
+      <c r="G48" t="str">
         <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
-      <c r="H45" t="str">
+      <c r="H48" t="str">
         <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
-      <c r="I45" t="str">
+      <c r="I48" t="str">
         <v>⚠ 入-7.1% 出-7.1% 缓-7.1%</v>
       </c>
-      <c r="J45" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K45" t="str">
+      <c r="J48" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K48" t="str">
         <v>待填</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="39">
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:D10"/>
@@ -9864,22 +10415,449 @@
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="C29:C30"/>
     <mergeCell ref="D29:D30"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K48"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>序号</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Trinity ID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>显示名</v>
+      </c>
+      <c r="D1" t="str">
+        <v>厂商</v>
+      </c>
+      <c r="E1" t="str">
+        <v>价格档位</v>
+      </c>
+      <c r="F1" t="str">
+        <v>上游模型ID</v>
+      </c>
+      <c r="G1" t="str">
+        <v>厂商官方价</v>
+      </c>
+      <c r="H1" t="str">
+        <v>供应商挂牌(元/百万tokens)</v>
+      </c>
+      <c r="I1" t="str">
+        <v>供应商vs官方</v>
+      </c>
+      <c r="J1" t="str">
+        <v>折扣</v>
+      </c>
+      <c r="K1" t="str">
+        <v>成本(元/百万tokens)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>豆包 Doubao-Seed-2.1-Pro</v>
+      </c>
+      <c r="D2" t="str">
+        <v>火山方舟</v>
+      </c>
+      <c r="E2" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F2" t="str">
+        <v>doubao-seed-2-1-pro</v>
+      </c>
+      <c r="G2" t="str">
+        <v>入 ¥6 · 出 ¥30 · 缓 ¥1.2</v>
+      </c>
+      <c r="H2" t="str">
+        <v>入 ¥6 · 出 ¥30 · 缓 ¥1.2</v>
+      </c>
+      <c r="I2" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J2" t="str">
+        <v>—</v>
+      </c>
+      <c r="K2" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F3" t="str">
+        <v>doubao-seed-2-1-turbo</v>
+      </c>
+      <c r="G3" t="str">
+        <v>入 ¥3 · 出 ¥15 · 缓 ¥0.6</v>
+      </c>
+      <c r="H3" t="str">
+        <v>入 ¥3 · 出 ¥15 · 缓 ¥0.6</v>
+      </c>
+      <c r="I3" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J3" t="str">
+        <v>—</v>
+      </c>
+      <c r="K3" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="str">
+        <v>输入≤32k</v>
+      </c>
+      <c r="F4" t="str">
+        <v>doubao-seed-2-0-pro</v>
+      </c>
+      <c r="G4" t="str">
+        <v>入 ¥3.2 · 出 ¥16 · 缓 ¥0.64</v>
+      </c>
+      <c r="H4" t="str">
+        <v>入 ¥3.2 · 出 ¥16 · 缓 ¥0.64</v>
+      </c>
+      <c r="I4" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J4" t="str">
+        <v>—</v>
+      </c>
+      <c r="K4" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="str">
+        <v>输入&gt;32k</v>
+      </c>
+      <c r="F5" t="str">
+        <v>doubao-seed-2-0-pro</v>
+      </c>
+      <c r="G5" t="str">
+        <v>入 ¥6.4 · 出 ¥32 · 缓 ¥1.28</v>
+      </c>
+      <c r="H5" t="str">
+        <v>入 ¥6.4 · 出 ¥32 · 缓 ¥1.28</v>
+      </c>
+      <c r="I5" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J5" t="str">
+        <v>—</v>
+      </c>
+      <c r="K5" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="str">
+        <v>输入≤32k</v>
+      </c>
+      <c r="F6" t="str">
+        <v>doubao-seed-2-0-lite</v>
+      </c>
+      <c r="G6" t="str">
+        <v>入 ¥0.6 · 出 ¥3.6 · 缓 ¥0.12</v>
+      </c>
+      <c r="H6" t="str">
+        <v>入 ¥0.6 · 出 ¥3.6 · 缓 ¥0.12</v>
+      </c>
+      <c r="I6" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J6" t="str">
+        <v>—</v>
+      </c>
+      <c r="K6" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="E7" t="str">
+        <v>输入&gt;32k</v>
+      </c>
+      <c r="F7" t="str">
+        <v>doubao-seed-2-0-lite</v>
+      </c>
+      <c r="G7" t="str">
+        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
+      </c>
+      <c r="H7" t="str">
+        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
+      </c>
+      <c r="I7" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J7" t="str">
+        <v>—</v>
+      </c>
+      <c r="K7" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="E8" t="str">
+        <v>输入≤32k</v>
+      </c>
+      <c r="F8" t="str">
+        <v>doubao-seed-2-0-mini</v>
+      </c>
+      <c r="G8" t="str">
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.04</v>
+      </c>
+      <c r="H8" t="str">
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.04</v>
+      </c>
+      <c r="I8" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J8" t="str">
+        <v>—</v>
+      </c>
+      <c r="K8" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="E9" t="str">
+        <v>输入&gt;32k</v>
+      </c>
+      <c r="F9" t="str">
+        <v>doubao-seed-2-0-mini</v>
+      </c>
+      <c r="G9" t="str">
+        <v>入 ¥0.4 · 出 ¥4 · 缓 ¥0.08</v>
+      </c>
+      <c r="H9" t="str">
+        <v>入 ¥0.4 · 出 ¥4 · 缓 ¥0.08</v>
+      </c>
+      <c r="I9" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J9" t="str">
+        <v>—</v>
+      </c>
+      <c r="K9" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="E10" t="str">
+        <v>输入≤32k</v>
+      </c>
+      <c r="F10" t="str">
+        <v>doubao-seed-1-8</v>
+      </c>
+      <c r="G10" t="str">
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+      </c>
+      <c r="H10" t="str">
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+      </c>
+      <c r="I10" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J10" t="str">
+        <v>—</v>
+      </c>
+      <c r="K10" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="E11" t="str">
+        <v>输入&gt;32k</v>
+      </c>
+      <c r="F11" t="str">
+        <v>doubao-seed-1-8</v>
+      </c>
+      <c r="G11" t="str">
+        <v>入 ¥1.6 · 出 ¥4 · 缓 ¥0.32</v>
+      </c>
+      <c r="H11" t="str">
+        <v>入 ¥1.6 · 出 ¥4 · 缓 ¥0.32</v>
+      </c>
+      <c r="I11" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J11" t="str">
+        <v>—</v>
+      </c>
+      <c r="K11" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="E12" t="str">
+        <v>输入≤32k</v>
+      </c>
+      <c r="F12" t="str">
+        <v>doubao-seed-1-6</v>
+      </c>
+      <c r="G12" t="str">
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+      </c>
+      <c r="H12" t="str">
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+      </c>
+      <c r="I12" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J12" t="str">
+        <v>—</v>
+      </c>
+      <c r="K12" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="E13" t="str">
+        <v>输入&gt;32k</v>
+      </c>
+      <c r="F13" t="str">
+        <v>doubao-seed-1-6</v>
+      </c>
+      <c r="G13" t="str">
+        <v>入 ¥1.6 · 出 ¥4 · 缓 ¥0.32</v>
+      </c>
+      <c r="H13" t="str">
+        <v>入 ¥1.6 · 出 ¥4 · 缓 ¥0.32</v>
+      </c>
+      <c r="I13" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J13" t="str">
+        <v>—</v>
+      </c>
+      <c r="K13" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="E14" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F14" t="str">
+        <v>doubao-pro-32k</v>
+      </c>
+      <c r="G14" t="str">
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+      </c>
+      <c r="H14" t="str">
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+      </c>
+      <c r="I14" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J14" t="str">
+        <v>—</v>
+      </c>
+      <c r="K14" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="E15" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F15" t="str">
+        <v>doubao-lite-32k</v>
+      </c>
+      <c r="G15" t="str">
+        <v>入 ¥0.3 · 出 ¥0.6 · 缓 ¥0.06</v>
+      </c>
+      <c r="H15" t="str">
+        <v>入 ¥0.3 · 出 ¥0.6 · 缓 ¥0.06</v>
+      </c>
+      <c r="I15" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J15" t="str">
+        <v>—</v>
+      </c>
+      <c r="K15" t="str">
+        <v>—</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:B15"/>
+    <mergeCell ref="C2:C15"/>
+    <mergeCell ref="D2:D15"/>
+  </mergeCells>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9991,34 +10969,34 @@
         <v>AIGC国内站</v>
       </c>
       <c r="B4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4" t="str">
-        <v>+0.7% ~ +50%</v>
+        <v>+0.7% ~ +7.7%</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="str">
-        <v>hy3-preview(+50%)</v>
+        <v>—</v>
       </c>
     </row>
     <row r="5">
@@ -10026,25 +11004,25 @@
         <v>AIGC国际站</v>
       </c>
       <c r="B5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G5">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" t="str">
         <v>+0.7% ~ +7.1%</v>
@@ -10056,49 +11034,64 @@
         <v>—</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>—— 不一致超过10% · 档位明细 ——</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>火山方舟</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="str">
+        <v>—</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="str">
+        <v>—</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>供应商</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Trinity ID</v>
-      </c>
-      <c r="C8" t="str">
-        <v>显示名</v>
-      </c>
-      <c r="D8" t="str">
-        <v>档位</v>
-      </c>
-      <c r="E8" t="str">
-        <v>最大上浮%</v>
-      </c>
-      <c r="F8" t="str">
-        <v>供应商vs官方</v>
+        <v>—— 不一致超过10% · 档位明细 ——</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TokenHub广州</v>
+        <v>供应商</v>
       </c>
       <c r="B9" t="str">
-        <v>deepseek-v4-flash</v>
+        <v>Trinity ID</v>
       </c>
       <c r="C9" t="str">
-        <v>DeepSeek V4 Flash</v>
+        <v>显示名</v>
       </c>
       <c r="D9" t="str">
-        <v>统一价</v>
+        <v>档位</v>
       </c>
       <c r="E9" t="str">
-        <v>+900%</v>
+        <v>最大上浮%</v>
       </c>
       <c r="F9" t="str">
-        <v>⚠ 缓+900%</v>
+        <v>供应商vs官方</v>
       </c>
     </row>
     <row r="10">
@@ -10106,39 +11099,39 @@
         <v>TokenHub广州</v>
       </c>
       <c r="B10" t="str">
-        <v>deepseek-v4-pro</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="C10" t="str">
-        <v>DeepSeek V4 Pro</v>
+        <v>DeepSeek V4 Flash</v>
       </c>
       <c r="D10" t="str">
         <v>统一价</v>
       </c>
       <c r="E10" t="str">
-        <v>+3900%</v>
+        <v>+900%</v>
       </c>
       <c r="F10" t="str">
-        <v>⚠ 入+300% 出+300% 缓+3900%</v>
+        <v>⚠ 缓+900%</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>百炼北京</v>
+        <v>TokenHub广州</v>
       </c>
       <c r="B11" t="str">
-        <v>deepseek-v4-flash</v>
+        <v>deepseek-v4-pro</v>
       </c>
       <c r="C11" t="str">
-        <v>DeepSeek V4 Flash</v>
+        <v>DeepSeek V4 Pro</v>
       </c>
       <c r="D11" t="str">
         <v>统一价</v>
       </c>
       <c r="E11" t="str">
-        <v>+900%</v>
+        <v>+3900%</v>
       </c>
       <c r="F11" t="str">
-        <v>⚠ 缓+900%</v>
+        <v>⚠ 入+300% 出+300% 缓+3900%</v>
       </c>
     </row>
     <row r="12">
@@ -10146,19 +11139,19 @@
         <v>百炼北京</v>
       </c>
       <c r="B12" t="str">
-        <v>deepseek-v4-pro</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="C12" t="str">
-        <v>DeepSeek V4 Pro</v>
+        <v>DeepSeek V4 Flash</v>
       </c>
       <c r="D12" t="str">
         <v>统一价</v>
       </c>
       <c r="E12" t="str">
-        <v>+9500%</v>
+        <v>+900%</v>
       </c>
       <c r="F12" t="str">
-        <v>⚠ 入+300% 出+300% 缓+9500%</v>
+        <v>⚠ 缓+900%</v>
       </c>
     </row>
     <row r="13">
@@ -10166,33 +11159,33 @@
         <v>百炼北京</v>
       </c>
       <c r="B13" t="str">
-        <v>qwen3.5-flash</v>
+        <v>deepseek-v4-pro</v>
       </c>
       <c r="C13" t="str">
-        <v>Qwen3.5 Flash</v>
+        <v>DeepSeek V4 Pro</v>
       </c>
       <c r="D13" t="str">
-        <v>0&lt;输入&lt;=128k</v>
+        <v>统一价</v>
       </c>
       <c r="E13" t="str">
-        <v>+100%</v>
+        <v>+9500%</v>
       </c>
       <c r="F13" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>⚠ 入+300% 出+300% 缓+9500%</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>百炼北京</v>
       </c>
       <c r="B14" t="str">
-        <v/>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>Qwen3.5 Flash</v>
       </c>
       <c r="D14" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>0&lt;输入&lt;=128k</v>
       </c>
       <c r="E14" t="str">
         <v>+100%</v>
@@ -10212,7 +11205,7 @@
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E15" t="str">
         <v>+100%</v>
@@ -10223,16 +11216,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>百炼北京</v>
+        <v/>
       </c>
       <c r="B16" t="str">
-        <v>qwen3.5-plus</v>
+        <v/>
       </c>
       <c r="C16" t="str">
-        <v>Qwen3.5 Plus</v>
+        <v/>
       </c>
       <c r="D16" t="str">
-        <v>输入&lt;=128k</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="E16" t="str">
         <v>+100%</v>
@@ -10243,16 +11236,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>百炼北京</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>Qwen3.5 Plus</v>
       </c>
       <c r="D17" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>输入&lt;=128k</v>
       </c>
       <c r="E17" t="str">
         <v>+100%</v>
@@ -10272,7 +11265,7 @@
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E18" t="str">
         <v>+100%</v>
@@ -10283,77 +11276,37 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>AIGC国内站</v>
+        <v/>
       </c>
       <c r="B19" t="str">
-        <v>hy3-preview</v>
+        <v/>
       </c>
       <c r="C19" t="str">
-        <v>Hy3 Preview</v>
+        <v/>
       </c>
       <c r="D19" t="str">
-        <v>输入&lt;16k</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="E19" t="str">
-        <v>+50%</v>
+        <v>+100%</v>
       </c>
       <c r="F19" t="str">
-        <v>⚠ 出+20% 缓+50%</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v/>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v>16k&lt;=输入&lt;32k</v>
-      </c>
-      <c r="E20" t="str">
-        <v>+33.3%</v>
-      </c>
-      <c r="F20" t="str">
-        <v>⚠ 缓+33.3%</v>
+        <v>⚠ 缓+100%</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
-      </c>
-      <c r="B21" t="str">
-        <v/>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
-        <v>输入&gt;=32k</v>
-      </c>
-      <c r="E21" t="str">
-        <v>+25%</v>
-      </c>
-      <c r="F21" t="str">
-        <v>⚠ 缓+25%</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>生成时间：2026-07-02T03:50:15Z</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
+        <v>生成时间：2026-07-02T08:55:34Z</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
         <v>说明：一致=与厂商官方价偏差&lt;0.5%（含 FX 7.5/7.25/6.5 最佳匹配）；不一致上浮=供应商高于官方的偏差%；模型级不一致=任一档位不一致</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/pricing/output/trinity-pricing-text.xlsx
+++ b/pricing/output/trinity-pricing-text.xlsx
@@ -9,7 +9,8 @@
     <sheet name="AIGC国内站" sheetId="4" r:id="rId4"/>
     <sheet name="AIGC国际站" sheetId="5" r:id="rId5"/>
     <sheet name="火山方舟" sheetId="6" r:id="rId6"/>
-    <sheet name="汇总-供应商vs官方" sheetId="7" r:id="rId7"/>
+    <sheet name="网聚云联云门户" sheetId="7" r:id="rId7"/>
+    <sheet name="汇总-供应商vs官方" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -403,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q91"/>
+  <dimension ref="A1:Q90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,10 +461,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>claude-opus-4-6</v>
+        <v>claude-fable-5</v>
       </c>
       <c r="B2" t="str">
-        <v>Claude Opus 4.6</v>
+        <v>Claude Fable 5</v>
       </c>
       <c r="C2" t="str">
         <v>Anthropic</v>
@@ -472,40 +473,40 @@
         <v>统一价</v>
       </c>
       <c r="E2" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="F2" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="G2" t="str">
         <v>—</v>
       </c>
       <c r="H2" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="I2" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="J2" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K2" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L2" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M2" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N2" t="str">
         <v>—</v>
       </c>
       <c r="O2" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P2" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="Q2" t="str">
         <v/>
@@ -513,10 +514,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>claude-opus-4-7</v>
+        <v>claude-opus-4-6</v>
       </c>
       <c r="B3" t="str">
-        <v>Claude Opus 4.7</v>
+        <v>Claude Opus 4.6</v>
       </c>
       <c r="C3" t="str">
         <v>Anthropic</v>
@@ -566,10 +567,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>claude-opus-4-8</v>
+        <v>claude-opus-4-7</v>
       </c>
       <c r="B4" t="str">
-        <v>Claude Opus 4.8</v>
+        <v>Claude Opus 4.7</v>
       </c>
       <c r="C4" t="str">
         <v>Anthropic</v>
@@ -578,7 +579,7 @@
         <v>统一价</v>
       </c>
       <c r="E4" t="str">
-        <v>入 $5 · 出 $25</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="F4" t="str">
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
@@ -599,30 +600,30 @@
         <v>0%</v>
       </c>
       <c r="L4" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M4" t="str">
-        <v>入✅ 出✅ 缓—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N4" t="str">
         <v>—</v>
       </c>
       <c r="O4" t="str">
-        <v>入✅ 出✅ 缓—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P4" t="str">
-        <v>入✅ 出✅ 缓—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q4" t="str">
-        <v>目录名 cd-opus-4.8</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>claude-sonnet-4-6</v>
+        <v>claude-opus-4-8</v>
       </c>
       <c r="B5" t="str">
-        <v>Claude Sonnet 4.6</v>
+        <v>Claude Opus 4.8</v>
       </c>
       <c r="C5" t="str">
         <v>Anthropic</v>
@@ -631,19 +632,19 @@
         <v>统一价</v>
       </c>
       <c r="E5" t="str">
-        <v>入 $3 · 出 $15 · 缓 $0.3</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="F5" t="str">
-        <v>入 $3 · 出 $15 · 缓 $0.3</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="G5" t="str">
         <v>—</v>
       </c>
       <c r="H5" t="str">
-        <v>入 $3 · 出 $15 · 缓 $0.3</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="I5" t="str">
-        <v>入 $3 · 出 $15 · 缓 $0.3</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="J5" t="str">
         <v>0%</v>
@@ -667,36 +668,36 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q5" t="str">
-        <v/>
+        <v>目录名 cd-opus-4.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>deepseek-v3.2</v>
+        <v>claude-sonnet-4-6</v>
       </c>
       <c r="B6" t="str">
-        <v>DeepSeek V3.2</v>
+        <v>Claude Sonnet 4.6</v>
       </c>
       <c r="C6" t="str">
-        <v>DeepSeek</v>
+        <v>Anthropic</v>
       </c>
       <c r="D6" t="str">
         <v>统一价</v>
       </c>
       <c r="E6" t="str">
-        <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
+        <v>入 $3 · 出 $15 · 缓 $0.3</v>
       </c>
       <c r="F6" t="str">
-        <v>入 $0.308 · 出 $0.462 · 缓 $0.062</v>
+        <v>入 $3 · 出 $15 · 缓 $0.3</v>
       </c>
       <c r="G6" t="str">
-        <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
+        <v>—</v>
       </c>
       <c r="H6" t="str">
-        <v>入 $0.2288 · 出 $0.3432 · 缓 $0.02288</v>
+        <v>入 $3 · 出 $15 · 缓 $0.3</v>
       </c>
       <c r="I6" t="str">
-        <v>入 $0.307692 · 出 $0.461538 · 缓 $0.061538</v>
+        <v>入 $3 · 出 $15 · 缓 $0.3</v>
       </c>
       <c r="J6" t="str">
         <v>0%</v>
@@ -708,69 +709,69 @@
         <v>0%</v>
       </c>
       <c r="M6" t="str">
-        <v>入✅ 出✅ 缓⚠+0.7%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N6" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O6" t="str">
-        <v>入⚠-25.6% 出⚠-25.6% 缓⚠-62.8%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P6" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q6" t="str">
-        <v>v3.2 价目见百炼模型定价；v4 见 DeepSeek API 文档</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>deepseek-v4-flash</v>
+        <v>claude-sonnet-5</v>
       </c>
       <c r="B7" t="str">
-        <v>DeepSeek V4 Flash</v>
+        <v>Claude Sonnet 5</v>
       </c>
       <c r="C7" t="str">
-        <v>DeepSeek</v>
+        <v>Anthropic</v>
       </c>
       <c r="D7" t="str">
         <v>统一价</v>
       </c>
       <c r="E7" t="str">
-        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
+        <v>—</v>
       </c>
       <c r="F7" t="str">
-        <v>入 $0.154 · 出 $0.308 · 缓 $0.003</v>
+        <v>—</v>
       </c>
       <c r="G7" t="str">
-        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.2</v>
+        <v>—</v>
       </c>
       <c r="H7" t="str">
-        <v>入 $0.098 · 出 $0.196 · 缓 $0.02</v>
+        <v>—</v>
       </c>
       <c r="I7" t="str">
-        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.030769</v>
+        <v>—</v>
       </c>
       <c r="J7" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K7" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L7" t="str">
-        <v>+900%</v>
+        <v>—</v>
       </c>
       <c r="M7" t="str">
-        <v>入✅ 出✅ 缓⚠-2.5%</v>
+        <v>—</v>
       </c>
       <c r="N7" t="str">
-        <v>入✅ 出✅ 缓⚠+900%</v>
+        <v>—</v>
       </c>
       <c r="O7" t="str">
-        <v>入⚠-36.3% 出⚠-36.3% 缓⚠+550%</v>
+        <v>—</v>
       </c>
       <c r="P7" t="str">
-        <v>入✅ 出✅ 缓⚠+900%</v>
+        <v>—</v>
       </c>
       <c r="Q7" t="str">
         <v/>
@@ -778,10 +779,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>deepseek-v4-flash-202605</v>
+        <v>deepseek-v3.2</v>
       </c>
       <c r="B8" t="str">
-        <v>DeepSeek V4 Flash Direct</v>
+        <v>DeepSeek V3.2</v>
       </c>
       <c r="C8" t="str">
         <v>DeepSeek</v>
@@ -790,19 +791,19 @@
         <v>统一价</v>
       </c>
       <c r="E8" t="str">
-        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
+        <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
       </c>
       <c r="F8" t="str">
-        <v>—</v>
+        <v>入 $0.308 · 出 $0.462 · 缓 $0.062</v>
       </c>
       <c r="G8" t="str">
-        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
+        <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
       </c>
       <c r="H8" t="str">
-        <v>入 $0.098 · 出 $0.196 · 缓 $0.02</v>
+        <v>入 $0.2288 · 出 $0.3432 · 缓 $0.02288</v>
       </c>
       <c r="I8" t="str">
-        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.307692 · 出 $0.461538 · 缓 $0.061538</v>
       </c>
       <c r="J8" t="str">
         <v>0%</v>
@@ -814,27 +815,27 @@
         <v>0%</v>
       </c>
       <c r="M8" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓⚠+0.7%</v>
       </c>
       <c r="N8" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O8" t="str">
-        <v>入⚠-36.3% 出⚠-36.3% 缓⚠+550%</v>
+        <v>入⚠-25.6% 出⚠-25.6% 缓⚠-62.8%</v>
       </c>
       <c r="P8" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q8" t="str">
-        <v/>
+        <v>v3.2 价目见百炼模型定价；v4 见 DeepSeek API 文档</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>deepseek-v4-pro</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="B9" t="str">
-        <v>DeepSeek V4 Pro</v>
+        <v>DeepSeek V4 Flash</v>
       </c>
       <c r="C9" t="str">
         <v>DeepSeek</v>
@@ -843,40 +844,40 @@
         <v>统一价</v>
       </c>
       <c r="E9" t="str">
-        <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
+        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="F9" t="str">
-        <v>入 $0.462 · 出 $0.923 · 缓 $0.004</v>
+        <v>入 $0.154 · 出 $0.308 · 缓 $0.003</v>
       </c>
       <c r="G9" t="str">
-        <v>入 ¥12 · 出 ¥24 · 缓 ¥1</v>
+        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.2</v>
       </c>
       <c r="H9" t="str">
-        <v>入 $0.435 · 出 $0.87 · 缓 $0.003625</v>
+        <v>入 $0.098 · 出 $0.196 · 缓 $0.02</v>
       </c>
       <c r="I9" t="str">
-        <v>入 $1.846154 · 出 $3.692308 · 缓 $0.153846</v>
+        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.030769</v>
       </c>
       <c r="J9" t="str">
-        <v>+300%</v>
+        <v>0%</v>
       </c>
       <c r="K9" t="str">
-        <v>+300%</v>
+        <v>0%</v>
       </c>
       <c r="L9" t="str">
-        <v>+3900%</v>
+        <v>+900%</v>
       </c>
       <c r="M9" t="str">
-        <v>入✅ 出✅ 缓⚠+4%</v>
+        <v>入✅ 出✅ 缓⚠-2.5%</v>
       </c>
       <c r="N9" t="str">
-        <v>入⚠+300% 出⚠+300% 缓⚠+3900%</v>
+        <v>入✅ 出✅ 缓⚠+900%</v>
       </c>
       <c r="O9" t="str">
-        <v>入⚠-5.8% 出⚠-5.8% 缓⚠-5.7%</v>
+        <v>入⚠-36.3% 出⚠-36.3% 缓⚠+550%</v>
       </c>
       <c r="P9" t="str">
-        <v>入⚠+300% 出⚠+300% 缓⚠+3900%</v>
+        <v>入✅ 出✅ 缓⚠+900%</v>
       </c>
       <c r="Q9" t="str">
         <v/>
@@ -884,10 +885,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>deepseek-v4-pro-202606</v>
+        <v>deepseek-v4-flash-202605</v>
       </c>
       <c r="B10" t="str">
-        <v>DeepSeek V4 Pro Direct</v>
+        <v>DeepSeek V4 Flash Direct</v>
       </c>
       <c r="C10" t="str">
         <v>DeepSeek</v>
@@ -896,19 +897,19 @@
         <v>统一价</v>
       </c>
       <c r="E10" t="str">
-        <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
+        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="F10" t="str">
         <v>—</v>
       </c>
       <c r="G10" t="str">
-        <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
+        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="H10" t="str">
-        <v>入 $0.435 · 出 $0.87 · 缓 $0.003625</v>
+        <v>入 $0.098 · 出 $0.196 · 缓 $0.02</v>
       </c>
       <c r="I10" t="str">
-        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
+        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
       </c>
       <c r="J10" t="str">
         <v>0%</v>
@@ -926,7 +927,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O10" t="str">
-        <v>入⚠-5.8% 出⚠-5.8% 缓⚠-5.7%</v>
+        <v>入⚠-36.3% 出⚠-36.3% 缓⚠+550%</v>
       </c>
       <c r="P10" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -937,96 +938,105 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>gemini-2.5-flash</v>
+        <v>deepseek-v4-pro</v>
       </c>
       <c r="B11" t="str">
-        <v>Gemini 2.5 Flash</v>
+        <v>DeepSeek V4 Pro</v>
       </c>
       <c r="C11" t="str">
-        <v>Google DeepMind</v>
+        <v>DeepSeek</v>
       </c>
       <c r="D11" t="str">
-        <v>输入：文本、图片、视频</v>
+        <v>统一价</v>
       </c>
       <c r="E11" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
       </c>
       <c r="F11" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>入 $0.462 · 出 $0.923 · 缓 $0.004</v>
       </c>
       <c r="G11" t="str">
-        <v>—</v>
+        <v>入 ¥12 · 出 ¥24 · 缓 ¥1</v>
       </c>
       <c r="H11" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>入 $0.435 · 出 $0.87 · 缓 $0.003625</v>
       </c>
       <c r="I11" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>入 $1.846154 · 出 $3.692308 · 缓 $0.153846</v>
       </c>
       <c r="J11" t="str">
-        <v>0%</v>
+        <v>+300%</v>
       </c>
       <c r="K11" t="str">
-        <v>0%</v>
+        <v>+300%</v>
       </c>
       <c r="L11" t="str">
-        <v>0%</v>
+        <v>+3900%</v>
       </c>
       <c r="M11" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅ 缓⚠+4%</v>
       </c>
       <c r="N11" t="str">
-        <v>—</v>
+        <v>入⚠+300% 出⚠+300% 缓⚠+3900%</v>
       </c>
       <c r="O11" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠-5.8% 出⚠-5.8% 缓⚠-5.7%</v>
       </c>
       <c r="P11" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠+300% 出⚠+300% 缓⚠+3900%</v>
       </c>
       <c r="Q11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="str">
+        <v>deepseek-v4-pro-202606</v>
+      </c>
+      <c r="B12" t="str">
+        <v>DeepSeek V4 Pro Direct</v>
+      </c>
+      <c r="C12" t="str">
+        <v>DeepSeek</v>
+      </c>
       <c r="D12" t="str">
-        <v>输入：音频</v>
+        <v>统一价</v>
       </c>
       <c r="E12" t="str">
-        <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
+        <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
       </c>
       <c r="F12" t="str">
-        <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
+        <v>—</v>
       </c>
       <c r="G12" t="str">
-        <v>—</v>
+        <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
       </c>
       <c r="H12" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>入 $0.435 · 出 $0.87 · 缓 $0.003625</v>
       </c>
       <c r="I12" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
       </c>
       <c r="J12" t="str">
-        <v>-70%</v>
+        <v>0%</v>
       </c>
       <c r="K12" t="str">
         <v>0%</v>
       </c>
       <c r="L12" t="str">
-        <v>-70%</v>
+        <v>0%</v>
       </c>
       <c r="M12" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N12" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O12" t="str">
-        <v>入⚠-70% 出✅ 缓⚠-70%</v>
+        <v>入⚠-5.8% 出⚠-5.8% 缓⚠-5.7%</v>
       </c>
       <c r="P12" t="str">
-        <v>ℹ 线上音频未单独定价</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q12" t="str">
         <v/>
@@ -1034,31 +1044,31 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>gemini-2.5-flash-lite</v>
+        <v>gemini-2.5-flash</v>
       </c>
       <c r="B13" t="str">
-        <v>Gemini 2.5 Flash Lite</v>
+        <v>Gemini 2.5 Flash</v>
       </c>
       <c r="C13" t="str">
         <v>Google DeepMind</v>
       </c>
       <c r="D13" t="str">
-        <v>统一价</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="E13" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="F13" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="G13" t="str">
         <v>—</v>
       </c>
       <c r="H13" t="str">
-        <v>入 $0.09999999999999999 · 出 $0.39999999999999997 · 缓 $0.01</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="I13" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="J13" t="str">
         <v>0%</v>
@@ -1086,41 +1096,32 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>gemini-2.5-flash-lite-preview</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Gemini 2.5 Flash Lite Preview</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Google DeepMind</v>
-      </c>
       <c r="D14" t="str">
-        <v>统一价</v>
+        <v>输入：音频</v>
       </c>
       <c r="E14" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+        <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
       </c>
       <c r="F14" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+        <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
       </c>
       <c r="G14" t="str">
         <v>—</v>
       </c>
       <c r="H14" t="str">
-        <v>入 $0.09999999999999999 · 出 $0.39999999999999997 · 缓 $0.01</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="I14" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="J14" t="str">
-        <v>0%</v>
+        <v>-70%</v>
       </c>
       <c r="K14" t="str">
         <v>0%</v>
       </c>
       <c r="L14" t="str">
-        <v>0%</v>
+        <v>-70%</v>
       </c>
       <c r="M14" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1129,42 +1130,42 @@
         <v>—</v>
       </c>
       <c r="O14" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠-70% 出✅ 缓⚠-70%</v>
       </c>
       <c r="P14" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>ℹ 线上音频未单独定价</v>
       </c>
       <c r="Q14" t="str">
-        <v>preview 别名，价目同 gemini-2.5-flash-lite</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>gemini-2.5-pro</v>
+        <v>gemini-2.5-flash-lite</v>
       </c>
       <c r="B15" t="str">
-        <v>Gemini 2.5 Pro</v>
+        <v>Gemini 2.5 Flash Lite</v>
       </c>
       <c r="C15" t="str">
         <v>Google DeepMind</v>
       </c>
       <c r="D15" t="str">
-        <v>输入≤20万个token</v>
+        <v>统一价</v>
       </c>
       <c r="E15" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="F15" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="G15" t="str">
         <v>—</v>
       </c>
       <c r="H15" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $0.09999999999999999 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
       <c r="I15" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="J15" t="str">
         <v>0%</v>
@@ -1192,23 +1193,32 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="str">
+        <v>gemini-2.5-flash-lite-preview</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Gemini 2.5 Flash Lite Preview</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Google DeepMind</v>
+      </c>
       <c r="D16" t="str">
-        <v>输入&gt;20万个token</v>
+        <v>统一价</v>
       </c>
       <c r="E16" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="F16" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="G16" t="str">
         <v>—</v>
       </c>
       <c r="H16" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $0.09999999999999999 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
       <c r="I16" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="J16" t="str">
         <v>0%</v>
@@ -1226,42 +1236,42 @@
         <v>—</v>
       </c>
       <c r="O16" t="str">
-        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P16" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>preview 别名，价目同 gemini-2.5-flash-lite</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>gemini-3-flash-preview</v>
+        <v>gemini-2.5-pro</v>
       </c>
       <c r="B17" t="str">
-        <v>Gemini 3 Flash Preview</v>
+        <v>Gemini 2.5 Pro</v>
       </c>
       <c r="C17" t="str">
         <v>Google DeepMind</v>
       </c>
       <c r="D17" t="str">
-        <v>输入：文本、图片、视频</v>
+        <v>输入≤20万个token</v>
       </c>
       <c r="E17" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="F17" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G17" t="str">
         <v>—</v>
       </c>
       <c r="H17" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.049999999999999996</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="I17" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="J17" t="str">
         <v>0%</v>
@@ -1290,31 +1300,31 @@
     </row>
     <row r="18">
       <c r="D18" t="str">
-        <v>输入：音频</v>
+        <v>输入&gt;20万个token</v>
       </c>
       <c r="E18" t="str">
-        <v>入 $1 · 出 $3 · 缓 $0.1</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="F18" t="str">
-        <v>入 $1 · 出 $3 · 缓 $0.1</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="G18" t="str">
         <v>—</v>
       </c>
       <c r="H18" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.049999999999999996</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="I18" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="J18" t="str">
-        <v>-50%</v>
+        <v>0%</v>
       </c>
       <c r="K18" t="str">
         <v>0%</v>
       </c>
       <c r="L18" t="str">
-        <v>-50%</v>
+        <v>0%</v>
       </c>
       <c r="M18" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1323,10 +1333,10 @@
         <v>—</v>
       </c>
       <c r="O18" t="str">
-        <v>入⚠-50% 出✅ 缓⚠-50%</v>
+        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
       <c r="P18" t="str">
-        <v>ℹ 线上音频未单独定价</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q18" t="str">
         <v/>
@@ -1334,10 +1344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>gemini-3.1-flash-lite</v>
+        <v>gemini-3-flash-preview</v>
       </c>
       <c r="B19" t="str">
-        <v>Gemini 3.1 Flash Lite</v>
+        <v>Gemini 3 Flash Preview</v>
       </c>
       <c r="C19" t="str">
         <v>Google DeepMind</v>
@@ -1346,19 +1356,19 @@
         <v>输入：文本、图片、视频</v>
       </c>
       <c r="E19" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
       <c r="F19" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
       <c r="G19" t="str">
         <v>—</v>
       </c>
       <c r="H19" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.049999999999999996</v>
       </c>
       <c r="I19" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
       <c r="J19" t="str">
         <v>0%</v>
@@ -1390,19 +1400,19 @@
         <v>输入：音频</v>
       </c>
       <c r="E20" t="str">
-        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
+        <v>入 $1 · 出 $3 · 缓 $0.1</v>
       </c>
       <c r="F20" t="str">
-        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
+        <v>入 $1 · 出 $3 · 缓 $0.1</v>
       </c>
       <c r="G20" t="str">
         <v>—</v>
       </c>
       <c r="H20" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.049999999999999996</v>
       </c>
       <c r="I20" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
       <c r="J20" t="str">
         <v>-50%</v>
@@ -1431,10 +1441,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>gemini-3.1-flash-lite-preview</v>
+        <v>gemini-3.1-flash-lite</v>
       </c>
       <c r="B21" t="str">
-        <v>Gemini 3.1 Flash Lite Preview</v>
+        <v>Gemini 3.1 Flash Lite</v>
       </c>
       <c r="C21" t="str">
         <v>Google DeepMind</v>
@@ -1528,31 +1538,31 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>gemini-3.1-pro-preview</v>
+        <v>gemini-3.1-flash-lite-preview</v>
       </c>
       <c r="B23" t="str">
-        <v>Gemini 3.1 Pro Preview</v>
+        <v>Gemini 3.1 Flash Lite Preview</v>
       </c>
       <c r="C23" t="str">
         <v>Google DeepMind</v>
       </c>
       <c r="D23" t="str">
-        <v>输入≤20万个token</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="E23" t="str">
-        <v>入 $2 · 出 $12 · 缓 $0.2</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
       <c r="F23" t="str">
-        <v>入 $2 · 出 $12 · 缓 $0.2</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
       <c r="G23" t="str">
         <v>—</v>
       </c>
       <c r="H23" t="str">
-        <v>入 $2 · 出 $12 · 缓 $0.19999999999999998</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
       </c>
       <c r="I23" t="str">
-        <v>入 $2 · 出 $12 · 缓 $0.2</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
       <c r="J23" t="str">
         <v>0%</v>
@@ -1581,31 +1591,31 @@
     </row>
     <row r="24">
       <c r="D24" t="str">
-        <v>输入&gt;20万个token</v>
+        <v>输入：音频</v>
       </c>
       <c r="E24" t="str">
-        <v>入 $4 · 出 $18 · 缓 $0.4</v>
+        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
       </c>
       <c r="F24" t="str">
-        <v>入 $4 · 出 $18 · 缓 $0.4</v>
+        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
       </c>
       <c r="G24" t="str">
         <v>—</v>
       </c>
       <c r="H24" t="str">
-        <v>入 $2 · 出 $12 · 缓 $0.19999999999999998</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
       </c>
       <c r="I24" t="str">
-        <v>入 $4 · 出 $18 · 缓 $0.4</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
       <c r="J24" t="str">
-        <v>0%</v>
+        <v>-50%</v>
       </c>
       <c r="K24" t="str">
         <v>0%</v>
       </c>
       <c r="L24" t="str">
-        <v>0%</v>
+        <v>-50%</v>
       </c>
       <c r="M24" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1614,10 +1624,10 @@
         <v>—</v>
       </c>
       <c r="O24" t="str">
-        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
+        <v>入⚠-50% 出✅ 缓⚠-50%</v>
       </c>
       <c r="P24" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>ℹ 线上音频未单独定价</v>
       </c>
       <c r="Q24" t="str">
         <v/>
@@ -1625,31 +1635,31 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>gemini-3.5-flash</v>
+        <v>gemini-3.1-pro-preview</v>
       </c>
       <c r="B25" t="str">
-        <v>Gemini 3.5 Flash</v>
+        <v>Gemini 3.1 Pro Preview</v>
       </c>
       <c r="C25" t="str">
         <v>Google DeepMind</v>
       </c>
       <c r="D25" t="str">
-        <v>输入：文本、图片、视频</v>
+        <v>输入≤20万个token</v>
       </c>
       <c r="E25" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
       <c r="F25" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
       <c r="G25" t="str">
         <v>—</v>
       </c>
       <c r="H25" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>入 $2 · 出 $12 · 缓 $0.19999999999999998</v>
       </c>
       <c r="I25" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
       <c r="J25" t="str">
         <v>0%</v>
@@ -1678,22 +1688,22 @@
     </row>
     <row r="26">
       <c r="D26" t="str">
-        <v>输入：音频</v>
+        <v>输入&gt;20万个token</v>
       </c>
       <c r="E26" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>入 $4 · 出 $18 · 缓 $0.4</v>
       </c>
       <c r="F26" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>入 $4 · 出 $18 · 缓 $0.4</v>
       </c>
       <c r="G26" t="str">
         <v>—</v>
       </c>
       <c r="H26" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>入 $2 · 出 $12 · 缓 $0.19999999999999998</v>
       </c>
       <c r="I26" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>入 $4 · 出 $18 · 缓 $0.4</v>
       </c>
       <c r="J26" t="str">
         <v>0%</v>
@@ -1711,10 +1721,10 @@
         <v>—</v>
       </c>
       <c r="O26" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
       <c r="P26" t="str">
-        <v>ℹ 线上音频未单独定价</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q26" t="str">
         <v/>
@@ -1722,31 +1732,31 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>glm-5</v>
+        <v>gemini-3.5-flash</v>
       </c>
       <c r="B27" t="str">
-        <v>GLM 5</v>
+        <v>Gemini 3.5 Flash</v>
       </c>
       <c r="C27" t="str">
-        <v>Zhipu</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="D27" t="str">
-        <v>32k&lt;=输入</v>
+        <v>输入：文本、图片、视频</v>
       </c>
       <c r="E27" t="str">
-        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="F27" t="str">
-        <v>—</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="G27" t="str">
-        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+        <v>—</v>
       </c>
       <c r="H27" t="str">
-        <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="I27" t="str">
-        <v>入 $0.923077 · 出 $3.384615 · 缓 $0.230769</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="J27" t="str">
         <v>0%</v>
@@ -1758,13 +1768,13 @@
         <v>0%</v>
       </c>
       <c r="M27" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N27" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O27" t="str">
-        <v>入⚠-35% 出⚠-43.3% 缓⚠-48%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P27" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1775,22 +1785,22 @@
     </row>
     <row r="28">
       <c r="D28" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>输入：音频</v>
       </c>
       <c r="E28" t="str">
-        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="F28" t="str">
-        <v>—</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="G28" t="str">
-        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+        <v>—</v>
       </c>
       <c r="H28" t="str">
-        <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="I28" t="str">
-        <v>入 $0.615385 · 出 $2.769231 · 缓 $0.153846</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="J28" t="str">
         <v>0%</v>
@@ -1802,24 +1812,33 @@
         <v>0%</v>
       </c>
       <c r="M28" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N28" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O28" t="str">
-        <v>入⚠-2.5% 出⚠-30.7% 缓⚠-22%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P28" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>ℹ 线上音频未单独定价</v>
       </c>
       <c r="Q28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="str">
+        <v>glm-5</v>
+      </c>
+      <c r="B29" t="str">
+        <v>GLM 5</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Zhipu</v>
+      </c>
       <c r="D29" t="str">
-        <v>输入：≤32K token</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="E29" t="str">
         <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
@@ -1828,7 +1847,7 @@
         <v>入 $0.616 · 出 $2.772 · 缓 $0.154</v>
       </c>
       <c r="G29" t="str">
-        <v>—</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="H29" t="str">
         <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
@@ -1849,7 +1868,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N29" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O29" t="str">
         <v>入⚠-2.5% 出⚠-30.7% 缓⚠-22%</v>
@@ -1863,7 +1882,7 @@
     </row>
     <row r="30">
       <c r="D30" t="str">
-        <v>输入：＞32K token</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="E30" t="str">
         <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
@@ -1872,7 +1891,7 @@
         <v>入 $0.924 · 出 $3.388 · 缓 $0.231</v>
       </c>
       <c r="G30" t="str">
-        <v>—</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="H30" t="str">
         <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
@@ -1893,7 +1912,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N30" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O30" t="str">
         <v>入⚠-35% 出⚠-43.3% 缓⚠-48%</v>
@@ -1916,22 +1935,22 @@
         <v>Zhipu</v>
       </c>
       <c r="D31" t="str">
-        <v>输入&gt;=32k</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="E31" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="F31" t="str">
-        <v>—</v>
+        <v>入 $0.77 · 出 $3.388 · 缓 $0.185</v>
       </c>
       <c r="G31" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="H31" t="str">
         <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="I31" t="str">
-        <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
+        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
       </c>
       <c r="J31" t="str">
         <v>0%</v>
@@ -1943,13 +1962,13 @@
         <v>0%</v>
       </c>
       <c r="M31" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N31" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O31" t="str">
-        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
+        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
       </c>
       <c r="P31" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1960,22 +1979,22 @@
     </row>
     <row r="32">
       <c r="D32" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="E32" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="F32" t="str">
-        <v>—</v>
+        <v>入 $1.078 · 出 $4.004 · 缓 $0.277</v>
       </c>
       <c r="G32" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="H32" t="str">
         <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="I32" t="str">
-        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
+        <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
       </c>
       <c r="J32" t="str">
         <v>0%</v>
@@ -1987,13 +2006,13 @@
         <v>0%</v>
       </c>
       <c r="M32" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N32" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O32" t="str">
-        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
+        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
       </c>
       <c r="P32" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2003,23 +2022,32 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="str">
+        <v>glm-5.1</v>
+      </c>
+      <c r="B33" t="str">
+        <v>GLM-5.1</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Zhipu</v>
+      </c>
       <c r="D33" t="str">
-        <v>输入：≤32K token</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="E33" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="F33" t="str">
-        <v>入 $0.77 · 出 $3.388 · 缓 $0.185</v>
+        <v>入 $0.924 · 出 $3.696 · 缓 $0.2</v>
       </c>
       <c r="G33" t="str">
-        <v>—</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="H33" t="str">
-        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
+        <v>入 $0.975 · 出 $4.300000000000001</v>
       </c>
       <c r="I33" t="str">
-        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
+        <v>入 $0.923077 · 出 $3.692308 · 缓 $0.2</v>
       </c>
       <c r="J33" t="str">
         <v>0%</v>
@@ -2034,10 +2062,10 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N33" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O33" t="str">
-        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
+        <v>入⚠+5.6% 出⚠+16.5%</v>
       </c>
       <c r="P33" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2048,22 +2076,22 @@
     </row>
     <row r="34">
       <c r="D34" t="str">
-        <v>输入：＞32K token</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="E34" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="F34" t="str">
-        <v>入 $1.078 · 出 $4.004 · 缓 $0.277</v>
+        <v>入 $1.232 · 出 $4.312 · 缓 $0.308</v>
       </c>
       <c r="G34" t="str">
-        <v>—</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="H34" t="str">
-        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
+        <v>入 $0.975 · 出 $4.300000000000001</v>
       </c>
       <c r="I34" t="str">
-        <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
+        <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
       </c>
       <c r="J34" t="str">
         <v>0%</v>
@@ -2078,10 +2106,10 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N34" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O34" t="str">
-        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
+        <v>入⚠-20.8% 出✅</v>
       </c>
       <c r="P34" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2092,16 +2120,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>glm-5.1</v>
+        <v>glm-5.2</v>
       </c>
       <c r="B35" t="str">
-        <v>GLM-5.1</v>
+        <v>GLM-5.2</v>
       </c>
       <c r="C35" t="str">
         <v>Zhipu</v>
       </c>
       <c r="D35" t="str">
-        <v>32k&lt;=输入</v>
+        <v>统一价</v>
       </c>
       <c r="E35" t="str">
         <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
@@ -2113,7 +2141,7 @@
         <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="H35" t="str">
-        <v>入 $0.975 · 出 $4.300000000000001</v>
+        <v>入 $0.9299999999999999 · 出 $3 · 缓 $0.18</v>
       </c>
       <c r="I35" t="str">
         <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
@@ -2134,7 +2162,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O35" t="str">
-        <v>入⚠-20.8% 出✅</v>
+        <v>入⚠-24.4% 出⚠-30.4% 缓⚠-41.5%</v>
       </c>
       <c r="P35" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2144,23 +2172,32 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="str">
+        <v>glm-5v-turbo</v>
+      </c>
+      <c r="B36" t="str">
+        <v>GLM-5V Turbo</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Zhipu</v>
+      </c>
       <c r="D36" t="str">
         <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="E36" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="F36" t="str">
         <v>—</v>
       </c>
       <c r="G36" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="H36" t="str">
-        <v>入 $0.975 · 出 $4.300000000000001</v>
+        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="I36" t="str">
-        <v>入 $0.923077 · 出 $3.692308 · 缓 $0.2</v>
+        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
       </c>
       <c r="J36" t="str">
         <v>0%</v>
@@ -2178,33 +2215,33 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O36" t="str">
-        <v>入⚠+5.6% 出⚠+16.5%</v>
+        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
       </c>
       <c r="P36" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q36" t="str">
-        <v/>
+        <v>多模态 Coding 基座</v>
       </c>
     </row>
     <row r="37">
       <c r="D37" t="str">
-        <v>输入：≤32K token</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="E37" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="F37" t="str">
-        <v>入 $0.924 · 出 $3.696 · 缓 $0.2</v>
+        <v>—</v>
       </c>
       <c r="G37" t="str">
-        <v>—</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="H37" t="str">
-        <v>入 $0.975 · 出 $4.300000000000001</v>
+        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="I37" t="str">
-        <v>入 $0.923077 · 出 $3.692308 · 缓 $0.2</v>
+        <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
       </c>
       <c r="J37" t="str">
         <v>0%</v>
@@ -2216,39 +2253,48 @@
         <v>0%</v>
       </c>
       <c r="M37" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N37" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O37" t="str">
-        <v>入⚠+5.6% 出⚠+16.5%</v>
+        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
       </c>
       <c r="P37" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q37" t="str">
-        <v/>
+        <v>多模态 Coding 基座</v>
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="str">
+        <v>gpt-4.1</v>
+      </c>
+      <c r="B38" t="str">
+        <v>GPT-4.1</v>
+      </c>
+      <c r="C38" t="str">
+        <v>OpenAI</v>
+      </c>
       <c r="D38" t="str">
-        <v>输入：＞32K token</v>
+        <v>统一价</v>
       </c>
       <c r="E38" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="F38" t="str">
-        <v>入 $1.232 · 出 $4.312 · 缓 $0.308</v>
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="G38" t="str">
         <v>—</v>
       </c>
       <c r="H38" t="str">
-        <v>入 $0.975 · 出 $4.300000000000001</v>
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="I38" t="str">
-        <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="J38" t="str">
         <v>0%</v>
@@ -2266,7 +2312,7 @@
         <v>—</v>
       </c>
       <c r="O38" t="str">
-        <v>入⚠-20.8% 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P38" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2277,31 +2323,31 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>glm-5.2</v>
+        <v>gpt-4o</v>
       </c>
       <c r="B39" t="str">
-        <v>GLM-5.2</v>
+        <v>GPT-4o</v>
       </c>
       <c r="C39" t="str">
-        <v>Zhipu</v>
+        <v>OpenAI</v>
       </c>
       <c r="D39" t="str">
         <v>统一价</v>
       </c>
       <c r="E39" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="F39" t="str">
-        <v>—</v>
+        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="G39" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>—</v>
       </c>
       <c r="H39" t="str">
-        <v>入 $0.9299999999999999 · 出 $3 · 缓 $0.18</v>
+        <v>入 $2.5 · 出 $10</v>
       </c>
       <c r="I39" t="str">
-        <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
+        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="J39" t="str">
         <v>0%</v>
@@ -2313,13 +2359,13 @@
         <v>0%</v>
       </c>
       <c r="M39" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N39" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O39" t="str">
-        <v>入⚠-24.4% 出⚠-30.4% 缓⚠-41.5%</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="P39" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2330,31 +2376,31 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>glm-5v-turbo</v>
+        <v>gpt-5</v>
       </c>
       <c r="B40" t="str">
-        <v>GLM-5V Turbo</v>
+        <v>GPT-5</v>
       </c>
       <c r="C40" t="str">
-        <v>Zhipu</v>
+        <v>OpenAI</v>
       </c>
       <c r="D40" t="str">
-        <v>输入&gt;=32k</v>
+        <v>统一价</v>
       </c>
       <c r="E40" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="F40" t="str">
-        <v>—</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G40" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>—</v>
       </c>
       <c r="H40" t="str">
-        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="I40" t="str">
-        <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="J40" t="str">
         <v>0%</v>
@@ -2366,39 +2412,48 @@
         <v>0%</v>
       </c>
       <c r="M40" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N40" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O40" t="str">
-        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P40" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q40" t="str">
-        <v>多模态 Coding 基座</v>
+        <v/>
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="str">
+        <v>gpt-5-nano</v>
+      </c>
+      <c r="B41" t="str">
+        <v>GPT-5 Nano</v>
+      </c>
+      <c r="C41" t="str">
+        <v>OpenAI</v>
+      </c>
       <c r="D41" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>统一价</v>
       </c>
       <c r="E41" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="F41" t="str">
-        <v>—</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="G41" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>—</v>
       </c>
       <c r="H41" t="str">
-        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
+        <v>入 $0.049999999999999996 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
       <c r="I41" t="str">
-        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="J41" t="str">
         <v>0%</v>
@@ -2410,27 +2465,27 @@
         <v>0%</v>
       </c>
       <c r="M41" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N41" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O41" t="str">
-        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
+        <v>入✅ 出✅ 缓⚠+100%</v>
       </c>
       <c r="P41" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q41" t="str">
-        <v>多模态 Coding 基座</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>gpt-4.1</v>
+        <v>gpt-5.1</v>
       </c>
       <c r="B42" t="str">
-        <v>GPT-4.1</v>
+        <v>GPT-5.1</v>
       </c>
       <c r="C42" t="str">
         <v>OpenAI</v>
@@ -2439,19 +2494,19 @@
         <v>统一价</v>
       </c>
       <c r="E42" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="F42" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G42" t="str">
         <v>—</v>
       </c>
       <c r="H42" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
       </c>
       <c r="I42" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="J42" t="str">
         <v>0%</v>
@@ -2469,7 +2524,7 @@
         <v>—</v>
       </c>
       <c r="O42" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅ 缓⚠+4%</v>
       </c>
       <c r="P42" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2480,10 +2535,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>gpt-4o</v>
+        <v>gpt-5.1-chat</v>
       </c>
       <c r="B43" t="str">
-        <v>GPT-4o</v>
+        <v>GPT-5.1 Chat</v>
       </c>
       <c r="C43" t="str">
         <v>OpenAI</v>
@@ -2492,19 +2547,19 @@
         <v>统一价</v>
       </c>
       <c r="E43" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="F43" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G43" t="str">
         <v>—</v>
       </c>
       <c r="H43" t="str">
-        <v>入 $2.5 · 出 $10</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
       </c>
       <c r="I43" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="J43" t="str">
         <v>0%</v>
@@ -2522,21 +2577,21 @@
         <v>—</v>
       </c>
       <c r="O43" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓⚠+4%</v>
       </c>
       <c r="P43" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q43" t="str">
-        <v/>
+        <v>目录名 gpt-5.1-chat</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>gpt-5</v>
+        <v>gpt-5.2</v>
       </c>
       <c r="B44" t="str">
-        <v>GPT-5</v>
+        <v>GPT-5.2</v>
       </c>
       <c r="C44" t="str">
         <v>OpenAI</v>
@@ -2545,19 +2600,19 @@
         <v>统一价</v>
       </c>
       <c r="E44" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="F44" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="G44" t="str">
         <v>—</v>
       </c>
       <c r="H44" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="I44" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="J44" t="str">
         <v>0%</v>
@@ -2586,10 +2641,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>gpt-5-nano</v>
+        <v>gpt-5.3-codex</v>
       </c>
       <c r="B45" t="str">
-        <v>GPT-5 Nano</v>
+        <v>GPT-5.3 Codex</v>
       </c>
       <c r="C45" t="str">
         <v>OpenAI</v>
@@ -2598,19 +2653,19 @@
         <v>统一价</v>
       </c>
       <c r="E45" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="F45" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.18</v>
       </c>
       <c r="G45" t="str">
         <v>—</v>
       </c>
       <c r="H45" t="str">
-        <v>入 $0.049999999999999996 · 出 $0.39999999999999997 · 缓 $0.01</v>
+        <v>—</v>
       </c>
       <c r="I45" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="J45" t="str">
         <v>0%</v>
@@ -2622,13 +2677,13 @@
         <v>0%</v>
       </c>
       <c r="M45" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅ 缓⚠+2.9%</v>
       </c>
       <c r="N45" t="str">
         <v>—</v>
       </c>
       <c r="O45" t="str">
-        <v>入✅ 出✅ 缓⚠+100%</v>
+        <v>—</v>
       </c>
       <c r="P45" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2639,31 +2694,31 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>gpt-5.1</v>
+        <v>gpt-5.4</v>
       </c>
       <c r="B46" t="str">
-        <v>GPT-5.1</v>
+        <v>GPT-5.4</v>
       </c>
       <c r="C46" t="str">
         <v>OpenAI</v>
       </c>
       <c r="D46" t="str">
-        <v>统一价</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="E46" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="F46" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="G46" t="str">
         <v>—</v>
       </c>
       <c r="H46" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="I46" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="J46" t="str">
         <v>0%</v>
@@ -2681,7 +2736,7 @@
         <v>—</v>
       </c>
       <c r="O46" t="str">
-        <v>入✅ 出✅ 缓⚠+4%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P46" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2691,32 +2746,23 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>gpt-5.1-chat</v>
-      </c>
-      <c r="B47" t="str">
-        <v>GPT-5.1 Chat</v>
-      </c>
-      <c r="C47" t="str">
-        <v>OpenAI</v>
-      </c>
       <c r="D47" t="str">
-        <v>统一价</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="E47" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="F47" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="G47" t="str">
         <v>—</v>
       </c>
       <c r="H47" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="I47" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="J47" t="str">
         <v>0%</v>
@@ -2734,21 +2780,21 @@
         <v>—</v>
       </c>
       <c r="O47" t="str">
-        <v>入✅ 出✅ 缓⚠+4%</v>
+        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
       <c r="P47" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q47" t="str">
-        <v>目录名 gpt-5.1-chat</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>gpt-5.2</v>
+        <v>gpt-5.4-mini</v>
       </c>
       <c r="B48" t="str">
-        <v>GPT-5.2</v>
+        <v>GPT-5.4 Mini</v>
       </c>
       <c r="C48" t="str">
         <v>OpenAI</v>
@@ -2757,19 +2803,19 @@
         <v>统一价</v>
       </c>
       <c r="E48" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="F48" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="G48" t="str">
         <v>—</v>
       </c>
       <c r="H48" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="I48" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="J48" t="str">
         <v>0%</v>
@@ -2798,31 +2844,31 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>gpt-5.3-codex</v>
+        <v>gpt-5.4-pro</v>
       </c>
       <c r="B49" t="str">
-        <v>GPT-5.3 Codex</v>
+        <v>GPT-5.4 Pro</v>
       </c>
       <c r="C49" t="str">
         <v>OpenAI</v>
       </c>
       <c r="D49" t="str">
-        <v>统一价</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="E49" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="F49" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.18</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="G49" t="str">
         <v>—</v>
       </c>
       <c r="H49" t="str">
-        <v>—</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="I49" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="J49" t="str">
         <v>0%</v>
@@ -2831,51 +2877,42 @@
         <v>0%</v>
       </c>
       <c r="L49" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M49" t="str">
-        <v>入✅ 出✅ 缓⚠+2.9%</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="N49" t="str">
         <v>—</v>
       </c>
       <c r="O49" t="str">
-        <v>—</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="P49" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="Q49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
-        <v>gpt-5.4</v>
-      </c>
-      <c r="B50" t="str">
-        <v>GPT-5.4</v>
-      </c>
-      <c r="C50" t="str">
-        <v>OpenAI</v>
-      </c>
       <c r="D50" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="E50" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="F50" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="G50" t="str">
         <v>—</v>
       </c>
       <c r="H50" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="I50" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="J50" t="str">
         <v>0%</v>
@@ -2884,42 +2921,51 @@
         <v>0%</v>
       </c>
       <c r="L50" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M50" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="N50" t="str">
         <v>—</v>
       </c>
       <c r="O50" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠-50% 出⚠-33.3%</v>
       </c>
       <c r="P50" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="Q50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="str">
+        <v>gpt-5.5</v>
+      </c>
+      <c r="B51" t="str">
+        <v>GPT-5.5</v>
+      </c>
+      <c r="C51" t="str">
+        <v>OpenAI</v>
+      </c>
       <c r="D51" t="str">
-        <v>输入&gt;272K context</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="E51" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="F51" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="G51" t="str">
         <v>—</v>
       </c>
       <c r="H51" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="I51" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="J51" t="str">
         <v>0%</v>
@@ -2937,7 +2983,7 @@
         <v>—</v>
       </c>
       <c r="O51" t="str">
-        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P51" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -2947,32 +2993,23 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="str">
-        <v>gpt-5.4-mini</v>
-      </c>
-      <c r="B52" t="str">
-        <v>GPT-5.4 Mini</v>
-      </c>
-      <c r="C52" t="str">
-        <v>OpenAI</v>
-      </c>
       <c r="D52" t="str">
-        <v>统一价</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="E52" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="F52" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="G52" t="str">
         <v>—</v>
       </c>
       <c r="H52" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="I52" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="J52" t="str">
         <v>0%</v>
@@ -2990,7 +3027,7 @@
         <v>—</v>
       </c>
       <c r="O52" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
       <c r="P52" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -3001,31 +3038,31 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>gpt-5.4-pro</v>
+        <v>hunyuan-role-latest</v>
       </c>
       <c r="B53" t="str">
-        <v>GPT-5.4 Pro</v>
+        <v>Hy-Role Latest</v>
       </c>
       <c r="C53" t="str">
-        <v>OpenAI</v>
+        <v>Tencent</v>
       </c>
       <c r="D53" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>统一价</v>
       </c>
       <c r="E53" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="F53" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>—</v>
       </c>
       <c r="G53" t="str">
-        <v>—</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="H53" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>—</v>
       </c>
       <c r="I53" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 $0.369231 · 出 $1.476923</v>
       </c>
       <c r="J53" t="str">
         <v>0%</v>
@@ -3037,39 +3074,48 @@
         <v>—</v>
       </c>
       <c r="M53" t="str">
+        <v>—</v>
+      </c>
+      <c r="N53" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="N53" t="str">
-        <v>—</v>
-      </c>
       <c r="O53" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="P53" t="str">
         <v>入✅ 出✅</v>
       </c>
       <c r="Q53" t="str">
-        <v/>
+        <v>Hy-Role-Latest</v>
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="str">
+        <v>hy-mt2-lite</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Hy-MT2 Lite</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Tencent</v>
+      </c>
       <c r="D54" t="str">
-        <v>输入&gt;272K context</v>
+        <v>统一价</v>
       </c>
       <c r="E54" t="str">
-        <v>入 $60 · 出 $270</v>
+        <v>入 ¥0.3 · 出 ¥1.2</v>
       </c>
       <c r="F54" t="str">
-        <v>入 $60 · 出 $270</v>
+        <v>—</v>
       </c>
       <c r="G54" t="str">
-        <v>—</v>
+        <v>入 ¥0.3 · 出 ¥1.2</v>
       </c>
       <c r="H54" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>—</v>
       </c>
       <c r="I54" t="str">
-        <v>入 $60 · 出 $270</v>
+        <v>入 $0.046154 · 出 $0.184615</v>
       </c>
       <c r="J54" t="str">
         <v>0%</v>
@@ -3081,13 +3127,13 @@
         <v>—</v>
       </c>
       <c r="M54" t="str">
+        <v>—</v>
+      </c>
+      <c r="N54" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="N54" t="str">
-        <v>—</v>
-      </c>
       <c r="O54" t="str">
-        <v>入⚠-50% 出⚠-33.3%</v>
+        <v>—</v>
       </c>
       <c r="P54" t="str">
         <v>入✅ 出✅</v>
@@ -3098,31 +3144,31 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>gpt-5.5</v>
+        <v>hy-mt2-plus</v>
       </c>
       <c r="B55" t="str">
-        <v>GPT-5.5</v>
+        <v>Hy-MT2 Plus</v>
       </c>
       <c r="C55" t="str">
-        <v>OpenAI</v>
+        <v>Tencent</v>
       </c>
       <c r="D55" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>统一价</v>
       </c>
       <c r="E55" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>入 ¥0.5 · 出 ¥2</v>
       </c>
       <c r="F55" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="G55" t="str">
-        <v>—</v>
+        <v>入 ¥0.5 · 出 ¥2</v>
       </c>
       <c r="H55" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="I55" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>入 $0.076923 · 出 $0.307692</v>
       </c>
       <c r="J55" t="str">
         <v>0%</v>
@@ -3131,42 +3177,51 @@
         <v>0%</v>
       </c>
       <c r="L55" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M55" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N55" t="str">
-        <v>—</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="O55" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P55" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="Q55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="str">
+        <v>hy-mt2-pro</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Hy-MT2 Pro</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Tencent</v>
+      </c>
       <c r="D56" t="str">
-        <v>输入&gt;272K context</v>
+        <v>统一价</v>
       </c>
       <c r="E56" t="str">
-        <v>入 $10 · 出 $45 · 缓 $1</v>
+        <v>入 ¥0.5 · 出 ¥2</v>
       </c>
       <c r="F56" t="str">
-        <v>入 $10 · 出 $45 · 缓 $1</v>
+        <v>—</v>
       </c>
       <c r="G56" t="str">
-        <v>—</v>
+        <v>入 ¥0.5 · 出 ¥2</v>
       </c>
       <c r="H56" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="I56" t="str">
-        <v>入 $10 · 出 $45 · 缓 $1</v>
+        <v>入 $0.076923 · 出 $0.307692</v>
       </c>
       <c r="J56" t="str">
         <v>0%</v>
@@ -3175,19 +3230,19 @@
         <v>0%</v>
       </c>
       <c r="L56" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M56" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N56" t="str">
-        <v>—</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="O56" t="str">
-        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
+        <v>—</v>
       </c>
       <c r="P56" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="Q56" t="str">
         <v/>
@@ -3195,10 +3250,10 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>hunyuan-role-latest</v>
+        <v>hy-role</v>
       </c>
       <c r="B57" t="str">
-        <v>Hy-Role Latest</v>
+        <v>Hy-Role</v>
       </c>
       <c r="C57" t="str">
         <v>Tencent</v>
@@ -3243,15 +3298,15 @@
         <v>入✅ 出✅</v>
       </c>
       <c r="Q57" t="str">
-        <v>Hy-Role-Latest</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>hy-mt2-lite</v>
+        <v>hy-vision-2.0-instruct</v>
       </c>
       <c r="B58" t="str">
-        <v>Hy-MT2 Lite</v>
+        <v>Hy-Vision 2.0 Instruct</v>
       </c>
       <c r="C58" t="str">
         <v>Tencent</v>
@@ -3260,19 +3315,19 @@
         <v>统一价</v>
       </c>
       <c r="E58" t="str">
-        <v>入 ¥0.3 · 出 ¥1.2</v>
+        <v>入 ¥7.5 · 出 ¥17.5</v>
       </c>
       <c r="F58" t="str">
         <v>—</v>
       </c>
       <c r="G58" t="str">
-        <v>入 ¥0.3 · 出 ¥1.2</v>
+        <v>—</v>
       </c>
       <c r="H58" t="str">
         <v>—</v>
       </c>
       <c r="I58" t="str">
-        <v>入 $0.046154 · 出 $0.184615</v>
+        <v>入 $1.153846 · 出 $2.692308</v>
       </c>
       <c r="J58" t="str">
         <v>0%</v>
@@ -3287,7 +3342,7 @@
         <v>—</v>
       </c>
       <c r="N58" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="O58" t="str">
         <v>—</v>
@@ -3296,36 +3351,36 @@
         <v>入✅ 出✅</v>
       </c>
       <c r="Q58" t="str">
-        <v/>
+        <v>多模态视觉理解 · 按 token 计费</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>hy-mt2-plus</v>
+        <v>hy3-preview</v>
       </c>
       <c r="B59" t="str">
-        <v>Hy-MT2 Plus</v>
+        <v>Hy3 Preview</v>
       </c>
       <c r="C59" t="str">
         <v>Tencent</v>
       </c>
       <c r="D59" t="str">
-        <v>统一价</v>
+        <v>输入&lt;16k</v>
       </c>
       <c r="E59" t="str">
-        <v>入 ¥0.5 · 出 ¥2</v>
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
       </c>
       <c r="F59" t="str">
         <v>—</v>
       </c>
       <c r="G59" t="str">
-        <v>入 ¥0.5 · 出 ¥2</v>
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
       </c>
       <c r="H59" t="str">
-        <v>—</v>
+        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
       <c r="I59" t="str">
-        <v>入 $0.076923 · 出 $0.307692</v>
+        <v>入 $0.184615 · 出 $0.615385 · 缓 $0.061538</v>
       </c>
       <c r="J59" t="str">
         <v>0%</v>
@@ -3334,51 +3389,42 @@
         <v>0%</v>
       </c>
       <c r="L59" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M59" t="str">
         <v>—</v>
       </c>
       <c r="N59" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O59" t="str">
-        <v>—</v>
+        <v>入⚠-65.9% 出⚠-65.9% 缓⚠-65.9%</v>
       </c>
       <c r="P59" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="str">
-        <v>hy-mt2-pro</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Hy-MT2 Pro</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Tencent</v>
-      </c>
       <c r="D60" t="str">
-        <v>统一价</v>
+        <v>16k&lt;=输入&lt;32k</v>
       </c>
       <c r="E60" t="str">
-        <v>入 ¥0.5 · 出 ¥2</v>
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
       <c r="F60" t="str">
         <v>—</v>
       </c>
       <c r="G60" t="str">
-        <v>入 ¥0.5 · 出 ¥2</v>
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
       <c r="H60" t="str">
-        <v>—</v>
+        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
       <c r="I60" t="str">
-        <v>入 $0.076923 · 出 $0.307692</v>
+        <v>入 $0.246154 · 出 $0.984615 · 缓 $0.092308</v>
       </c>
       <c r="J60" t="str">
         <v>0%</v>
@@ -3387,51 +3433,42 @@
         <v>0%</v>
       </c>
       <c r="L60" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M60" t="str">
         <v>—</v>
       </c>
       <c r="N60" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O60" t="str">
-        <v>—</v>
+        <v>入⚠-74.4% 出⚠-78.7% 缓⚠-77.2%</v>
       </c>
       <c r="P60" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="str">
-        <v>hy-role</v>
-      </c>
-      <c r="B61" t="str">
-        <v>Hy-Role</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Tencent</v>
-      </c>
       <c r="D61" t="str">
-        <v>统一价</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="E61" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="F61" t="str">
         <v>—</v>
       </c>
       <c r="G61" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="H61" t="str">
-        <v>—</v>
+        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
       <c r="I61" t="str">
-        <v>入 $0.369231 · 出 $1.476923</v>
+        <v>入 $0.307692 · 出 $1.230769 · 缓 $0.123077</v>
       </c>
       <c r="J61" t="str">
         <v>0%</v>
@@ -3440,19 +3477,19 @@
         <v>0%</v>
       </c>
       <c r="L61" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M61" t="str">
         <v>—</v>
       </c>
       <c r="N61" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O61" t="str">
-        <v>—</v>
+        <v>入⚠-79.5% 出⚠-82.9% 缓⚠-82.9%</v>
       </c>
       <c r="P61" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q61" t="str">
         <v/>
@@ -3460,31 +3497,31 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>hy-vision-2.0-instruct</v>
+        <v>kimi-k2.5</v>
       </c>
       <c r="B62" t="str">
-        <v>Hy-Vision 2.0 Instruct</v>
+        <v>Kimi K2.5</v>
       </c>
       <c r="C62" t="str">
-        <v>Tencent</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="D62" t="str">
         <v>统一价</v>
       </c>
       <c r="E62" t="str">
-        <v>入 ¥7.5 · 出 ¥17.5</v>
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
       </c>
       <c r="F62" t="str">
-        <v>—</v>
+        <v>入 $0.616 · 出 $3.234 · 缓 $0.108</v>
       </c>
       <c r="G62" t="str">
-        <v>—</v>
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
       </c>
       <c r="H62" t="str">
-        <v>—</v>
+        <v>入 $0.375 · 出 $2.025</v>
       </c>
       <c r="I62" t="str">
-        <v>入 $1.153846 · 出 $2.692308</v>
+        <v>入 $0.615385 · 出 $3.230769 · 缓 $0.107692</v>
       </c>
       <c r="J62" t="str">
         <v>0%</v>
@@ -3493,51 +3530,51 @@
         <v>0%</v>
       </c>
       <c r="L62" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M62" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="N62" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O62" t="str">
-        <v>—</v>
+        <v>入⚠-39.1% 出⚠-37.3%</v>
       </c>
       <c r="P62" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q62" t="str">
-        <v>多模态视觉理解 · 按 token 计费</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>hy3-preview</v>
+        <v>kimi-k2.6</v>
       </c>
       <c r="B63" t="str">
-        <v>Hy3 Preview</v>
+        <v>Kimi K2.6</v>
       </c>
       <c r="C63" t="str">
-        <v>Tencent</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="D63" t="str">
-        <v>输入&lt;16k</v>
+        <v>统一价</v>
       </c>
       <c r="E63" t="str">
-        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
       </c>
       <c r="F63" t="str">
         <v>—</v>
       </c>
       <c r="G63" t="str">
-        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
       </c>
       <c r="H63" t="str">
-        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
+        <v>入 $0.55 · 出 $3.1999999999999997 · 缓 $0.11</v>
       </c>
       <c r="I63" t="str">
-        <v>入 $0.184615 · 出 $0.615385 · 缓 $0.061538</v>
+        <v>入 $1 · 出 $4.153846 · 缓 $0.169231</v>
       </c>
       <c r="J63" t="str">
         <v>0%</v>
@@ -3555,7 +3592,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O63" t="str">
-        <v>入⚠-65.9% 出⚠-65.9% 缓⚠-65.9%</v>
+        <v>入⚠-45% 出⚠-23% 缓⚠-35%</v>
       </c>
       <c r="P63" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -3565,23 +3602,32 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="str">
+        <v>kimi-k2.7-code</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Kimi K2.7 Code</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Moonshot AI</v>
+      </c>
       <c r="D64" t="str">
-        <v>16k&lt;=输入&lt;32k</v>
+        <v>统一价</v>
       </c>
       <c r="E64" t="str">
-        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
       </c>
       <c r="F64" t="str">
         <v>—</v>
       </c>
       <c r="G64" t="str">
-        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
       </c>
       <c r="H64" t="str">
-        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
+        <v>入 $0.74 · 出 $3.5 · 缓 $0.15</v>
       </c>
       <c r="I64" t="str">
-        <v>入 $0.246154 · 出 $0.984615 · 缓 $0.092308</v>
+        <v>入 $1 · 出 $4.153846</v>
       </c>
       <c r="J64" t="str">
         <v>0%</v>
@@ -3590,7 +3636,7 @@
         <v>0%</v>
       </c>
       <c r="L64" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M64" t="str">
         <v>—</v>
@@ -3599,33 +3645,42 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O64" t="str">
-        <v>入⚠-74.4% 出⚠-78.7% 缓⚠-77.2%</v>
+        <v>入⚠-26% 出⚠-15.7% 缓⚠-25%</v>
       </c>
       <c r="P64" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="Q64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="str">
+        <v>kimi-k2.7-code-highspeed</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Kimi K2.7 Code HighSpeed</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Moonshot AI</v>
+      </c>
       <c r="D65" t="str">
-        <v>输入&gt;=32k</v>
+        <v>统一价</v>
       </c>
       <c r="E65" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
+        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
       </c>
       <c r="F65" t="str">
         <v>—</v>
       </c>
       <c r="G65" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
+        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
       </c>
       <c r="H65" t="str">
-        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I65" t="str">
-        <v>入 $0.307692 · 出 $1.230769 · 缓 $0.123077</v>
+        <v>入 $2 · 出 $8.307692 · 缓 $0.4</v>
       </c>
       <c r="J65" t="str">
         <v>0%</v>
@@ -3643,33 +3698,42 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O65" t="str">
-        <v>入⚠-79.5% 出⚠-82.9% 缓⚠-82.9%</v>
+        <v>—</v>
       </c>
       <c r="P65" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q65" t="str">
-        <v/>
+        <v>K2.7 Code 高速版</v>
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="str">
+        <v>minimax-m2.5</v>
+      </c>
+      <c r="B66" t="str">
+        <v>MiniMax M2.5</v>
+      </c>
+      <c r="C66" t="str">
+        <v>MiniMax</v>
+      </c>
       <c r="D66" t="str">
-        <v>输入长度（0, 16k）</v>
+        <v>统一价</v>
       </c>
       <c r="E66" t="str">
-        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
       </c>
       <c r="F66" t="str">
-        <v>—</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.03</v>
       </c>
       <c r="G66" t="str">
-        <v>—</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
       </c>
       <c r="H66" t="str">
-        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
+        <v>入 $0.12 · 出 $0.48</v>
       </c>
       <c r="I66" t="str">
-        <v>入 $0.184615 · 出 $0.615385 · 缓 $0.061538</v>
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.032308</v>
       </c>
       <c r="J66" t="str">
         <v>0%</v>
@@ -3681,13 +3745,13 @@
         <v>0%</v>
       </c>
       <c r="M66" t="str">
-        <v>—</v>
+        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
       <c r="N66" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O66" t="str">
-        <v>入⚠-65.9% 出⚠-65.9% 缓⚠-65.9%</v>
+        <v>入⚠-62.9% 出⚠-62.9%</v>
       </c>
       <c r="P66" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -3698,31 +3762,31 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>kimi-k2.5</v>
+        <v>minimax-m2.7</v>
       </c>
       <c r="B67" t="str">
-        <v>Kimi K2.5</v>
+        <v>MiniMax M2.7</v>
       </c>
       <c r="C67" t="str">
-        <v>Moonshot AI</v>
+        <v>MiniMax</v>
       </c>
       <c r="D67" t="str">
         <v>统一价</v>
       </c>
       <c r="E67" t="str">
-        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="F67" t="str">
-        <v>入 $0.616 · 出 $3.234 · 缓 $0.108</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="G67" t="str">
-        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="H67" t="str">
-        <v>入 $0.375 · 出 $2.025</v>
+        <v>入 $0.18 · 出 $0.72</v>
       </c>
       <c r="I67" t="str">
-        <v>入 $0.615385 · 出 $3.230769 · 缓 $0.107692</v>
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
       <c r="J67" t="str">
         <v>0%</v>
@@ -3734,13 +3798,13 @@
         <v>0%</v>
       </c>
       <c r="M67" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
       <c r="N67" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O67" t="str">
-        <v>入⚠-39.1% 出⚠-37.3%</v>
+        <v>入⚠-44.3% 出⚠-44.3%</v>
       </c>
       <c r="P67" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -3751,31 +3815,31 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>kimi-k2.6</v>
+        <v>minimax-m3</v>
       </c>
       <c r="B68" t="str">
-        <v>Kimi K2.6</v>
+        <v>MiniMax M3</v>
       </c>
       <c r="C68" t="str">
-        <v>Moonshot AI</v>
+        <v>MiniMax</v>
       </c>
       <c r="D68" t="str">
-        <v>统一价</v>
+        <v>输入&lt;=512k</v>
       </c>
       <c r="E68" t="str">
-        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="F68" t="str">
         <v>—</v>
       </c>
       <c r="G68" t="str">
-        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="H68" t="str">
-        <v>入 $0.55 · 出 $3.1999999999999997 · 缓 $0.11</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="I68" t="str">
-        <v>入 $1 · 出 $4.153846 · 缓 $0.169231</v>
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
       <c r="J68" t="str">
         <v>0%</v>
@@ -3793,42 +3857,33 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O68" t="str">
-        <v>入⚠-45% 出⚠-23% 缓⚠-35%</v>
+        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
       <c r="P68" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q68" t="str">
-        <v/>
+        <v>512k 以上输入档仍在内测开放中</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="str">
-        <v>kimi-k2.7-code</v>
-      </c>
-      <c r="B69" t="str">
-        <v>Kimi K2.7 Code</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Moonshot AI</v>
-      </c>
       <c r="D69" t="str">
-        <v>统一价</v>
+        <v>512k&lt;输入</v>
       </c>
       <c r="E69" t="str">
-        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
+        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="F69" t="str">
         <v>—</v>
       </c>
       <c r="G69" t="str">
-        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
+        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="H69" t="str">
-        <v>入 $0.74 · 出 $3.5 · 缓 $0.15</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="I69" t="str">
-        <v>入 $1 · 出 $4.153846</v>
+        <v>入 $0.646154 · 出 $2.584615 · 缓 $0.129231</v>
       </c>
       <c r="J69" t="str">
         <v>0%</v>
@@ -3837,7 +3892,7 @@
         <v>0%</v>
       </c>
       <c r="L69" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M69" t="str">
         <v>—</v>
@@ -3846,42 +3901,42 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O69" t="str">
-        <v>入⚠-26% 出⚠-15.7% 缓⚠-25%</v>
+        <v>入⚠-53.6% 出⚠-53.6% 缓⚠-53.6%</v>
       </c>
       <c r="P69" t="str">
-        <v>入✅ 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q69" t="str">
-        <v/>
+        <v>512k 以上输入档仍在内测开放中</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>kimi-k2.7-code-highspeed</v>
+        <v>qwen-flash</v>
       </c>
       <c r="B70" t="str">
-        <v>Kimi K2.7 Code HighSpeed</v>
+        <v>Qwen Flash</v>
       </c>
       <c r="C70" t="str">
-        <v>Moonshot AI</v>
+        <v>Tongyi</v>
       </c>
       <c r="D70" t="str">
-        <v>统一价</v>
+        <v>0&lt;Token≤128K</v>
       </c>
       <c r="E70" t="str">
-        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
+        <v>入 ¥0.15 · 出 ¥1.5 · 缓 ¥0.03</v>
       </c>
       <c r="F70" t="str">
         <v>—</v>
       </c>
       <c r="G70" t="str">
-        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
+        <v>—</v>
       </c>
       <c r="H70" t="str">
         <v>—</v>
       </c>
       <c r="I70" t="str">
-        <v>入 $2 · 出 $8.307692 · 缓 $0.4</v>
+        <v>入 $0.023077 · 出 $0.230769 · 缓 $0.004615</v>
       </c>
       <c r="J70" t="str">
         <v>0%</v>
@@ -3896,7 +3951,7 @@
         <v>—</v>
       </c>
       <c r="N70" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O70" t="str">
         <v>—</v>
@@ -3905,110 +3960,92 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q70" t="str">
-        <v>K2.7 Code 高速版</v>
+        <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="str">
-        <v>minimax-m2.5</v>
-      </c>
-      <c r="B71" t="str">
-        <v>MiniMax M2.5</v>
-      </c>
-      <c r="C71" t="str">
-        <v>MiniMax</v>
-      </c>
       <c r="D71" t="str">
-        <v>统一价</v>
+        <v>128K&lt;Token≤256K</v>
       </c>
       <c r="E71" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+        <v>入 ¥0.6 · 出 ¥6 · 缓 ¥0.12</v>
       </c>
       <c r="F71" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.03</v>
+        <v>—</v>
       </c>
       <c r="G71" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+        <v>—</v>
       </c>
       <c r="H71" t="str">
-        <v>入 $0.12 · 出 $0.48</v>
+        <v>—</v>
       </c>
       <c r="I71" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.032308</v>
+        <v>—</v>
       </c>
       <c r="J71" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K71" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L71" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M71" t="str">
-        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
+        <v>—</v>
       </c>
       <c r="N71" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O71" t="str">
-        <v>入⚠-62.9% 出⚠-62.9%</v>
+        <v>—</v>
       </c>
       <c r="P71" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>ℹ 线上无同档</v>
       </c>
       <c r="Q71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="str">
-        <v>minimax-m2.7</v>
-      </c>
-      <c r="B72" t="str">
-        <v>MiniMax M2.7</v>
-      </c>
-      <c r="C72" t="str">
-        <v>MiniMax</v>
-      </c>
       <c r="D72" t="str">
-        <v>统一价</v>
+        <v>256K&lt;Token≤1M</v>
       </c>
       <c r="E72" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
       </c>
       <c r="F72" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
+        <v>—</v>
       </c>
       <c r="G72" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>—</v>
       </c>
       <c r="H72" t="str">
-        <v>入 $0.18 · 出 $0.72</v>
+        <v>—</v>
       </c>
       <c r="I72" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
+        <v>—</v>
       </c>
       <c r="J72" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K72" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L72" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M72" t="str">
-        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
+        <v>—</v>
       </c>
       <c r="N72" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O72" t="str">
-        <v>入⚠-44.3% 出⚠-44.3%</v>
+        <v>—</v>
       </c>
       <c r="P72" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>ℹ 线上无同档</v>
       </c>
       <c r="Q72" t="str">
         <v/>
@@ -4016,31 +4053,31 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>minimax-m3</v>
+        <v>qwen-max</v>
       </c>
       <c r="B73" t="str">
-        <v>MiniMax M3</v>
+        <v>Qwen Max</v>
       </c>
       <c r="C73" t="str">
-        <v>MiniMax</v>
+        <v>Tongyi</v>
       </c>
       <c r="D73" t="str">
-        <v>输入&lt;=512k</v>
+        <v>无阶梯计价</v>
       </c>
       <c r="E73" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="F73" t="str">
         <v>—</v>
       </c>
       <c r="G73" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>—</v>
       </c>
       <c r="H73" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
+        <v>—</v>
       </c>
       <c r="I73" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
+        <v>入 $0.369231 · 出 $1.476923 · 缓 $0.082759</v>
       </c>
       <c r="J73" t="str">
         <v>0%</v>
@@ -4049,42 +4086,51 @@
         <v>0%</v>
       </c>
       <c r="L73" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M73" t="str">
         <v>—</v>
       </c>
       <c r="N73" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O73" t="str">
-        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
+        <v>—</v>
       </c>
       <c r="P73" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅ 缓—</v>
       </c>
       <c r="Q73" t="str">
-        <v>512k 以上输入档仍在内测开放中</v>
+        <v/>
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="str">
+        <v>qwen-plus</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Qwen Plus</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="D74" t="str">
-        <v>512k&lt;输入</v>
+        <v>0&lt;Token≤128K</v>
       </c>
       <c r="E74" t="str">
-        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
       </c>
       <c r="F74" t="str">
         <v>—</v>
       </c>
       <c r="G74" t="str">
-        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
+        <v>—</v>
       </c>
       <c r="H74" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
+        <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
       </c>
       <c r="I74" t="str">
-        <v>入 $0.646154 · 出 $2.584615 · 缓 $0.129231</v>
+        <v>入 $0.123077 · 出 $0.307692 · 缓 $0.024615</v>
       </c>
       <c r="J74" t="str">
         <v>0%</v>
@@ -4099,33 +4145,24 @@
         <v>—</v>
       </c>
       <c r="N74" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O74" t="str">
-        <v>入⚠-53.6% 出⚠-53.6% 缓⚠-53.6%</v>
+        <v>入⚠+111.3% 出⚠+153.5% 缓⚠+111.3%</v>
       </c>
       <c r="P74" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q74" t="str">
-        <v>512k 以上输入档仍在内测开放中</v>
+        <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="str">
-        <v>qwen-flash</v>
-      </c>
-      <c r="B75" t="str">
-        <v>Qwen Flash</v>
-      </c>
-      <c r="C75" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="D75" t="str">
-        <v>0&lt;Token≤128K</v>
+        <v>128K&lt;Token≤256K</v>
       </c>
       <c r="E75" t="str">
-        <v>入 ¥0.15 · 出 ¥1.5 · 缓 ¥0.03</v>
+        <v>入 ¥2.4 · 出 ¥20 · 缓 ¥0.48</v>
       </c>
       <c r="F75" t="str">
         <v>—</v>
@@ -4134,19 +4171,19 @@
         <v>—</v>
       </c>
       <c r="H75" t="str">
-        <v>—</v>
+        <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
       </c>
       <c r="I75" t="str">
-        <v>入 $0.023077 · 出 $0.230769 · 缓 $0.004615</v>
+        <v>—</v>
       </c>
       <c r="J75" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K75" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L75" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M75" t="str">
         <v>—</v>
@@ -4155,10 +4192,10 @@
         <v>—</v>
       </c>
       <c r="O75" t="str">
-        <v>—</v>
+        <v>入⚠-29.6% 出⚠-74.6% 缓⚠-29.6%</v>
       </c>
       <c r="P75" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>ℹ 线上无同档</v>
       </c>
       <c r="Q75" t="str">
         <v/>
@@ -4166,10 +4203,10 @@
     </row>
     <row r="76">
       <c r="D76" t="str">
-        <v>128K&lt;Token≤256K</v>
+        <v>256K&lt;Token≤1M</v>
       </c>
       <c r="E76" t="str">
-        <v>入 ¥0.6 · 出 ¥6 · 缓 ¥0.12</v>
+        <v>入 ¥4.8 · 出 ¥48 · 缓 ¥0.96</v>
       </c>
       <c r="F76" t="str">
         <v>—</v>
@@ -4178,7 +4215,7 @@
         <v>—</v>
       </c>
       <c r="H76" t="str">
-        <v>—</v>
+        <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
       </c>
       <c r="I76" t="str">
         <v>—</v>
@@ -4199,7 +4236,7 @@
         <v>—</v>
       </c>
       <c r="O76" t="str">
-        <v>—</v>
+        <v>入⚠-64.8% 出⚠-89.4% 缓⚠-64.8%</v>
       </c>
       <c r="P76" t="str">
         <v>ℹ 线上无同档</v>
@@ -4209,11 +4246,20 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="str">
+        <v>qwen-turbo</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Qwen Turbo</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="D77" t="str">
-        <v>256K&lt;Token≤1M</v>
+        <v>统一价</v>
       </c>
       <c r="E77" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
+        <v>入 ¥0.3 · 出 ¥0.6</v>
       </c>
       <c r="F77" t="str">
         <v>—</v>
@@ -4225,13 +4271,13 @@
         <v>—</v>
       </c>
       <c r="I77" t="str">
-        <v>—</v>
+        <v>入 $0.046154 · 出 $0.092308 · 缓 $0.010345</v>
       </c>
       <c r="J77" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="K77" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L77" t="str">
         <v>—</v>
@@ -4246,7 +4292,7 @@
         <v>—</v>
       </c>
       <c r="P77" t="str">
-        <v>ℹ 线上无同档</v>
+        <v>入✅ 出✅ 缓—</v>
       </c>
       <c r="Q77" t="str">
         <v/>
@@ -4254,31 +4300,31 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>qwen-max</v>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="B78" t="str">
-        <v>Qwen Max</v>
+        <v>Qwen3.5 Flash</v>
       </c>
       <c r="C78" t="str">
         <v>Tongyi</v>
       </c>
       <c r="D78" t="str">
-        <v>无阶梯计价</v>
+        <v>0&lt;输入&lt;=128k</v>
       </c>
       <c r="E78" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="F78" t="str">
         <v>—</v>
       </c>
       <c r="G78" t="str">
-        <v>—</v>
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="H78" t="str">
-        <v>—</v>
+        <v>入 $0.065 · 出 $0.26</v>
       </c>
       <c r="I78" t="str">
-        <v>入 $0.369231 · 出 $1.476923 · 缓 $0.082759</v>
+        <v>入 $0.030769 · 出 $0.307692 · 缓 $0.003077</v>
       </c>
       <c r="J78" t="str">
         <v>0%</v>
@@ -4287,110 +4333,92 @@
         <v>0%</v>
       </c>
       <c r="L78" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M78" t="str">
         <v>—</v>
       </c>
       <c r="N78" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O78" t="str">
-        <v>—</v>
+        <v>入⚠+111.3% 出⚠-15.5%</v>
       </c>
       <c r="P78" t="str">
-        <v>入✅ 出✅ 缓—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="str">
-        <v>qwen-plus</v>
-      </c>
-      <c r="B79" t="str">
-        <v>Qwen Plus</v>
-      </c>
-      <c r="C79" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="D79" t="str">
-        <v>0&lt;Token≤128K</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E79" t="str">
-        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
       </c>
       <c r="F79" t="str">
         <v>—</v>
       </c>
       <c r="G79" t="str">
-        <v>—</v>
+        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
       </c>
       <c r="H79" t="str">
-        <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
+        <v>入 $0.065 · 出 $0.26</v>
       </c>
       <c r="I79" t="str">
-        <v>入 $0.123077 · 出 $0.307692 · 缓 $0.024615</v>
+        <v>—</v>
       </c>
       <c r="J79" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K79" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L79" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M79" t="str">
         <v>—</v>
       </c>
       <c r="N79" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O79" t="str">
-        <v>入⚠+111.3% 出⚠+153.5% 缓⚠+111.3%</v>
+        <v>入⚠-47.2% 出⚠-78.9%</v>
       </c>
       <c r="P79" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>ℹ 线上无同档</v>
       </c>
       <c r="Q79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="str">
-        <v>qwen-turbo</v>
-      </c>
-      <c r="B80" t="str">
-        <v>Qwen Turbo</v>
-      </c>
-      <c r="C80" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="D80" t="str">
-        <v>统一价</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="E80" t="str">
-        <v>入 ¥0.3 · 出 ¥0.6</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
       </c>
       <c r="F80" t="str">
         <v>—</v>
       </c>
       <c r="G80" t="str">
-        <v>—</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
       </c>
       <c r="H80" t="str">
-        <v>—</v>
+        <v>入 $0.065 · 出 $0.26</v>
       </c>
       <c r="I80" t="str">
-        <v>入 $0.046154 · 出 $0.092308 · 缓 $0.010345</v>
+        <v>—</v>
       </c>
       <c r="J80" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K80" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L80" t="str">
         <v>—</v>
@@ -4399,13 +4427,13 @@
         <v>—</v>
       </c>
       <c r="N80" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O80" t="str">
-        <v>—</v>
+        <v>入⚠-64.8% 出⚠-85.9%</v>
       </c>
       <c r="P80" t="str">
-        <v>入✅ 出✅ 缓—</v>
+        <v>ℹ 线上无同档</v>
       </c>
       <c r="Q80" t="str">
         <v/>
@@ -4413,31 +4441,31 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>qwen3.5-flash</v>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="B81" t="str">
-        <v>Qwen3.5 Flash</v>
+        <v>Qwen3.5 Plus</v>
       </c>
       <c r="C81" t="str">
         <v>Tongyi</v>
       </c>
       <c r="D81" t="str">
-        <v>0&lt;输入&lt;=128k</v>
+        <v>输入&lt;=128k</v>
       </c>
       <c r="E81" t="str">
-        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
+        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
       </c>
       <c r="F81" t="str">
         <v>—</v>
       </c>
       <c r="G81" t="str">
-        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
+        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
       </c>
       <c r="H81" t="str">
-        <v>入 $0.065 · 出 $0.26</v>
+        <v>入 $0.3 · 出 $1.7999999999999998</v>
       </c>
       <c r="I81" t="str">
-        <v>入 $0.030769 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.123077 · 出 $0.738462 · 缓 $0.012308</v>
       </c>
       <c r="J81" t="str">
         <v>0%</v>
@@ -4455,7 +4483,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O81" t="str">
-        <v>入⚠+111.3% 出⚠-15.5%</v>
+        <v>入⚠+143.7% 出⚠+143.7%</v>
       </c>
       <c r="P81" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -4469,16 +4497,16 @@
         <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E82" t="str">
-        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
       </c>
       <c r="F82" t="str">
         <v>—</v>
       </c>
       <c r="G82" t="str">
-        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
       </c>
       <c r="H82" t="str">
-        <v>入 $0.065 · 出 $0.26</v>
+        <v>入 $0.3 · 出 $1.7999999999999998</v>
       </c>
       <c r="I82" t="str">
         <v>—</v>
@@ -4499,7 +4527,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O82" t="str">
-        <v>入⚠-47.2% 出⚠-78.9%</v>
+        <v>入⚠-2.5% 出⚠-2.5%</v>
       </c>
       <c r="P82" t="str">
         <v>ℹ 线上无同档</v>
@@ -4513,16 +4541,16 @@
         <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="E83" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
+        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
       </c>
       <c r="F83" t="str">
         <v>—</v>
       </c>
       <c r="G83" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
+        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
       </c>
       <c r="H83" t="str">
-        <v>入 $0.065 · 出 $0.26</v>
+        <v>入 $0.3 · 出 $1.7999999999999998</v>
       </c>
       <c r="I83" t="str">
         <v>—</v>
@@ -4543,7 +4571,7 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O83" t="str">
-        <v>入⚠-64.8% 出⚠-85.9%</v>
+        <v>入⚠-51.3% 出⚠-51.3%</v>
       </c>
       <c r="P83" t="str">
         <v>ℹ 线上无同档</v>
@@ -4554,31 +4582,31 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>qwen3.5-plus</v>
+        <v>qwen3.6-flash</v>
       </c>
       <c r="B84" t="str">
-        <v>Qwen3.5 Plus</v>
+        <v>Qwen3.6 Flash</v>
       </c>
       <c r="C84" t="str">
         <v>Tongyi</v>
       </c>
       <c r="D84" t="str">
-        <v>输入&lt;=128k</v>
+        <v>0&lt;Token≤256K</v>
       </c>
       <c r="E84" t="str">
-        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
       </c>
       <c r="F84" t="str">
         <v>—</v>
       </c>
       <c r="G84" t="str">
-        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+        <v>—</v>
       </c>
       <c r="H84" t="str">
-        <v>入 $0.3 · 出 $1.7999999999999998</v>
+        <v>入 $0.1875 · 出 $1.125</v>
       </c>
       <c r="I84" t="str">
-        <v>入 $0.123077 · 出 $0.738462 · 缓 $0.012308</v>
+        <v>入 $0.184615 · 出 $1.107692 · 缓 $0.036923</v>
       </c>
       <c r="J84" t="str">
         <v>0%</v>
@@ -4593,10 +4621,10 @@
         <v>—</v>
       </c>
       <c r="N84" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O84" t="str">
-        <v>入⚠+143.7% 出⚠+143.7%</v>
+        <v>入⚠+1.6% 出⚠+1.6%</v>
       </c>
       <c r="P84" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -4607,19 +4635,19 @@
     </row>
     <row r="85">
       <c r="D85" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>256K&lt;Token≤1M</v>
       </c>
       <c r="E85" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
       </c>
       <c r="F85" t="str">
         <v>—</v>
       </c>
       <c r="G85" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+        <v>—</v>
       </c>
       <c r="H85" t="str">
-        <v>入 $0.3 · 出 $1.7999999999999998</v>
+        <v>入 $0.1875 · 出 $1.125</v>
       </c>
       <c r="I85" t="str">
         <v>—</v>
@@ -4637,10 +4665,10 @@
         <v>—</v>
       </c>
       <c r="N85" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O85" t="str">
-        <v>入⚠-2.5% 出⚠-2.5%</v>
+        <v>入⚠-74.6% 出⚠-74.6%</v>
       </c>
       <c r="P85" t="str">
         <v>ℹ 线上无同档</v>
@@ -4650,64 +4678,64 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="str">
+        <v>qwen3.6-plus</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Qwen3.6 Plus</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="D86" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>0&lt;Token≤256K</v>
       </c>
       <c r="E86" t="str">
-        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
       </c>
       <c r="F86" t="str">
         <v>—</v>
       </c>
       <c r="G86" t="str">
-        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
+        <v>—</v>
       </c>
       <c r="H86" t="str">
-        <v>入 $0.3 · 出 $1.7999999999999998</v>
+        <v>入 $0.325 · 出 $1.95</v>
       </c>
       <c r="I86" t="str">
-        <v>—</v>
+        <v>入 $0.307692 · 出 $1.846154 · 缓 $0.061538</v>
       </c>
       <c r="J86" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="K86" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L86" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M86" t="str">
         <v>—</v>
       </c>
       <c r="N86" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O86" t="str">
-        <v>入⚠-51.3% 出⚠-51.3%</v>
+        <v>入⚠+5.6% 出⚠+5.6%</v>
       </c>
       <c r="P86" t="str">
-        <v>ℹ 线上无同档</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="str">
-        <v>qwen3.6-flash</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Qwen3.6 Flash</v>
-      </c>
-      <c r="C87" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="D87" t="str">
         <v>256K&lt;Token≤1M</v>
       </c>
       <c r="E87" t="str">
-        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
+        <v>入 ¥8 · 出 ¥48 · 缓 ¥1.6</v>
       </c>
       <c r="F87" t="str">
         <v>—</v>
@@ -4716,7 +4744,7 @@
         <v>—</v>
       </c>
       <c r="H87" t="str">
-        <v>入 $0.1875 · 出 $1.125</v>
+        <v>入 $0.325 · 出 $1.95</v>
       </c>
       <c r="I87" t="str">
         <v>—</v>
@@ -4737,7 +4765,7 @@
         <v>—</v>
       </c>
       <c r="O87" t="str">
-        <v>入⚠-74.6% 出⚠-74.6%</v>
+        <v>入⚠-73.6% 出⚠-73.6%</v>
       </c>
       <c r="P87" t="str">
         <v>ℹ 线上无同档</v>
@@ -4747,11 +4775,20 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="str">
+        <v>qwen3.7-max</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Qwen3.7 Max</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="D88" t="str">
-        <v>0&lt;Token≤256K</v>
+        <v>0&lt;Token≤1M</v>
       </c>
       <c r="E88" t="str">
-        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
+        <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
       </c>
       <c r="F88" t="str">
         <v>—</v>
@@ -4760,10 +4797,10 @@
         <v>—</v>
       </c>
       <c r="H88" t="str">
-        <v>入 $0.1875 · 出 $1.125</v>
+        <v>入 $1.25 · 出 $3.75 · 缓 $0.25</v>
       </c>
       <c r="I88" t="str">
-        <v>入 $0.184615 · 出 $1.107692 · 缓 $0.036923</v>
+        <v>入 $1.846154 · 出 $5.538462 · 缓 $0.369231</v>
       </c>
       <c r="J88" t="str">
         <v>0%</v>
@@ -4781,7 +4818,7 @@
         <v>—</v>
       </c>
       <c r="O88" t="str">
-        <v>入⚠+1.6% 出⚠+1.6%</v>
+        <v>入⚠-32.3% 出⚠-32.3% 缓⚠-32.3%</v>
       </c>
       <c r="P88" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -4792,10 +4829,10 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>qwen3.6-plus</v>
+        <v>qwen3.7-plus</v>
       </c>
       <c r="B89" t="str">
-        <v>Qwen3.6 Plus</v>
+        <v>Qwen3.7 Plus</v>
       </c>
       <c r="C89" t="str">
         <v>Tongyi</v>
@@ -4804,7 +4841,7 @@
         <v>0&lt;Token≤256K</v>
       </c>
       <c r="E89" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
       </c>
       <c r="F89" t="str">
         <v>—</v>
@@ -4813,10 +4850,10 @@
         <v>—</v>
       </c>
       <c r="H89" t="str">
-        <v>入 $0.325 · 出 $1.95</v>
+        <v>入 $0.32 · 出 $1.28 · 缓 $0.064</v>
       </c>
       <c r="I89" t="str">
-        <v>入 $0.307692 · 出 $1.846154 · 缓 $0.061538</v>
+        <v>入 $0.307692 · 出 $1.230769 · 缓 $0.061538</v>
       </c>
       <c r="J89" t="str">
         <v>0%</v>
@@ -4834,7 +4871,7 @@
         <v>—</v>
       </c>
       <c r="O89" t="str">
-        <v>入⚠+5.6% 出⚠+5.6%</v>
+        <v>入⚠+4% 出⚠+4% 缓⚠+4%</v>
       </c>
       <c r="P89" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -4844,20 +4881,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="str">
-        <v>qwen3.7-max</v>
-      </c>
-      <c r="B90" t="str">
-        <v>Qwen3.7 Max</v>
-      </c>
-      <c r="C90" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="D90" t="str">
-        <v>0&lt;Token≤1M</v>
+        <v>256K&lt;Token≤1M</v>
       </c>
       <c r="E90" t="str">
-        <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.2</v>
       </c>
       <c r="F90" t="str">
         <v>—</v>
@@ -4866,19 +4894,19 @@
         <v>—</v>
       </c>
       <c r="H90" t="str">
-        <v>入 $1.25 · 出 $3.75 · 缓 $0.25</v>
+        <v>入 $0.32 · 出 $1.28 · 缓 $0.064</v>
       </c>
       <c r="I90" t="str">
-        <v>入 $1.846154 · 出 $5.538462 · 缓 $0.369231</v>
+        <v>—</v>
       </c>
       <c r="J90" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K90" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L90" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M90" t="str">
         <v>—</v>
@@ -4887,76 +4915,20 @@
         <v>—</v>
       </c>
       <c r="O90" t="str">
-        <v>入⚠-32.3% 出⚠-32.3% 缓⚠-32.3%</v>
+        <v>入⚠-65.3% 出⚠-65.3% 缓⚠-65.3%</v>
       </c>
       <c r="P90" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>ℹ 线上无同档</v>
       </c>
       <c r="Q90" t="str">
         <v/>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>qwen3.7-plus</v>
-      </c>
-      <c r="B91" t="str">
-        <v>Qwen3.7 Plus</v>
-      </c>
-      <c r="C91" t="str">
-        <v>Tongyi</v>
-      </c>
-      <c r="D91" t="str">
-        <v>0&lt;Token≤256K</v>
-      </c>
-      <c r="E91" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
-      </c>
-      <c r="F91" t="str">
-        <v>—</v>
-      </c>
-      <c r="G91" t="str">
-        <v>—</v>
-      </c>
-      <c r="H91" t="str">
-        <v>入 $0.32 · 出 $1.28 · 缓 $0.064</v>
-      </c>
-      <c r="I91" t="str">
-        <v>入 $0.307692 · 出 $1.230769 · 缓 $0.061538</v>
-      </c>
-      <c r="J91" t="str">
-        <v>0%</v>
-      </c>
-      <c r="K91" t="str">
-        <v>0%</v>
-      </c>
-      <c r="L91" t="str">
-        <v>0%</v>
-      </c>
-      <c r="M91" t="str">
-        <v>—</v>
-      </c>
-      <c r="N91" t="str">
-        <v>—</v>
-      </c>
-      <c r="O91" t="str">
-        <v>入⚠+4% 出⚠+4% 缓⚠+4%</v>
-      </c>
-      <c r="P91" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="Q91" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
+  <mergeCells count="69">
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:C18"/>
@@ -4972,48 +4944,60 @@
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="C35:C38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="B63:B66"/>
-    <mergeCell ref="C63:C66"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="A75:A77"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="C75:C77"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="C70:C72"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="C78:C80"/>
     <mergeCell ref="A81:A83"/>
     <mergeCell ref="B81:B83"/>
     <mergeCell ref="C81:C83"/>
-    <mergeCell ref="A84:A86"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="C84:C86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q90"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5246,16 +5230,16 @@
         <v>Zhipu</v>
       </c>
       <c r="E7" t="str">
-        <v>32k&lt;=输入</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="F7" t="str">
         <v>glm-5</v>
       </c>
       <c r="G7" t="str">
-        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="H7" t="str">
-        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="I7" t="str">
         <v>✅ 一致</v>
@@ -5272,16 +5256,16 @@
         <v>7</v>
       </c>
       <c r="E8" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="F8" t="str">
         <v>glm-5</v>
       </c>
       <c r="G8" t="str">
-        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="H8" t="str">
-        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="I8" t="str">
         <v>✅ 一致</v>
@@ -5307,16 +5291,16 @@
         <v>Zhipu</v>
       </c>
       <c r="E9" t="str">
-        <v>输入&gt;=32k</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="F9" t="str">
         <v>glm-5-turbo</v>
       </c>
       <c r="G9" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="H9" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="I9" t="str">
         <v>✅ 一致</v>
@@ -5333,16 +5317,16 @@
         <v>9</v>
       </c>
       <c r="E10" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="F10" t="str">
         <v>glm-5-turbo</v>
       </c>
       <c r="G10" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="H10" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="I10" t="str">
         <v>✅ 一致</v>
@@ -5368,16 +5352,16 @@
         <v>Zhipu</v>
       </c>
       <c r="E11" t="str">
-        <v>32k&lt;=输入</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="F11" t="str">
         <v>glm-5.1</v>
       </c>
       <c r="G11" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="H11" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="I11" t="str">
         <v>✅ 一致</v>
@@ -5394,16 +5378,16 @@
         <v>11</v>
       </c>
       <c r="E12" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="F12" t="str">
         <v>glm-5.1</v>
       </c>
       <c r="G12" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="H12" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="I12" t="str">
         <v>✅ 一致</v>
@@ -5464,16 +5448,16 @@
         <v>Zhipu</v>
       </c>
       <c r="E14" t="str">
-        <v>输入&gt;=32k</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="F14" t="str">
         <v>glm-5v-turbo</v>
       </c>
       <c r="G14" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="H14" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="I14" t="str">
         <v>✅ 一致</v>
@@ -5490,16 +5474,16 @@
         <v>14</v>
       </c>
       <c r="E15" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="F15" t="str">
         <v>glm-5v-turbo</v>
       </c>
       <c r="G15" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="H15" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="I15" t="str">
         <v>✅ 一致</v>
@@ -6253,7 +6237,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6409,16 +6393,16 @@
         <v>Zhipu</v>
       </c>
       <c r="E5" t="str">
-        <v>32k&lt;=输入</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="F5" t="str">
         <v>glm-5</v>
       </c>
       <c r="G5" t="str">
-        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="H5" t="str">
-        <v>入 ¥6 · 出 ¥22</v>
+        <v>入 ¥4 · 出 ¥18</v>
       </c>
       <c r="I5" t="str">
         <v>✅ 一致</v>
@@ -6435,16 +6419,16 @@
         <v>5</v>
       </c>
       <c r="E6" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="F6" t="str">
         <v>glm-5</v>
       </c>
       <c r="G6" t="str">
-        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="H6" t="str">
-        <v>入 ¥4 · 出 ¥18</v>
+        <v>入 ¥6 · 出 ¥22</v>
       </c>
       <c r="I6" t="str">
         <v>✅ 一致</v>
@@ -6470,16 +6454,16 @@
         <v>Zhipu</v>
       </c>
       <c r="E7" t="str">
-        <v>32k&lt;=输入</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="F7" t="str">
         <v>glm-5.1</v>
       </c>
       <c r="G7" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="H7" t="str">
-        <v>入 ¥8 · 出 ¥28</v>
+        <v>入 ¥6 · 出 ¥24</v>
       </c>
       <c r="I7" t="str">
         <v>✅ 一致</v>
@@ -6496,16 +6480,16 @@
         <v>7</v>
       </c>
       <c r="E8" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="F8" t="str">
         <v>glm-5.1</v>
       </c>
       <c r="G8" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="H8" t="str">
-        <v>入 ¥6 · 出 ¥24</v>
+        <v>入 ¥8 · 出 ¥28</v>
       </c>
       <c r="I8" t="str">
         <v>✅ 一致</v>
@@ -6853,26 +6837,17 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v>qwen-turbo</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Qwen Turbo</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="E19" t="str">
-        <v>统一价</v>
+        <v>128K&lt;Token≤256K</v>
       </c>
       <c r="F19" t="str">
-        <v>qwen-turbo</v>
+        <v>qwen-plus</v>
       </c>
       <c r="G19" t="str">
-        <v>入 ¥0.3 · 出 ¥0.6</v>
+        <v>入 ¥2.4 · 出 ¥20 · 缓 ¥0.48</v>
       </c>
       <c r="H19" t="str">
-        <v>入 ¥0.3 · 出 ¥0.6</v>
+        <v>入 ¥2.4 · 出 ¥20 · 缓 ¥0.48</v>
       </c>
       <c r="I19" t="str">
         <v>✅ 一致</v>
@@ -6888,29 +6863,20 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>qwen3.5-flash</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Qwen3.5 Flash</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="E20" t="str">
-        <v>0&lt;输入&lt;=128k</v>
+        <v>256K&lt;Token≤1M</v>
       </c>
       <c r="F20" t="str">
-        <v>qwen3.5-flash</v>
+        <v>qwen-plus</v>
       </c>
       <c r="G20" t="str">
-        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
+        <v>入 ¥4.8 · 出 ¥48 · 缓 ¥0.96</v>
       </c>
       <c r="H20" t="str">
-        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.04</v>
+        <v>入 ¥4.8 · 出 ¥48 · 缓 ¥0.96</v>
       </c>
       <c r="I20" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>✅ 一致</v>
       </c>
       <c r="J20" t="str">
         <v>待填</v>
@@ -6923,20 +6889,29 @@
       <c r="A21">
         <v>20</v>
       </c>
+      <c r="B21" t="str">
+        <v>qwen-turbo</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Qwen Turbo</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="E21" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>统一价</v>
       </c>
       <c r="F21" t="str">
-        <v>qwen3.5-flash</v>
+        <v>qwen-turbo</v>
       </c>
       <c r="G21" t="str">
-        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
+        <v>入 ¥0.3 · 出 ¥0.6</v>
       </c>
       <c r="H21" t="str">
-        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.16</v>
+        <v>入 ¥0.3 · 出 ¥0.6</v>
       </c>
       <c r="I21" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>✅ 一致</v>
       </c>
       <c r="J21" t="str">
         <v>待填</v>
@@ -6949,17 +6924,26 @@
       <c r="A22">
         <v>21</v>
       </c>
+      <c r="B22" t="str">
+        <v>qwen3.5-flash</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Qwen3.5 Flash</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="E22" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>0&lt;输入&lt;=128k</v>
       </c>
       <c r="F22" t="str">
         <v>qwen3.5-flash</v>
       </c>
       <c r="G22" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="H22" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.04</v>
       </c>
       <c r="I22" t="str">
         <v>⚠ 缓+100%</v>
@@ -6975,26 +6959,17 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="str">
-        <v>qwen3.5-plus</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Qwen3.5 Plus</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="E23" t="str">
-        <v>输入&lt;=128k</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="F23" t="str">
-        <v>qwen3.5-plus</v>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="G23" t="str">
-        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
       </c>
       <c r="H23" t="str">
-        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.16</v>
+        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.16</v>
       </c>
       <c r="I23" t="str">
         <v>⚠ 缓+100%</v>
@@ -7011,16 +6986,16 @@
         <v>23</v>
       </c>
       <c r="E24" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="F24" t="str">
-        <v>qwen3.5-plus</v>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="G24" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
       </c>
       <c r="H24" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
       </c>
       <c r="I24" t="str">
         <v>⚠ 缓+100%</v>
@@ -7036,17 +7011,26 @@
       <c r="A25">
         <v>24</v>
       </c>
+      <c r="B25" t="str">
+        <v>qwen3.5-plus</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Qwen3.5 Plus</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="E25" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>输入&lt;=128k</v>
       </c>
       <c r="F25" t="str">
         <v>qwen3.5-plus</v>
       </c>
       <c r="G25" t="str">
-        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
+        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
       </c>
       <c r="H25" t="str">
-        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.8</v>
+        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.16</v>
       </c>
       <c r="I25" t="str">
         <v>⚠ 缓+100%</v>
@@ -7062,29 +7046,20 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="str">
-        <v>qwen3.6-flash</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Qwen3.6 Flash</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="E26" t="str">
-        <v>256K&lt;Token≤1M</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="F26" t="str">
-        <v>qwen3.6-flash</v>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="G26" t="str">
-        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
       </c>
       <c r="H26" t="str">
-        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
       </c>
       <c r="I26" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 缓+100%</v>
       </c>
       <c r="J26" t="str">
         <v>待填</v>
@@ -7098,19 +7073,19 @@
         <v>26</v>
       </c>
       <c r="E27" t="str">
-        <v>0&lt;Token≤256K</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="F27" t="str">
-        <v>qwen3.6-flash</v>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="G27" t="str">
-        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
+        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
       </c>
       <c r="H27" t="str">
-        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
+        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.8</v>
       </c>
       <c r="I27" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 缓+100%</v>
       </c>
       <c r="J27" t="str">
         <v>待填</v>
@@ -7124,10 +7099,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>qwen3.6-plus</v>
+        <v>qwen3.6-flash</v>
       </c>
       <c r="C28" t="str">
-        <v>Qwen3.6 Plus</v>
+        <v>Qwen3.6 Flash</v>
       </c>
       <c r="D28" t="str">
         <v>Tongyi</v>
@@ -7136,13 +7111,13 @@
         <v>0&lt;Token≤256K</v>
       </c>
       <c r="F28" t="str">
-        <v>qwen3.6-plus</v>
+        <v>qwen3.6-flash</v>
       </c>
       <c r="G28" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
+        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
       </c>
       <c r="H28" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
+        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
       </c>
       <c r="I28" t="str">
         <v>✅ 一致</v>
@@ -7158,26 +7133,17 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="str">
-        <v>qwen3.7-max</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Qwen3.7 Max</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="E29" t="str">
-        <v>0&lt;Token≤1M</v>
+        <v>256K&lt;Token≤1M</v>
       </c>
       <c r="F29" t="str">
-        <v>qwen3.7-max</v>
+        <v>qwen3.6-flash</v>
       </c>
       <c r="G29" t="str">
-        <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
+        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
       </c>
       <c r="H29" t="str">
-        <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
+        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
       </c>
       <c r="I29" t="str">
         <v>✅ 一致</v>
@@ -7194,10 +7160,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>qwen3.7-plus</v>
+        <v>qwen3.6-plus</v>
       </c>
       <c r="C30" t="str">
-        <v>Qwen3.7 Plus</v>
+        <v>Qwen3.6 Plus</v>
       </c>
       <c r="D30" t="str">
         <v>Tongyi</v>
@@ -7206,26 +7172,148 @@
         <v>0&lt;Token≤256K</v>
       </c>
       <c r="F30" t="str">
+        <v>qwen3.6-plus</v>
+      </c>
+      <c r="G30" t="str">
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
+      </c>
+      <c r="H30" t="str">
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
+      </c>
+      <c r="I30" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J30" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K30" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="E31" t="str">
+        <v>256K&lt;Token≤1M</v>
+      </c>
+      <c r="F31" t="str">
+        <v>qwen3.6-plus</v>
+      </c>
+      <c r="G31" t="str">
+        <v>入 ¥8 · 出 ¥48 · 缓 ¥1.6</v>
+      </c>
+      <c r="H31" t="str">
+        <v>入 ¥8 · 出 ¥48 · 缓 ¥1.6</v>
+      </c>
+      <c r="I31" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J31" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K31" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>qwen3.7-max</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Qwen3.7 Max</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="E32" t="str">
+        <v>0&lt;Token≤1M</v>
+      </c>
+      <c r="F32" t="str">
+        <v>qwen3.7-max</v>
+      </c>
+      <c r="G32" t="str">
+        <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
+      </c>
+      <c r="H32" t="str">
+        <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
+      </c>
+      <c r="I32" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J32" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K32" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
         <v>qwen3.7-plus</v>
       </c>
-      <c r="G30" t="str">
+      <c r="C33" t="str">
+        <v>Qwen3.7 Plus</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="E33" t="str">
+        <v>0&lt;Token≤256K</v>
+      </c>
+      <c r="F33" t="str">
+        <v>qwen3.7-plus</v>
+      </c>
+      <c r="G33" t="str">
         <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
       </c>
-      <c r="H30" t="str">
+      <c r="H33" t="str">
         <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
       </c>
-      <c r="I30" t="str">
-        <v>✅ 一致</v>
-      </c>
-      <c r="J30" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K30" t="str">
+      <c r="I33" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J33" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K33" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="E34" t="str">
+        <v>256K&lt;Token≤1M</v>
+      </c>
+      <c r="F34" t="str">
+        <v>qwen3.7-plus</v>
+      </c>
+      <c r="G34" t="str">
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.2</v>
+      </c>
+      <c r="H34" t="str">
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.2</v>
+      </c>
+      <c r="I34" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J34" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K34" t="str">
         <v>待填</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="27">
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
@@ -7235,18 +7323,27 @@
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="D14:D16"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K34"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7906,7 +8003,7 @@
         <v>Zhipu</v>
       </c>
       <c r="E21" t="str">
-        <v>输入：≤32K token</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="F21" t="str">
         <v>5</v>
@@ -7932,7 +8029,7 @@
         <v>21</v>
       </c>
       <c r="E22" t="str">
-        <v>输入：＞32K token</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="F22" t="str">
         <v>5</v>
@@ -7967,7 +8064,7 @@
         <v>Zhipu</v>
       </c>
       <c r="E23" t="str">
-        <v>输入：≤32K token</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="F23" t="str">
         <v>5-Turbo</v>
@@ -7993,7 +8090,7 @@
         <v>23</v>
       </c>
       <c r="E24" t="str">
-        <v>输入：＞32K token</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="F24" t="str">
         <v>5-Turbo</v>
@@ -8028,7 +8125,7 @@
         <v>Zhipu</v>
       </c>
       <c r="E25" t="str">
-        <v>输入：≤32K token</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="F25" t="str">
         <v>5.1（new）</v>
@@ -8054,7 +8151,7 @@
         <v>25</v>
       </c>
       <c r="E26" t="str">
-        <v>输入：＞32K token</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="F26" t="str">
         <v>5.1（new）</v>
@@ -8587,16 +8684,16 @@
         <v>Tencent</v>
       </c>
       <c r="E42" t="str">
-        <v>16k&lt;=输入&lt;32k</v>
+        <v>输入&lt;16k</v>
       </c>
       <c r="F42" t="str">
         <v>3-preview</v>
       </c>
       <c r="G42" t="str">
-        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
       </c>
       <c r="H42" t="str">
-        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
       </c>
       <c r="I42" t="str">
         <v>✅ 一致</v>
@@ -8613,16 +8710,16 @@
         <v>42</v>
       </c>
       <c r="E43" t="str">
-        <v>输入&gt;=32k</v>
+        <v>16k&lt;=输入&lt;32k</v>
       </c>
       <c r="F43" t="str">
         <v>3-preview</v>
       </c>
       <c r="G43" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
       <c r="H43" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
       <c r="I43" t="str">
         <v>✅ 一致</v>
@@ -8639,16 +8736,16 @@
         <v>43</v>
       </c>
       <c r="E44" t="str">
-        <v>输入长度（0, 16k）</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="F44" t="str">
         <v>3-preview</v>
       </c>
       <c r="G44" t="str">
-        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="H44" t="str">
-        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="I44" t="str">
         <v>✅ 一致</v>
@@ -8718,7 +8815,7 @@
         <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
       </c>
       <c r="H46" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
       </c>
       <c r="I46" t="str">
         <v>✅ 一致</v>
@@ -8753,7 +8850,7 @@
         <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="H47" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="I47" t="str">
         <v>✅ 一致</v>
@@ -8945,7 +9042,7 @@
         <v>Opus 4.5</v>
       </c>
       <c r="G4" t="str">
-        <v>入 $5 · 出 $25</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="H4" t="str">
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
@@ -9611,7 +9708,7 @@
         <v>Zhipu</v>
       </c>
       <c r="E25" t="str">
-        <v>输入：≤32K token</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="F25" t="str">
         <v>5</v>
@@ -9637,7 +9734,7 @@
         <v>25</v>
       </c>
       <c r="E26" t="str">
-        <v>输入：＞32K token</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="F26" t="str">
         <v>5</v>
@@ -9672,7 +9769,7 @@
         <v>Zhipu</v>
       </c>
       <c r="E27" t="str">
-        <v>输入：≤32K token</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="F27" t="str">
         <v>5-Turbo</v>
@@ -9698,7 +9795,7 @@
         <v>27</v>
       </c>
       <c r="E28" t="str">
-        <v>输入：＞32K token</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="F28" t="str">
         <v>5-Turbo</v>
@@ -9733,7 +9830,7 @@
         <v>Zhipu</v>
       </c>
       <c r="E29" t="str">
-        <v>输入：≤32K token</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="F29" t="str">
         <v>5.1（new）</v>
@@ -9759,7 +9856,7 @@
         <v>29</v>
       </c>
       <c r="E30" t="str">
-        <v>输入：＞32K token</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="F30" t="str">
         <v>5.1（new）</v>
@@ -10857,7 +10954,1300 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K40"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>序号</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Trinity ID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>显示名</v>
+      </c>
+      <c r="D1" t="str">
+        <v>厂商</v>
+      </c>
+      <c r="E1" t="str">
+        <v>价格档位</v>
+      </c>
+      <c r="F1" t="str">
+        <v>上游模型ID</v>
+      </c>
+      <c r="G1" t="str">
+        <v>厂商官方价</v>
+      </c>
+      <c r="H1" t="str">
+        <v>供应商挂牌(USD/百万tokens)</v>
+      </c>
+      <c r="I1" t="str">
+        <v>供应商vs官方</v>
+      </c>
+      <c r="J1" t="str">
+        <v>折扣</v>
+      </c>
+      <c r="K1" t="str">
+        <v>成本(USD/百万tokens)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>gemini-2.5-flash</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Gemini gemini-2.5-flash</v>
+      </c>
+      <c r="D2" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E2" t="str">
+        <v>输入:文本/图片/视频</v>
+      </c>
+      <c r="F2" t="str">
+        <v>gemini-2.5-flash</v>
+      </c>
+      <c r="G2" t="str">
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+      </c>
+      <c r="H2" t="str">
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+      </c>
+      <c r="I2" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J2" t="str">
+        <v>—</v>
+      </c>
+      <c r="K2" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>输入:音频</v>
+      </c>
+      <c r="F3" t="str">
+        <v>gemini-2.5-flash</v>
+      </c>
+      <c r="G3" t="str">
+        <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
+      </c>
+      <c r="H3" t="str">
+        <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
+      </c>
+      <c r="I3" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J3" t="str">
+        <v>—</v>
+      </c>
+      <c r="K3" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>gemini-2.5-flash-lite</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Gemini gemini-2.5-flash-lite</v>
+      </c>
+      <c r="D4" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E4" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F4" t="str">
+        <v>gemini-2.5-flash-lite</v>
+      </c>
+      <c r="G4" t="str">
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+      </c>
+      <c r="H4" t="str">
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+      </c>
+      <c r="I4" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J4" t="str">
+        <v>—</v>
+      </c>
+      <c r="K4" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>gemini-2.5-flash-lite-preview</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Gemini gemini-2.5-flash-lite-preview</v>
+      </c>
+      <c r="D5" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E5" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F5" t="str">
+        <v>gemini-2.5-flash-lite-preview</v>
+      </c>
+      <c r="G5" t="str">
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+      </c>
+      <c r="H5" t="str">
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+      </c>
+      <c r="I5" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J5" t="str">
+        <v>—</v>
+      </c>
+      <c r="K5" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>gemini-2.5-pro</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Gemini gemini-2.5-pro</v>
+      </c>
+      <c r="D6" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E6" t="str">
+        <v>输入&lt;=20万个token</v>
+      </c>
+      <c r="F6" t="str">
+        <v>gemini-2.5-pro</v>
+      </c>
+      <c r="G6" t="str">
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+      </c>
+      <c r="H6" t="str">
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+      </c>
+      <c r="I6" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J6" t="str">
+        <v>—</v>
+      </c>
+      <c r="K6" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="E7" t="str">
+        <v>输入&gt;20万个token</v>
+      </c>
+      <c r="F7" t="str">
+        <v>gemini-2.5-pro</v>
+      </c>
+      <c r="G7" t="str">
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+      </c>
+      <c r="H7" t="str">
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+      </c>
+      <c r="I7" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J7" t="str">
+        <v>—</v>
+      </c>
+      <c r="K7" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>gemini-3-flash-preview</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Gemini gemini-3-flash-preview</v>
+      </c>
+      <c r="D8" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E8" t="str">
+        <v>输入:文本/图片/视频</v>
+      </c>
+      <c r="F8" t="str">
+        <v>gemini-3-flash-preview</v>
+      </c>
+      <c r="G8" t="str">
+        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
+      </c>
+      <c r="H8" t="str">
+        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
+      </c>
+      <c r="I8" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J8" t="str">
+        <v>—</v>
+      </c>
+      <c r="K8" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="E9" t="str">
+        <v>输入:音频</v>
+      </c>
+      <c r="F9" t="str">
+        <v>gemini-3-flash-preview</v>
+      </c>
+      <c r="G9" t="str">
+        <v>入 $1 · 出 $3 · 缓 $0.1</v>
+      </c>
+      <c r="H9" t="str">
+        <v>入 $1 · 出 $3 · 缓 $0.1</v>
+      </c>
+      <c r="I9" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J9" t="str">
+        <v>—</v>
+      </c>
+      <c r="K9" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="E10" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F10" t="str">
+        <v>gemini-3-pro-preview</v>
+      </c>
+      <c r="G10" t="str">
+        <v>入 $2 · 出 $12 · 缓 $0.2</v>
+      </c>
+      <c r="H10" t="str">
+        <v>入 $2 · 出 $12 · 缓 $0.2</v>
+      </c>
+      <c r="I10" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J10" t="str">
+        <v>—</v>
+      </c>
+      <c r="K10" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>gemini-3.1-flash-lite</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Gemini gemini-3.1-flash-lite</v>
+      </c>
+      <c r="D11" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E11" t="str">
+        <v>输入:文本/图片/视频</v>
+      </c>
+      <c r="F11" t="str">
+        <v>gemini-3.1-flash-lite</v>
+      </c>
+      <c r="G11" t="str">
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+      </c>
+      <c r="H11" t="str">
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+      </c>
+      <c r="I11" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J11" t="str">
+        <v>—</v>
+      </c>
+      <c r="K11" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="E12" t="str">
+        <v>输入:音频</v>
+      </c>
+      <c r="F12" t="str">
+        <v>gemini-3.1-flash-lite</v>
+      </c>
+      <c r="G12" t="str">
+        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
+      </c>
+      <c r="H12" t="str">
+        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
+      </c>
+      <c r="I12" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J12" t="str">
+        <v>—</v>
+      </c>
+      <c r="K12" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="E13" t="str">
+        <v>输入:文本/图片/视频</v>
+      </c>
+      <c r="F13" t="str">
+        <v>gemini-3.1-flash-lite-preview</v>
+      </c>
+      <c r="G13" t="str">
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+      </c>
+      <c r="H13" t="str">
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+      </c>
+      <c r="I13" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J13" t="str">
+        <v>—</v>
+      </c>
+      <c r="K13" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="E14" t="str">
+        <v>输入:音频</v>
+      </c>
+      <c r="F14" t="str">
+        <v>gemini-3.1-flash-lite-preview</v>
+      </c>
+      <c r="G14" t="str">
+        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
+      </c>
+      <c r="H14" t="str">
+        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
+      </c>
+      <c r="I14" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J14" t="str">
+        <v>—</v>
+      </c>
+      <c r="K14" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>gemini-3.1-pro-preview</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Gemini gemini-3.1-pro-preview</v>
+      </c>
+      <c r="D15" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E15" t="str">
+        <v>输入&lt;=20万个token</v>
+      </c>
+      <c r="F15" t="str">
+        <v>gemini-3.1-pro-preview</v>
+      </c>
+      <c r="G15" t="str">
+        <v>入 $2 · 出 $12 · 缓 $0.2</v>
+      </c>
+      <c r="H15" t="str">
+        <v>入 $2 · 出 $12 · 缓 $0.2</v>
+      </c>
+      <c r="I15" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J15" t="str">
+        <v>—</v>
+      </c>
+      <c r="K15" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="E16" t="str">
+        <v>输入&gt;20万个token</v>
+      </c>
+      <c r="F16" t="str">
+        <v>gemini-3.1-pro-preview</v>
+      </c>
+      <c r="G16" t="str">
+        <v>入 $4 · 出 $18 · 缓 $0.4</v>
+      </c>
+      <c r="H16" t="str">
+        <v>入 $4 · 出 $18 · 缓 $0.4</v>
+      </c>
+      <c r="I16" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J16" t="str">
+        <v>—</v>
+      </c>
+      <c r="K16" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>gemini-3.5-flash</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Gemini gemini-3.5-flash</v>
+      </c>
+      <c r="D17" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E17" t="str">
+        <v>输入:文本/图片/视频</v>
+      </c>
+      <c r="F17" t="str">
+        <v>gemini-3.5-flash</v>
+      </c>
+      <c r="G17" t="str">
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+      </c>
+      <c r="H17" t="str">
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+      </c>
+      <c r="I17" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J17" t="str">
+        <v>—</v>
+      </c>
+      <c r="K17" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="E18" t="str">
+        <v>输入:音频</v>
+      </c>
+      <c r="F18" t="str">
+        <v>gemini-3.5-flash</v>
+      </c>
+      <c r="G18" t="str">
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+      </c>
+      <c r="H18" t="str">
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+      </c>
+      <c r="I18" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J18" t="str">
+        <v>—</v>
+      </c>
+      <c r="K18" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="E19" t="str">
+        <v>输入&lt;=272K context</v>
+      </c>
+      <c r="F19" t="str">
+        <v>chat-latest</v>
+      </c>
+      <c r="G19" t="str">
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+      </c>
+      <c r="H19" t="str">
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+      </c>
+      <c r="I19" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J19" t="str">
+        <v>—</v>
+      </c>
+      <c r="K19" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="E20" t="str">
+        <v>输入&gt;272K context</v>
+      </c>
+      <c r="F20" t="str">
+        <v>chat-latest</v>
+      </c>
+      <c r="G20" t="str">
+        <v>入 $10 · 出 $45 · 缓 $1</v>
+      </c>
+      <c r="H20" t="str">
+        <v>入 $10 · 出 $45 · 缓 $1</v>
+      </c>
+      <c r="I20" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J20" t="str">
+        <v>—</v>
+      </c>
+      <c r="K20" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>gpt-4.1</v>
+      </c>
+      <c r="C21" t="str">
+        <v>GPT gpt-4.1</v>
+      </c>
+      <c r="D21" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E21" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F21" t="str">
+        <v>gpt-4.1</v>
+      </c>
+      <c r="G21" t="str">
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+      </c>
+      <c r="H21" t="str">
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+      </c>
+      <c r="I21" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J21" t="str">
+        <v>—</v>
+      </c>
+      <c r="K21" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>gpt-4o</v>
+      </c>
+      <c r="C22" t="str">
+        <v>GPT gpt-4o</v>
+      </c>
+      <c r="D22" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E22" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F22" t="str">
+        <v>gpt-4o</v>
+      </c>
+      <c r="G22" t="str">
+        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+      </c>
+      <c r="H22" t="str">
+        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+      </c>
+      <c r="I22" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J22" t="str">
+        <v>—</v>
+      </c>
+      <c r="K22" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>gpt-5</v>
+      </c>
+      <c r="C23" t="str">
+        <v>GPT gpt-5</v>
+      </c>
+      <c r="D23" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E23" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F23" t="str">
+        <v>gpt-5</v>
+      </c>
+      <c r="G23" t="str">
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+      </c>
+      <c r="H23" t="str">
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+      </c>
+      <c r="I23" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J23" t="str">
+        <v>—</v>
+      </c>
+      <c r="K23" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="E24" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F24" t="str">
+        <v>gpt-5-chat-latest</v>
+      </c>
+      <c r="G24" t="str">
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+      </c>
+      <c r="H24" t="str">
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+      </c>
+      <c r="I24" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J24" t="str">
+        <v>—</v>
+      </c>
+      <c r="K24" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>gpt-5-mini</v>
+      </c>
+      <c r="C25" t="str">
+        <v>GPT gpt-5-mini</v>
+      </c>
+      <c r="D25" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E25" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F25" t="str">
+        <v>gpt-5-mini</v>
+      </c>
+      <c r="G25" t="str">
+        <v>入 $0.25 · 出 $2 · 缓 $0.025</v>
+      </c>
+      <c r="H25" t="str">
+        <v>入 $0.25 · 出 $2 · 缓 $0.025</v>
+      </c>
+      <c r="I25" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J25" t="str">
+        <v>—</v>
+      </c>
+      <c r="K25" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>gpt-5-nano</v>
+      </c>
+      <c r="C26" t="str">
+        <v>GPT gpt-5-nano</v>
+      </c>
+      <c r="D26" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E26" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F26" t="str">
+        <v>gpt-5-nano</v>
+      </c>
+      <c r="G26" t="str">
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+      </c>
+      <c r="H26" t="str">
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+      </c>
+      <c r="I26" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J26" t="str">
+        <v>—</v>
+      </c>
+      <c r="K26" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>gpt-5.1</v>
+      </c>
+      <c r="C27" t="str">
+        <v>GPT gpt-5.1</v>
+      </c>
+      <c r="D27" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E27" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F27" t="str">
+        <v>gpt-5.1</v>
+      </c>
+      <c r="G27" t="str">
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+      </c>
+      <c r="H27" t="str">
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+      </c>
+      <c r="I27" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J27" t="str">
+        <v>—</v>
+      </c>
+      <c r="K27" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>gpt-5.1-chat</v>
+      </c>
+      <c r="C28" t="str">
+        <v>GPT gpt-5.1-chat-latest</v>
+      </c>
+      <c r="D28" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E28" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F28" t="str">
+        <v>gpt-5.1-chat-latest</v>
+      </c>
+      <c r="G28" t="str">
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+      </c>
+      <c r="H28" t="str">
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+      </c>
+      <c r="I28" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J28" t="str">
+        <v>—</v>
+      </c>
+      <c r="K28" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>gpt-5.2</v>
+      </c>
+      <c r="C29" t="str">
+        <v>GPT gpt-5.2</v>
+      </c>
+      <c r="D29" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E29" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F29" t="str">
+        <v>gpt-5.2</v>
+      </c>
+      <c r="G29" t="str">
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+      </c>
+      <c r="H29" t="str">
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+      </c>
+      <c r="I29" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J29" t="str">
+        <v>—</v>
+      </c>
+      <c r="K29" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="E30" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F30" t="str">
+        <v>gpt-5.2-chat-latest</v>
+      </c>
+      <c r="G30" t="str">
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+      </c>
+      <c r="H30" t="str">
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+      </c>
+      <c r="I30" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J30" t="str">
+        <v>—</v>
+      </c>
+      <c r="K30" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="E31" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F31" t="str">
+        <v>gpt-5.3-chat-latest</v>
+      </c>
+      <c r="G31" t="str">
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+      </c>
+      <c r="H31" t="str">
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+      </c>
+      <c r="I31" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J31" t="str">
+        <v>—</v>
+      </c>
+      <c r="K31" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>gpt-5.3-codex</v>
+      </c>
+      <c r="C32" t="str">
+        <v>GPT gpt-5.3-codex</v>
+      </c>
+      <c r="D32" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E32" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F32" t="str">
+        <v>gpt-5.3-codex</v>
+      </c>
+      <c r="G32" t="str">
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+      </c>
+      <c r="H32" t="str">
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+      </c>
+      <c r="I32" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J32" t="str">
+        <v>—</v>
+      </c>
+      <c r="K32" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>gpt-5.4</v>
+      </c>
+      <c r="C33" t="str">
+        <v>GPT gpt-5.4</v>
+      </c>
+      <c r="D33" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E33" t="str">
+        <v>输入&lt;=272K context</v>
+      </c>
+      <c r="F33" t="str">
+        <v>gpt-5.4</v>
+      </c>
+      <c r="G33" t="str">
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+      </c>
+      <c r="H33" t="str">
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+      </c>
+      <c r="I33" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J33" t="str">
+        <v>—</v>
+      </c>
+      <c r="K33" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="E34" t="str">
+        <v>输入&gt;272K context</v>
+      </c>
+      <c r="F34" t="str">
+        <v>gpt-5.4</v>
+      </c>
+      <c r="G34" t="str">
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+      </c>
+      <c r="H34" t="str">
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+      </c>
+      <c r="I34" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J34" t="str">
+        <v>—</v>
+      </c>
+      <c r="K34" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>gpt-5.4-mini</v>
+      </c>
+      <c r="C35" t="str">
+        <v>GPT gpt-5.4-mini</v>
+      </c>
+      <c r="D35" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E35" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F35" t="str">
+        <v>gpt-5.4-mini</v>
+      </c>
+      <c r="G35" t="str">
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+      </c>
+      <c r="H35" t="str">
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+      </c>
+      <c r="I35" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J35" t="str">
+        <v>—</v>
+      </c>
+      <c r="K35" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>gpt-5.4-nano</v>
+      </c>
+      <c r="C36" t="str">
+        <v>GPT gpt-5.4-nano</v>
+      </c>
+      <c r="D36" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E36" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F36" t="str">
+        <v>gpt-5.4-nano</v>
+      </c>
+      <c r="G36" t="str">
+        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
+      </c>
+      <c r="H36" t="str">
+        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
+      </c>
+      <c r="I36" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J36" t="str">
+        <v>—</v>
+      </c>
+      <c r="K36" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>gpt-5.4-pro</v>
+      </c>
+      <c r="C37" t="str">
+        <v>GPT gpt-5.4-pro</v>
+      </c>
+      <c r="D37" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E37" t="str">
+        <v>输入&lt;=272K context</v>
+      </c>
+      <c r="F37" t="str">
+        <v>gpt-5.4-pro</v>
+      </c>
+      <c r="G37" t="str">
+        <v>入 $30 · 出 $180</v>
+      </c>
+      <c r="H37" t="str">
+        <v>入 $30 · 出 $180</v>
+      </c>
+      <c r="I37" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J37" t="str">
+        <v>—</v>
+      </c>
+      <c r="K37" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="E38" t="str">
+        <v>输入&gt;272K context</v>
+      </c>
+      <c r="F38" t="str">
+        <v>gpt-5.4-pro</v>
+      </c>
+      <c r="G38" t="str">
+        <v>入 $60 · 出 $270</v>
+      </c>
+      <c r="H38" t="str">
+        <v>入 $60 · 出 $270</v>
+      </c>
+      <c r="I38" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J38" t="str">
+        <v>—</v>
+      </c>
+      <c r="K38" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>gpt-5.5</v>
+      </c>
+      <c r="C39" t="str">
+        <v>GPT gpt-5.5</v>
+      </c>
+      <c r="D39" t="str">
+        <v>网聚云联-云门户</v>
+      </c>
+      <c r="E39" t="str">
+        <v>输入&lt;=272K context</v>
+      </c>
+      <c r="F39" t="str">
+        <v>gpt-5.5</v>
+      </c>
+      <c r="G39" t="str">
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+      </c>
+      <c r="H39" t="str">
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+      </c>
+      <c r="I39" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J39" t="str">
+        <v>—</v>
+      </c>
+      <c r="K39" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="E40" t="str">
+        <v>输入&gt;272K context</v>
+      </c>
+      <c r="F40" t="str">
+        <v>gpt-5.5</v>
+      </c>
+      <c r="G40" t="str">
+        <v>入 $10 · 出 $45 · 缓 $1</v>
+      </c>
+      <c r="H40" t="str">
+        <v>入 $10 · 出 $45 · 缓 $1</v>
+      </c>
+      <c r="I40" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J40" t="str">
+        <v>—</v>
+      </c>
+      <c r="K40" t="str">
+        <v>—</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="33">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="D17:D20"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+  </mergeCells>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K40"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10946,10 +12336,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -11069,49 +12459,64 @@
         <v>—</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>—— 不一致超过10% · 档位明细 ——</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>网聚云联云门户</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>29</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="str">
+        <v>—</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="str">
+        <v>—</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>供应商</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Trinity ID</v>
-      </c>
-      <c r="C9" t="str">
-        <v>显示名</v>
-      </c>
-      <c r="D9" t="str">
-        <v>档位</v>
-      </c>
-      <c r="E9" t="str">
-        <v>最大上浮%</v>
-      </c>
-      <c r="F9" t="str">
-        <v>供应商vs官方</v>
+        <v>—— 不一致超过10% · 档位明细 ——</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TokenHub广州</v>
+        <v>供应商</v>
       </c>
       <c r="B10" t="str">
-        <v>deepseek-v4-flash</v>
+        <v>Trinity ID</v>
       </c>
       <c r="C10" t="str">
-        <v>DeepSeek V4 Flash</v>
+        <v>显示名</v>
       </c>
       <c r="D10" t="str">
-        <v>统一价</v>
+        <v>档位</v>
       </c>
       <c r="E10" t="str">
-        <v>+900%</v>
+        <v>最大上浮%</v>
       </c>
       <c r="F10" t="str">
-        <v>⚠ 缓+900%</v>
+        <v>供应商vs官方</v>
       </c>
     </row>
     <row r="11">
@@ -11119,39 +12524,39 @@
         <v>TokenHub广州</v>
       </c>
       <c r="B11" t="str">
-        <v>deepseek-v4-pro</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="C11" t="str">
-        <v>DeepSeek V4 Pro</v>
+        <v>DeepSeek V4 Flash</v>
       </c>
       <c r="D11" t="str">
         <v>统一价</v>
       </c>
       <c r="E11" t="str">
-        <v>+3900%</v>
+        <v>+900%</v>
       </c>
       <c r="F11" t="str">
-        <v>⚠ 入+300% 出+300% 缓+3900%</v>
+        <v>⚠ 缓+900%</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>百炼北京</v>
+        <v>TokenHub广州</v>
       </c>
       <c r="B12" t="str">
-        <v>deepseek-v4-flash</v>
+        <v>deepseek-v4-pro</v>
       </c>
       <c r="C12" t="str">
-        <v>DeepSeek V4 Flash</v>
+        <v>DeepSeek V4 Pro</v>
       </c>
       <c r="D12" t="str">
         <v>统一价</v>
       </c>
       <c r="E12" t="str">
-        <v>+900%</v>
+        <v>+3900%</v>
       </c>
       <c r="F12" t="str">
-        <v>⚠ 缓+900%</v>
+        <v>⚠ 入+300% 出+300% 缓+3900%</v>
       </c>
     </row>
     <row r="13">
@@ -11159,19 +12564,19 @@
         <v>百炼北京</v>
       </c>
       <c r="B13" t="str">
-        <v>deepseek-v4-pro</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="C13" t="str">
-        <v>DeepSeek V4 Pro</v>
+        <v>DeepSeek V4 Flash</v>
       </c>
       <c r="D13" t="str">
         <v>统一价</v>
       </c>
       <c r="E13" t="str">
-        <v>+9500%</v>
+        <v>+900%</v>
       </c>
       <c r="F13" t="str">
-        <v>⚠ 入+300% 出+300% 缓+9500%</v>
+        <v>⚠ 缓+900%</v>
       </c>
     </row>
     <row r="14">
@@ -11179,33 +12584,33 @@
         <v>百炼北京</v>
       </c>
       <c r="B14" t="str">
-        <v>qwen3.5-flash</v>
+        <v>deepseek-v4-pro</v>
       </c>
       <c r="C14" t="str">
-        <v>Qwen3.5 Flash</v>
+        <v>DeepSeek V4 Pro</v>
       </c>
       <c r="D14" t="str">
-        <v>0&lt;输入&lt;=128k</v>
+        <v>统一价</v>
       </c>
       <c r="E14" t="str">
-        <v>+100%</v>
+        <v>+9500%</v>
       </c>
       <c r="F14" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>⚠ 入+300% 出+300% 缓+9500%</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>百炼北京</v>
       </c>
       <c r="B15" t="str">
-        <v/>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>Qwen3.5 Flash</v>
       </c>
       <c r="D15" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>0&lt;输入&lt;=128k</v>
       </c>
       <c r="E15" t="str">
         <v>+100%</v>
@@ -11225,7 +12630,7 @@
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E16" t="str">
         <v>+100%</v>
@@ -11236,16 +12641,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>百炼北京</v>
+        <v/>
       </c>
       <c r="B17" t="str">
-        <v>qwen3.5-plus</v>
+        <v/>
       </c>
       <c r="C17" t="str">
-        <v>Qwen3.5 Plus</v>
+        <v/>
       </c>
       <c r="D17" t="str">
-        <v>输入&lt;=128k</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="E17" t="str">
         <v>+100%</v>
@@ -11256,16 +12661,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>百炼北京</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>Qwen3.5 Plus</v>
       </c>
       <c r="D18" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>输入&lt;=128k</v>
       </c>
       <c r="E18" t="str">
         <v>+100%</v>
@@ -11285,7 +12690,7 @@
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E19" t="str">
         <v>+100%</v>
@@ -11294,19 +12699,39 @@
         <v>⚠ 缓+100%</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>生成时间：2026-07-02T08:55:34Z</v>
+    <row r="20">
+      <c r="A20" t="str">
+        <v/>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>256k&lt;输入&lt;=1M</v>
+      </c>
+      <c r="E20" t="str">
+        <v>+100%</v>
+      </c>
+      <c r="F20" t="str">
+        <v>⚠ 缓+100%</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
+        <v>生成时间：2026-07-02T12:38:43Z</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
         <v>说明：一致=与厂商官方价偏差&lt;0.5%（含 FX 7.5/7.25/6.5 最佳匹配）；不一致上浮=供应商高于官方的偏差%；模型级不一致=任一档位不一致</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/pricing/output/trinity-pricing-text.xlsx
+++ b/pricing/output/trinity-pricing-text.xlsx
@@ -405,144 +405,150 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q88"/>
+  <dimension ref="A1:R110"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>原厂 modelId</v>
+      </c>
+      <c r="B1" t="str">
         <v>Trinity ID</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>显示名</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>厂商</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>档位</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>厂商官方价</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>AIGC国际</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>TokenHub</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>OpenRouter</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>线上刊例</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>刊例vs官方_入</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>刊例vs官方_出</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>刊例vs官方_缓</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>AIGCvs官方</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>TokenHub vs官方</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>ORvs官方</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>刊例结论</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>备注</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>claude-fable-5</v>
+        <v>claude-opus-4-6</v>
       </c>
       <c r="B2" t="str">
-        <v>Claude Fable 5</v>
+        <v>claude-opus-4-6</v>
       </c>
       <c r="C2" t="str">
+        <v>Claude Opus 4.6</v>
+      </c>
+      <c r="D2" t="str">
         <v>Anthropic</v>
       </c>
-      <c r="D2" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E2" t="str">
-        <v>—</v>
+        <v>标准价</v>
       </c>
       <c r="F2" t="str">
-        <v>—</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="G2" t="str">
-        <v>—</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="H2" t="str">
         <v>—</v>
       </c>
       <c r="I2" t="str">
-        <v>入 $10 · 出 $50 · 缓 $1</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="J2" t="str">
-        <v>—</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="K2" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L2" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M2" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N2" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O2" t="str">
         <v>—</v>
       </c>
       <c r="P2" t="str">
-        <v>入— 出— 缓—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q2" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>claude-opus-4-6</v>
+        <v>claude-opus-4-7</v>
       </c>
       <c r="B3" t="str">
-        <v>Claude Opus 4.6</v>
+        <v>claude-opus-4-7</v>
       </c>
       <c r="C3" t="str">
+        <v>Claude Opus 4.7</v>
+      </c>
+      <c r="D3" t="str">
         <v>Anthropic</v>
       </c>
-      <c r="D3" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E3" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>标准价</v>
       </c>
       <c r="F3" t="str">
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="G3" t="str">
-        <v>—</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="H3" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="I3" t="str">
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="J3" t="str">
-        <v>0%</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="K3" t="str">
         <v>0%</v>
@@ -551,51 +557,54 @@
         <v>0%</v>
       </c>
       <c r="M3" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N3" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N3" t="str">
-        <v>—</v>
-      </c>
       <c r="O3" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P3" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q3" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>claude-opus-4-7</v>
+        <v>claude-opus-4-8</v>
       </c>
       <c r="B4" t="str">
-        <v>Claude Opus 4.7</v>
+        <v>claude-opus-4-8</v>
       </c>
       <c r="C4" t="str">
+        <v>Claude Opus 4.8</v>
+      </c>
+      <c r="D4" t="str">
         <v>Anthropic</v>
       </c>
-      <c r="D4" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E4" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>标准价</v>
       </c>
       <c r="F4" t="str">
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="G4" t="str">
-        <v>—</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="H4" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="I4" t="str">
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="J4" t="str">
-        <v>0%</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="K4" t="str">
         <v>0%</v>
@@ -604,51 +613,54 @@
         <v>0%</v>
       </c>
       <c r="M4" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N4" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N4" t="str">
-        <v>—</v>
-      </c>
       <c r="O4" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P4" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q4" t="str">
-        <v/>
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R4" t="str">
+        <v>目录名 cd-opus-4.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>claude-opus-4-8</v>
+        <v>claude-sonnet-4-6</v>
       </c>
       <c r="B5" t="str">
-        <v>Claude Opus 4.8</v>
+        <v>claude-sonnet-4-6</v>
       </c>
       <c r="C5" t="str">
+        <v>Claude Sonnet 4.6</v>
+      </c>
+      <c r="D5" t="str">
         <v>Anthropic</v>
       </c>
-      <c r="D5" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E5" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>标准价</v>
       </c>
       <c r="F5" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>入 $3 · 出 $15 · 缓 $0.3</v>
       </c>
       <c r="G5" t="str">
-        <v>—</v>
+        <v>入 $3 · 出 $15 · 缓 $0.3</v>
       </c>
       <c r="H5" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="I5" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>入 $3 · 出 $15 · 缓 $0.3</v>
       </c>
       <c r="J5" t="str">
-        <v>0%</v>
+        <v>入 $3 · 出 $15 · 缓 $0.3</v>
       </c>
       <c r="K5" t="str">
         <v>0%</v>
@@ -657,51 +669,54 @@
         <v>0%</v>
       </c>
       <c r="M5" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N5" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N5" t="str">
-        <v>—</v>
-      </c>
       <c r="O5" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P5" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q5" t="str">
-        <v>目录名 cd-opus-4.8</v>
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>claude-sonnet-4-6</v>
+        <v>deepseek-v3.2</v>
       </c>
       <c r="B6" t="str">
-        <v>Claude Sonnet 4.6</v>
+        <v>deepseek-v3.2</v>
       </c>
       <c r="C6" t="str">
-        <v>Anthropic</v>
+        <v>DeepSeek V3.2</v>
       </c>
       <c r="D6" t="str">
-        <v>统一价</v>
+        <v>DeepSeek</v>
       </c>
       <c r="E6" t="str">
-        <v>入 $3 · 出 $15 · 缓 $0.3</v>
+        <v>标准价</v>
       </c>
       <c r="F6" t="str">
-        <v>入 $3 · 出 $15 · 缓 $0.3</v>
+        <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
       </c>
       <c r="G6" t="str">
-        <v>—</v>
+        <v>入 $0.308 · 出 $0.462 · 缓 $0.062</v>
       </c>
       <c r="H6" t="str">
-        <v>入 $3 · 出 $15 · 缓 $0.3</v>
+        <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
       </c>
       <c r="I6" t="str">
-        <v>入 $3 · 出 $15 · 缓 $0.3</v>
+        <v>入 $0.2288 · 出 $0.3432 · 缓 $0.02288</v>
       </c>
       <c r="J6" t="str">
-        <v>0%</v>
+        <v>入 $0.307692 · 出 $0.461538 · 缓 $0.061538</v>
       </c>
       <c r="K6" t="str">
         <v>0%</v>
@@ -710,104 +725,110 @@
         <v>0%</v>
       </c>
       <c r="M6" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="N6" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓⚠+0.7%</v>
       </c>
       <c r="O6" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P6" t="str">
+        <v>入⚠-25.6% 出⚠-25.6% 缓⚠-62.8%</v>
+      </c>
+      <c r="Q6" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q6" t="str">
-        <v/>
+      <c r="R6" t="str">
+        <v>v3.2 价目见百炼模型定价；v4 见 DeepSeek API 文档</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>claude-sonnet-5</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="B7" t="str">
-        <v>Claude Sonnet 5</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="C7" t="str">
-        <v>Anthropic</v>
+        <v>DeepSeek V4 Flash Direct</v>
       </c>
       <c r="D7" t="str">
-        <v>统一价</v>
+        <v>DeepSeek</v>
       </c>
       <c r="E7" t="str">
-        <v>—</v>
+        <v>标准价</v>
       </c>
       <c r="F7" t="str">
-        <v>—</v>
+        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="G7" t="str">
-        <v>—</v>
+        <v>入 $0.154 · 出 $0.308 · 缓 $0.003</v>
       </c>
       <c r="H7" t="str">
-        <v>—</v>
+        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.2</v>
       </c>
       <c r="I7" t="str">
-        <v>入 $2 · 出 $10 · 缓 $0.2</v>
+        <v>入 $0.098 · 出 $0.196 · 缓 $0.02</v>
       </c>
       <c r="J7" t="str">
-        <v>—</v>
+        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
       </c>
       <c r="K7" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L7" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M7" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N7" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓⚠-2.5%</v>
       </c>
       <c r="O7" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓⚠+900%</v>
       </c>
       <c r="P7" t="str">
-        <v>入— 出— 缓—</v>
+        <v>入⚠-36.3% 出⚠-36.3% 缓⚠+550%</v>
       </c>
       <c r="Q7" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>deepseek-v3.2</v>
+        <v>deepseek-v4-pro</v>
       </c>
       <c r="B8" t="str">
-        <v>DeepSeek V3.2</v>
+        <v>deepseek-v4-pro</v>
       </c>
       <c r="C8" t="str">
+        <v>DeepSeek V4 Pro Direct</v>
+      </c>
+      <c r="D8" t="str">
         <v>DeepSeek</v>
       </c>
-      <c r="D8" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E8" t="str">
-        <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
+        <v>标准价</v>
       </c>
       <c r="F8" t="str">
-        <v>入 $0.308 · 出 $0.462 · 缓 $0.062</v>
+        <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
       </c>
       <c r="G8" t="str">
-        <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
+        <v>入 $0.462 · 出 $0.923 · 缓 $0.004</v>
       </c>
       <c r="H8" t="str">
-        <v>入 $0.2288 · 出 $0.3432 · 缓 $0.02288</v>
+        <v>入 ¥12 · 出 ¥24 · 缓 ¥1</v>
       </c>
       <c r="I8" t="str">
-        <v>入 $0.307692 · 出 $0.461538 · 缓 $0.061538</v>
+        <v>入 $0.435 · 出 $0.87 · 缓 $0.003625</v>
       </c>
       <c r="J8" t="str">
-        <v>0%</v>
+        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
       </c>
       <c r="K8" t="str">
         <v>0%</v>
@@ -816,51 +837,54 @@
         <v>0%</v>
       </c>
       <c r="M8" t="str">
-        <v>入✅ 出✅ 缓⚠+0.7%</v>
+        <v>0%</v>
       </c>
       <c r="N8" t="str">
+        <v>入✅ 出✅ 缓⚠+4%</v>
+      </c>
+      <c r="O8" t="str">
+        <v>入⚠+300% 出⚠+300% 缓⚠+3900%</v>
+      </c>
+      <c r="P8" t="str">
+        <v>入⚠-5.8% 出⚠-5.8% 缓⚠-5.7%</v>
+      </c>
+      <c r="Q8" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O8" t="str">
-        <v>入⚠-25.6% 出⚠-25.6% 缓⚠-62.8%</v>
-      </c>
-      <c r="P8" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>v3.2 价目见百炼模型定价；v4 见 DeepSeek API 文档</v>
+      <c r="R8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>deepseek-v4-flash</v>
+        <v>gemini-2.5-flash</v>
       </c>
       <c r="B9" t="str">
-        <v>DeepSeek V4 Flash Direct</v>
+        <v>gemini-2.5-flash</v>
       </c>
       <c r="C9" t="str">
-        <v>DeepSeek</v>
+        <v>Gemini 2.5 Flash</v>
       </c>
       <c r="D9" t="str">
-        <v>统一价</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E9" t="str">
-        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
+        <v>输入:文本/图片/视频</v>
       </c>
       <c r="F9" t="str">
-        <v>入 $0.154 · 出 $0.308 · 缓 $0.003</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="G9" t="str">
-        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.2</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="H9" t="str">
-        <v>入 $0.098 · 出 $0.196 · 缓 $0.02</v>
+        <v>—</v>
       </c>
       <c r="I9" t="str">
-        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="J9" t="str">
-        <v>0%</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="K9" t="str">
         <v>0%</v>
@@ -869,104 +893,98 @@
         <v>0%</v>
       </c>
       <c r="M9" t="str">
-        <v>入✅ 出✅ 缓⚠-2.5%</v>
+        <v>0%</v>
       </c>
       <c r="N9" t="str">
-        <v>入✅ 出✅ 缓⚠+900%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O9" t="str">
-        <v>入⚠-36.3% 出⚠-36.3% 缓⚠+550%</v>
+        <v>—</v>
       </c>
       <c r="P9" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q9" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>deepseek-v4-pro</v>
-      </c>
-      <c r="B10" t="str">
-        <v>DeepSeek V4 Pro Direct</v>
-      </c>
-      <c r="C10" t="str">
-        <v>DeepSeek</v>
-      </c>
-      <c r="D10" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E10" t="str">
-        <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
+        <v>输入:音频</v>
       </c>
       <c r="F10" t="str">
-        <v>入 $0.462 · 出 $0.923 · 缓 $0.004</v>
+        <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
       </c>
       <c r="G10" t="str">
-        <v>入 ¥12 · 出 ¥24 · 缓 ¥1</v>
+        <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
       </c>
       <c r="H10" t="str">
-        <v>入 $0.435 · 出 $0.87 · 缓 $0.003625</v>
+        <v>—</v>
       </c>
       <c r="I10" t="str">
-        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="J10" t="str">
-        <v>0%</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="K10" t="str">
-        <v>0%</v>
+        <v>-70%</v>
       </c>
       <c r="L10" t="str">
         <v>0%</v>
       </c>
       <c r="M10" t="str">
-        <v>入✅ 出✅ 缓⚠+4%</v>
+        <v>-70%</v>
       </c>
       <c r="N10" t="str">
-        <v>入⚠+300% 出⚠+300% 缓⚠+3900%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O10" t="str">
-        <v>入⚠-5.8% 出⚠-5.8% 缓⚠-5.7%</v>
+        <v>—</v>
       </c>
       <c r="P10" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠-70% 出✅ 缓⚠-70%</v>
       </c>
       <c r="Q10" t="str">
+        <v>ℹ 线上音频未单独定价</v>
+      </c>
+      <c r="R10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>gemini-2.5-flash</v>
+        <v>gemini-2.5-flash-lite</v>
       </c>
       <c r="B11" t="str">
-        <v>Gemini 2.5 Flash</v>
+        <v>gemini-2.5-flash-lite</v>
       </c>
       <c r="C11" t="str">
+        <v>Gemini 2.5 Flash Lite</v>
+      </c>
+      <c r="D11" t="str">
         <v>Google DeepMind</v>
       </c>
-      <c r="D11" t="str">
-        <v>输入：文本、图片、视频</v>
-      </c>
       <c r="E11" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>标准价</v>
       </c>
       <c r="F11" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="G11" t="str">
-        <v>—</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="H11" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>—</v>
       </c>
       <c r="I11" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>入 $0.09999999999999999 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
       <c r="J11" t="str">
-        <v>0%</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="K11" t="str">
         <v>0%</v>
@@ -975,95 +993,110 @@
         <v>0%</v>
       </c>
       <c r="M11" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N11" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N11" t="str">
-        <v>—</v>
-      </c>
       <c r="O11" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P11" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q11" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="str">
+        <v>gemini-2.5-flash-lite-preview</v>
+      </c>
+      <c r="B12" t="str">
+        <v>gemini-2.5-flash-lite-preview</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Gemini 2.5 Flash Lite Preview</v>
+      </c>
       <c r="D12" t="str">
-        <v>输入：音频</v>
+        <v>Google DeepMind</v>
       </c>
       <c r="E12" t="str">
-        <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
+        <v>标准价</v>
       </c>
       <c r="F12" t="str">
-        <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="G12" t="str">
-        <v>—</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="H12" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>—</v>
       </c>
       <c r="I12" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>入 $0.09999999999999999 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
       <c r="J12" t="str">
-        <v>-70%</v>
+        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="K12" t="str">
         <v>0%</v>
       </c>
       <c r="L12" t="str">
-        <v>-70%</v>
+        <v>0%</v>
       </c>
       <c r="M12" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N12" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N12" t="str">
-        <v>—</v>
-      </c>
       <c r="O12" t="str">
-        <v>入⚠-70% 出✅ 缓⚠-70%</v>
+        <v>—</v>
       </c>
       <c r="P12" t="str">
-        <v>ℹ 线上音频未单独定价</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q12" t="str">
-        <v/>
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R12" t="str">
+        <v>preview 别名，价目同 gemini-2.5-flash-lite</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>gemini-2.5-flash-lite</v>
+        <v>gemini-2.5-pro</v>
       </c>
       <c r="B13" t="str">
-        <v>Gemini 2.5 Flash Lite</v>
+        <v>gemini-2.5-pro</v>
       </c>
       <c r="C13" t="str">
+        <v>Gemini 2.5 Pro</v>
+      </c>
+      <c r="D13" t="str">
         <v>Google DeepMind</v>
       </c>
-      <c r="D13" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E13" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+        <v>输入&lt;=20万个token</v>
       </c>
       <c r="F13" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G13" t="str">
-        <v>—</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="H13" t="str">
-        <v>入 $0.09999999999999999 · 出 $0.39999999999999997 · 缓 $0.01</v>
+        <v>—</v>
       </c>
       <c r="I13" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="J13" t="str">
-        <v>0%</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="K13" t="str">
         <v>0%</v>
@@ -1072,51 +1105,42 @@
         <v>0%</v>
       </c>
       <c r="M13" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N13" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N13" t="str">
-        <v>—</v>
-      </c>
       <c r="O13" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P13" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q13" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>gemini-2.5-flash-lite-preview</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Gemini 2.5 Flash Lite Preview</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Google DeepMind</v>
-      </c>
-      <c r="D14" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E14" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+        <v>输入&gt;20万个token</v>
       </c>
       <c r="F14" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="G14" t="str">
-        <v>—</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="H14" t="str">
-        <v>入 $0.09999999999999999 · 出 $0.39999999999999997 · 缓 $0.01</v>
+        <v>—</v>
       </c>
       <c r="I14" t="str">
-        <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="J14" t="str">
-        <v>0%</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="K14" t="str">
         <v>0%</v>
@@ -1125,51 +1149,54 @@
         <v>0%</v>
       </c>
       <c r="M14" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N14" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N14" t="str">
-        <v>—</v>
-      </c>
       <c r="O14" t="str">
+        <v>—</v>
+      </c>
+      <c r="P14" t="str">
+        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
+      </c>
+      <c r="Q14" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="P14" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="Q14" t="str">
-        <v>preview 别名，价目同 gemini-2.5-flash-lite</v>
+      <c r="R14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>gemini-2.5-pro</v>
+        <v>gemini-3-flash-preview</v>
       </c>
       <c r="B15" t="str">
-        <v>Gemini 2.5 Pro</v>
+        <v>gemini-3-flash-preview</v>
       </c>
       <c r="C15" t="str">
+        <v>Gemini 3 Flash Preview</v>
+      </c>
+      <c r="D15" t="str">
         <v>Google DeepMind</v>
       </c>
-      <c r="D15" t="str">
-        <v>输入≤20万个token</v>
-      </c>
       <c r="E15" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>输入:文本/图片/视频</v>
       </c>
       <c r="F15" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
       <c r="G15" t="str">
-        <v>—</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
       <c r="H15" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>—</v>
       </c>
       <c r="I15" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.049999999999999996</v>
       </c>
       <c r="J15" t="str">
-        <v>0%</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
       <c r="K15" t="str">
         <v>0%</v>
@@ -1178,95 +1205,98 @@
         <v>0%</v>
       </c>
       <c r="M15" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N15" t="str">
-        <v>—</v>
-      </c>
       <c r="O15" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q15" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="D16" t="str">
-        <v>输入&gt;20万个token</v>
-      </c>
       <c r="E16" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>输入:音频</v>
       </c>
       <c r="F16" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $1 · 出 $3 · 缓 $0.1</v>
       </c>
       <c r="G16" t="str">
-        <v>—</v>
+        <v>入 $1 · 出 $3 · 缓 $0.1</v>
       </c>
       <c r="H16" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>—</v>
       </c>
       <c r="I16" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.049999999999999996</v>
       </c>
       <c r="J16" t="str">
-        <v>0%</v>
+        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
       <c r="K16" t="str">
-        <v>0%</v>
+        <v>-50%</v>
       </c>
       <c r="L16" t="str">
         <v>0%</v>
       </c>
       <c r="M16" t="str">
+        <v>-50%</v>
+      </c>
+      <c r="N16" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N16" t="str">
-        <v>—</v>
-      </c>
       <c r="O16" t="str">
-        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
+        <v>—</v>
       </c>
       <c r="P16" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠-50% 出✅ 缓⚠-50%</v>
       </c>
       <c r="Q16" t="str">
+        <v>ℹ 线上音频未单独定价</v>
+      </c>
+      <c r="R16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>gemini-3-flash-preview</v>
+        <v>gemini-3.1-flash-lite</v>
       </c>
       <c r="B17" t="str">
-        <v>Gemini 3 Flash Preview</v>
+        <v>gemini-3.1-flash-lite</v>
       </c>
       <c r="C17" t="str">
+        <v>Gemini 3.1 Flash Lite</v>
+      </c>
+      <c r="D17" t="str">
         <v>Google DeepMind</v>
       </c>
-      <c r="D17" t="str">
-        <v>输入：文本、图片、视频</v>
-      </c>
       <c r="E17" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
+        <v>输入:文本/图片/视频</v>
       </c>
       <c r="F17" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
       <c r="G17" t="str">
-        <v>—</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
       <c r="H17" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.049999999999999996</v>
+        <v>—</v>
       </c>
       <c r="I17" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
       </c>
       <c r="J17" t="str">
-        <v>0%</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
       <c r="K17" t="str">
         <v>0%</v>
@@ -1275,95 +1305,98 @@
         <v>0%</v>
       </c>
       <c r="M17" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N17" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N17" t="str">
-        <v>—</v>
-      </c>
       <c r="O17" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P17" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q17" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="D18" t="str">
-        <v>输入：音频</v>
-      </c>
       <c r="E18" t="str">
-        <v>入 $1 · 出 $3 · 缓 $0.1</v>
+        <v>输入:音频</v>
       </c>
       <c r="F18" t="str">
-        <v>入 $1 · 出 $3 · 缓 $0.1</v>
+        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
       </c>
       <c r="G18" t="str">
-        <v>—</v>
+        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
       </c>
       <c r="H18" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.049999999999999996</v>
+        <v>—</v>
       </c>
       <c r="I18" t="str">
-        <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
       </c>
       <c r="J18" t="str">
+        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+      </c>
+      <c r="K18" t="str">
         <v>-50%</v>
       </c>
-      <c r="K18" t="str">
-        <v>0%</v>
-      </c>
       <c r="L18" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M18" t="str">
         <v>-50%</v>
       </c>
-      <c r="M18" t="str">
+      <c r="N18" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N18" t="str">
-        <v>—</v>
-      </c>
       <c r="O18" t="str">
+        <v>—</v>
+      </c>
+      <c r="P18" t="str">
         <v>入⚠-50% 出✅ 缓⚠-50%</v>
       </c>
-      <c r="P18" t="str">
+      <c r="Q18" t="str">
         <v>ℹ 线上音频未单独定价</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="R18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>gemini-3.1-flash-lite</v>
+        <v>gemini-3.1-pro-preview</v>
       </c>
       <c r="B19" t="str">
-        <v>Gemini 3.1 Flash Lite</v>
+        <v>gemini-3.1-pro-preview</v>
       </c>
       <c r="C19" t="str">
+        <v>Gemini 3.1 Pro Preview</v>
+      </c>
+      <c r="D19" t="str">
         <v>Google DeepMind</v>
       </c>
-      <c r="D19" t="str">
-        <v>输入：文本、图片、视频</v>
-      </c>
       <c r="E19" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+        <v>输入&lt;=20万个token</v>
       </c>
       <c r="F19" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+        <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
       <c r="G19" t="str">
-        <v>—</v>
+        <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
       <c r="H19" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I19" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+        <v>入 $2 · 出 $12 · 缓 $0.19999999999999998</v>
       </c>
       <c r="J19" t="str">
-        <v>0%</v>
+        <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
       <c r="K19" t="str">
         <v>0%</v>
@@ -1372,95 +1405,98 @@
         <v>0%</v>
       </c>
       <c r="M19" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N19" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N19" t="str">
-        <v>—</v>
-      </c>
       <c r="O19" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P19" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q19" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="D20" t="str">
-        <v>输入：音频</v>
-      </c>
       <c r="E20" t="str">
-        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
+        <v>输入&gt;20万个token</v>
       </c>
       <c r="F20" t="str">
-        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
+        <v>入 $4 · 出 $18 · 缓 $0.4</v>
       </c>
       <c r="G20" t="str">
-        <v>—</v>
+        <v>入 $4 · 出 $18 · 缓 $0.4</v>
       </c>
       <c r="H20" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I20" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+        <v>入 $2 · 出 $12 · 缓 $0.19999999999999998</v>
       </c>
       <c r="J20" t="str">
-        <v>-50%</v>
+        <v>入 $4 · 出 $18 · 缓 $0.4</v>
       </c>
       <c r="K20" t="str">
         <v>0%</v>
       </c>
       <c r="L20" t="str">
-        <v>-50%</v>
+        <v>0%</v>
       </c>
       <c r="M20" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N20" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N20" t="str">
-        <v>—</v>
-      </c>
       <c r="O20" t="str">
-        <v>入⚠-50% 出✅ 缓⚠-50%</v>
+        <v>—</v>
       </c>
       <c r="P20" t="str">
-        <v>ℹ 线上音频未单独定价</v>
+        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
       <c r="Q20" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>gemini-3.1-flash-lite-preview</v>
+        <v>gemini-3.5-flash</v>
       </c>
       <c r="B21" t="str">
-        <v>Gemini 3.1 Flash Lite Preview</v>
+        <v>gemini-3.5-flash</v>
       </c>
       <c r="C21" t="str">
+        <v>Gemini 3.5 Flash</v>
+      </c>
+      <c r="D21" t="str">
         <v>Google DeepMind</v>
       </c>
-      <c r="D21" t="str">
-        <v>输入：文本、图片、视频</v>
-      </c>
       <c r="E21" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+        <v>输入:文本/图片/视频</v>
       </c>
       <c r="F21" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="G21" t="str">
-        <v>—</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="H21" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I21" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="J21" t="str">
-        <v>0%</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="K21" t="str">
         <v>0%</v>
@@ -1469,289 +1505,322 @@
         <v>0%</v>
       </c>
       <c r="M21" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N21" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N21" t="str">
-        <v>—</v>
-      </c>
       <c r="O21" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P21" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q21" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="D22" t="str">
-        <v>输入：音频</v>
-      </c>
       <c r="E22" t="str">
-        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
+        <v>输入:音频</v>
       </c>
       <c r="F22" t="str">
-        <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="G22" t="str">
-        <v>—</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="H22" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I22" t="str">
-        <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="J22" t="str">
-        <v>-50%</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="K22" t="str">
         <v>0%</v>
       </c>
       <c r="L22" t="str">
-        <v>-50%</v>
+        <v>0%</v>
       </c>
       <c r="M22" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N22" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N22" t="str">
-        <v>—</v>
-      </c>
       <c r="O22" t="str">
-        <v>入⚠-50% 出✅ 缓⚠-50%</v>
+        <v>—</v>
       </c>
       <c r="P22" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="Q22" t="str">
         <v>ℹ 线上音频未单独定价</v>
       </c>
-      <c r="Q22" t="str">
+      <c r="R22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>gemini-3.1-pro-preview</v>
+        <v>grok-4.3</v>
       </c>
       <c r="B23" t="str">
-        <v>Gemini 3.1 Pro Preview</v>
+        <v>grok-4.3</v>
       </c>
       <c r="C23" t="str">
-        <v>Google DeepMind</v>
+        <v>GK</v>
       </c>
       <c r="D23" t="str">
-        <v>输入≤20万个token</v>
+        <v>GK</v>
       </c>
       <c r="E23" t="str">
-        <v>入 $2 · 出 $12 · 缓 $0.2</v>
+        <v>标准价</v>
       </c>
       <c r="F23" t="str">
-        <v>入 $2 · 出 $12 · 缓 $0.2</v>
+        <v>入 $1.25 · 出 $2.5 · 缓 $0.2</v>
       </c>
       <c r="G23" t="str">
         <v>—</v>
       </c>
       <c r="H23" t="str">
-        <v>入 $2 · 出 $12 · 缓 $0.19999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I23" t="str">
-        <v>入 $2 · 出 $12 · 缓 $0.2</v>
+        <v>—</v>
       </c>
       <c r="J23" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K23" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L23" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M23" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N23" t="str">
         <v>—</v>
       </c>
       <c r="O23" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P23" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="Q23" t="str">
-        <v/>
+        <v>— 未上架</v>
+      </c>
+      <c r="R23" t="str">
+        <v>目录名 gk-4.3</v>
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="str">
+        <v>grok-4.20-0309-non-reasoning</v>
+      </c>
+      <c r="B24" t="str">
+        <v>—</v>
+      </c>
+      <c r="C24" t="str">
+        <v>GK</v>
+      </c>
       <c r="D24" t="str">
-        <v>输入&gt;20万个token</v>
+        <v>GK</v>
       </c>
       <c r="E24" t="str">
-        <v>入 $4 · 出 $18 · 缓 $0.4</v>
+        <v>标准价</v>
       </c>
       <c r="F24" t="str">
-        <v>入 $4 · 出 $18 · 缓 $0.4</v>
+        <v>入 $1.25 · 出 $2.5 · 缓 $0.2</v>
       </c>
       <c r="G24" t="str">
         <v>—</v>
       </c>
       <c r="H24" t="str">
-        <v>入 $2 · 出 $12 · 缓 $0.19999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I24" t="str">
-        <v>入 $4 · 出 $18 · 缓 $0.4</v>
+        <v>—</v>
       </c>
       <c r="J24" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K24" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L24" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M24" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N24" t="str">
         <v>—</v>
       </c>
       <c r="O24" t="str">
-        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
+        <v>—</v>
       </c>
       <c r="P24" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="Q24" t="str">
-        <v/>
+        <v>— 未接入</v>
+      </c>
+      <c r="R24" t="str">
+        <v>目录名 gk-4-20-non-reasoning</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>gemini-3.5-flash</v>
+        <v>grok-4.20-0309-reasoning</v>
       </c>
       <c r="B25" t="str">
-        <v>Gemini 3.5 Flash</v>
+        <v>—</v>
       </c>
       <c r="C25" t="str">
-        <v>Google DeepMind</v>
+        <v>GK</v>
       </c>
       <c r="D25" t="str">
-        <v>输入：文本、图片、视频</v>
+        <v>GK</v>
       </c>
       <c r="E25" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>标准价</v>
       </c>
       <c r="F25" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>入 $1.25 · 出 $2.5 · 缓 $0.2</v>
       </c>
       <c r="G25" t="str">
         <v>—</v>
       </c>
       <c r="H25" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>—</v>
       </c>
       <c r="I25" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>—</v>
       </c>
       <c r="J25" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K25" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L25" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M25" t="str">
+        <v>—</v>
+      </c>
+      <c r="N25" t="str">
+        <v>—</v>
+      </c>
+      <c r="O25" t="str">
+        <v>—</v>
+      </c>
+      <c r="P25" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R25" t="str">
+        <v>目录名 gk-4-20-reasoning</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>gpt-4.1</v>
+      </c>
+      <c r="B26" t="str">
+        <v>gpt-4.1</v>
+      </c>
+      <c r="C26" t="str">
+        <v>GPT-4.1</v>
+      </c>
+      <c r="D26" t="str">
+        <v>OpenAI</v>
+      </c>
+      <c r="E26" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F26" t="str">
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+      </c>
+      <c r="G26" t="str">
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+      </c>
+      <c r="H26" t="str">
+        <v>—</v>
+      </c>
+      <c r="I26" t="str">
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+      </c>
+      <c r="J26" t="str">
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+      </c>
+      <c r="K26" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L26" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M26" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N26" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N25" t="str">
-        <v>—</v>
-      </c>
-      <c r="O25" t="str">
+      <c r="O26" t="str">
+        <v>—</v>
+      </c>
+      <c r="P26" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="P25" t="str">
+      <c r="Q26" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="D26" t="str">
-        <v>输入：音频</v>
-      </c>
-      <c r="E26" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
-      </c>
-      <c r="F26" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
-      </c>
-      <c r="G26" t="str">
-        <v>—</v>
-      </c>
-      <c r="H26" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
-      </c>
-      <c r="I26" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
-      </c>
-      <c r="J26" t="str">
-        <v>0%</v>
-      </c>
-      <c r="K26" t="str">
-        <v>0%</v>
-      </c>
-      <c r="L26" t="str">
-        <v>0%</v>
-      </c>
-      <c r="M26" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="N26" t="str">
-        <v>—</v>
-      </c>
-      <c r="O26" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="P26" t="str">
-        <v>ℹ 线上音频未单独定价</v>
-      </c>
-      <c r="Q26" t="str">
+      <c r="R26" t="str">
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>glm-5</v>
+        <v>gpt-4o</v>
       </c>
       <c r="B27" t="str">
-        <v>GLM 5</v>
+        <v>gpt-4o</v>
       </c>
       <c r="C27" t="str">
-        <v>Zhipu</v>
+        <v>GPT-4o</v>
       </c>
       <c r="D27" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>OpenAI</v>
       </c>
       <c r="E27" t="str">
-        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+        <v>标准价</v>
       </c>
       <c r="F27" t="str">
-        <v>入 $0.616 · 出 $2.772 · 缓 $0.154</v>
+        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="G27" t="str">
-        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="H27" t="str">
-        <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
+        <v>—</v>
       </c>
       <c r="I27" t="str">
-        <v>入 $0.615385 · 出 $2.769231 · 缓 $0.153846</v>
+        <v>入 $2.5 · 出 $10</v>
       </c>
       <c r="J27" t="str">
-        <v>0%</v>
+        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="K27" t="str">
         <v>0%</v>
@@ -1760,42 +1829,54 @@
         <v>0%</v>
       </c>
       <c r="M27" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="N27" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O27" t="str">
-        <v>入⚠-2.5% 出⚠-30.7% 缓⚠-22%</v>
+        <v>—</v>
       </c>
       <c r="P27" t="str">
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="Q27" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q27" t="str">
+      <c r="R27" t="str">
         <v/>
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="str">
+        <v>gpt-5</v>
+      </c>
+      <c r="B28" t="str">
+        <v>gpt-5</v>
+      </c>
+      <c r="C28" t="str">
+        <v>GPT-5</v>
+      </c>
       <c r="D28" t="str">
-        <v>32k&lt;=输入</v>
+        <v>OpenAI</v>
       </c>
       <c r="E28" t="str">
-        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+        <v>标准价</v>
       </c>
       <c r="F28" t="str">
-        <v>入 $0.924 · 出 $3.388 · 缓 $0.231</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G28" t="str">
-        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="H28" t="str">
-        <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
+        <v>—</v>
       </c>
       <c r="I28" t="str">
-        <v>入 $0.923077 · 出 $3.384615 · 缓 $0.230769</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="J28" t="str">
-        <v>0%</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="K28" t="str">
         <v>0%</v>
@@ -1804,95 +1885,110 @@
         <v>0%</v>
       </c>
       <c r="M28" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="N28" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O28" t="str">
-        <v>入⚠-35% 出⚠-43.3% 缓⚠-48%</v>
+        <v>—</v>
       </c>
       <c r="P28" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q28" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>glm-5-turbo</v>
+        <v>gpt-5-mini</v>
       </c>
       <c r="B29" t="str">
-        <v>GLM 5 Turbo</v>
+        <v>gpt-5-mini</v>
       </c>
       <c r="C29" t="str">
-        <v>Zhipu</v>
+        <v>GPT</v>
       </c>
       <c r="D29" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>GPT</v>
       </c>
       <c r="E29" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>标准价</v>
       </c>
       <c r="F29" t="str">
-        <v>入 $0.77 · 出 $3.388 · 缓 $0.185</v>
+        <v>入 $0.25 · 出 $2 · 缓 $0.025</v>
       </c>
       <c r="G29" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>—</v>
       </c>
       <c r="H29" t="str">
-        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
+        <v>—</v>
       </c>
       <c r="I29" t="str">
-        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
+        <v>—</v>
       </c>
       <c r="J29" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K29" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L29" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M29" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N29" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O29" t="str">
-        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
+        <v>—</v>
       </c>
       <c r="P29" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="Q29" t="str">
+        <v>— 未上架</v>
+      </c>
+      <c r="R29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="str">
+        <v>gpt-5-nano</v>
+      </c>
+      <c r="B30" t="str">
+        <v>gpt-5-nano</v>
+      </c>
+      <c r="C30" t="str">
+        <v>GPT-5 Nano</v>
+      </c>
       <c r="D30" t="str">
-        <v>输入&gt;=32k</v>
+        <v>OpenAI</v>
       </c>
       <c r="E30" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>标准价</v>
       </c>
       <c r="F30" t="str">
-        <v>入 $1.078 · 出 $4.004 · 缓 $0.277</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="G30" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="H30" t="str">
-        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
+        <v>—</v>
       </c>
       <c r="I30" t="str">
-        <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
+        <v>入 $0.049999999999999996 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
       <c r="J30" t="str">
-        <v>0%</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="K30" t="str">
         <v>0%</v>
@@ -1901,51 +1997,54 @@
         <v>0%</v>
       </c>
       <c r="M30" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="N30" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O30" t="str">
-        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
+        <v>—</v>
       </c>
       <c r="P30" t="str">
+        <v>入✅ 出✅ 缓⚠+100%</v>
+      </c>
+      <c r="Q30" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q30" t="str">
+      <c r="R30" t="str">
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>glm-5.1</v>
+        <v>gpt-5.1</v>
       </c>
       <c r="B31" t="str">
-        <v>GLM-5.1</v>
+        <v>gpt-5.1</v>
       </c>
       <c r="C31" t="str">
-        <v>Zhipu</v>
+        <v>GPT-5.1</v>
       </c>
       <c r="D31" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>OpenAI</v>
       </c>
       <c r="E31" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>标准价</v>
       </c>
       <c r="F31" t="str">
-        <v>入 $0.924 · 出 $3.696 · 缓 $0.2</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G31" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="H31" t="str">
-        <v>入 $0.975 · 出 $4.300000000000001</v>
+        <v>—</v>
       </c>
       <c r="I31" t="str">
-        <v>入 $0.923077 · 出 $3.692308 · 缓 $0.2</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
       </c>
       <c r="J31" t="str">
-        <v>0%</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="K31" t="str">
         <v>0%</v>
@@ -1954,42 +2053,54 @@
         <v>0%</v>
       </c>
       <c r="M31" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="N31" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O31" t="str">
-        <v>入⚠+5.6% 出⚠+16.5%</v>
+        <v>—</v>
       </c>
       <c r="P31" t="str">
+        <v>入✅ 出✅ 缓⚠+4%</v>
+      </c>
+      <c r="Q31" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q31" t="str">
+      <c r="R31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="str">
+        <v>gpt-5.2</v>
+      </c>
+      <c r="B32" t="str">
+        <v>gpt-5.2</v>
+      </c>
+      <c r="C32" t="str">
+        <v>GPT-5.2</v>
+      </c>
       <c r="D32" t="str">
-        <v>32k&lt;=输入</v>
+        <v>OpenAI</v>
       </c>
       <c r="E32" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>标准价</v>
       </c>
       <c r="F32" t="str">
-        <v>入 $1.232 · 出 $4.312 · 缓 $0.308</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="G32" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="H32" t="str">
-        <v>入 $0.975 · 出 $4.300000000000001</v>
+        <v>—</v>
       </c>
       <c r="I32" t="str">
-        <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="J32" t="str">
-        <v>0%</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="K32" t="str">
         <v>0%</v>
@@ -1998,51 +2109,54 @@
         <v>0%</v>
       </c>
       <c r="M32" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="N32" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O32" t="str">
-        <v>入⚠-20.8% 出✅</v>
+        <v>—</v>
       </c>
       <c r="P32" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q32" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>glm-5.2</v>
+        <v>gpt-5.3-codex</v>
       </c>
       <c r="B33" t="str">
-        <v>GLM-5.2</v>
+        <v>gpt-5.3-codex</v>
       </c>
       <c r="C33" t="str">
-        <v>Zhipu</v>
+        <v>GPT-5.3 Codex</v>
       </c>
       <c r="D33" t="str">
-        <v>统一价</v>
+        <v>OpenAI</v>
       </c>
       <c r="E33" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>标准价</v>
       </c>
       <c r="F33" t="str">
-        <v>—</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="G33" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.18</v>
       </c>
       <c r="H33" t="str">
-        <v>入 $0.9299999999999999 · 出 $3 · 缓 $0.18</v>
+        <v>—</v>
       </c>
       <c r="I33" t="str">
-        <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
+        <v>—</v>
       </c>
       <c r="J33" t="str">
-        <v>0%</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="K33" t="str">
         <v>0%</v>
@@ -2051,51 +2165,54 @@
         <v>0%</v>
       </c>
       <c r="M33" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N33" t="str">
+        <v>入✅ 出✅ 缓⚠+2.9%</v>
+      </c>
+      <c r="O33" t="str">
+        <v>—</v>
+      </c>
+      <c r="P33" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q33" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O33" t="str">
-        <v>入⚠-24.4% 出⚠-30.4% 缓⚠-41.5%</v>
-      </c>
-      <c r="P33" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="Q33" t="str">
+      <c r="R33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>glm-5v-turbo</v>
+        <v>gpt-5.4</v>
       </c>
       <c r="B34" t="str">
-        <v>GLM-5V Turbo</v>
+        <v>gpt-5.4</v>
       </c>
       <c r="C34" t="str">
-        <v>Zhipu</v>
+        <v>GPT-5.4</v>
       </c>
       <c r="D34" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>OpenAI</v>
       </c>
       <c r="E34" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="F34" t="str">
-        <v>—</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="G34" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="H34" t="str">
-        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
+        <v>—</v>
       </c>
       <c r="I34" t="str">
-        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="J34" t="str">
-        <v>0%</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="K34" t="str">
         <v>0%</v>
@@ -2104,42 +2221,42 @@
         <v>0%</v>
       </c>
       <c r="M34" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N34" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O34" t="str">
-        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
+        <v>—</v>
       </c>
       <c r="P34" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q34" t="str">
-        <v>多模态 Coding 基座</v>
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
-      <c r="D35" t="str">
-        <v>输入&gt;=32k</v>
-      </c>
       <c r="E35" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="F35" t="str">
-        <v>—</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="G35" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="H35" t="str">
-        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
+        <v>—</v>
       </c>
       <c r="I35" t="str">
-        <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="J35" t="str">
-        <v>0%</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="K35" t="str">
         <v>0%</v>
@@ -2148,51 +2265,54 @@
         <v>0%</v>
       </c>
       <c r="M35" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N35" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O35" t="str">
-        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
+        <v>—</v>
       </c>
       <c r="P35" t="str">
+        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
+      </c>
+      <c r="Q35" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q35" t="str">
-        <v>多模态 Coding 基座</v>
+      <c r="R35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>gpt-4.1</v>
+        <v>gpt-5.4-mini</v>
       </c>
       <c r="B36" t="str">
-        <v>GPT-4.1</v>
+        <v>gpt-5.4-mini</v>
       </c>
       <c r="C36" t="str">
+        <v>GPT-5.4 Mini</v>
+      </c>
+      <c r="D36" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="D36" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E36" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>标准价</v>
       </c>
       <c r="F36" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="G36" t="str">
-        <v>—</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="H36" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="I36" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="J36" t="str">
-        <v>0%</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="K36" t="str">
         <v>0%</v>
@@ -2201,104 +2321,110 @@
         <v>0%</v>
       </c>
       <c r="M36" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N36" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N36" t="str">
-        <v>—</v>
-      </c>
       <c r="O36" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P36" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q36" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>gpt-4o</v>
+        <v>gpt-5.4-nano</v>
       </c>
       <c r="B37" t="str">
-        <v>GPT-4o</v>
+        <v>gpt-5.4-nano</v>
       </c>
       <c r="C37" t="str">
-        <v>OpenAI</v>
+        <v>GPT</v>
       </c>
       <c r="D37" t="str">
-        <v>统一价</v>
+        <v>GPT</v>
       </c>
       <c r="E37" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>标准价</v>
       </c>
       <c r="F37" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
       </c>
       <c r="G37" t="str">
         <v>—</v>
       </c>
       <c r="H37" t="str">
-        <v>入 $2.5 · 出 $10</v>
+        <v>—</v>
       </c>
       <c r="I37" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>—</v>
       </c>
       <c r="J37" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K37" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L37" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M37" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N37" t="str">
         <v>—</v>
       </c>
       <c r="O37" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="P37" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="Q37" t="str">
+        <v>— 未上架</v>
+      </c>
+      <c r="R37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>gpt-5</v>
+        <v>gpt-5.4-pro</v>
       </c>
       <c r="B38" t="str">
-        <v>GPT-5</v>
+        <v>gpt-5.4-pro</v>
       </c>
       <c r="C38" t="str">
+        <v>GPT-5.4 Pro</v>
+      </c>
+      <c r="D38" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="D38" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E38" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="F38" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="G38" t="str">
-        <v>—</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="H38" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>—</v>
       </c>
       <c r="I38" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="J38" t="str">
-        <v>0%</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="K38" t="str">
         <v>0%</v>
@@ -2307,51 +2433,42 @@
         <v>0%</v>
       </c>
       <c r="M38" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N38" t="str">
-        <v>—</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="O38" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P38" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="Q38" t="str">
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="R38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>gpt-5-nano</v>
-      </c>
-      <c r="B39" t="str">
-        <v>GPT-5 Nano</v>
-      </c>
-      <c r="C39" t="str">
-        <v>OpenAI</v>
-      </c>
-      <c r="D39" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E39" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="F39" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="G39" t="str">
-        <v>—</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="H39" t="str">
-        <v>入 $0.049999999999999996 · 出 $0.39999999999999997 · 缓 $0.01</v>
+        <v>—</v>
       </c>
       <c r="I39" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="J39" t="str">
-        <v>0%</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="K39" t="str">
         <v>0%</v>
@@ -2360,51 +2477,54 @@
         <v>0%</v>
       </c>
       <c r="M39" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N39" t="str">
-        <v>—</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="O39" t="str">
-        <v>入✅ 出✅ 缓⚠+100%</v>
+        <v>—</v>
       </c>
       <c r="P39" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠-50% 出⚠-33.3%</v>
       </c>
       <c r="Q39" t="str">
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="R39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>gpt-5.1</v>
+        <v>gpt-5.5</v>
       </c>
       <c r="B40" t="str">
-        <v>GPT-5.1</v>
+        <v>gpt-5.5</v>
       </c>
       <c r="C40" t="str">
+        <v>GPT-5.5</v>
+      </c>
+      <c r="D40" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="D40" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E40" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="F40" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="G40" t="str">
-        <v>—</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="H40" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
+        <v>—</v>
       </c>
       <c r="I40" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="J40" t="str">
-        <v>0%</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="K40" t="str">
         <v>0%</v>
@@ -2413,51 +2533,42 @@
         <v>0%</v>
       </c>
       <c r="M40" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N40" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N40" t="str">
-        <v>—</v>
-      </c>
       <c r="O40" t="str">
-        <v>入✅ 出✅ 缓⚠+4%</v>
+        <v>—</v>
       </c>
       <c r="P40" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q40" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>gpt-5.1-chat</v>
-      </c>
-      <c r="B41" t="str">
-        <v>GPT-5.1 Chat</v>
-      </c>
-      <c r="C41" t="str">
-        <v>OpenAI</v>
-      </c>
-      <c r="D41" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E41" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="F41" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="G41" t="str">
-        <v>—</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="H41" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
+        <v>—</v>
       </c>
       <c r="I41" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="J41" t="str">
-        <v>0%</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="K41" t="str">
         <v>0%</v>
@@ -2466,92 +2577,86 @@
         <v>0%</v>
       </c>
       <c r="M41" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N41" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N41" t="str">
-        <v>—</v>
-      </c>
       <c r="O41" t="str">
-        <v>入✅ 出✅ 缓⚠+4%</v>
+        <v>—</v>
       </c>
       <c r="P41" t="str">
+        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
+      </c>
+      <c r="Q41" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q41" t="str">
-        <v>目录名 gpt-5.1-chat</v>
+      <c r="R41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>gpt-5.2</v>
+        <v>chat-latest</v>
       </c>
       <c r="B42" t="str">
-        <v>GPT-5.2</v>
+        <v>—</v>
       </c>
       <c r="C42" t="str">
-        <v>OpenAI</v>
+        <v>GPT</v>
       </c>
       <c r="D42" t="str">
-        <v>统一价</v>
+        <v>GPT</v>
       </c>
       <c r="E42" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="F42" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="G42" t="str">
         <v>—</v>
       </c>
       <c r="H42" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>—</v>
       </c>
       <c r="I42" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>—</v>
       </c>
       <c r="J42" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K42" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L42" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M42" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N42" t="str">
         <v>—</v>
       </c>
       <c r="O42" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P42" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="Q42" t="str">
-        <v/>
+        <v>— 未接入</v>
+      </c>
+      <c r="R42" t="str">
+        <v>对应 gpt-5.5 instant</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
-        <v>gpt-5.3-codex</v>
-      </c>
-      <c r="B43" t="str">
-        <v>GPT-5.3 Codex</v>
-      </c>
-      <c r="C43" t="str">
-        <v>OpenAI</v>
-      </c>
-      <c r="D43" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E43" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="F43" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.18</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="G43" t="str">
         <v>—</v>
@@ -2560,19 +2665,19 @@
         <v>—</v>
       </c>
       <c r="I43" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>—</v>
       </c>
       <c r="J43" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K43" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L43" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M43" t="str">
-        <v>入✅ 出✅ 缓⚠+2.9%</v>
+        <v>—</v>
       </c>
       <c r="N43" t="str">
         <v>—</v>
@@ -2581,139 +2686,157 @@
         <v>—</v>
       </c>
       <c r="P43" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="Q43" t="str">
-        <v/>
+        <v>— 未接入</v>
+      </c>
+      <c r="R43" t="str">
+        <v>对应 gpt-5.5 instant</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>gpt-5.4</v>
+        <v>gpt-5.2-chat-latest</v>
       </c>
       <c r="B44" t="str">
-        <v>GPT-5.4</v>
+        <v>—</v>
       </c>
       <c r="C44" t="str">
-        <v>OpenAI</v>
+        <v>GPT</v>
       </c>
       <c r="D44" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>GPT</v>
       </c>
       <c r="E44" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>标准价</v>
       </c>
       <c r="F44" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="G44" t="str">
         <v>—</v>
       </c>
       <c r="H44" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>—</v>
       </c>
       <c r="I44" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>—</v>
       </c>
       <c r="J44" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K44" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L44" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M44" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N44" t="str">
         <v>—</v>
       </c>
       <c r="O44" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P44" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="Q44" t="str">
-        <v/>
+        <v>— 未接入</v>
+      </c>
+      <c r="R44" t="str">
+        <v>目录名 gpt-5.2-chat</v>
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="str">
+        <v>gpt-5.3-chat-latest</v>
+      </c>
+      <c r="B45" t="str">
+        <v>—</v>
+      </c>
+      <c r="C45" t="str">
+        <v>GPT</v>
+      </c>
       <c r="D45" t="str">
-        <v>输入&gt;272K context</v>
+        <v>GPT</v>
       </c>
       <c r="E45" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>标准价</v>
       </c>
       <c r="F45" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G45" t="str">
         <v>—</v>
       </c>
       <c r="H45" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>—</v>
       </c>
       <c r="I45" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="J45" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K45" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L45" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="M45" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="N45" t="str">
         <v>—</v>
       </c>
       <c r="O45" t="str">
-        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
+        <v>—</v>
       </c>
       <c r="P45" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="Q45" t="str">
-        <v/>
+        <v>— 未接入</v>
+      </c>
+      <c r="R45" t="str">
+        <v>目录名 gpt-5.3-chat</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>gpt-5.4-mini</v>
+        <v>kimi-k2.5</v>
       </c>
       <c r="B46" t="str">
-        <v>GPT-5.4 Mini</v>
+        <v>kimi-k2.5</v>
       </c>
       <c r="C46" t="str">
-        <v>OpenAI</v>
+        <v>Kimi K2.5</v>
       </c>
       <c r="D46" t="str">
-        <v>统一价</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="E46" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>标准价</v>
       </c>
       <c r="F46" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
       </c>
       <c r="G46" t="str">
-        <v>—</v>
+        <v>入 $0.616 · 出 $3.234 · 缓 $0.108</v>
       </c>
       <c r="H46" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
       </c>
       <c r="I46" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $0.375 · 出 $2.025</v>
       </c>
       <c r="J46" t="str">
-        <v>0%</v>
+        <v>入 $0.615385 · 出 $3.230769 · 缓 $0.107692</v>
       </c>
       <c r="K46" t="str">
         <v>0%</v>
@@ -2722,148 +2845,166 @@
         <v>0%</v>
       </c>
       <c r="M46" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N46" t="str">
         <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="N46" t="str">
-        <v>—</v>
       </c>
       <c r="O46" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P46" t="str">
+        <v>入⚠-39.1% 出⚠-37.3%</v>
+      </c>
+      <c r="Q46" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q46" t="str">
+      <c r="R46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>gpt-5.4-pro</v>
+        <v>kimi-k2.6</v>
       </c>
       <c r="B47" t="str">
-        <v>GPT-5.4 Pro</v>
+        <v>kimi-k2.6</v>
       </c>
       <c r="C47" t="str">
-        <v>OpenAI</v>
+        <v>Kimi K2.6</v>
       </c>
       <c r="D47" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="E47" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>标准价</v>
       </c>
       <c r="F47" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
       </c>
       <c r="G47" t="str">
         <v>—</v>
       </c>
       <c r="H47" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
       </c>
       <c r="I47" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 $0.55 · 出 $3.1999999999999997 · 缓 $0.11</v>
       </c>
       <c r="J47" t="str">
-        <v>0%</v>
+        <v>入 $1 · 出 $4.153846 · 缓 $0.169231</v>
       </c>
       <c r="K47" t="str">
         <v>0%</v>
       </c>
       <c r="L47" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M47" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N47" t="str">
+        <v>—</v>
+      </c>
+      <c r="O47" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="P47" t="str">
+        <v>入⚠-45% 出⚠-23% 缓⚠-35%</v>
+      </c>
+      <c r="Q47" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>kimi-k2.7-code</v>
+      </c>
+      <c r="B48" t="str">
+        <v>kimi-k2.7-code</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Kimi K2.7 Code</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Moonshot AI</v>
+      </c>
+      <c r="E48" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F48" t="str">
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
+      </c>
+      <c r="G48" t="str">
+        <v>—</v>
+      </c>
+      <c r="H48" t="str">
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
+      </c>
+      <c r="I48" t="str">
+        <v>入 $0.74 · 出 $3.5 · 缓 $0.15</v>
+      </c>
+      <c r="J48" t="str">
+        <v>入 $1 · 出 $4.153846</v>
+      </c>
+      <c r="K48" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L48" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M48" t="str">
+        <v>—</v>
+      </c>
+      <c r="N48" t="str">
+        <v>—</v>
+      </c>
+      <c r="O48" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="P48" t="str">
+        <v>入⚠-26% 出⚠-15.7% 缓⚠-25%</v>
+      </c>
+      <c r="Q48" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="N47" t="str">
-        <v>—</v>
-      </c>
-      <c r="O47" t="str">
-        <v>入✅ 出✅</v>
-      </c>
-      <c r="P47" t="str">
-        <v>入✅ 出✅</v>
-      </c>
-      <c r="Q47" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="D48" t="str">
-        <v>输入&gt;272K context</v>
-      </c>
-      <c r="E48" t="str">
-        <v>入 $60 · 出 $270</v>
-      </c>
-      <c r="F48" t="str">
-        <v>入 $60 · 出 $270</v>
-      </c>
-      <c r="G48" t="str">
-        <v>—</v>
-      </c>
-      <c r="H48" t="str">
-        <v>入 $30 · 出 $180</v>
-      </c>
-      <c r="I48" t="str">
-        <v>入 $60 · 出 $270</v>
-      </c>
-      <c r="J48" t="str">
-        <v>0%</v>
-      </c>
-      <c r="K48" t="str">
-        <v>0%</v>
-      </c>
-      <c r="L48" t="str">
-        <v>—</v>
-      </c>
-      <c r="M48" t="str">
-        <v>入✅ 出✅</v>
-      </c>
-      <c r="N48" t="str">
-        <v>—</v>
-      </c>
-      <c r="O48" t="str">
-        <v>入⚠-50% 出⚠-33.3%</v>
-      </c>
-      <c r="P48" t="str">
-        <v>入✅ 出✅</v>
-      </c>
-      <c r="Q48" t="str">
+      <c r="R48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>gpt-5.5</v>
+        <v>kimi-k2.7-code-highspeed</v>
       </c>
       <c r="B49" t="str">
-        <v>GPT-5.5</v>
+        <v>kimi-k2.7-code-highspeed</v>
       </c>
       <c r="C49" t="str">
-        <v>OpenAI</v>
+        <v>Kimi K2.7 Code HighSpeed</v>
       </c>
       <c r="D49" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="E49" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>标准价</v>
       </c>
       <c r="F49" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
       </c>
       <c r="G49" t="str">
         <v>—</v>
       </c>
       <c r="H49" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
       </c>
       <c r="I49" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="J49" t="str">
-        <v>0%</v>
+        <v>入 $2 · 出 $8.307692 · 缓 $0.4</v>
       </c>
       <c r="K49" t="str">
         <v>0%</v>
@@ -2872,7 +3013,7 @@
         <v>0%</v>
       </c>
       <c r="M49" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="N49" t="str">
         <v>—</v>
@@ -2881,33 +3022,45 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P49" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q49" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q49" t="str">
-        <v/>
+      <c r="R49" t="str">
+        <v>K2.7 Code 高速版</v>
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="str">
+        <v>minimax-m2.5</v>
+      </c>
+      <c r="B50" t="str">
+        <v>minimax-m2.5</v>
+      </c>
+      <c r="C50" t="str">
+        <v>MiniMax M2.5</v>
+      </c>
       <c r="D50" t="str">
-        <v>输入&gt;272K context</v>
+        <v>MiniMax</v>
       </c>
       <c r="E50" t="str">
-        <v>入 $10 · 出 $45 · 缓 $1</v>
+        <v>标准价</v>
       </c>
       <c r="F50" t="str">
-        <v>入 $10 · 出 $45 · 缓 $1</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
       </c>
       <c r="G50" t="str">
-        <v>—</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.03</v>
       </c>
       <c r="H50" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
       </c>
       <c r="I50" t="str">
-        <v>入 $10 · 出 $45 · 缓 $1</v>
+        <v>入 $0.12 · 出 $0.48</v>
       </c>
       <c r="J50" t="str">
-        <v>0%</v>
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.032308</v>
       </c>
       <c r="K50" t="str">
         <v>0%</v>
@@ -2916,213 +3069,213 @@
         <v>0%</v>
       </c>
       <c r="M50" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N50" t="str">
+        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
+      </c>
+      <c r="O50" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="N50" t="str">
-        <v>—</v>
-      </c>
-      <c r="O50" t="str">
-        <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
-      </c>
       <c r="P50" t="str">
+        <v>入⚠-62.9% 出⚠-62.9%</v>
+      </c>
+      <c r="Q50" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q50" t="str">
+      <c r="R50" t="str">
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>hunyuan-role-latest</v>
+        <v>minimax-m2.7</v>
       </c>
       <c r="B51" t="str">
-        <v>Hy-Role Latest</v>
+        <v>minimax-m2.7</v>
       </c>
       <c r="C51" t="str">
-        <v>Tencent</v>
+        <v>MiniMax M2.7</v>
       </c>
       <c r="D51" t="str">
-        <v>统一价</v>
+        <v>MiniMax</v>
       </c>
       <c r="E51" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>标准价</v>
       </c>
       <c r="F51" t="str">
-        <v>—</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="G51" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="H51" t="str">
-        <v>—</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="I51" t="str">
-        <v>入 $0.369231 · 出 $1.476923</v>
+        <v>入 $0.18 · 出 $0.72</v>
       </c>
       <c r="J51" t="str">
-        <v>0%</v>
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
       <c r="K51" t="str">
         <v>0%</v>
       </c>
       <c r="L51" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M51" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N51" t="str">
-        <v>入✅ 出✅</v>
+        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
       <c r="O51" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P51" t="str">
-        <v>入✅ 出✅</v>
+        <v>入⚠-44.3% 出⚠-44.3%</v>
       </c>
       <c r="Q51" t="str">
-        <v>Hy-Role-Latest</v>
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R51" t="str">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>hy-mt2-lite</v>
+        <v>minimax-m3</v>
       </c>
       <c r="B52" t="str">
-        <v>Hy-MT2 Lite</v>
+        <v>minimax-m3</v>
       </c>
       <c r="C52" t="str">
-        <v>Tencent</v>
+        <v>MiniMax M3</v>
       </c>
       <c r="D52" t="str">
-        <v>统一价</v>
+        <v>MiniMax</v>
       </c>
       <c r="E52" t="str">
-        <v>入 ¥0.3 · 出 ¥1.2</v>
+        <v>输入≤512k</v>
       </c>
       <c r="F52" t="str">
-        <v>—</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="G52" t="str">
-        <v>入 ¥0.3 · 出 ¥1.2</v>
+        <v>—</v>
       </c>
       <c r="H52" t="str">
-        <v>—</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="I52" t="str">
-        <v>入 $0.046154 · 出 $0.184615</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="J52" t="str">
-        <v>0%</v>
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
       <c r="K52" t="str">
         <v>0%</v>
       </c>
       <c r="L52" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M52" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N52" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="O52" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P52" t="str">
-        <v>入✅ 出✅</v>
+        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
       <c r="Q52" t="str">
-        <v/>
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R52" t="str">
+        <v>512k 以上输入档仍在内测开放中</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="str">
-        <v>hy-mt2-plus</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Hy-MT2 Plus</v>
-      </c>
-      <c r="C53" t="str">
-        <v>Tencent</v>
-      </c>
-      <c r="D53" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E53" t="str">
-        <v>入 ¥0.5 · 出 ¥2</v>
+        <v>输入&gt;512k</v>
       </c>
       <c r="F53" t="str">
-        <v>—</v>
+        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="G53" t="str">
-        <v>入 ¥0.5 · 出 ¥2</v>
+        <v>—</v>
       </c>
       <c r="H53" t="str">
-        <v>—</v>
+        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="I53" t="str">
-        <v>入 $0.076923 · 出 $0.307692</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="J53" t="str">
-        <v>0%</v>
+        <v>入 $0.646154 · 出 $2.584615 · 缓 $0.129231</v>
       </c>
       <c r="K53" t="str">
         <v>0%</v>
       </c>
       <c r="L53" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M53" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N53" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="O53" t="str">
-        <v>—</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P53" t="str">
-        <v>入✅ 出✅</v>
+        <v>入⚠-53.6% 出⚠-53.6% 缓⚠-53.6%</v>
       </c>
       <c r="Q53" t="str">
-        <v/>
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R53" t="str">
+        <v>512k 以上输入档仍在内测开放中</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>hy-mt2-pro</v>
+        <v>glm-4.7</v>
       </c>
       <c r="B54" t="str">
-        <v>Hy-MT2 Pro</v>
+        <v>glm-4-7-251222</v>
       </c>
       <c r="C54" t="str">
-        <v>Tencent</v>
+        <v>智谱</v>
       </c>
       <c r="D54" t="str">
-        <v>统一价</v>
+        <v>智谱</v>
       </c>
       <c r="E54" t="str">
-        <v>入 ¥0.5 · 出 ¥2</v>
+        <v>输入≤32k，输出≤0.2k</v>
       </c>
       <c r="F54" t="str">
-        <v>—</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
       </c>
       <c r="G54" t="str">
-        <v>入 ¥0.5 · 出 ¥2</v>
+        <v>—</v>
       </c>
       <c r="H54" t="str">
         <v>—</v>
       </c>
       <c r="I54" t="str">
-        <v>入 $0.076923 · 出 $0.307692</v>
+        <v>—</v>
       </c>
       <c r="J54" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K54" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L54" t="str">
         <v>—</v>
@@ -3131,51 +3284,42 @@
         <v>—</v>
       </c>
       <c r="N54" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="O54" t="str">
         <v>—</v>
       </c>
       <c r="P54" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="Q54" t="str">
-        <v/>
+        <v>— 未上架</v>
+      </c>
+      <c r="R54" t="str">
+        <v>Trinity ID glm-4-7-251222</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="str">
-        <v>hy-role</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Hy-Role</v>
-      </c>
-      <c r="C55" t="str">
-        <v>Tencent</v>
-      </c>
-      <c r="D55" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E55" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>输入≤32k，输出&gt;0.2k</v>
       </c>
       <c r="F55" t="str">
-        <v>—</v>
+        <v>入 ¥3 · 出 ¥14 · 缓 ¥0.6</v>
       </c>
       <c r="G55" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>—</v>
       </c>
       <c r="H55" t="str">
         <v>—</v>
       </c>
       <c r="I55" t="str">
-        <v>入 $0.369231 · 出 $1.476923</v>
+        <v>—</v>
       </c>
       <c r="J55" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K55" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L55" t="str">
         <v>—</v>
@@ -3184,36 +3328,27 @@
         <v>—</v>
       </c>
       <c r="N55" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="O55" t="str">
         <v>—</v>
       </c>
       <c r="P55" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="Q55" t="str">
-        <v/>
+        <v>— 未上架</v>
+      </c>
+      <c r="R55" t="str">
+        <v>Trinity ID glm-4-7-251222</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="str">
-        <v>hy-vision-2.0-instruct</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Hy-Vision 2.0 Instruct</v>
-      </c>
-      <c r="C56" t="str">
-        <v>Tencent</v>
-      </c>
-      <c r="D56" t="str">
-        <v>标准价</v>
-      </c>
       <c r="E56" t="str">
-        <v>入 ¥7.5 · 出 ¥17.5</v>
+        <v>输入&gt;32k</v>
       </c>
       <c r="F56" t="str">
-        <v>—</v>
+        <v>入 ¥4 · 出 ¥16 · 缓 ¥0.8</v>
       </c>
       <c r="G56" t="str">
         <v>—</v>
@@ -3222,13 +3357,13 @@
         <v>—</v>
       </c>
       <c r="I56" t="str">
-        <v>入 $1.153846 · 出 $2.692308</v>
+        <v>—</v>
       </c>
       <c r="J56" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="K56" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="L56" t="str">
         <v>—</v>
@@ -3243,42 +3378,45 @@
         <v>—</v>
       </c>
       <c r="P56" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="Q56" t="str">
-        <v>多模态视觉理解 · 按 token 计费</v>
+        <v>— 未上架</v>
+      </c>
+      <c r="R56" t="str">
+        <v>Trinity ID glm-4-7-251222</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>hy3-preview</v>
+        <v>glm-5</v>
       </c>
       <c r="B57" t="str">
-        <v>Hy3 Preview</v>
+        <v>glm-5</v>
       </c>
       <c r="C57" t="str">
-        <v>Tencent</v>
+        <v>GLM 5</v>
       </c>
       <c r="D57" t="str">
-        <v>输入&lt;16k</v>
+        <v>Zhipu</v>
       </c>
       <c r="E57" t="str">
-        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+        <v>输入&lt;32k</v>
       </c>
       <c r="F57" t="str">
-        <v>—</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="G57" t="str">
-        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+        <v>入 $0.616 · 出 $2.772 · 缓 $0.154</v>
       </c>
       <c r="H57" t="str">
-        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="I57" t="str">
-        <v>入 $0.184615 · 出 $0.615385 · 缓 $0.061538</v>
+        <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
       </c>
       <c r="J57" t="str">
-        <v>0%</v>
+        <v>入 $0.615385 · 出 $2.769231 · 缓 $0.153846</v>
       </c>
       <c r="K57" t="str">
         <v>0%</v>
@@ -3287,42 +3425,42 @@
         <v>0%</v>
       </c>
       <c r="M57" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N57" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O57" t="str">
-        <v>入⚠-65.9% 出⚠-65.9% 缓⚠-65.9%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P57" t="str">
+        <v>入⚠-2.5% 出⚠-30.7% 缓⚠-22%</v>
+      </c>
+      <c r="Q57" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q57" t="str">
+      <c r="R57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="D58" t="str">
-        <v>16k&lt;=输入&lt;32k</v>
-      </c>
       <c r="E58" t="str">
-        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
+        <v>输入≥32k</v>
       </c>
       <c r="F58" t="str">
-        <v>—</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="G58" t="str">
-        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
+        <v>入 $0.924 · 出 $3.388 · 缓 $0.231</v>
       </c>
       <c r="H58" t="str">
-        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="I58" t="str">
-        <v>入 $0.246154 · 出 $0.984615 · 缓 $0.092308</v>
+        <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
       </c>
       <c r="J58" t="str">
-        <v>0%</v>
+        <v>入 $0.923077 · 出 $3.384615 · 缓 $0.230769</v>
       </c>
       <c r="K58" t="str">
         <v>0%</v>
@@ -3331,42 +3469,54 @@
         <v>0%</v>
       </c>
       <c r="M58" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N58" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O58" t="str">
-        <v>入⚠-74.4% 出⚠-78.7% 缓⚠-77.2%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P58" t="str">
+        <v>入⚠-35% 出⚠-43.3% 缓⚠-48%</v>
+      </c>
+      <c r="Q58" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q58" t="str">
+      <c r="R58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="str">
+        <v>glm-5-turbo</v>
+      </c>
+      <c r="B59" t="str">
+        <v>glm-5-turbo</v>
+      </c>
+      <c r="C59" t="str">
+        <v>GLM 5 Turbo</v>
+      </c>
       <c r="D59" t="str">
-        <v>输入&gt;=32k</v>
+        <v>Zhipu</v>
       </c>
       <c r="E59" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
+        <v>输入&lt;32k</v>
       </c>
       <c r="F59" t="str">
-        <v>—</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="G59" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
+        <v>入 $0.77 · 出 $3.388 · 缓 $0.185</v>
       </c>
       <c r="H59" t="str">
-        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="I59" t="str">
-        <v>入 $0.307692 · 出 $1.230769 · 缓 $0.123077</v>
+        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="J59" t="str">
-        <v>0%</v>
+        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
       </c>
       <c r="K59" t="str">
         <v>0%</v>
@@ -3375,51 +3525,42 @@
         <v>0%</v>
       </c>
       <c r="M59" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N59" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O59" t="str">
-        <v>入⚠-79.5% 出⚠-82.9% 缓⚠-82.9%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P59" t="str">
+        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
+      </c>
+      <c r="Q59" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q59" t="str">
+      <c r="R59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="str">
-        <v>kimi-k2.5</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Kimi K2.5</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Moonshot AI</v>
-      </c>
-      <c r="D60" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E60" t="str">
-        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+        <v>输入≥32k</v>
       </c>
       <c r="F60" t="str">
-        <v>入 $0.616 · 出 $3.234 · 缓 $0.108</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="G60" t="str">
-        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+        <v>入 $1.078 · 出 $4.004 · 缓 $0.277</v>
       </c>
       <c r="H60" t="str">
-        <v>入 $0.375 · 出 $2.025</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="I60" t="str">
-        <v>入 $0.615385 · 出 $3.230769 · 缓 $0.107692</v>
+        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="J60" t="str">
-        <v>0%</v>
+        <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
       </c>
       <c r="K60" t="str">
         <v>0%</v>
@@ -3428,51 +3569,54 @@
         <v>0%</v>
       </c>
       <c r="M60" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="N60" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O60" t="str">
-        <v>入⚠-39.1% 出⚠-37.3%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P60" t="str">
+        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
+      </c>
+      <c r="Q60" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q60" t="str">
+      <c r="R60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>kimi-k2.6</v>
+        <v>glm-5.1</v>
       </c>
       <c r="B61" t="str">
-        <v>Kimi K2.6</v>
+        <v>glm-5.1</v>
       </c>
       <c r="C61" t="str">
-        <v>Moonshot AI</v>
+        <v>GLM-5.1</v>
       </c>
       <c r="D61" t="str">
-        <v>统一价</v>
+        <v>Zhipu</v>
       </c>
       <c r="E61" t="str">
-        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
+        <v>输入&lt;32k</v>
       </c>
       <c r="F61" t="str">
-        <v>—</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="G61" t="str">
-        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
+        <v>入 $0.924 · 出 $3.696 · 缓 $0.2</v>
       </c>
       <c r="H61" t="str">
-        <v>入 $0.55 · 出 $3.1999999999999997 · 缓 $0.11</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="I61" t="str">
-        <v>入 $1 · 出 $4.153846 · 缓 $0.169231</v>
+        <v>入 $0.975 · 出 $4.300000000000001</v>
       </c>
       <c r="J61" t="str">
-        <v>0%</v>
+        <v>入 $0.923077 · 出 $3.692308 · 缓 $0.2</v>
       </c>
       <c r="K61" t="str">
         <v>0%</v>
@@ -3481,104 +3625,98 @@
         <v>0%</v>
       </c>
       <c r="M61" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N61" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O61" t="str">
-        <v>入⚠-45% 出⚠-23% 缓⚠-35%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P61" t="str">
+        <v>入⚠+5.6% 出⚠+16.5%</v>
+      </c>
+      <c r="Q61" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q61" t="str">
+      <c r="R61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="str">
-        <v>kimi-k2.7-code</v>
-      </c>
-      <c r="B62" t="str">
-        <v>Kimi K2.7 Code</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Moonshot AI</v>
-      </c>
-      <c r="D62" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E62" t="str">
-        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
+        <v>输入≥32k</v>
       </c>
       <c r="F62" t="str">
-        <v>—</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="G62" t="str">
-        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
+        <v>入 $1.232 · 出 $4.312 · 缓 $0.308</v>
       </c>
       <c r="H62" t="str">
-        <v>入 $0.74 · 出 $3.5 · 缓 $0.15</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="I62" t="str">
-        <v>入 $1 · 出 $4.153846</v>
+        <v>入 $0.975 · 出 $4.300000000000001</v>
       </c>
       <c r="J62" t="str">
-        <v>0%</v>
+        <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
       </c>
       <c r="K62" t="str">
         <v>0%</v>
       </c>
       <c r="L62" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M62" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N62" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="O62" t="str">
-        <v>入⚠-26% 出⚠-15.7% 缓⚠-25%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P62" t="str">
-        <v>入✅ 出✅</v>
+        <v>入⚠-20.8% 出✅</v>
       </c>
       <c r="Q62" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>kimi-k2.7-code-highspeed</v>
+        <v>glm-5.2</v>
       </c>
       <c r="B63" t="str">
-        <v>Kimi K2.7 Code HighSpeed</v>
+        <v>glm-5.2</v>
       </c>
       <c r="C63" t="str">
-        <v>Moonshot AI</v>
+        <v>GLM-5.2</v>
       </c>
       <c r="D63" t="str">
-        <v>统一价</v>
+        <v>Zhipu</v>
       </c>
       <c r="E63" t="str">
-        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
+        <v>标准价</v>
       </c>
       <c r="F63" t="str">
-        <v>—</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="G63" t="str">
-        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
+        <v>—</v>
       </c>
       <c r="H63" t="str">
-        <v>—</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="I63" t="str">
-        <v>入 $2 · 出 $8.307692 · 缓 $0.4</v>
+        <v>入 $0.9299999999999999 · 出 $3 · 缓 $0.18</v>
       </c>
       <c r="J63" t="str">
-        <v>0%</v>
+        <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
       </c>
       <c r="K63" t="str">
         <v>0%</v>
@@ -3587,51 +3725,54 @@
         <v>0%</v>
       </c>
       <c r="M63" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N63" t="str">
+        <v>—</v>
+      </c>
+      <c r="O63" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O63" t="str">
-        <v>—</v>
-      </c>
       <c r="P63" t="str">
+        <v>入⚠-24.4% 出⚠-30.4% 缓⚠-41.5%</v>
+      </c>
+      <c r="Q63" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q63" t="str">
-        <v>K2.7 Code 高速版</v>
+      <c r="R63" t="str">
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>minimax-m2.5</v>
+        <v>glm-5v-turbo</v>
       </c>
       <c r="B64" t="str">
-        <v>MiniMax M2.5</v>
+        <v>glm-5v-turbo</v>
       </c>
       <c r="C64" t="str">
-        <v>MiniMax</v>
+        <v>GLM-5V Turbo</v>
       </c>
       <c r="D64" t="str">
-        <v>统一价</v>
+        <v>Zhipu</v>
       </c>
       <c r="E64" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+        <v>输入&lt;32k</v>
       </c>
       <c r="F64" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.03</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="G64" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+        <v>—</v>
       </c>
       <c r="H64" t="str">
-        <v>入 $0.12 · 出 $0.48</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="I64" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.032308</v>
+        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="J64" t="str">
-        <v>0%</v>
+        <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
       </c>
       <c r="K64" t="str">
         <v>0%</v>
@@ -3640,51 +3781,42 @@
         <v>0%</v>
       </c>
       <c r="M64" t="str">
-        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
+        <v>0%</v>
       </c>
       <c r="N64" t="str">
+        <v>—</v>
+      </c>
+      <c r="O64" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O64" t="str">
-        <v>入⚠-62.9% 出⚠-62.9%</v>
-      </c>
       <c r="P64" t="str">
+        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
+      </c>
+      <c r="Q64" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q64" t="str">
-        <v/>
+      <c r="R64" t="str">
+        <v>多模态 Coding 基座</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="str">
-        <v>minimax-m2.7</v>
-      </c>
-      <c r="B65" t="str">
-        <v>MiniMax M2.7</v>
-      </c>
-      <c r="C65" t="str">
-        <v>MiniMax</v>
-      </c>
-      <c r="D65" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E65" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>输入≥32k</v>
       </c>
       <c r="F65" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="G65" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>—</v>
       </c>
       <c r="H65" t="str">
-        <v>入 $0.18 · 出 $0.72</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="I65" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
+        <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
       <c r="J65" t="str">
-        <v>0%</v>
+        <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
       </c>
       <c r="K65" t="str">
         <v>0%</v>
@@ -3693,51 +3825,54 @@
         <v>0%</v>
       </c>
       <c r="M65" t="str">
-        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
+        <v>0%</v>
       </c>
       <c r="N65" t="str">
+        <v>—</v>
+      </c>
+      <c r="O65" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O65" t="str">
-        <v>入⚠-44.3% 出⚠-44.3%</v>
-      </c>
       <c r="P65" t="str">
+        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
+      </c>
+      <c r="Q65" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q65" t="str">
-        <v/>
+      <c r="R65" t="str">
+        <v>多模态 Coding 基座</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>minimax-m3</v>
+        <v>hunyuan-role-latest</v>
       </c>
       <c r="B66" t="str">
-        <v>MiniMax M3</v>
+        <v>hunyuan-role-latest</v>
       </c>
       <c r="C66" t="str">
-        <v>MiniMax</v>
+        <v>Hy-Role Latest</v>
       </c>
       <c r="D66" t="str">
-        <v>输入&lt;=512k</v>
+        <v>Tencent</v>
       </c>
       <c r="E66" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>标准价</v>
       </c>
       <c r="F66" t="str">
-        <v>—</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="G66" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>—</v>
       </c>
       <c r="H66" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="I66" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
+        <v>—</v>
       </c>
       <c r="J66" t="str">
-        <v>0%</v>
+        <v>入 $0.369231 · 出 $1.476923</v>
       </c>
       <c r="K66" t="str">
         <v>0%</v>
@@ -3749,39 +3884,51 @@
         <v>—</v>
       </c>
       <c r="N66" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O66" t="str">
-        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="P66" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="Q66" t="str">
-        <v>512k 以上输入档仍在内测开放中</v>
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="R66" t="str">
+        <v>Hy-Role-Latest</v>
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="str">
+        <v>hy-mt2-lite</v>
+      </c>
+      <c r="B67" t="str">
+        <v>hy-mt2-lite</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Hy-MT2 Lite</v>
+      </c>
       <c r="D67" t="str">
-        <v>512k&lt;输入</v>
+        <v>Tencent</v>
       </c>
       <c r="E67" t="str">
-        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
+        <v>标准价</v>
       </c>
       <c r="F67" t="str">
-        <v>—</v>
+        <v>入 ¥0.3 · 出 ¥1.2</v>
       </c>
       <c r="G67" t="str">
-        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
+        <v>—</v>
       </c>
       <c r="H67" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
+        <v>入 ¥0.3 · 出 ¥1.2</v>
       </c>
       <c r="I67" t="str">
-        <v>入 $0.646154 · 出 $2.584615 · 缓 $0.129231</v>
+        <v>—</v>
       </c>
       <c r="J67" t="str">
-        <v>0%</v>
+        <v>入 $0.046154 · 出 $0.184615</v>
       </c>
       <c r="K67" t="str">
         <v>0%</v>
@@ -3793,48 +3940,51 @@
         <v>—</v>
       </c>
       <c r="N67" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O67" t="str">
-        <v>入⚠-53.6% 出⚠-53.6% 缓⚠-53.6%</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="P67" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="Q67" t="str">
-        <v>512k 以上输入档仍在内测开放中</v>
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="R67" t="str">
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>qwen-flash</v>
+        <v>hy-mt2-plus</v>
       </c>
       <c r="B68" t="str">
-        <v>Qwen Flash</v>
+        <v>hy-mt2-plus</v>
       </c>
       <c r="C68" t="str">
-        <v>Tongyi</v>
+        <v>Hy-MT2 Plus</v>
       </c>
       <c r="D68" t="str">
-        <v>0&lt;Token≤128K</v>
+        <v>Tencent</v>
       </c>
       <c r="E68" t="str">
-        <v>入 ¥0.15 · 出 ¥1.5 · 缓 ¥0.03</v>
+        <v>标准价</v>
       </c>
       <c r="F68" t="str">
-        <v>—</v>
+        <v>入 ¥0.5 · 出 ¥2</v>
       </c>
       <c r="G68" t="str">
         <v>—</v>
       </c>
       <c r="H68" t="str">
-        <v>—</v>
+        <v>入 ¥0.5 · 出 ¥2</v>
       </c>
       <c r="I68" t="str">
-        <v>入 $0.023077 · 出 $0.230769 · 缓 $0.004615</v>
+        <v>—</v>
       </c>
       <c r="J68" t="str">
-        <v>0%</v>
+        <v>入 $0.076923 · 出 $0.307692</v>
       </c>
       <c r="K68" t="str">
         <v>0%</v>
@@ -3849,42 +3999,54 @@
         <v>—</v>
       </c>
       <c r="O68" t="str">
-        <v>—</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="P68" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="Q68" t="str">
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="R68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="str">
+        <v>hy-mt2-pro</v>
+      </c>
+      <c r="B69" t="str">
+        <v>hy-mt2-pro</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Hy-MT2 Pro</v>
+      </c>
       <c r="D69" t="str">
-        <v>128K&lt;Token≤256K</v>
+        <v>Tencent</v>
       </c>
       <c r="E69" t="str">
-        <v>入 ¥0.6 · 出 ¥6 · 缓 ¥0.12</v>
+        <v>标准价</v>
       </c>
       <c r="F69" t="str">
-        <v>—</v>
+        <v>入 ¥0.5 · 出 ¥2</v>
       </c>
       <c r="G69" t="str">
         <v>—</v>
       </c>
       <c r="H69" t="str">
-        <v>—</v>
+        <v>入 ¥0.5 · 出 ¥2</v>
       </c>
       <c r="I69" t="str">
         <v>—</v>
       </c>
       <c r="J69" t="str">
-        <v>—</v>
+        <v>入 $0.076923 · 出 $0.307692</v>
       </c>
       <c r="K69" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L69" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M69" t="str">
         <v>—</v>
@@ -3893,42 +4055,54 @@
         <v>—</v>
       </c>
       <c r="O69" t="str">
-        <v>—</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="P69" t="str">
-        <v>ℹ 线上无同档</v>
+        <v>—</v>
       </c>
       <c r="Q69" t="str">
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="R69" t="str">
         <v/>
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="str">
+        <v>hy-role</v>
+      </c>
+      <c r="B70" t="str">
+        <v>hy-role</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Hy-Role</v>
+      </c>
       <c r="D70" t="str">
-        <v>256K&lt;Token≤1M</v>
+        <v>Tencent</v>
       </c>
       <c r="E70" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
+        <v>标准价</v>
       </c>
       <c r="F70" t="str">
-        <v>—</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="G70" t="str">
         <v>—</v>
       </c>
       <c r="H70" t="str">
-        <v>—</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="I70" t="str">
         <v>—</v>
       </c>
       <c r="J70" t="str">
-        <v>—</v>
+        <v>入 $0.369231 · 出 $1.476923</v>
       </c>
       <c r="K70" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L70" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M70" t="str">
         <v>—</v>
@@ -3937,33 +4111,36 @@
         <v>—</v>
       </c>
       <c r="O70" t="str">
-        <v>—</v>
+        <v>入✅ 出✅</v>
       </c>
       <c r="P70" t="str">
-        <v>ℹ 线上无同档</v>
+        <v>—</v>
       </c>
       <c r="Q70" t="str">
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="R70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>qwen-max</v>
+        <v>hy-vision-2.0-instruct</v>
       </c>
       <c r="B71" t="str">
-        <v>Qwen Max</v>
+        <v>hy-vision-2.0-instruct</v>
       </c>
       <c r="C71" t="str">
-        <v>Tongyi</v>
+        <v>Hy-Vision 2.0 Instruct</v>
       </c>
       <c r="D71" t="str">
-        <v>无阶梯计价</v>
+        <v>Tencent</v>
       </c>
       <c r="E71" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>标准价</v>
       </c>
       <c r="F71" t="str">
-        <v>—</v>
+        <v>入 ¥7.5 · 出 ¥17.5</v>
       </c>
       <c r="G71" t="str">
         <v>—</v>
@@ -3972,16 +4149,16 @@
         <v>—</v>
       </c>
       <c r="I71" t="str">
-        <v>入 $0.369231 · 出 $1.476923 · 缓 $0.082759</v>
+        <v>—</v>
       </c>
       <c r="J71" t="str">
-        <v>0%</v>
+        <v>入 $1.153846 · 出 $2.692308</v>
       </c>
       <c r="K71" t="str">
         <v>0%</v>
       </c>
       <c r="L71" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M71" t="str">
         <v>—</v>
@@ -3993,42 +4170,45 @@
         <v>—</v>
       </c>
       <c r="P71" t="str">
-        <v>入✅ 出✅ 缓—</v>
+        <v>—</v>
       </c>
       <c r="Q71" t="str">
-        <v/>
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="R71" t="str">
+        <v>多模态视觉理解 · 按 token 计费</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>qwen-plus</v>
+        <v>hy3-preview</v>
       </c>
       <c r="B72" t="str">
-        <v>Qwen Plus</v>
+        <v>hy3-preview</v>
       </c>
       <c r="C72" t="str">
-        <v>Tongyi</v>
+        <v>Hy3 Preview</v>
       </c>
       <c r="D72" t="str">
-        <v>0&lt;Token≤128K</v>
+        <v>Tencent</v>
       </c>
       <c r="E72" t="str">
-        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+        <v>输入&lt;16k</v>
       </c>
       <c r="F72" t="str">
-        <v>—</v>
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
       </c>
       <c r="G72" t="str">
         <v>—</v>
       </c>
       <c r="H72" t="str">
-        <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
       </c>
       <c r="I72" t="str">
-        <v>入 $0.123077 · 出 $0.307692 · 缓 $0.024615</v>
+        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
       <c r="J72" t="str">
-        <v>0%</v>
+        <v>入 $0.184615 · 出 $0.615385 · 缓 $0.061538</v>
       </c>
       <c r="K72" t="str">
         <v>0%</v>
@@ -4037,127 +4217,130 @@
         <v>0%</v>
       </c>
       <c r="M72" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N72" t="str">
         <v>—</v>
       </c>
       <c r="O72" t="str">
-        <v>入⚠+111.3% 出⚠+153.5% 缓⚠+111.3%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P72" t="str">
+        <v>入⚠-65.9% 出⚠-65.9% 缓⚠-65.9%</v>
+      </c>
+      <c r="Q72" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q72" t="str">
+      <c r="R72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="D73" t="str">
-        <v>128K&lt;Token≤256K</v>
-      </c>
       <c r="E73" t="str">
-        <v>入 ¥2.4 · 出 ¥20 · 缓 ¥0.48</v>
+        <v>16k≤输入&lt;32k</v>
       </c>
       <c r="F73" t="str">
-        <v>—</v>
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
       <c r="G73" t="str">
         <v>—</v>
       </c>
       <c r="H73" t="str">
-        <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
       <c r="I73" t="str">
-        <v>—</v>
+        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
       <c r="J73" t="str">
-        <v>—</v>
+        <v>入 $0.246154 · 出 $0.984615 · 缓 $0.092308</v>
       </c>
       <c r="K73" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L73" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M73" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N73" t="str">
         <v>—</v>
       </c>
       <c r="O73" t="str">
-        <v>入⚠-29.6% 出⚠-74.6% 缓⚠-29.6%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P73" t="str">
-        <v>ℹ 线上无同档</v>
+        <v>入⚠-74.4% 出⚠-78.7% 缓⚠-77.2%</v>
       </c>
       <c r="Q73" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="D74" t="str">
-        <v>256K&lt;Token≤1M</v>
-      </c>
       <c r="E74" t="str">
-        <v>入 ¥4.8 · 出 ¥48 · 缓 ¥0.96</v>
+        <v>输入≥32k</v>
       </c>
       <c r="F74" t="str">
-        <v>—</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="G74" t="str">
         <v>—</v>
       </c>
       <c r="H74" t="str">
-        <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="I74" t="str">
-        <v>—</v>
+        <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
       <c r="J74" t="str">
-        <v>—</v>
+        <v>入 $0.307692 · 出 $1.230769 · 缓 $0.123077</v>
       </c>
       <c r="K74" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="L74" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M74" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N74" t="str">
         <v>—</v>
       </c>
       <c r="O74" t="str">
-        <v>入⚠-64.8% 出⚠-89.4% 缓⚠-64.8%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P74" t="str">
-        <v>ℹ 线上无同档</v>
+        <v>入⚠-79.5% 出⚠-82.9% 缓⚠-82.9%</v>
       </c>
       <c r="Q74" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>qwen-turbo</v>
+        <v>qwen-flash</v>
       </c>
       <c r="B75" t="str">
-        <v>Qwen Turbo</v>
+        <v>qwen-flash</v>
       </c>
       <c r="C75" t="str">
+        <v>Qwen Flash</v>
+      </c>
+      <c r="D75" t="str">
         <v>Tongyi</v>
       </c>
-      <c r="D75" t="str">
-        <v>统一价</v>
-      </c>
       <c r="E75" t="str">
-        <v>入 ¥0.3 · 出 ¥0.6</v>
+        <v>输入≤128k</v>
       </c>
       <c r="F75" t="str">
-        <v>—</v>
+        <v>入 ¥0.15 · 出 ¥1.5 · 缓 ¥0.03</v>
       </c>
       <c r="G75" t="str">
         <v>—</v>
@@ -4166,19 +4349,19 @@
         <v>—</v>
       </c>
       <c r="I75" t="str">
-        <v>入 $0.046154 · 出 $0.092308 · 缓 $0.010345</v>
+        <v>—</v>
       </c>
       <c r="J75" t="str">
-        <v>0%</v>
+        <v>入 $0.023077 · 出 $0.230769 · 缓 $0.004615</v>
       </c>
       <c r="K75" t="str">
         <v>0%</v>
       </c>
       <c r="L75" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="M75" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N75" t="str">
         <v>—</v>
@@ -4187,183 +4370,189 @@
         <v>—</v>
       </c>
       <c r="P75" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q75" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="E76" t="str">
+        <v>128k&lt;输入≤256k</v>
+      </c>
+      <c r="F76" t="str">
+        <v>入 ¥0.6 · 出 ¥6 · 缓 ¥0.12</v>
+      </c>
+      <c r="G76" t="str">
+        <v>—</v>
+      </c>
+      <c r="H76" t="str">
+        <v>—</v>
+      </c>
+      <c r="I76" t="str">
+        <v>—</v>
+      </c>
+      <c r="J76" t="str">
+        <v>—</v>
+      </c>
+      <c r="K76" t="str">
+        <v>—</v>
+      </c>
+      <c r="L76" t="str">
+        <v>—</v>
+      </c>
+      <c r="M76" t="str">
+        <v>—</v>
+      </c>
+      <c r="N76" t="str">
+        <v>—</v>
+      </c>
+      <c r="O76" t="str">
+        <v>—</v>
+      </c>
+      <c r="P76" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q76" t="str">
+        <v>ℹ 线上无同档</v>
+      </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="E77" t="str">
+        <v>256k&lt;输入≤1M</v>
+      </c>
+      <c r="F77" t="str">
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
+      </c>
+      <c r="G77" t="str">
+        <v>—</v>
+      </c>
+      <c r="H77" t="str">
+        <v>—</v>
+      </c>
+      <c r="I77" t="str">
+        <v>—</v>
+      </c>
+      <c r="J77" t="str">
+        <v>—</v>
+      </c>
+      <c r="K77" t="str">
+        <v>—</v>
+      </c>
+      <c r="L77" t="str">
+        <v>—</v>
+      </c>
+      <c r="M77" t="str">
+        <v>—</v>
+      </c>
+      <c r="N77" t="str">
+        <v>—</v>
+      </c>
+      <c r="O77" t="str">
+        <v>—</v>
+      </c>
+      <c r="P77" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q77" t="str">
+        <v>ℹ 线上无同档</v>
+      </c>
+      <c r="R77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>qwen-max</v>
+      </c>
+      <c r="B78" t="str">
+        <v>qwen-max</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Qwen Max</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="E78" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F78" t="str">
+        <v>入 ¥2.4 · 出 ¥9.6</v>
+      </c>
+      <c r="G78" t="str">
+        <v>—</v>
+      </c>
+      <c r="H78" t="str">
+        <v>—</v>
+      </c>
+      <c r="I78" t="str">
+        <v>—</v>
+      </c>
+      <c r="J78" t="str">
+        <v>入 $0.369231 · 出 $1.476923 · 缓 $0.082759</v>
+      </c>
+      <c r="K78" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L78" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M78" t="str">
+        <v>—</v>
+      </c>
+      <c r="N78" t="str">
+        <v>—</v>
+      </c>
+      <c r="O78" t="str">
+        <v>—</v>
+      </c>
+      <c r="P78" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q78" t="str">
         <v>入✅ 出✅ 缓—</v>
       </c>
-      <c r="Q75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>qwen3.5-flash</v>
-      </c>
-      <c r="B76" t="str">
-        <v>Qwen3.5 Flash</v>
-      </c>
-      <c r="C76" t="str">
-        <v>Tongyi</v>
-      </c>
-      <c r="D76" t="str">
-        <v>0&lt;输入&lt;=128k</v>
-      </c>
-      <c r="E76" t="str">
-        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
-      </c>
-      <c r="F76" t="str">
-        <v>—</v>
-      </c>
-      <c r="G76" t="str">
-        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
-      </c>
-      <c r="H76" t="str">
-        <v>入 $0.065 · 出 $0.26</v>
-      </c>
-      <c r="I76" t="str">
-        <v>入 $0.030769 · 出 $0.307692 · 缓 $0.003077</v>
-      </c>
-      <c r="J76" t="str">
-        <v>0%</v>
-      </c>
-      <c r="K76" t="str">
-        <v>0%</v>
-      </c>
-      <c r="L76" t="str">
-        <v>0%</v>
-      </c>
-      <c r="M76" t="str">
-        <v>—</v>
-      </c>
-      <c r="N76" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="O76" t="str">
-        <v>入⚠+111.3% 出⚠-15.5%</v>
-      </c>
-      <c r="P76" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="Q76" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="D77" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
-      </c>
-      <c r="E77" t="str">
-        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
-      </c>
-      <c r="F77" t="str">
-        <v>—</v>
-      </c>
-      <c r="G77" t="str">
-        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
-      </c>
-      <c r="H77" t="str">
-        <v>入 $0.065 · 出 $0.26</v>
-      </c>
-      <c r="I77" t="str">
-        <v>—</v>
-      </c>
-      <c r="J77" t="str">
-        <v>—</v>
-      </c>
-      <c r="K77" t="str">
-        <v>—</v>
-      </c>
-      <c r="L77" t="str">
-        <v>—</v>
-      </c>
-      <c r="M77" t="str">
-        <v>—</v>
-      </c>
-      <c r="N77" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="O77" t="str">
-        <v>入⚠-47.2% 出⚠-78.9%</v>
-      </c>
-      <c r="P77" t="str">
-        <v>ℹ 线上无同档</v>
-      </c>
-      <c r="Q77" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="D78" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
-      </c>
-      <c r="E78" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
-      </c>
-      <c r="F78" t="str">
-        <v>—</v>
-      </c>
-      <c r="G78" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
-      </c>
-      <c r="H78" t="str">
-        <v>入 $0.065 · 出 $0.26</v>
-      </c>
-      <c r="I78" t="str">
-        <v>—</v>
-      </c>
-      <c r="J78" t="str">
-        <v>—</v>
-      </c>
-      <c r="K78" t="str">
-        <v>—</v>
-      </c>
-      <c r="L78" t="str">
-        <v>—</v>
-      </c>
-      <c r="M78" t="str">
-        <v>—</v>
-      </c>
-      <c r="N78" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="O78" t="str">
-        <v>入⚠-64.8% 出⚠-85.9%</v>
-      </c>
-      <c r="P78" t="str">
-        <v>ℹ 线上无同档</v>
-      </c>
-      <c r="Q78" t="str">
+      <c r="R78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>qwen3.5-plus</v>
+        <v>qwen-plus</v>
       </c>
       <c r="B79" t="str">
-        <v>Qwen3.5 Plus</v>
+        <v>qwen-plus</v>
       </c>
       <c r="C79" t="str">
+        <v>Qwen Plus</v>
+      </c>
+      <c r="D79" t="str">
         <v>Tongyi</v>
       </c>
-      <c r="D79" t="str">
-        <v>输入&lt;=128k</v>
-      </c>
       <c r="E79" t="str">
-        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+        <v>输入≤128k</v>
       </c>
       <c r="F79" t="str">
-        <v>—</v>
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
       </c>
       <c r="G79" t="str">
-        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+        <v>—</v>
       </c>
       <c r="H79" t="str">
-        <v>入 $0.3 · 出 $1.7999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I79" t="str">
-        <v>入 $0.123077 · 出 $0.738462 · 缓 $0.012308</v>
+        <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
       </c>
       <c r="J79" t="str">
-        <v>0%</v>
+        <v>入 $0.123077 · 出 $0.307692 · 缓 $0.024615</v>
       </c>
       <c r="K79" t="str">
         <v>0%</v>
@@ -4372,39 +4561,39 @@
         <v>0%</v>
       </c>
       <c r="M79" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N79" t="str">
+        <v>—</v>
+      </c>
+      <c r="O79" t="str">
+        <v>—</v>
+      </c>
+      <c r="P79" t="str">
+        <v>入⚠+111.3% 出⚠+153.5% 缓⚠+111.3%</v>
+      </c>
+      <c r="Q79" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O79" t="str">
-        <v>入⚠+143.7% 出⚠+143.7%</v>
-      </c>
-      <c r="P79" t="str">
-        <v>入✅ 出✅ 缓✅</v>
-      </c>
-      <c r="Q79" t="str">
+      <c r="R79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="D80" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
-      </c>
       <c r="E80" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+        <v>128k&lt;输入≤256k</v>
       </c>
       <c r="F80" t="str">
-        <v>—</v>
+        <v>入 ¥2.4 · 出 ¥20 · 缓 ¥0.48</v>
       </c>
       <c r="G80" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+        <v>—</v>
       </c>
       <c r="H80" t="str">
-        <v>入 $0.3 · 出 $1.7999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I80" t="str">
-        <v>—</v>
+        <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
       </c>
       <c r="J80" t="str">
         <v>—</v>
@@ -4419,36 +4608,36 @@
         <v>—</v>
       </c>
       <c r="N80" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O80" t="str">
-        <v>入⚠-2.5% 出⚠-2.5%</v>
+        <v>—</v>
       </c>
       <c r="P80" t="str">
+        <v>入⚠-29.6% 出⚠-74.6% 缓⚠-29.6%</v>
+      </c>
+      <c r="Q80" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="Q80" t="str">
+      <c r="R80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="D81" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
-      </c>
       <c r="E81" t="str">
-        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
+        <v>256k&lt;输入≤1M</v>
       </c>
       <c r="F81" t="str">
-        <v>—</v>
+        <v>入 ¥4.8 · 出 ¥48 · 缓 ¥0.96</v>
       </c>
       <c r="G81" t="str">
-        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
+        <v>—</v>
       </c>
       <c r="H81" t="str">
-        <v>入 $0.3 · 出 $1.7999999999999998</v>
+        <v>—</v>
       </c>
       <c r="I81" t="str">
-        <v>—</v>
+        <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
       </c>
       <c r="J81" t="str">
         <v>—</v>
@@ -4463,48 +4652,51 @@
         <v>—</v>
       </c>
       <c r="N81" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="O81" t="str">
-        <v>入⚠-51.3% 出⚠-51.3%</v>
+        <v>—</v>
       </c>
       <c r="P81" t="str">
+        <v>入⚠-64.8% 出⚠-89.4% 缓⚠-64.8%</v>
+      </c>
+      <c r="Q81" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="Q81" t="str">
+      <c r="R81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>qwen3.6-flash</v>
+        <v>qwen-turbo</v>
       </c>
       <c r="B82" t="str">
-        <v>Qwen3.6 Flash</v>
+        <v>qwen-turbo</v>
       </c>
       <c r="C82" t="str">
+        <v>Qwen Turbo</v>
+      </c>
+      <c r="D82" t="str">
         <v>Tongyi</v>
       </c>
-      <c r="D82" t="str">
-        <v>0&lt;Token≤256K</v>
-      </c>
       <c r="E82" t="str">
-        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
+        <v>标准价</v>
       </c>
       <c r="F82" t="str">
-        <v>—</v>
+        <v>入 ¥0.3 · 出 ¥0.6</v>
       </c>
       <c r="G82" t="str">
         <v>—</v>
       </c>
       <c r="H82" t="str">
-        <v>入 $0.1875 · 出 $1.125</v>
+        <v>—</v>
       </c>
       <c r="I82" t="str">
-        <v>入 $0.184615 · 出 $1.107692 · 缓 $0.036923</v>
+        <v>—</v>
       </c>
       <c r="J82" t="str">
-        <v>0%</v>
+        <v>入 $0.046154 · 出 $0.092308 · 缓 $0.010345</v>
       </c>
       <c r="K82" t="str">
         <v>0%</v>
@@ -4519,387 +4711,1558 @@
         <v>—</v>
       </c>
       <c r="O82" t="str">
-        <v>入⚠+1.6% 出⚠+1.6%</v>
+        <v>—</v>
       </c>
       <c r="P82" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q82" t="str">
+        <v>入✅ 出✅ 缓—</v>
+      </c>
+      <c r="R82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>qwen3.5-flash</v>
+      </c>
+      <c r="B83" t="str">
+        <v>qwen3.5-flash</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Qwen3.5 Flash</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="E83" t="str">
+        <v>输入≤128k</v>
+      </c>
+      <c r="F83" t="str">
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
+      </c>
+      <c r="G83" t="str">
+        <v>—</v>
+      </c>
+      <c r="H83" t="str">
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
+      </c>
+      <c r="I83" t="str">
+        <v>入 $0.065 · 出 $0.26</v>
+      </c>
+      <c r="J83" t="str">
+        <v>入 $0.030769 · 出 $0.307692 · 缓 $0.003077</v>
+      </c>
+      <c r="K83" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L83" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M83" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N83" t="str">
+        <v>—</v>
+      </c>
+      <c r="O83" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q82" t="str">
+      <c r="P83" t="str">
+        <v>入⚠+111.3% 出⚠-15.5%</v>
+      </c>
+      <c r="Q83" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R83" t="str">
         <v/>
       </c>
     </row>
-    <row r="83">
-      <c r="D83" t="str">
-        <v>256K&lt;Token≤1M</v>
-      </c>
-      <c r="E83" t="str">
-        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
-      </c>
-      <c r="F83" t="str">
-        <v>—</v>
-      </c>
-      <c r="G83" t="str">
-        <v>—</v>
-      </c>
-      <c r="H83" t="str">
-        <v>入 $0.1875 · 出 $1.125</v>
-      </c>
-      <c r="I83" t="str">
-        <v>—</v>
-      </c>
-      <c r="J83" t="str">
-        <v>—</v>
-      </c>
-      <c r="K83" t="str">
-        <v>—</v>
-      </c>
-      <c r="L83" t="str">
-        <v>—</v>
-      </c>
-      <c r="M83" t="str">
-        <v>—</v>
-      </c>
-      <c r="N83" t="str">
-        <v>—</v>
-      </c>
-      <c r="O83" t="str">
-        <v>入⚠-74.6% 出⚠-74.6%</v>
-      </c>
-      <c r="P83" t="str">
+    <row r="84">
+      <c r="E84" t="str">
+        <v>128k&lt;输入≤256k</v>
+      </c>
+      <c r="F84" t="str">
+        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
+      </c>
+      <c r="G84" t="str">
+        <v>—</v>
+      </c>
+      <c r="H84" t="str">
+        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
+      </c>
+      <c r="I84" t="str">
+        <v>入 $0.065 · 出 $0.26</v>
+      </c>
+      <c r="J84" t="str">
+        <v>—</v>
+      </c>
+      <c r="K84" t="str">
+        <v>—</v>
+      </c>
+      <c r="L84" t="str">
+        <v>—</v>
+      </c>
+      <c r="M84" t="str">
+        <v>—</v>
+      </c>
+      <c r="N84" t="str">
+        <v>—</v>
+      </c>
+      <c r="O84" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="P84" t="str">
+        <v>入⚠-47.2% 出⚠-78.9%</v>
+      </c>
+      <c r="Q84" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="Q83" t="str">
+      <c r="R84" t="str">
         <v/>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>qwen3.6-plus</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Qwen3.6 Plus</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Tongyi</v>
-      </c>
-      <c r="D84" t="str">
-        <v>0&lt;Token≤256K</v>
-      </c>
-      <c r="E84" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
-      </c>
-      <c r="F84" t="str">
-        <v>—</v>
-      </c>
-      <c r="G84" t="str">
-        <v>—</v>
-      </c>
-      <c r="H84" t="str">
-        <v>入 $0.325 · 出 $1.95</v>
-      </c>
-      <c r="I84" t="str">
-        <v>入 $0.307692 · 出 $1.846154 · 缓 $0.061538</v>
-      </c>
-      <c r="J84" t="str">
-        <v>0%</v>
-      </c>
-      <c r="K84" t="str">
-        <v>0%</v>
-      </c>
-      <c r="L84" t="str">
-        <v>0%</v>
-      </c>
-      <c r="M84" t="str">
-        <v>—</v>
-      </c>
-      <c r="N84" t="str">
-        <v>—</v>
-      </c>
-      <c r="O84" t="str">
-        <v>入⚠+5.6% 出⚠+5.6%</v>
-      </c>
-      <c r="P84" t="str">
+    <row r="85">
+      <c r="E85" t="str">
+        <v>256k&lt;输入≤1M</v>
+      </c>
+      <c r="F85" t="str">
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
+      </c>
+      <c r="G85" t="str">
+        <v>—</v>
+      </c>
+      <c r="H85" t="str">
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
+      </c>
+      <c r="I85" t="str">
+        <v>入 $0.065 · 出 $0.26</v>
+      </c>
+      <c r="J85" t="str">
+        <v>—</v>
+      </c>
+      <c r="K85" t="str">
+        <v>—</v>
+      </c>
+      <c r="L85" t="str">
+        <v>—</v>
+      </c>
+      <c r="M85" t="str">
+        <v>—</v>
+      </c>
+      <c r="N85" t="str">
+        <v>—</v>
+      </c>
+      <c r="O85" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q84" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="D85" t="str">
-        <v>256K&lt;Token≤1M</v>
-      </c>
-      <c r="E85" t="str">
-        <v>入 ¥8 · 出 ¥48 · 缓 ¥1.6</v>
-      </c>
-      <c r="F85" t="str">
-        <v>—</v>
-      </c>
-      <c r="G85" t="str">
-        <v>—</v>
-      </c>
-      <c r="H85" t="str">
-        <v>入 $0.325 · 出 $1.95</v>
-      </c>
-      <c r="I85" t="str">
-        <v>—</v>
-      </c>
-      <c r="J85" t="str">
-        <v>—</v>
-      </c>
-      <c r="K85" t="str">
-        <v>—</v>
-      </c>
-      <c r="L85" t="str">
-        <v>—</v>
-      </c>
-      <c r="M85" t="str">
-        <v>—</v>
-      </c>
-      <c r="N85" t="str">
-        <v>—</v>
-      </c>
-      <c r="O85" t="str">
-        <v>入⚠-73.6% 出⚠-73.6%</v>
-      </c>
       <c r="P85" t="str">
+        <v>入⚠-64.8% 出⚠-85.9%</v>
+      </c>
+      <c r="Q85" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="Q85" t="str">
+      <c r="R85" t="str">
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
+        <v>qwen3.5-plus</v>
+      </c>
+      <c r="B86" t="str">
+        <v>qwen3.5-plus</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Qwen3.5 Plus</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="E86" t="str">
+        <v>输入≤128k</v>
+      </c>
+      <c r="F86" t="str">
+        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+      </c>
+      <c r="G86" t="str">
+        <v>—</v>
+      </c>
+      <c r="H86" t="str">
+        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+      </c>
+      <c r="I86" t="str">
+        <v>入 $0.3 · 出 $1.7999999999999998</v>
+      </c>
+      <c r="J86" t="str">
+        <v>入 $0.123077 · 出 $0.738462 · 缓 $0.012308</v>
+      </c>
+      <c r="K86" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L86" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M86" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N86" t="str">
+        <v>—</v>
+      </c>
+      <c r="O86" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="P86" t="str">
+        <v>入⚠+143.7% 出⚠+143.7%</v>
+      </c>
+      <c r="Q86" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="E87" t="str">
+        <v>128k&lt;输入≤256k</v>
+      </c>
+      <c r="F87" t="str">
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+      </c>
+      <c r="G87" t="str">
+        <v>—</v>
+      </c>
+      <c r="H87" t="str">
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+      </c>
+      <c r="I87" t="str">
+        <v>入 $0.3 · 出 $1.7999999999999998</v>
+      </c>
+      <c r="J87" t="str">
+        <v>—</v>
+      </c>
+      <c r="K87" t="str">
+        <v>—</v>
+      </c>
+      <c r="L87" t="str">
+        <v>—</v>
+      </c>
+      <c r="M87" t="str">
+        <v>—</v>
+      </c>
+      <c r="N87" t="str">
+        <v>—</v>
+      </c>
+      <c r="O87" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="P87" t="str">
+        <v>入⚠-2.5% 出⚠-2.5%</v>
+      </c>
+      <c r="Q87" t="str">
+        <v>ℹ 线上无同档</v>
+      </c>
+      <c r="R87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="E88" t="str">
+        <v>256k&lt;输入≤1M</v>
+      </c>
+      <c r="F88" t="str">
+        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
+      </c>
+      <c r="G88" t="str">
+        <v>—</v>
+      </c>
+      <c r="H88" t="str">
+        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
+      </c>
+      <c r="I88" t="str">
+        <v>入 $0.3 · 出 $1.7999999999999998</v>
+      </c>
+      <c r="J88" t="str">
+        <v>—</v>
+      </c>
+      <c r="K88" t="str">
+        <v>—</v>
+      </c>
+      <c r="L88" t="str">
+        <v>—</v>
+      </c>
+      <c r="M88" t="str">
+        <v>—</v>
+      </c>
+      <c r="N88" t="str">
+        <v>—</v>
+      </c>
+      <c r="O88" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="P88" t="str">
+        <v>入⚠-51.3% 出⚠-51.3%</v>
+      </c>
+      <c r="Q88" t="str">
+        <v>ℹ 线上无同档</v>
+      </c>
+      <c r="R88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>qwen3.6-flash</v>
+      </c>
+      <c r="B89" t="str">
+        <v>qwen3.6-flash</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Qwen3.6 Flash</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="E89" t="str">
+        <v>输入≤256k</v>
+      </c>
+      <c r="F89" t="str">
+        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
+      </c>
+      <c r="G89" t="str">
+        <v>—</v>
+      </c>
+      <c r="H89" t="str">
+        <v>—</v>
+      </c>
+      <c r="I89" t="str">
+        <v>入 $0.1875 · 出 $1.125</v>
+      </c>
+      <c r="J89" t="str">
+        <v>入 $0.184615 · 出 $1.107692 · 缓 $0.036923</v>
+      </c>
+      <c r="K89" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L89" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M89" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N89" t="str">
+        <v>—</v>
+      </c>
+      <c r="O89" t="str">
+        <v>—</v>
+      </c>
+      <c r="P89" t="str">
+        <v>入⚠+1.6% 出⚠+1.6%</v>
+      </c>
+      <c r="Q89" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="E90" t="str">
+        <v>256k&lt;输入≤1M</v>
+      </c>
+      <c r="F90" t="str">
+        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
+      </c>
+      <c r="G90" t="str">
+        <v>—</v>
+      </c>
+      <c r="H90" t="str">
+        <v>—</v>
+      </c>
+      <c r="I90" t="str">
+        <v>入 $0.1875 · 出 $1.125</v>
+      </c>
+      <c r="J90" t="str">
+        <v>—</v>
+      </c>
+      <c r="K90" t="str">
+        <v>—</v>
+      </c>
+      <c r="L90" t="str">
+        <v>—</v>
+      </c>
+      <c r="M90" t="str">
+        <v>—</v>
+      </c>
+      <c r="N90" t="str">
+        <v>—</v>
+      </c>
+      <c r="O90" t="str">
+        <v>—</v>
+      </c>
+      <c r="P90" t="str">
+        <v>入⚠-74.6% 出⚠-74.6%</v>
+      </c>
+      <c r="Q90" t="str">
+        <v>ℹ 线上无同档</v>
+      </c>
+      <c r="R90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>qwen3.6-plus</v>
+      </c>
+      <c r="B91" t="str">
+        <v>qwen3.6-plus</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Qwen3.6 Plus</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="E91" t="str">
+        <v>输入≤256k</v>
+      </c>
+      <c r="F91" t="str">
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
+      </c>
+      <c r="G91" t="str">
+        <v>—</v>
+      </c>
+      <c r="H91" t="str">
+        <v>—</v>
+      </c>
+      <c r="I91" t="str">
+        <v>入 $0.325 · 出 $1.95</v>
+      </c>
+      <c r="J91" t="str">
+        <v>入 $0.307692 · 出 $1.846154 · 缓 $0.061538</v>
+      </c>
+      <c r="K91" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L91" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M91" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N91" t="str">
+        <v>—</v>
+      </c>
+      <c r="O91" t="str">
+        <v>—</v>
+      </c>
+      <c r="P91" t="str">
+        <v>入⚠+5.6% 出⚠+5.6%</v>
+      </c>
+      <c r="Q91" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="R91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="E92" t="str">
+        <v>256k&lt;输入≤1M</v>
+      </c>
+      <c r="F92" t="str">
+        <v>入 ¥8 · 出 ¥48 · 缓 ¥1.6</v>
+      </c>
+      <c r="G92" t="str">
+        <v>—</v>
+      </c>
+      <c r="H92" t="str">
+        <v>—</v>
+      </c>
+      <c r="I92" t="str">
+        <v>入 $0.325 · 出 $1.95</v>
+      </c>
+      <c r="J92" t="str">
+        <v>—</v>
+      </c>
+      <c r="K92" t="str">
+        <v>—</v>
+      </c>
+      <c r="L92" t="str">
+        <v>—</v>
+      </c>
+      <c r="M92" t="str">
+        <v>—</v>
+      </c>
+      <c r="N92" t="str">
+        <v>—</v>
+      </c>
+      <c r="O92" t="str">
+        <v>—</v>
+      </c>
+      <c r="P92" t="str">
+        <v>入⚠-73.6% 出⚠-73.6%</v>
+      </c>
+      <c r="Q92" t="str">
+        <v>ℹ 线上无同档</v>
+      </c>
+      <c r="R92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
         <v>qwen3.7-max</v>
       </c>
-      <c r="B86" t="str">
+      <c r="B93" t="str">
+        <v>qwen3.7-max</v>
+      </c>
+      <c r="C93" t="str">
         <v>Qwen3.7 Max</v>
       </c>
-      <c r="C86" t="str">
+      <c r="D93" t="str">
         <v>Tongyi</v>
       </c>
-      <c r="D86" t="str">
-        <v>0&lt;Token≤1M</v>
-      </c>
-      <c r="E86" t="str">
+      <c r="E93" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F93" t="str">
         <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
       </c>
-      <c r="F86" t="str">
-        <v>—</v>
-      </c>
-      <c r="G86" t="str">
-        <v>—</v>
-      </c>
-      <c r="H86" t="str">
+      <c r="G93" t="str">
+        <v>—</v>
+      </c>
+      <c r="H93" t="str">
+        <v>—</v>
+      </c>
+      <c r="I93" t="str">
         <v>入 $1.25 · 出 $3.75 · 缓 $0.25</v>
       </c>
-      <c r="I86" t="str">
+      <c r="J93" t="str">
         <v>入 $1.846154 · 出 $5.538462 · 缓 $0.369231</v>
       </c>
-      <c r="J86" t="str">
-        <v>0%</v>
-      </c>
-      <c r="K86" t="str">
-        <v>0%</v>
-      </c>
-      <c r="L86" t="str">
-        <v>0%</v>
-      </c>
-      <c r="M86" t="str">
-        <v>—</v>
-      </c>
-      <c r="N86" t="str">
-        <v>—</v>
-      </c>
-      <c r="O86" t="str">
+      <c r="K93" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L93" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M93" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N93" t="str">
+        <v>—</v>
+      </c>
+      <c r="O93" t="str">
+        <v>—</v>
+      </c>
+      <c r="P93" t="str">
         <v>入⚠-32.3% 出⚠-32.3% 缓⚠-32.3%</v>
       </c>
-      <c r="P86" t="str">
+      <c r="Q93" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q86" t="str">
+      <c r="R93" t="str">
         <v/>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="str">
+    <row r="94">
+      <c r="A94" t="str">
         <v>qwen3.7-plus</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B94" t="str">
+        <v>qwen3.7-plus</v>
+      </c>
+      <c r="C94" t="str">
         <v>Qwen3.7 Plus</v>
       </c>
-      <c r="C87" t="str">
+      <c r="D94" t="str">
         <v>Tongyi</v>
       </c>
-      <c r="D87" t="str">
-        <v>0&lt;Token≤256K</v>
-      </c>
-      <c r="E87" t="str">
+      <c r="E94" t="str">
+        <v>输入≤256k</v>
+      </c>
+      <c r="F94" t="str">
         <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
       </c>
-      <c r="F87" t="str">
-        <v>—</v>
-      </c>
-      <c r="G87" t="str">
-        <v>—</v>
-      </c>
-      <c r="H87" t="str">
+      <c r="G94" t="str">
+        <v>—</v>
+      </c>
+      <c r="H94" t="str">
+        <v>—</v>
+      </c>
+      <c r="I94" t="str">
         <v>入 $0.32 · 出 $1.28 · 缓 $0.064</v>
       </c>
-      <c r="I87" t="str">
+      <c r="J94" t="str">
         <v>入 $0.307692 · 出 $1.230769 · 缓 $0.061538</v>
       </c>
-      <c r="J87" t="str">
-        <v>0%</v>
-      </c>
-      <c r="K87" t="str">
-        <v>0%</v>
-      </c>
-      <c r="L87" t="str">
-        <v>0%</v>
-      </c>
-      <c r="M87" t="str">
-        <v>—</v>
-      </c>
-      <c r="N87" t="str">
-        <v>—</v>
-      </c>
-      <c r="O87" t="str">
+      <c r="K94" t="str">
+        <v>0%</v>
+      </c>
+      <c r="L94" t="str">
+        <v>0%</v>
+      </c>
+      <c r="M94" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N94" t="str">
+        <v>—</v>
+      </c>
+      <c r="O94" t="str">
+        <v>—</v>
+      </c>
+      <c r="P94" t="str">
         <v>入⚠+4% 出⚠+4% 缓⚠+4%</v>
       </c>
-      <c r="P87" t="str">
+      <c r="Q94" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="Q87" t="str">
+      <c r="R94" t="str">
         <v/>
       </c>
     </row>
-    <row r="88">
-      <c r="D88" t="str">
-        <v>256K&lt;Token≤1M</v>
-      </c>
-      <c r="E88" t="str">
+    <row r="95">
+      <c r="E95" t="str">
+        <v>256k&lt;输入≤1M</v>
+      </c>
+      <c r="F95" t="str">
         <v>入 ¥6 · 出 ¥24 · 缓 ¥1.2</v>
       </c>
-      <c r="F88" t="str">
-        <v>—</v>
-      </c>
-      <c r="G88" t="str">
-        <v>—</v>
-      </c>
-      <c r="H88" t="str">
+      <c r="G95" t="str">
+        <v>—</v>
+      </c>
+      <c r="H95" t="str">
+        <v>—</v>
+      </c>
+      <c r="I95" t="str">
         <v>入 $0.32 · 出 $1.28 · 缓 $0.064</v>
       </c>
-      <c r="I88" t="str">
-        <v>—</v>
-      </c>
-      <c r="J88" t="str">
-        <v>—</v>
-      </c>
-      <c r="K88" t="str">
-        <v>—</v>
-      </c>
-      <c r="L88" t="str">
-        <v>—</v>
-      </c>
-      <c r="M88" t="str">
-        <v>—</v>
-      </c>
-      <c r="N88" t="str">
-        <v>—</v>
-      </c>
-      <c r="O88" t="str">
+      <c r="J95" t="str">
+        <v>—</v>
+      </c>
+      <c r="K95" t="str">
+        <v>—</v>
+      </c>
+      <c r="L95" t="str">
+        <v>—</v>
+      </c>
+      <c r="M95" t="str">
+        <v>—</v>
+      </c>
+      <c r="N95" t="str">
+        <v>—</v>
+      </c>
+      <c r="O95" t="str">
+        <v>—</v>
+      </c>
+      <c r="P95" t="str">
         <v>入⚠-65.3% 出⚠-65.3% 缓⚠-65.3%</v>
       </c>
-      <c r="P88" t="str">
+      <c r="Q95" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="Q88" t="str">
+      <c r="R95" t="str">
         <v/>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>doubao-lite-32k</v>
+      </c>
+      <c r="B96" t="str">
+        <v>—</v>
+      </c>
+      <c r="C96" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="D96" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="E96" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F96" t="str">
+        <v>入 ¥0.3 · 出 ¥0.6 · 缓 ¥0.06</v>
+      </c>
+      <c r="G96" t="str">
+        <v>—</v>
+      </c>
+      <c r="H96" t="str">
+        <v>—</v>
+      </c>
+      <c r="I96" t="str">
+        <v>—</v>
+      </c>
+      <c r="J96" t="str">
+        <v>—</v>
+      </c>
+      <c r="K96" t="str">
+        <v>—</v>
+      </c>
+      <c r="L96" t="str">
+        <v>—</v>
+      </c>
+      <c r="M96" t="str">
+        <v>—</v>
+      </c>
+      <c r="N96" t="str">
+        <v>—</v>
+      </c>
+      <c r="O96" t="str">
+        <v>—</v>
+      </c>
+      <c r="P96" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q96" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>doubao-pro-32k</v>
+      </c>
+      <c r="B97" t="str">
+        <v>—</v>
+      </c>
+      <c r="C97" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="D97" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="E97" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F97" t="str">
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+      </c>
+      <c r="G97" t="str">
+        <v>—</v>
+      </c>
+      <c r="H97" t="str">
+        <v>—</v>
+      </c>
+      <c r="I97" t="str">
+        <v>—</v>
+      </c>
+      <c r="J97" t="str">
+        <v>—</v>
+      </c>
+      <c r="K97" t="str">
+        <v>—</v>
+      </c>
+      <c r="L97" t="str">
+        <v>—</v>
+      </c>
+      <c r="M97" t="str">
+        <v>—</v>
+      </c>
+      <c r="N97" t="str">
+        <v>—</v>
+      </c>
+      <c r="O97" t="str">
+        <v>—</v>
+      </c>
+      <c r="P97" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q97" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>doubao-seed-1-6</v>
+      </c>
+      <c r="B98" t="str">
+        <v>—</v>
+      </c>
+      <c r="C98" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="D98" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="E98" t="str">
+        <v>输入≤32k</v>
+      </c>
+      <c r="F98" t="str">
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+      </c>
+      <c r="G98" t="str">
+        <v>—</v>
+      </c>
+      <c r="H98" t="str">
+        <v>—</v>
+      </c>
+      <c r="I98" t="str">
+        <v>—</v>
+      </c>
+      <c r="J98" t="str">
+        <v>—</v>
+      </c>
+      <c r="K98" t="str">
+        <v>—</v>
+      </c>
+      <c r="L98" t="str">
+        <v>—</v>
+      </c>
+      <c r="M98" t="str">
+        <v>—</v>
+      </c>
+      <c r="N98" t="str">
+        <v>—</v>
+      </c>
+      <c r="O98" t="str">
+        <v>—</v>
+      </c>
+      <c r="P98" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q98" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="E99" t="str">
+        <v>输入&gt;32k</v>
+      </c>
+      <c r="F99" t="str">
+        <v>入 ¥1.6 · 出 ¥4 · 缓 ¥0.32</v>
+      </c>
+      <c r="G99" t="str">
+        <v>—</v>
+      </c>
+      <c r="H99" t="str">
+        <v>—</v>
+      </c>
+      <c r="I99" t="str">
+        <v>—</v>
+      </c>
+      <c r="J99" t="str">
+        <v>—</v>
+      </c>
+      <c r="K99" t="str">
+        <v>—</v>
+      </c>
+      <c r="L99" t="str">
+        <v>—</v>
+      </c>
+      <c r="M99" t="str">
+        <v>—</v>
+      </c>
+      <c r="N99" t="str">
+        <v>—</v>
+      </c>
+      <c r="O99" t="str">
+        <v>—</v>
+      </c>
+      <c r="P99" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q99" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>doubao-seed-1-8</v>
+      </c>
+      <c r="B100" t="str">
+        <v>—</v>
+      </c>
+      <c r="C100" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="D100" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="E100" t="str">
+        <v>输入≤32k</v>
+      </c>
+      <c r="F100" t="str">
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+      </c>
+      <c r="G100" t="str">
+        <v>—</v>
+      </c>
+      <c r="H100" t="str">
+        <v>—</v>
+      </c>
+      <c r="I100" t="str">
+        <v>—</v>
+      </c>
+      <c r="J100" t="str">
+        <v>—</v>
+      </c>
+      <c r="K100" t="str">
+        <v>—</v>
+      </c>
+      <c r="L100" t="str">
+        <v>—</v>
+      </c>
+      <c r="M100" t="str">
+        <v>—</v>
+      </c>
+      <c r="N100" t="str">
+        <v>—</v>
+      </c>
+      <c r="O100" t="str">
+        <v>—</v>
+      </c>
+      <c r="P100" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q100" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="E101" t="str">
+        <v>输入&gt;32k</v>
+      </c>
+      <c r="F101" t="str">
+        <v>入 ¥1.6 · 出 ¥4 · 缓 ¥0.32</v>
+      </c>
+      <c r="G101" t="str">
+        <v>—</v>
+      </c>
+      <c r="H101" t="str">
+        <v>—</v>
+      </c>
+      <c r="I101" t="str">
+        <v>—</v>
+      </c>
+      <c r="J101" t="str">
+        <v>—</v>
+      </c>
+      <c r="K101" t="str">
+        <v>—</v>
+      </c>
+      <c r="L101" t="str">
+        <v>—</v>
+      </c>
+      <c r="M101" t="str">
+        <v>—</v>
+      </c>
+      <c r="N101" t="str">
+        <v>—</v>
+      </c>
+      <c r="O101" t="str">
+        <v>—</v>
+      </c>
+      <c r="P101" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q101" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>doubao-seed-2-0-lite</v>
+      </c>
+      <c r="B102" t="str">
+        <v>—</v>
+      </c>
+      <c r="C102" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="D102" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="E102" t="str">
+        <v>输入≤32k</v>
+      </c>
+      <c r="F102" t="str">
+        <v>入 ¥0.6 · 出 ¥3.6 · 缓 ¥0.12</v>
+      </c>
+      <c r="G102" t="str">
+        <v>—</v>
+      </c>
+      <c r="H102" t="str">
+        <v>—</v>
+      </c>
+      <c r="I102" t="str">
+        <v>—</v>
+      </c>
+      <c r="J102" t="str">
+        <v>—</v>
+      </c>
+      <c r="K102" t="str">
+        <v>—</v>
+      </c>
+      <c r="L102" t="str">
+        <v>—</v>
+      </c>
+      <c r="M102" t="str">
+        <v>—</v>
+      </c>
+      <c r="N102" t="str">
+        <v>—</v>
+      </c>
+      <c r="O102" t="str">
+        <v>—</v>
+      </c>
+      <c r="P102" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q102" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="E103" t="str">
+        <v>输入&gt;32k</v>
+      </c>
+      <c r="F103" t="str">
+        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
+      </c>
+      <c r="G103" t="str">
+        <v>—</v>
+      </c>
+      <c r="H103" t="str">
+        <v>—</v>
+      </c>
+      <c r="I103" t="str">
+        <v>—</v>
+      </c>
+      <c r="J103" t="str">
+        <v>—</v>
+      </c>
+      <c r="K103" t="str">
+        <v>—</v>
+      </c>
+      <c r="L103" t="str">
+        <v>—</v>
+      </c>
+      <c r="M103" t="str">
+        <v>—</v>
+      </c>
+      <c r="N103" t="str">
+        <v>—</v>
+      </c>
+      <c r="O103" t="str">
+        <v>—</v>
+      </c>
+      <c r="P103" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q103" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>doubao-seed-2-0-mini</v>
+      </c>
+      <c r="B104" t="str">
+        <v>—</v>
+      </c>
+      <c r="C104" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="D104" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="E104" t="str">
+        <v>输入≤32k</v>
+      </c>
+      <c r="F104" t="str">
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.04</v>
+      </c>
+      <c r="G104" t="str">
+        <v>—</v>
+      </c>
+      <c r="H104" t="str">
+        <v>—</v>
+      </c>
+      <c r="I104" t="str">
+        <v>—</v>
+      </c>
+      <c r="J104" t="str">
+        <v>—</v>
+      </c>
+      <c r="K104" t="str">
+        <v>—</v>
+      </c>
+      <c r="L104" t="str">
+        <v>—</v>
+      </c>
+      <c r="M104" t="str">
+        <v>—</v>
+      </c>
+      <c r="N104" t="str">
+        <v>—</v>
+      </c>
+      <c r="O104" t="str">
+        <v>—</v>
+      </c>
+      <c r="P104" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q104" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="E105" t="str">
+        <v>输入&gt;32k</v>
+      </c>
+      <c r="F105" t="str">
+        <v>入 ¥0.4 · 出 ¥4 · 缓 ¥0.08</v>
+      </c>
+      <c r="G105" t="str">
+        <v>—</v>
+      </c>
+      <c r="H105" t="str">
+        <v>—</v>
+      </c>
+      <c r="I105" t="str">
+        <v>—</v>
+      </c>
+      <c r="J105" t="str">
+        <v>—</v>
+      </c>
+      <c r="K105" t="str">
+        <v>—</v>
+      </c>
+      <c r="L105" t="str">
+        <v>—</v>
+      </c>
+      <c r="M105" t="str">
+        <v>—</v>
+      </c>
+      <c r="N105" t="str">
+        <v>—</v>
+      </c>
+      <c r="O105" t="str">
+        <v>—</v>
+      </c>
+      <c r="P105" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q105" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>doubao-seed-2-0-pro</v>
+      </c>
+      <c r="B106" t="str">
+        <v>—</v>
+      </c>
+      <c r="C106" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="D106" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="E106" t="str">
+        <v>输入≤32k</v>
+      </c>
+      <c r="F106" t="str">
+        <v>入 ¥3.2 · 出 ¥16 · 缓 ¥0.64</v>
+      </c>
+      <c r="G106" t="str">
+        <v>—</v>
+      </c>
+      <c r="H106" t="str">
+        <v>—</v>
+      </c>
+      <c r="I106" t="str">
+        <v>—</v>
+      </c>
+      <c r="J106" t="str">
+        <v>—</v>
+      </c>
+      <c r="K106" t="str">
+        <v>—</v>
+      </c>
+      <c r="L106" t="str">
+        <v>—</v>
+      </c>
+      <c r="M106" t="str">
+        <v>—</v>
+      </c>
+      <c r="N106" t="str">
+        <v>—</v>
+      </c>
+      <c r="O106" t="str">
+        <v>—</v>
+      </c>
+      <c r="P106" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q106" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="E107" t="str">
+        <v>输入(32k,128k]</v>
+      </c>
+      <c r="F107" t="str">
+        <v>入 ¥4.8 · 出 ¥24 · 缓 ¥0.96</v>
+      </c>
+      <c r="G107" t="str">
+        <v>—</v>
+      </c>
+      <c r="H107" t="str">
+        <v>—</v>
+      </c>
+      <c r="I107" t="str">
+        <v>—</v>
+      </c>
+      <c r="J107" t="str">
+        <v>—</v>
+      </c>
+      <c r="K107" t="str">
+        <v>—</v>
+      </c>
+      <c r="L107" t="str">
+        <v>—</v>
+      </c>
+      <c r="M107" t="str">
+        <v>—</v>
+      </c>
+      <c r="N107" t="str">
+        <v>—</v>
+      </c>
+      <c r="O107" t="str">
+        <v>—</v>
+      </c>
+      <c r="P107" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q107" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="E108" t="str">
+        <v>输入(128k,256k]</v>
+      </c>
+      <c r="F108" t="str">
+        <v>入 ¥9.6 · 出 ¥48 · 缓 ¥1.92</v>
+      </c>
+      <c r="G108" t="str">
+        <v>—</v>
+      </c>
+      <c r="H108" t="str">
+        <v>—</v>
+      </c>
+      <c r="I108" t="str">
+        <v>—</v>
+      </c>
+      <c r="J108" t="str">
+        <v>—</v>
+      </c>
+      <c r="K108" t="str">
+        <v>—</v>
+      </c>
+      <c r="L108" t="str">
+        <v>—</v>
+      </c>
+      <c r="M108" t="str">
+        <v>—</v>
+      </c>
+      <c r="N108" t="str">
+        <v>—</v>
+      </c>
+      <c r="O108" t="str">
+        <v>—</v>
+      </c>
+      <c r="P108" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q108" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>doubao-seed-2-1-pro</v>
+      </c>
+      <c r="B109" t="str">
+        <v>—</v>
+      </c>
+      <c r="C109" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="D109" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="E109" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F109" t="str">
+        <v>入 ¥6 · 出 ¥30 · 缓 ¥1.2</v>
+      </c>
+      <c r="G109" t="str">
+        <v>—</v>
+      </c>
+      <c r="H109" t="str">
+        <v>—</v>
+      </c>
+      <c r="I109" t="str">
+        <v>—</v>
+      </c>
+      <c r="J109" t="str">
+        <v>—</v>
+      </c>
+      <c r="K109" t="str">
+        <v>—</v>
+      </c>
+      <c r="L109" t="str">
+        <v>—</v>
+      </c>
+      <c r="M109" t="str">
+        <v>—</v>
+      </c>
+      <c r="N109" t="str">
+        <v>—</v>
+      </c>
+      <c r="O109" t="str">
+        <v>—</v>
+      </c>
+      <c r="P109" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q109" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>doubao-seed-2-1-turbo</v>
+      </c>
+      <c r="B110" t="str">
+        <v>—</v>
+      </c>
+      <c r="C110" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="D110" t="str">
+        <v>豆包</v>
+      </c>
+      <c r="E110" t="str">
+        <v>标准价</v>
+      </c>
+      <c r="F110" t="str">
+        <v>入 ¥3 · 出 ¥15 · 缓 ¥0.6</v>
+      </c>
+      <c r="G110" t="str">
+        <v>—</v>
+      </c>
+      <c r="H110" t="str">
+        <v>—</v>
+      </c>
+      <c r="I110" t="str">
+        <v>—</v>
+      </c>
+      <c r="J110" t="str">
+        <v>—</v>
+      </c>
+      <c r="K110" t="str">
+        <v>—</v>
+      </c>
+      <c r="L110" t="str">
+        <v>—</v>
+      </c>
+      <c r="M110" t="str">
+        <v>—</v>
+      </c>
+      <c r="N110" t="str">
+        <v>—</v>
+      </c>
+      <c r="O110" t="str">
+        <v>—</v>
+      </c>
+      <c r="P110" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q110" t="str">
+        <v>— 未接入</v>
+      </c>
+      <c r="R110" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="69">
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
+  <mergeCells count="116">
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="C21:C22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D21:D22"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="C34:C35"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="B68:B70"/>
-    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="D54:D56"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
     <mergeCell ref="A72:A74"/>
     <mergeCell ref="B72:B74"/>
     <mergeCell ref="C72:C74"/>
-    <mergeCell ref="A76:A78"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="D72:D74"/>
+    <mergeCell ref="A75:A77"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="C75:C77"/>
+    <mergeCell ref="D75:D77"/>
     <mergeCell ref="A79:A81"/>
     <mergeCell ref="B79:B81"/>
     <mergeCell ref="C79:C81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D79:D81"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="B83:B85"/>
+    <mergeCell ref="C83:C85"/>
+    <mergeCell ref="D83:D85"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="B86:B88"/>
+    <mergeCell ref="C86:C88"/>
+    <mergeCell ref="D86:D88"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="D89:D90"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:D92"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="A106:A108"/>
+    <mergeCell ref="B106:B108"/>
+    <mergeCell ref="C106:C108"/>
+    <mergeCell ref="D106:D108"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q88"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R110"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5081,34 +6444,34 @@
         <v>火山方舟</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="str">
-        <v>—</v>
+        <v>+100% ~ +3900%</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="str">
-        <v>—</v>
+        <v>deepseek-v3.2(+100%)；deepseek-v4-flash(+900%)；deepseek-v4-pro(+3900%)</v>
       </c>
     </row>
     <row r="7">
@@ -5406,19 +6769,79 @@
         <v>⚠ 缓+100%</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>火山方舟</v>
+      </c>
+      <c r="B22" t="str">
+        <v>deepseek-v3.2</v>
+      </c>
+      <c r="C22" t="str">
+        <v>DeepSeek V3.2</v>
+      </c>
+      <c r="D22" t="str">
+        <v>输入(32k,128k]</v>
+      </c>
+      <c r="E22" t="str">
+        <v>+100%</v>
+      </c>
+      <c r="F22" t="str">
+        <v>⚠ 入+100% 出+100%</v>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>生成时间：2026-07-03T03:32:36Z</v>
+        <v>火山方舟</v>
+      </c>
+      <c r="B23" t="str">
+        <v>deepseek-v4-flash</v>
+      </c>
+      <c r="C23" t="str">
+        <v>DeepSeek V4 Flash Direct</v>
+      </c>
+      <c r="D23" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="E23" t="str">
+        <v>+900%</v>
+      </c>
+      <c r="F23" t="str">
+        <v>⚠ 缓+900%</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
+        <v>火山方舟</v>
+      </c>
+      <c r="B24" t="str">
+        <v>deepseek-v4-pro</v>
+      </c>
+      <c r="C24" t="str">
+        <v>DeepSeek V4 Pro Direct</v>
+      </c>
+      <c r="D24" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="E24" t="str">
+        <v>+3900%</v>
+      </c>
+      <c r="F24" t="str">
+        <v>⚠ 入+300% 出+300% 缓+3900%</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>生成时间：2026-07-03T07:14:54Z</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
         <v>说明：一致=与厂商官方价偏差&lt;0.5%（含 FX 7.5/7.25/6.5 最佳匹配）；不一致上浮=供应商高于官方的偏差%；模型级不一致=任一档位不一致</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K27"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -11322,7 +12745,7 @@
         <v>16</v>
       </c>
       <c r="E17" t="str">
-        <v>输入≤32k</v>
+        <v>输入≤32k·输出≤0.2k</v>
       </c>
       <c r="F17" t="str">
         <v>doubao-seed-1.8</v>
@@ -11348,7 +12771,7 @@
         <v>17</v>
       </c>
       <c r="E18" t="str">
-        <v>输入≤32k</v>
+        <v>输入≤32k·输出≤0.2k</v>
       </c>
       <c r="F18" t="str">
         <v>doubao-seed-1.8</v>
@@ -11556,7 +12979,7 @@
         <v>25</v>
       </c>
       <c r="E26" t="str">
-        <v>输入≤32k</v>
+        <v>输入≤32k·输出≤0.2k</v>
       </c>
       <c r="F26" t="str">
         <v>doubao-seed-1.6</v>
@@ -11582,7 +13005,7 @@
         <v>26</v>
       </c>
       <c r="E27" t="str">
-        <v>输入≤32k</v>
+        <v>输入≤32k·输出≤0.2k</v>
       </c>
       <c r="F27" t="str">
         <v>doubao-seed-1.6</v>
@@ -11660,7 +13083,7 @@
         <v>29</v>
       </c>
       <c r="E30" t="str">
-        <v>输入≤32k</v>
+        <v>输入≤32k·输出≤0.2k</v>
       </c>
       <c r="F30" t="str">
         <v>doubao-seed-1.6-lite</v>
@@ -11686,7 +13109,7 @@
         <v>30</v>
       </c>
       <c r="E31" t="str">
-        <v>输入≤32k</v>
+        <v>输入≤32k·输出≤0.2k</v>
       </c>
       <c r="F31" t="str">
         <v>doubao-seed-1.6-lite</v>
@@ -12023,20 +13446,29 @@
       <c r="A44">
         <v>43</v>
       </c>
+      <c r="B44" t="str">
+        <v>glm-5.2</v>
+      </c>
+      <c r="C44" t="str">
+        <v>智谱 GLM-5.2</v>
+      </c>
+      <c r="D44" t="str">
+        <v>火山方舟</v>
+      </c>
       <c r="E44" t="str">
         <v>标准价</v>
       </c>
       <c r="F44" t="str">
-        <v>doubao-1.5-vision-pro</v>
+        <v>glm-5.2</v>
       </c>
       <c r="G44" t="str">
-        <v>—</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="H44" t="str">
         <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="I44" t="str">
-        <v>—</v>
+        <v>✅ 一致</v>
       </c>
       <c r="J44" t="str">
         <v>—</v>
@@ -12049,20 +13481,29 @@
       <c r="A45">
         <v>44</v>
       </c>
+      <c r="B45" t="str">
+        <v>glm-4-7-251222</v>
+      </c>
+      <c r="C45" t="str">
+        <v>智谱 GLM-4.7</v>
+      </c>
+      <c r="D45" t="str">
+        <v>火山方舟</v>
+      </c>
       <c r="E45" t="str">
-        <v>输入≤32k</v>
+        <v>输入≤32k·输出≤0.2k</v>
       </c>
       <c r="F45" t="str">
-        <v>doubao-1.5-vision-pro</v>
+        <v>glm-4.7</v>
       </c>
       <c r="G45" t="str">
-        <v>—</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
       </c>
       <c r="H45" t="str">
         <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
       </c>
       <c r="I45" t="str">
-        <v>—</v>
+        <v>✅ 一致</v>
       </c>
       <c r="J45" t="str">
         <v>—</v>
@@ -12076,19 +13517,19 @@
         <v>45</v>
       </c>
       <c r="E46" t="str">
-        <v>输入≤32k</v>
+        <v>输入≤32k·输出≤0.2k</v>
       </c>
       <c r="F46" t="str">
-        <v>doubao-1.5-vision-pro</v>
+        <v>glm-4.7</v>
       </c>
       <c r="G46" t="str">
-        <v>—</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
       </c>
       <c r="H46" t="str">
         <v>入 ¥3 · 出 ¥14 · 缓 ¥0.6</v>
       </c>
       <c r="I46" t="str">
-        <v>—</v>
+        <v>⚠ 入+50% 出+75% 缓+50%</v>
       </c>
       <c r="J46" t="str">
         <v>—</v>
@@ -12102,19 +13543,19 @@
         <v>46</v>
       </c>
       <c r="E47" t="str">
-        <v>输入长度 (32, 200]</v>
+        <v>输入(32k,200k]</v>
       </c>
       <c r="F47" t="str">
-        <v>doubao-1.5-vision-pro</v>
+        <v>glm-4.7</v>
       </c>
       <c r="G47" t="str">
-        <v>—</v>
+        <v>入 ¥4 · 出 ¥16 · 缓 ¥0.8</v>
       </c>
       <c r="H47" t="str">
         <v>入 ¥4 · 出 ¥16 · 缓 ¥0.8</v>
       </c>
       <c r="I47" t="str">
-        <v>—</v>
+        <v>✅ 一致</v>
       </c>
       <c r="J47" t="str">
         <v>—</v>
@@ -12127,20 +13568,29 @@
       <c r="A48">
         <v>47</v>
       </c>
+      <c r="B48" t="str">
+        <v>deepseek-v4-pro</v>
+      </c>
+      <c r="C48" t="str">
+        <v>DeepSeek deepseek-v4-pro</v>
+      </c>
+      <c r="D48" t="str">
+        <v>火山方舟</v>
+      </c>
       <c r="E48" t="str">
         <v>标准价</v>
       </c>
       <c r="F48" t="str">
-        <v>doubao-1.5-vision-pro</v>
+        <v>deepseek-v4-pro</v>
       </c>
       <c r="G48" t="str">
-        <v>—</v>
+        <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
       </c>
       <c r="H48" t="str">
         <v>入 ¥12 · 出 ¥24 · 缓 ¥1</v>
       </c>
       <c r="I48" t="str">
-        <v>—</v>
+        <v>⚠ 入+300% 出+300% 缓+3900%</v>
       </c>
       <c r="J48" t="str">
         <v>—</v>
@@ -12153,20 +13603,29 @@
       <c r="A49">
         <v>48</v>
       </c>
+      <c r="B49" t="str">
+        <v>deepseek-v4-flash</v>
+      </c>
+      <c r="C49" t="str">
+        <v>DeepSeek deepseek-v4-flash</v>
+      </c>
+      <c r="D49" t="str">
+        <v>火山方舟</v>
+      </c>
       <c r="E49" t="str">
         <v>标准价</v>
       </c>
       <c r="F49" t="str">
-        <v>doubao-1.5-vision-pro</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="G49" t="str">
-        <v>—</v>
+        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="H49" t="str">
         <v>入 ¥1 · 出 ¥2 · 缓 ¥0.2</v>
       </c>
       <c r="I49" t="str">
-        <v>—</v>
+        <v>⚠ 缓+900%</v>
       </c>
       <c r="J49" t="str">
         <v>—</v>
@@ -12179,20 +13638,29 @@
       <c r="A50">
         <v>49</v>
       </c>
+      <c r="B50" t="str">
+        <v>deepseek-v3.2</v>
+      </c>
+      <c r="C50" t="str">
+        <v>DeepSeek deepseek-v3.2</v>
+      </c>
+      <c r="D50" t="str">
+        <v>火山方舟</v>
+      </c>
       <c r="E50" t="str">
         <v>输入≤32k</v>
       </c>
       <c r="F50" t="str">
-        <v>doubao-1.5-vision-pro</v>
+        <v>deepseek-v3.2</v>
       </c>
       <c r="G50" t="str">
-        <v>—</v>
+        <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
       </c>
       <c r="H50" t="str">
         <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
       </c>
       <c r="I50" t="str">
-        <v>—</v>
+        <v>✅ 一致</v>
       </c>
       <c r="J50" t="str">
         <v>—</v>
@@ -12209,16 +13677,16 @@
         <v>输入(32k,128k]</v>
       </c>
       <c r="F51" t="str">
-        <v>doubao-1.5-vision-pro</v>
+        <v>deepseek-v3.2</v>
       </c>
       <c r="G51" t="str">
-        <v>—</v>
+        <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
       </c>
       <c r="H51" t="str">
         <v>入 ¥4 · 出 ¥6 · 缓 ¥0.4</v>
       </c>
       <c r="I51" t="str">
-        <v>—</v>
+        <v>⚠ 入+100% 出+100%</v>
       </c>
       <c r="J51" t="str">
         <v>—</v>
@@ -12235,7 +13703,7 @@
         <v>标准价</v>
       </c>
       <c r="F52" t="str">
-        <v>doubao-1.5-vision-pro</v>
+        <v>deepseek-v3.1</v>
       </c>
       <c r="G52" t="str">
         <v>—</v>
@@ -12261,7 +13729,7 @@
         <v>标准价</v>
       </c>
       <c r="F53" t="str">
-        <v>doubao-1.5-vision-pro</v>
+        <v>deepseek-v3</v>
       </c>
       <c r="G53" t="str">
         <v>—</v>
@@ -12287,7 +13755,7 @@
         <v>标准价</v>
       </c>
       <c r="F54" t="str">
-        <v>doubao-1.5-vision-pro</v>
+        <v>deepseek-r1</v>
       </c>
       <c r="G54" t="str">
         <v>—</v>
@@ -12306,10 +13774,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:B54"/>
-    <mergeCell ref="C2:C54"/>
-    <mergeCell ref="D2:D54"/>
+  <mergeCells count="9">
+    <mergeCell ref="B2:B43"/>
+    <mergeCell ref="C2:C43"/>
+    <mergeCell ref="D2:D43"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="D50:D54"/>
   </mergeCells>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:K54"/>
@@ -13612,7 +15086,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K117"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16601,16 +18075,16 @@
         <v>96</v>
       </c>
       <c r="E97" t="str">
-        <v>输入&gt;32k</v>
+        <v>输入(32k,128k]</v>
       </c>
       <c r="F97" t="str">
         <v>doubao-seed-2-0-pro</v>
       </c>
       <c r="G97" t="str">
-        <v>入 ¥6.4 · 出 ¥32 · 缓 ¥1.28</v>
+        <v>入 ¥4.8 · 出 ¥24 · 缓 ¥0.96</v>
       </c>
       <c r="H97" t="str">
-        <v>入 ¥6.4 · 出 ¥32 · 缓 ¥1.28</v>
+        <v>入 ¥4.8 · 出 ¥24 · 缓 ¥0.96</v>
       </c>
       <c r="I97" t="str">
         <v>✅ 一致</v>
@@ -16627,16 +18101,16 @@
         <v>97</v>
       </c>
       <c r="E98" t="str">
-        <v>标准价</v>
+        <v>输入(128k,256k]</v>
       </c>
       <c r="F98" t="str">
-        <v>doubao-seed-2-1-pro</v>
+        <v>doubao-seed-2-0-pro</v>
       </c>
       <c r="G98" t="str">
-        <v>入 ¥6 · 出 ¥30 · 缓 ¥1.2</v>
+        <v>入 ¥9.6 · 出 ¥48 · 缓 ¥1.92</v>
       </c>
       <c r="H98" t="str">
-        <v>入 ¥6 · 出 ¥30 · 缓 ¥1.2</v>
+        <v>入 ¥9.6 · 出 ¥48 · 缓 ¥1.92</v>
       </c>
       <c r="I98" t="str">
         <v>✅ 一致</v>
@@ -16656,13 +18130,13 @@
         <v>标准价</v>
       </c>
       <c r="F99" t="str">
-        <v>doubao-seed-2-1-turbo</v>
+        <v>doubao-seed-2-1-pro</v>
       </c>
       <c r="G99" t="str">
-        <v>入 ¥3 · 出 ¥15 · 缓 ¥0.6</v>
+        <v>入 ¥6 · 出 ¥30 · 缓 ¥1.2</v>
       </c>
       <c r="H99" t="str">
-        <v>入 ¥3 · 出 ¥15 · 缓 ¥0.6</v>
+        <v>入 ¥6 · 出 ¥30 · 缓 ¥1.2</v>
       </c>
       <c r="I99" t="str">
         <v>✅ 一致</v>
@@ -16682,13 +18156,13 @@
         <v>标准价</v>
       </c>
       <c r="F100" t="str">
-        <v>grok-4-1-fast-non-reasoning</v>
+        <v>doubao-seed-2-1-turbo</v>
       </c>
       <c r="G100" t="str">
-        <v>入 $1.25 · 出 $2.5 · 缓 $0.2</v>
+        <v>入 ¥3 · 出 ¥15 · 缓 ¥0.6</v>
       </c>
       <c r="H100" t="str">
-        <v>入 $1.25 · 出 $2.5 · 缓 $0.2</v>
+        <v>入 ¥3 · 出 ¥15 · 缓 ¥0.6</v>
       </c>
       <c r="I100" t="str">
         <v>✅ 一致</v>
@@ -16708,7 +18182,7 @@
         <v>标准价</v>
       </c>
       <c r="F101" t="str">
-        <v>grok-4-1-fast-reasoning</v>
+        <v>grok-4-1-fast-non-reasoning</v>
       </c>
       <c r="G101" t="str">
         <v>入 $1.25 · 出 $2.5 · 缓 $0.2</v>
@@ -16734,7 +18208,7 @@
         <v>标准价</v>
       </c>
       <c r="F102" t="str">
-        <v>grok-4.20-0309-non-reasoning</v>
+        <v>grok-4-1-fast-reasoning</v>
       </c>
       <c r="G102" t="str">
         <v>入 $1.25 · 出 $2.5 · 缓 $0.2</v>
@@ -16760,7 +18234,7 @@
         <v>标准价</v>
       </c>
       <c r="F103" t="str">
-        <v>grok-4.20-0309-reasoning</v>
+        <v>grok-4.20-0309-non-reasoning</v>
       </c>
       <c r="G103" t="str">
         <v>入 $1.25 · 出 $2.5 · 缓 $0.2</v>
@@ -16782,20 +18256,11 @@
       <c r="A104">
         <v>103</v>
       </c>
-      <c r="B104" t="str">
-        <v>grok-4.3</v>
-      </c>
-      <c r="C104" t="str">
-        <v>GK grok-4.3</v>
-      </c>
-      <c r="D104" t="str">
-        <v>中转站-cust</v>
-      </c>
       <c r="E104" t="str">
         <v>标准价</v>
       </c>
       <c r="F104" t="str">
-        <v>grok-4.3</v>
+        <v>grok-4.20-0309-reasoning</v>
       </c>
       <c r="G104" t="str">
         <v>入 $1.25 · 出 $2.5 · 缓 $0.2</v>
@@ -16818,25 +18283,25 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>glm-4-7-251222</v>
+        <v>grok-4.3</v>
       </c>
       <c r="C105" t="str">
-        <v>智谱 glm-4.7</v>
+        <v>GK grok-4.3</v>
       </c>
       <c r="D105" t="str">
         <v>中转站-cust</v>
       </c>
       <c r="E105" t="str">
-        <v>输入≤32k，输出≤0.2k</v>
+        <v>标准价</v>
       </c>
       <c r="F105" t="str">
-        <v>glm-4.7</v>
+        <v>grok-4.3</v>
       </c>
       <c r="G105" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
+        <v>入 $1.25 · 出 $2.5 · 缓 $0.2</v>
       </c>
       <c r="H105" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
+        <v>入 $1.25 · 出 $2.5 · 缓 $0.2</v>
       </c>
       <c r="I105" t="str">
         <v>✅ 一致</v>
@@ -16852,17 +18317,26 @@
       <c r="A106">
         <v>105</v>
       </c>
+      <c r="B106" t="str">
+        <v>glm-4-7-251222</v>
+      </c>
+      <c r="C106" t="str">
+        <v>智谱 glm-4.7</v>
+      </c>
+      <c r="D106" t="str">
+        <v>中转站-cust</v>
+      </c>
       <c r="E106" t="str">
-        <v>输入≤32k，输出&gt;0.2k</v>
+        <v>输入≤32k，输出≤0.2k</v>
       </c>
       <c r="F106" t="str">
         <v>glm-4.7</v>
       </c>
       <c r="G106" t="str">
-        <v>入 ¥3 · 出 ¥14 · 缓 ¥0.6</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
       </c>
       <c r="H106" t="str">
-        <v>入 ¥3 · 出 ¥14 · 缓 ¥0.6</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
       </c>
       <c r="I106" t="str">
         <v>✅ 一致</v>
@@ -16879,16 +18353,16 @@
         <v>106</v>
       </c>
       <c r="E107" t="str">
-        <v>输入&gt;32k</v>
+        <v>输入≤32k，输出&gt;0.2k</v>
       </c>
       <c r="F107" t="str">
         <v>glm-4.7</v>
       </c>
       <c r="G107" t="str">
-        <v>入 ¥4 · 出 ¥16 · 缓 ¥0.8</v>
+        <v>入 ¥3 · 出 ¥14 · 缓 ¥0.6</v>
       </c>
       <c r="H107" t="str">
-        <v>入 ¥4 · 出 ¥16 · 缓 ¥0.8</v>
+        <v>入 ¥3 · 出 ¥14 · 缓 ¥0.6</v>
       </c>
       <c r="I107" t="str">
         <v>✅ 一致</v>
@@ -16904,26 +18378,17 @@
       <c r="A108">
         <v>107</v>
       </c>
-      <c r="B108" t="str">
-        <v>glm-5</v>
-      </c>
-      <c r="C108" t="str">
-        <v>智谱 glm-5</v>
-      </c>
-      <c r="D108" t="str">
-        <v>中转站-cust</v>
-      </c>
       <c r="E108" t="str">
-        <v>输入&lt;32k</v>
+        <v>输入&gt;32k</v>
       </c>
       <c r="F108" t="str">
-        <v>glm-5</v>
+        <v>glm-4.7</v>
       </c>
       <c r="G108" t="str">
-        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+        <v>入 ¥4 · 出 ¥16 · 缓 ¥0.8</v>
       </c>
       <c r="H108" t="str">
-        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+        <v>入 ¥4 · 出 ¥16 · 缓 ¥0.8</v>
       </c>
       <c r="I108" t="str">
         <v>✅ 一致</v>
@@ -16939,17 +18404,26 @@
       <c r="A109">
         <v>108</v>
       </c>
+      <c r="B109" t="str">
+        <v>glm-5</v>
+      </c>
+      <c r="C109" t="str">
+        <v>智谱 glm-5</v>
+      </c>
+      <c r="D109" t="str">
+        <v>中转站-cust</v>
+      </c>
       <c r="E109" t="str">
-        <v>输入≥32k</v>
+        <v>输入&lt;32k</v>
       </c>
       <c r="F109" t="str">
         <v>glm-5</v>
       </c>
       <c r="G109" t="str">
-        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="H109" t="str">
-        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="I109" t="str">
         <v>✅ 一致</v>
@@ -16965,26 +18439,17 @@
       <c r="A110">
         <v>109</v>
       </c>
-      <c r="B110" t="str">
-        <v>glm-5-turbo</v>
-      </c>
-      <c r="C110" t="str">
-        <v>智谱 glm-5-turbo</v>
-      </c>
-      <c r="D110" t="str">
-        <v>中转站-cust</v>
-      </c>
       <c r="E110" t="str">
-        <v>输入&lt;32k</v>
+        <v>输入≥32k</v>
       </c>
       <c r="F110" t="str">
-        <v>glm-5-turbo</v>
+        <v>glm-5</v>
       </c>
       <c r="G110" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="H110" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="I110" t="str">
         <v>✅ 一致</v>
@@ -17000,17 +18465,26 @@
       <c r="A111">
         <v>110</v>
       </c>
+      <c r="B111" t="str">
+        <v>glm-5-turbo</v>
+      </c>
+      <c r="C111" t="str">
+        <v>智谱 glm-5-turbo</v>
+      </c>
+      <c r="D111" t="str">
+        <v>中转站-cust</v>
+      </c>
       <c r="E111" t="str">
-        <v>输入≥32k</v>
+        <v>输入&lt;32k</v>
       </c>
       <c r="F111" t="str">
         <v>glm-5-turbo</v>
       </c>
       <c r="G111" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="H111" t="str">
-        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="I111" t="str">
         <v>✅ 一致</v>
@@ -17026,26 +18500,17 @@
       <c r="A112">
         <v>111</v>
       </c>
-      <c r="B112" t="str">
-        <v>glm-5.1</v>
-      </c>
-      <c r="C112" t="str">
-        <v>智谱 glm-5.1</v>
-      </c>
-      <c r="D112" t="str">
-        <v>中转站-cust</v>
-      </c>
       <c r="E112" t="str">
-        <v>输入&lt;32k</v>
+        <v>输入≥32k</v>
       </c>
       <c r="F112" t="str">
-        <v>glm-5.1</v>
+        <v>glm-5-turbo</v>
       </c>
       <c r="G112" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="H112" t="str">
-        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="I112" t="str">
         <v>✅ 一致</v>
@@ -17061,17 +18526,26 @@
       <c r="A113">
         <v>112</v>
       </c>
+      <c r="B113" t="str">
+        <v>glm-5.1</v>
+      </c>
+      <c r="C113" t="str">
+        <v>智谱 glm-5.1</v>
+      </c>
+      <c r="D113" t="str">
+        <v>中转站-cust</v>
+      </c>
       <c r="E113" t="str">
-        <v>输入≥32k</v>
+        <v>输入&lt;32k</v>
       </c>
       <c r="F113" t="str">
         <v>glm-5.1</v>
       </c>
       <c r="G113" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="H113" t="str">
-        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="I113" t="str">
         <v>✅ 一致</v>
@@ -17087,20 +18561,11 @@
       <c r="A114">
         <v>113</v>
       </c>
-      <c r="B114" t="str">
-        <v>glm-5.2</v>
-      </c>
-      <c r="C114" t="str">
-        <v>智谱 glm-5.2</v>
-      </c>
-      <c r="D114" t="str">
-        <v>中转站-cust</v>
-      </c>
       <c r="E114" t="str">
-        <v>标准价</v>
+        <v>输入≥32k</v>
       </c>
       <c r="F114" t="str">
-        <v>glm-5.2</v>
+        <v>glm-5.1</v>
       </c>
       <c r="G114" t="str">
         <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
@@ -17123,25 +18588,25 @@
         <v>114</v>
       </c>
       <c r="B115" t="str">
-        <v>glm-5v-turbo</v>
+        <v>glm-5.2</v>
       </c>
       <c r="C115" t="str">
-        <v>智谱 glm-5v-turbo</v>
+        <v>智谱 glm-5.2</v>
       </c>
       <c r="D115" t="str">
         <v>中转站-cust</v>
       </c>
       <c r="E115" t="str">
-        <v>输入&lt;32k</v>
+        <v>标准价</v>
       </c>
       <c r="F115" t="str">
-        <v>glm-5v-turbo</v>
+        <v>glm-5.2</v>
       </c>
       <c r="G115" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="H115" t="str">
-        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="I115" t="str">
         <v>✅ 一致</v>
@@ -17157,25 +18622,60 @@
       <c r="A116">
         <v>115</v>
       </c>
+      <c r="B116" t="str">
+        <v>glm-5v-turbo</v>
+      </c>
+      <c r="C116" t="str">
+        <v>智谱 glm-5v-turbo</v>
+      </c>
+      <c r="D116" t="str">
+        <v>中转站-cust</v>
+      </c>
       <c r="E116" t="str">
-        <v>输入≥32k</v>
+        <v>输入&lt;32k</v>
       </c>
       <c r="F116" t="str">
         <v>glm-5v-turbo</v>
       </c>
       <c r="G116" t="str">
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+      </c>
+      <c r="H116" t="str">
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+      </c>
+      <c r="I116" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J116" t="str">
+        <v>—</v>
+      </c>
+      <c r="K116" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="E117" t="str">
+        <v>输入≥32k</v>
+      </c>
+      <c r="F117" t="str">
+        <v>glm-5v-turbo</v>
+      </c>
+      <c r="G117" t="str">
         <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
-      <c r="H116" t="str">
+      <c r="H117" t="str">
         <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
-      <c r="I116" t="str">
-        <v>✅ 一致</v>
-      </c>
-      <c r="J116" t="str">
-        <v>—</v>
-      </c>
-      <c r="K116" t="str">
+      <c r="I117" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J117" t="str">
+        <v>—</v>
+      </c>
+      <c r="K117" t="str">
         <v>—</v>
       </c>
     </row>
@@ -17238,27 +18738,27 @@
     <mergeCell ref="B75:B76"/>
     <mergeCell ref="C75:C76"/>
     <mergeCell ref="D75:D76"/>
-    <mergeCell ref="B83:B103"/>
-    <mergeCell ref="C83:C103"/>
-    <mergeCell ref="D83:D103"/>
-    <mergeCell ref="B105:B107"/>
-    <mergeCell ref="C105:C107"/>
-    <mergeCell ref="D105:D107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="D110:D111"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="D112:D113"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="C115:C116"/>
-    <mergeCell ref="D115:D116"/>
+    <mergeCell ref="B83:B104"/>
+    <mergeCell ref="C83:C104"/>
+    <mergeCell ref="D83:D104"/>
+    <mergeCell ref="B106:B108"/>
+    <mergeCell ref="C106:C108"/>
+    <mergeCell ref="D106:D108"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="D109:D110"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:D112"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="D113:D114"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="D116:D117"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K116"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K117"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/pricing/output/trinity-pricing-text.xlsx
+++ b/pricing/output/trinity-pricing-text.xlsx
@@ -6831,7 +6831,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>生成时间：2026-07-03T07:14:54Z</v>
+        <v>生成时间：2026-07-03T07:41:47Z</v>
       </c>
     </row>
     <row r="27">

--- a/pricing/output/trinity-pricing-text.xlsx
+++ b/pricing/output/trinity-pricing-text.xlsx
@@ -3166,34 +3166,34 @@
         <v>—</v>
       </c>
       <c r="H52" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="I52" t="str">
         <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="J52" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
+        <v>入 $0.646154 · 出 $2.584615 · 缓 $0.129231</v>
       </c>
       <c r="K52" t="str">
-        <v>0%</v>
+        <v>+100%</v>
       </c>
       <c r="L52" t="str">
-        <v>0%</v>
+        <v>+100%</v>
       </c>
       <c r="M52" t="str">
-        <v>0%</v>
+        <v>+100%</v>
       </c>
       <c r="N52" t="str">
         <v>—</v>
       </c>
       <c r="O52" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠+100% 出⚠+100% 缓⚠+100%</v>
       </c>
       <c r="P52" t="str">
         <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
       <c r="Q52" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠+100% 出⚠+100% 缓⚠+100%</v>
       </c>
       <c r="R52" t="str">
         <v>512k 以上输入档仍在内测开放中</v>
@@ -6262,7 +6262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6307,31 +6307,31 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="str">
-        <v>+900% ~ +3900%</v>
+        <v>+100% ~ +3900%</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="str">
-        <v>deepseek-v4-flash(+900%)；deepseek-v4-pro(+3900%)</v>
+        <v>deepseek-v4-flash(+900%)；deepseek-v4-pro(+3900%)；minimax-m3(+100%)</v>
       </c>
     </row>
     <row r="3">
@@ -6517,31 +6517,31 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G8">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
-        <v>—</v>
+        <v>+100%</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="str">
-        <v>—</v>
+        <v>minimax-m3(+100%)</v>
       </c>
     </row>
     <row r="10">
@@ -6611,22 +6611,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>百炼北京</v>
+        <v>TokenHub广州</v>
       </c>
       <c r="B14" t="str">
-        <v>deepseek-v4-flash</v>
+        <v>minimax-m3</v>
       </c>
       <c r="C14" t="str">
-        <v>DeepSeek V4 Flash Direct</v>
+        <v>MiniMax M3</v>
       </c>
       <c r="D14" t="str">
-        <v>统一价</v>
+        <v>512k&lt;输入</v>
       </c>
       <c r="E14" t="str">
-        <v>+900%</v>
+        <v>+100%</v>
       </c>
       <c r="F14" t="str">
-        <v>⚠ 缓+900%</v>
+        <v>⚠ 入+100% 出+100% 缓+100%</v>
       </c>
     </row>
     <row r="15">
@@ -6634,19 +6634,19 @@
         <v>百炼北京</v>
       </c>
       <c r="B15" t="str">
-        <v>deepseek-v4-pro</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="C15" t="str">
-        <v>DeepSeek V4 Pro Direct</v>
+        <v>DeepSeek V4 Flash Direct</v>
       </c>
       <c r="D15" t="str">
         <v>统一价</v>
       </c>
       <c r="E15" t="str">
-        <v>+9500%</v>
+        <v>+900%</v>
       </c>
       <c r="F15" t="str">
-        <v>⚠ 入+300% 出+300% 缓+9500%</v>
+        <v>⚠ 缓+900%</v>
       </c>
     </row>
     <row r="16">
@@ -6654,33 +6654,33 @@
         <v>百炼北京</v>
       </c>
       <c r="B16" t="str">
-        <v>qwen3.5-flash</v>
+        <v>deepseek-v4-pro</v>
       </c>
       <c r="C16" t="str">
-        <v>Qwen3.5 Flash</v>
+        <v>DeepSeek V4 Pro Direct</v>
       </c>
       <c r="D16" t="str">
-        <v>0&lt;输入&lt;=128k</v>
+        <v>统一价</v>
       </c>
       <c r="E16" t="str">
-        <v>+100%</v>
+        <v>+9500%</v>
       </c>
       <c r="F16" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>⚠ 入+300% 出+300% 缓+9500%</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>百炼北京</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>Qwen3.5 Flash</v>
       </c>
       <c r="D17" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>0&lt;输入&lt;=128k</v>
       </c>
       <c r="E17" t="str">
         <v>+100%</v>
@@ -6700,7 +6700,7 @@
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E18" t="str">
         <v>+100%</v>
@@ -6711,16 +6711,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>百炼北京</v>
+        <v/>
       </c>
       <c r="B19" t="str">
-        <v>qwen3.5-plus</v>
+        <v/>
       </c>
       <c r="C19" t="str">
-        <v>Qwen3.5 Plus</v>
+        <v/>
       </c>
       <c r="D19" t="str">
-        <v>输入&lt;=128k</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="E19" t="str">
         <v>+100%</v>
@@ -6731,16 +6731,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v/>
+        <v>百炼北京</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>Qwen3.5 Plus</v>
       </c>
       <c r="D20" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>输入&lt;=128k</v>
       </c>
       <c r="E20" t="str">
         <v>+100%</v>
@@ -6760,7 +6760,7 @@
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E21" t="str">
         <v>+100%</v>
@@ -6771,22 +6771,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>火山方舟</v>
+        <v/>
       </c>
       <c r="B22" t="str">
-        <v>deepseek-v3.2</v>
+        <v/>
       </c>
       <c r="C22" t="str">
-        <v>DeepSeek V3.2</v>
+        <v/>
       </c>
       <c r="D22" t="str">
-        <v>输入(32k,128k]</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="E22" t="str">
         <v>+100%</v>
       </c>
       <c r="F22" t="str">
-        <v>⚠ 入+100% 出+100%</v>
+        <v>⚠ 缓+100%</v>
       </c>
     </row>
     <row r="23">
@@ -6794,19 +6794,19 @@
         <v>火山方舟</v>
       </c>
       <c r="B23" t="str">
-        <v>deepseek-v4-flash</v>
+        <v>deepseek-v3.2</v>
       </c>
       <c r="C23" t="str">
-        <v>DeepSeek V4 Flash Direct</v>
+        <v>DeepSeek V3.2</v>
       </c>
       <c r="D23" t="str">
-        <v>统一价</v>
+        <v>输入(32k,128k]</v>
       </c>
       <c r="E23" t="str">
-        <v>+900%</v>
+        <v>+100%</v>
       </c>
       <c r="F23" t="str">
-        <v>⚠ 缓+900%</v>
+        <v>⚠ 入+100% 出+100%</v>
       </c>
     </row>
     <row r="24">
@@ -6814,41 +6814,81 @@
         <v>火山方舟</v>
       </c>
       <c r="B24" t="str">
-        <v>deepseek-v4-pro</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="C24" t="str">
-        <v>DeepSeek V4 Pro Direct</v>
+        <v>DeepSeek V4 Flash Direct</v>
       </c>
       <c r="D24" t="str">
         <v>统一价</v>
       </c>
       <c r="E24" t="str">
+        <v>+900%</v>
+      </c>
+      <c r="F24" t="str">
+        <v>⚠ 缓+900%</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>火山方舟</v>
+      </c>
+      <c r="B25" t="str">
+        <v>deepseek-v4-pro</v>
+      </c>
+      <c r="C25" t="str">
+        <v>DeepSeek V4 Pro Direct</v>
+      </c>
+      <c r="D25" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="E25" t="str">
         <v>+3900%</v>
       </c>
-      <c r="F24" t="str">
+      <c r="F25" t="str">
         <v>⚠ 入+300% 出+300% 缓+3900%</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>生成时间：2026-07-03T07:41:47Z</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
+        <v>中转站-cust</v>
+      </c>
+      <c r="B26" t="str">
+        <v>minimax-m3</v>
+      </c>
+      <c r="C26" t="str">
+        <v>MiniMax M3</v>
+      </c>
+      <c r="D26" t="str">
+        <v>512k&lt;输入</v>
+      </c>
+      <c r="E26" t="str">
+        <v>+100%</v>
+      </c>
+      <c r="F26" t="str">
+        <v>⚠ 入+100% 出+100% 缓+100%</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>生成时间：2026-07-03T09:37:10Z</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
         <v>说明：一致=与厂商官方价偏差&lt;0.5%（含 FX 7.5/7.25/6.5 最佳匹配）；不一致上浮=供应商高于官方的偏差%；模型级不一致=任一档位不一致</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K29"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7755,7 +7795,7 @@
         <v>MiniMax</v>
       </c>
       <c r="E28" t="str">
-        <v>输入&lt;=512k</v>
+        <v>512k&lt;输入</v>
       </c>
       <c r="F28" t="str">
         <v>minimax-m3</v>
@@ -7764,10 +7804,10 @@
         <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="H28" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="I28" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 入+100% 出+100% 缓+100%</v>
       </c>
       <c r="J28" t="str">
         <v>待填</v>
@@ -7780,17 +7820,26 @@
       <c r="A29">
         <v>28</v>
       </c>
+      <c r="B29" t="str">
+        <v>qwen3.5-flash</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Qwen3.5 Flash</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="E29" t="str">
-        <v>512k&lt;输入</v>
+        <v>0&lt;输入&lt;=128k</v>
       </c>
       <c r="F29" t="str">
-        <v>minimax-m3</v>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="G29" t="str">
-        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="H29" t="str">
-        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="I29" t="str">
         <v>✅ 一致</v>
@@ -7806,26 +7855,17 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="str">
-        <v>qwen3.5-flash</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Qwen3.5 Flash</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="E30" t="str">
-        <v>0&lt;输入&lt;=128k</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="F30" t="str">
         <v>qwen3.5-flash</v>
       </c>
       <c r="G30" t="str">
-        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
+        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
       </c>
       <c r="H30" t="str">
-        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
+        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
       </c>
       <c r="I30" t="str">
         <v>✅ 一致</v>
@@ -7842,16 +7882,16 @@
         <v>30</v>
       </c>
       <c r="E31" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="F31" t="str">
         <v>qwen3.5-flash</v>
       </c>
       <c r="G31" t="str">
-        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
       </c>
       <c r="H31" t="str">
-        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
       </c>
       <c r="I31" t="str">
         <v>✅ 一致</v>
@@ -7867,17 +7907,26 @@
       <c r="A32">
         <v>31</v>
       </c>
+      <c r="B32" t="str">
+        <v>qwen3.5-plus</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Qwen3.5 Plus</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="E32" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>输入&lt;=128k</v>
       </c>
       <c r="F32" t="str">
-        <v>qwen3.5-flash</v>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="G32" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
+        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
       </c>
       <c r="H32" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
+        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
       </c>
       <c r="I32" t="str">
         <v>✅ 一致</v>
@@ -7893,26 +7942,17 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="str">
-        <v>qwen3.5-plus</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Qwen3.5 Plus</v>
-      </c>
-      <c r="D33" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="E33" t="str">
-        <v>输入&lt;=128k</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="F33" t="str">
         <v>qwen3.5-plus</v>
       </c>
       <c r="G33" t="str">
-        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
       </c>
       <c r="H33" t="str">
-        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
       </c>
       <c r="I33" t="str">
         <v>✅ 一致</v>
@@ -7929,16 +7969,16 @@
         <v>33</v>
       </c>
       <c r="E34" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="F34" t="str">
         <v>qwen3.5-plus</v>
       </c>
       <c r="G34" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
       </c>
       <c r="H34" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
       </c>
       <c r="I34" t="str">
         <v>✅ 一致</v>
@@ -7950,34 +7990,8 @@
         <v>待填</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="E35" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
-      </c>
-      <c r="F35" t="str">
-        <v>qwen3.5-plus</v>
-      </c>
-      <c r="G35" t="str">
-        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
-      </c>
-      <c r="H35" t="str">
-        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
-      </c>
-      <c r="I35" t="str">
-        <v>✅ 一致</v>
-      </c>
-      <c r="J35" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K35" t="str">
-        <v>待填</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="21">
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
@@ -7993,18 +8007,15 @@
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="C19:C21"/>
     <mergeCell ref="D19:D21"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K34"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -16774,13 +16785,13 @@
         <v>minimax-m3</v>
       </c>
       <c r="G54" t="str">
-        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="H54" t="str">
         <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="I54" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 入+100% 出+100% 缓+100%</v>
       </c>
       <c r="J54" t="str">
         <v>—</v>

--- a/pricing/output/trinity-pricing-text.xlsx
+++ b/pricing/output/trinity-pricing-text.xlsx
@@ -3166,34 +3166,34 @@
         <v>—</v>
       </c>
       <c r="H52" t="str">
-        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
+        <v>—</v>
       </c>
       <c r="I52" t="str">
         <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="J52" t="str">
-        <v>入 $0.646154 · 出 $2.584615 · 缓 $0.129231</v>
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
       <c r="K52" t="str">
-        <v>+100%</v>
+        <v>0%</v>
       </c>
       <c r="L52" t="str">
-        <v>+100%</v>
+        <v>0%</v>
       </c>
       <c r="M52" t="str">
-        <v>+100%</v>
+        <v>0%</v>
       </c>
       <c r="N52" t="str">
         <v>—</v>
       </c>
       <c r="O52" t="str">
-        <v>入⚠+100% 出⚠+100% 缓⚠+100%</v>
+        <v>—</v>
       </c>
       <c r="P52" t="str">
         <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
       <c r="Q52" t="str">
-        <v>入⚠+100% 出⚠+100% 缓⚠+100%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R52" t="str">
         <v>512k 以上输入档仍在内测开放中</v>
@@ -6262,7 +6262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6339,34 +6339,34 @@
         <v>百炼北京</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I3" t="str">
-        <v>+100% ~ +9500%</v>
+        <v>+7.7% ~ +900%</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K3" t="str">
-        <v>deepseek-v4-flash(+900%)；deepseek-v4-pro(+9500%)；qwen3.5-flash(+100%)；qwen3.5-plus(+100%)</v>
+        <v>deepseek-v4-flash(+900%)；deepseek-v4-pro(+300%)；glm-5(+20%)；glm-5.1(+20%)；qwen3.5-flash(+100%)；qwen3.5-plus(+100%)</v>
       </c>
     </row>
     <row r="4">
@@ -6663,10 +6663,10 @@
         <v>统一价</v>
       </c>
       <c r="E16" t="str">
-        <v>+9500%</v>
+        <v>+300%</v>
       </c>
       <c r="F16" t="str">
-        <v>⚠ 入+300% 出+300% 缓+9500%</v>
+        <v>⚠ 入+300% 出+300%</v>
       </c>
     </row>
     <row r="17">
@@ -6674,19 +6674,19 @@
         <v>百炼北京</v>
       </c>
       <c r="B17" t="str">
-        <v>qwen3.5-flash</v>
+        <v>glm-5</v>
       </c>
       <c r="C17" t="str">
-        <v>Qwen3.5 Flash</v>
+        <v>GLM 5</v>
       </c>
       <c r="D17" t="str">
-        <v>0&lt;输入&lt;=128k</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="E17" t="str">
-        <v>+100%</v>
+        <v>+20%</v>
       </c>
       <c r="F17" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>⚠ 缓-20%</v>
       </c>
     </row>
     <row r="18">
@@ -6700,67 +6700,67 @@
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="E18" t="str">
-        <v>+100%</v>
+        <v>+20%</v>
       </c>
       <c r="F18" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>⚠ 缓-20%</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>百炼北京</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>glm-5.1</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>GLM-5.1</v>
       </c>
       <c r="D19" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="E19" t="str">
-        <v>+100%</v>
+        <v>+7.7%</v>
       </c>
       <c r="F19" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>⚠ 缓-7.7%</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>百炼北京</v>
+        <v/>
       </c>
       <c r="B20" t="str">
-        <v>qwen3.5-plus</v>
+        <v/>
       </c>
       <c r="C20" t="str">
-        <v>Qwen3.5 Plus</v>
+        <v/>
       </c>
       <c r="D20" t="str">
-        <v>输入&lt;=128k</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="E20" t="str">
-        <v>+100%</v>
+        <v>+20%</v>
       </c>
       <c r="F20" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>⚠ 缓-20%</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>百炼北京</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>Qwen3.5 Flash</v>
       </c>
       <c r="D21" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>0&lt;输入&lt;=128k</v>
       </c>
       <c r="E21" t="str">
         <v>+100%</v>
@@ -6780,7 +6780,7 @@
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E22" t="str">
         <v>+100%</v>
@@ -6791,97 +6791,262 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>火山方舟</v>
+        <v/>
       </c>
       <c r="B23" t="str">
-        <v>deepseek-v3.2</v>
+        <v/>
       </c>
       <c r="C23" t="str">
-        <v>DeepSeek V3.2</v>
+        <v/>
       </c>
       <c r="D23" t="str">
-        <v>输入(32k,128k]</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="E23" t="str">
         <v>+100%</v>
       </c>
       <c r="F23" t="str">
-        <v>⚠ 入+100% 出+100%</v>
+        <v>⚠ 缓+100%</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>火山方舟</v>
+        <v>百炼北京</v>
       </c>
       <c r="B24" t="str">
-        <v>deepseek-v4-flash</v>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="C24" t="str">
-        <v>DeepSeek V4 Flash Direct</v>
+        <v>Qwen3.5 Plus</v>
       </c>
       <c r="D24" t="str">
-        <v>统一价</v>
+        <v>输入&lt;=128k</v>
       </c>
       <c r="E24" t="str">
-        <v>+900%</v>
+        <v>+100%</v>
       </c>
       <c r="F24" t="str">
-        <v>⚠ 缓+900%</v>
+        <v>⚠ 缓+100%</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>火山方舟</v>
+        <v/>
       </c>
       <c r="B25" t="str">
-        <v>deepseek-v4-pro</v>
+        <v/>
       </c>
       <c r="C25" t="str">
-        <v>DeepSeek V4 Pro Direct</v>
+        <v/>
       </c>
       <c r="D25" t="str">
-        <v>统一价</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E25" t="str">
-        <v>+3900%</v>
+        <v>+100%</v>
       </c>
       <c r="F25" t="str">
-        <v>⚠ 入+300% 出+300% 缓+3900%</v>
+        <v>⚠ 缓+100%</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>中转站-cust</v>
+        <v/>
       </c>
       <c r="B26" t="str">
-        <v>minimax-m3</v>
+        <v/>
       </c>
       <c r="C26" t="str">
-        <v>MiniMax M3</v>
+        <v/>
       </c>
       <c r="D26" t="str">
-        <v>512k&lt;输入</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="E26" t="str">
         <v>+100%</v>
       </c>
       <c r="F26" t="str">
-        <v>⚠ 入+100% 出+100% 缓+100%</v>
+        <v>⚠ 缓+100%</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>火山方舟</v>
+      </c>
+      <c r="B27" t="str">
+        <v>deepseek-v3.2</v>
+      </c>
+      <c r="C27" t="str">
+        <v>DeepSeek V3.2</v>
+      </c>
+      <c r="D27" t="str">
+        <v>输入(32k,128k]</v>
+      </c>
+      <c r="E27" t="str">
+        <v>+100%</v>
+      </c>
+      <c r="F27" t="str">
+        <v>⚠ 入+100% 出+100%</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>生成时间：2026-07-03T09:37:10Z</v>
+        <v>火山方舟</v>
+      </c>
+      <c r="B28" t="str">
+        <v>deepseek-v4-flash</v>
+      </c>
+      <c r="C28" t="str">
+        <v>DeepSeek V4 Flash Direct</v>
+      </c>
+      <c r="D28" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="E28" t="str">
+        <v>+900%</v>
+      </c>
+      <c r="F28" t="str">
+        <v>⚠ 缓+900%</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>说明：一致=与厂商官方价偏差&lt;0.5%（含 FX 7.5/7.25/6.5 最佳匹配）；不一致上浮=供应商高于官方的偏差%；模型级不一致=任一档位不一致</v>
+        <v>火山方舟</v>
+      </c>
+      <c r="B29" t="str">
+        <v>deepseek-v4-pro</v>
+      </c>
+      <c r="C29" t="str">
+        <v>DeepSeek V4 Pro Direct</v>
+      </c>
+      <c r="D29" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="E29" t="str">
+        <v>+3900%</v>
+      </c>
+      <c r="F29" t="str">
+        <v>⚠ 入+300% 出+300% 缓+3900%</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>中转站-cust</v>
+      </c>
+      <c r="B30" t="str">
+        <v>minimax-m3</v>
+      </c>
+      <c r="C30" t="str">
+        <v>MiniMax M3</v>
+      </c>
+      <c r="D30" t="str">
+        <v>512k&lt;输入</v>
+      </c>
+      <c r="E30" t="str">
+        <v>+100%</v>
+      </c>
+      <c r="F30" t="str">
+        <v>⚠ 入+100% 出+100% 缓+100%</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>—— 偏差≥50% · 待核验（未登记例外）——</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>供应商</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Trinity ID</v>
+      </c>
+      <c r="C33" t="str">
+        <v>显示名</v>
+      </c>
+      <c r="D33" t="str">
+        <v>档位</v>
+      </c>
+      <c r="E33" t="str">
+        <v>偏差%</v>
+      </c>
+      <c r="F33" t="str">
+        <v>供应商vs官方</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TokenHub广州</v>
+      </c>
+      <c r="B34" t="str">
+        <v>minimax-m3</v>
+      </c>
+      <c r="C34" t="str">
+        <v>MiniMax M3</v>
+      </c>
+      <c r="D34" t="str">
+        <v>512k&lt;输入</v>
+      </c>
+      <c r="E34" t="str">
+        <v>+100%</v>
+      </c>
+      <c r="F34" t="str">
+        <v>⚠ 入+100% 出+100% 缓+100%</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>火山方舟</v>
+      </c>
+      <c r="B35" t="str">
+        <v>deepseek-v3.2</v>
+      </c>
+      <c r="C35" t="str">
+        <v>DeepSeek V3.2</v>
+      </c>
+      <c r="D35" t="str">
+        <v>输入(32k,128k]</v>
+      </c>
+      <c r="E35" t="str">
+        <v>+100%</v>
+      </c>
+      <c r="F35" t="str">
+        <v>⚠ 入+100% 出+100%</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>中转站-cust</v>
+      </c>
+      <c r="B36" t="str">
+        <v>minimax-m3</v>
+      </c>
+      <c r="C36" t="str">
+        <v>MiniMax M3</v>
+      </c>
+      <c r="D36" t="str">
+        <v>512k&lt;输入</v>
+      </c>
+      <c r="E36" t="str">
+        <v>+100%</v>
+      </c>
+      <c r="F36" t="str">
+        <v>⚠ 入+100% 出+100% 缓+100%</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>生成时间：2026-07-06T10:02:50Z</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>说明：一致=与厂商官方价偏差&lt;0.5%；≥50%且未登记例外标「待核验」须人工复核；模型级不一致=任一档位不一致</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K39"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8022,7 +8187,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8152,10 +8317,10 @@
         <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
       </c>
       <c r="H4" t="str">
-        <v>入 ¥12 · 出 ¥24 · 缓 ¥2.4</v>
+        <v>入 ¥12 · 出 ¥24</v>
       </c>
       <c r="I4" t="str">
-        <v>⚠ 入+300% 出+300% 缓+9500%</v>
+        <v>⚠ 入+300% 出+300%</v>
       </c>
       <c r="J4" t="str">
         <v>待填</v>
@@ -8187,10 +8352,10 @@
         <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="H5" t="str">
-        <v>入 ¥4 · 出 ¥18</v>
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥0.8</v>
       </c>
       <c r="I5" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 缓-20%</v>
       </c>
       <c r="J5" t="str">
         <v>待填</v>
@@ -8213,10 +8378,10 @@
         <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="H6" t="str">
-        <v>入 ¥6 · 出 ¥22</v>
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="I6" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 缓-20%</v>
       </c>
       <c r="J6" t="str">
         <v>待填</v>
@@ -8248,10 +8413,10 @@
         <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="H7" t="str">
-        <v>入 ¥6 · 出 ¥24</v>
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.2</v>
       </c>
       <c r="I7" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 缓-7.7%</v>
       </c>
       <c r="J7" t="str">
         <v>待填</v>
@@ -8274,10 +8439,10 @@
         <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="H8" t="str">
-        <v>入 ¥8 · 出 ¥28</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥1.6</v>
       </c>
       <c r="I8" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 缓-20%</v>
       </c>
       <c r="J8" t="str">
         <v>待填</v>
@@ -8309,7 +8474,7 @@
         <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="H9" t="str">
-        <v>入 ¥8 · 出 ¥28</v>
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="I9" t="str">
         <v>✅ 一致</v>
@@ -8344,7 +8509,7 @@
         <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
       </c>
       <c r="H10" t="str">
-        <v>入 ¥4 · 出 ¥21</v>
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
       </c>
       <c r="I10" t="str">
         <v>✅ 一致</v>
@@ -8379,7 +8544,7 @@
         <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
       </c>
       <c r="H11" t="str">
-        <v>入 ¥6.5 · 出 ¥27</v>
+        <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.0985</v>
       </c>
       <c r="I11" t="str">
         <v>✅ 一致</v>
@@ -8431,25 +8596,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>minimax-m2.5</v>
+        <v>kimi-k2.7-code-highspeed</v>
       </c>
       <c r="C13" t="str">
-        <v>MiniMax M2.5</v>
+        <v>Kimi K2.7 Code HighSpeed</v>
       </c>
       <c r="D13" t="str">
-        <v>MiniMax</v>
+        <v>Moonshot AI</v>
       </c>
       <c r="E13" t="str">
         <v>统一价</v>
       </c>
       <c r="F13" t="str">
-        <v>MiniMax-M2.5</v>
+        <v>kimi-k2.7-code-highspeed</v>
       </c>
       <c r="G13" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
       </c>
       <c r="H13" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4</v>
+        <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
       </c>
       <c r="I13" t="str">
         <v>✅ 一致</v>
@@ -8466,25 +8631,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>qwen-flash</v>
+        <v>minimax-m2.5</v>
       </c>
       <c r="C14" t="str">
-        <v>Qwen Flash</v>
+        <v>MiniMax M2.5</v>
       </c>
       <c r="D14" t="str">
-        <v>Tongyi</v>
+        <v>MiniMax</v>
       </c>
       <c r="E14" t="str">
-        <v>0&lt;Token≤128K</v>
+        <v>统一价</v>
       </c>
       <c r="F14" t="str">
-        <v>qwen-flash</v>
+        <v>minimax-m2.5</v>
       </c>
       <c r="G14" t="str">
-        <v>入 ¥0.15 · 出 ¥1.5 · 缓 ¥0.03</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
       </c>
       <c r="H14" t="str">
-        <v>入 ¥0.15 · 出 ¥1.5 · 缓 ¥0.03</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
       </c>
       <c r="I14" t="str">
         <v>✅ 一致</v>
@@ -8500,17 +8665,26 @@
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="B15" t="str">
+        <v>minimax-m2.7</v>
+      </c>
+      <c r="C15" t="str">
+        <v>MiniMax M2.7</v>
+      </c>
+      <c r="D15" t="str">
+        <v>MiniMax</v>
+      </c>
       <c r="E15" t="str">
-        <v>128K&lt;Token≤256K</v>
+        <v>统一价</v>
       </c>
       <c r="F15" t="str">
-        <v>qwen-flash</v>
+        <v>minimax-m2.7</v>
       </c>
       <c r="G15" t="str">
-        <v>入 ¥0.6 · 出 ¥6 · 缓 ¥0.12</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="H15" t="str">
-        <v>入 ¥0.6 · 出 ¥6 · 缓 ¥0.12</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="I15" t="str">
         <v>✅ 一致</v>
@@ -8526,17 +8700,26 @@
       <c r="A16">
         <v>15</v>
       </c>
+      <c r="B16" t="str">
+        <v>minimax-m3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>MiniMax M3</v>
+      </c>
+      <c r="D16" t="str">
+        <v>MiniMax</v>
+      </c>
       <c r="E16" t="str">
-        <v>256K&lt;Token≤1M</v>
+        <v>统一价</v>
       </c>
       <c r="F16" t="str">
-        <v>qwen-flash</v>
+        <v>minimax-m3</v>
       </c>
       <c r="G16" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
+        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="H16" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
+        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="I16" t="str">
         <v>✅ 一致</v>
@@ -8553,25 +8736,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>qwen-max</v>
+        <v>qwen-flash</v>
       </c>
       <c r="C17" t="str">
-        <v>Qwen Max</v>
+        <v>Qwen Flash</v>
       </c>
       <c r="D17" t="str">
         <v>Tongyi</v>
       </c>
       <c r="E17" t="str">
-        <v>无阶梯计价</v>
+        <v>0&lt;Token≤128K</v>
       </c>
       <c r="F17" t="str">
-        <v>qwen-max</v>
+        <v>qwen-flash</v>
       </c>
       <c r="G17" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>入 ¥0.15 · 出 ¥1.5 · 缓 ¥0.03</v>
       </c>
       <c r="H17" t="str">
-        <v>入 ¥2.4 · 出 ¥9.6</v>
+        <v>入 ¥0.15 · 出 ¥1.5 · 缓 ¥0.03</v>
       </c>
       <c r="I17" t="str">
         <v>✅ 一致</v>
@@ -8587,26 +8770,17 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v>qwen-plus</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Qwen Plus</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="E18" t="str">
-        <v>0&lt;Token≤128K</v>
+        <v>128K&lt;Token≤256K</v>
       </c>
       <c r="F18" t="str">
-        <v>qwen-plus</v>
+        <v>qwen-flash</v>
       </c>
       <c r="G18" t="str">
-        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+        <v>入 ¥0.6 · 出 ¥6 · 缓 ¥0.12</v>
       </c>
       <c r="H18" t="str">
-        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
+        <v>入 ¥0.6 · 出 ¥6 · 缓 ¥0.12</v>
       </c>
       <c r="I18" t="str">
         <v>✅ 一致</v>
@@ -8623,16 +8797,16 @@
         <v>18</v>
       </c>
       <c r="E19" t="str">
-        <v>128K&lt;Token≤256K</v>
+        <v>256K&lt;Token≤1M</v>
       </c>
       <c r="F19" t="str">
-        <v>qwen-plus</v>
+        <v>qwen-flash</v>
       </c>
       <c r="G19" t="str">
-        <v>入 ¥2.4 · 出 ¥20 · 缓 ¥0.48</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
       </c>
       <c r="H19" t="str">
-        <v>入 ¥2.4 · 出 ¥20 · 缓 ¥0.48</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
       </c>
       <c r="I19" t="str">
         <v>✅ 一致</v>
@@ -8648,17 +8822,26 @@
       <c r="A20">
         <v>19</v>
       </c>
+      <c r="B20" t="str">
+        <v>qwen-max</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Qwen Max</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="E20" t="str">
-        <v>256K&lt;Token≤1M</v>
+        <v>无阶梯计价</v>
       </c>
       <c r="F20" t="str">
-        <v>qwen-plus</v>
+        <v>qwen-max</v>
       </c>
       <c r="G20" t="str">
-        <v>入 ¥4.8 · 出 ¥48 · 缓 ¥0.96</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="H20" t="str">
-        <v>入 ¥4.8 · 出 ¥48 · 缓 ¥0.96</v>
+        <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
       <c r="I20" t="str">
         <v>✅ 一致</v>
@@ -8675,25 +8858,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>qwen-turbo</v>
+        <v>qwen-plus</v>
       </c>
       <c r="C21" t="str">
-        <v>Qwen Turbo</v>
+        <v>Qwen Plus</v>
       </c>
       <c r="D21" t="str">
         <v>Tongyi</v>
       </c>
       <c r="E21" t="str">
-        <v>统一价</v>
+        <v>0&lt;Token≤128K</v>
       </c>
       <c r="F21" t="str">
-        <v>qwen-turbo</v>
+        <v>qwen-plus</v>
       </c>
       <c r="G21" t="str">
-        <v>入 ¥0.3 · 出 ¥0.6</v>
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
       </c>
       <c r="H21" t="str">
-        <v>入 ¥0.3 · 出 ¥0.6</v>
+        <v>入 ¥0.8 · 出 ¥2 · 缓 ¥0.16</v>
       </c>
       <c r="I21" t="str">
         <v>✅ 一致</v>
@@ -8709,29 +8892,20 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="str">
-        <v>qwen3.5-flash</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Qwen3.5 Flash</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="E22" t="str">
-        <v>0&lt;输入&lt;=128k</v>
+        <v>128K&lt;Token≤256K</v>
       </c>
       <c r="F22" t="str">
-        <v>qwen3.5-flash</v>
+        <v>qwen-plus</v>
       </c>
       <c r="G22" t="str">
-        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
+        <v>入 ¥2.4 · 出 ¥20 · 缓 ¥0.48</v>
       </c>
       <c r="H22" t="str">
-        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.04</v>
+        <v>入 ¥2.4 · 出 ¥20 · 缓 ¥0.48</v>
       </c>
       <c r="I22" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>✅ 一致</v>
       </c>
       <c r="J22" t="str">
         <v>待填</v>
@@ -8745,19 +8919,19 @@
         <v>22</v>
       </c>
       <c r="E23" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>256K&lt;Token≤1M</v>
       </c>
       <c r="F23" t="str">
-        <v>qwen3.5-flash</v>
+        <v>qwen-plus</v>
       </c>
       <c r="G23" t="str">
-        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
+        <v>入 ¥4.8 · 出 ¥48 · 缓 ¥0.96</v>
       </c>
       <c r="H23" t="str">
-        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.16</v>
+        <v>入 ¥4.8 · 出 ¥48 · 缓 ¥0.96</v>
       </c>
       <c r="I23" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>✅ 一致</v>
       </c>
       <c r="J23" t="str">
         <v>待填</v>
@@ -8770,20 +8944,29 @@
       <c r="A24">
         <v>23</v>
       </c>
+      <c r="B24" t="str">
+        <v>qwen-turbo</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Qwen Turbo</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="E24" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>统一价</v>
       </c>
       <c r="F24" t="str">
-        <v>qwen3.5-flash</v>
+        <v>qwen-turbo</v>
       </c>
       <c r="G24" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
+        <v>入 ¥0.3 · 出 ¥0.6</v>
       </c>
       <c r="H24" t="str">
-        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
+        <v>入 ¥0.3 · 出 ¥0.6</v>
       </c>
       <c r="I24" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>✅ 一致</v>
       </c>
       <c r="J24" t="str">
         <v>待填</v>
@@ -8797,25 +8980,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>qwen3.5-plus</v>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="C25" t="str">
-        <v>Qwen3.5 Plus</v>
+        <v>Qwen3.5 Flash</v>
       </c>
       <c r="D25" t="str">
         <v>Tongyi</v>
       </c>
       <c r="E25" t="str">
-        <v>输入&lt;=128k</v>
+        <v>0&lt;输入&lt;=128k</v>
       </c>
       <c r="F25" t="str">
-        <v>qwen3.5-plus</v>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="G25" t="str">
-        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="H25" t="str">
-        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.16</v>
+        <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.04</v>
       </c>
       <c r="I25" t="str">
         <v>⚠ 缓+100%</v>
@@ -8835,13 +9018,13 @@
         <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="F26" t="str">
-        <v>qwen3.5-plus</v>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="G26" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
+        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
       </c>
       <c r="H26" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
+        <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.16</v>
       </c>
       <c r="I26" t="str">
         <v>⚠ 缓+100%</v>
@@ -8861,13 +9044,13 @@
         <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="F27" t="str">
-        <v>qwen3.5-plus</v>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="G27" t="str">
-        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
       </c>
       <c r="H27" t="str">
-        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.8</v>
+        <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.24</v>
       </c>
       <c r="I27" t="str">
         <v>⚠ 缓+100%</v>
@@ -8884,28 +9067,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>qwen3.6-flash</v>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="C28" t="str">
-        <v>Qwen3.6 Flash</v>
+        <v>Qwen3.5 Plus</v>
       </c>
       <c r="D28" t="str">
         <v>Tongyi</v>
       </c>
       <c r="E28" t="str">
-        <v>0&lt;Token≤256K</v>
+        <v>输入&lt;=128k</v>
       </c>
       <c r="F28" t="str">
-        <v>qwen3.6-flash</v>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="G28" t="str">
-        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
+        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
       </c>
       <c r="H28" t="str">
-        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
+        <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.16</v>
       </c>
       <c r="I28" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 缓+100%</v>
       </c>
       <c r="J28" t="str">
         <v>待填</v>
@@ -8919,19 +9102,19 @@
         <v>28</v>
       </c>
       <c r="E29" t="str">
-        <v>256K&lt;Token≤1M</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="F29" t="str">
-        <v>qwen3.6-flash</v>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="G29" t="str">
-        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
       </c>
       <c r="H29" t="str">
-        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
       </c>
       <c r="I29" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 缓+100%</v>
       </c>
       <c r="J29" t="str">
         <v>待填</v>
@@ -8944,29 +9127,20 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="str">
-        <v>qwen3.6-plus</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Qwen3.6 Plus</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="E30" t="str">
-        <v>0&lt;Token≤256K</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="F30" t="str">
-        <v>qwen3.6-plus</v>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="G30" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
+        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
       </c>
       <c r="H30" t="str">
-        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
+        <v>入 ¥4 · 出 ¥24 · 缓 ¥0.8</v>
       </c>
       <c r="I30" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 缓+100%</v>
       </c>
       <c r="J30" t="str">
         <v>待填</v>
@@ -8979,17 +9153,26 @@
       <c r="A31">
         <v>30</v>
       </c>
+      <c r="B31" t="str">
+        <v>qwen3.6-flash</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Qwen3.6 Flash</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Tongyi</v>
+      </c>
       <c r="E31" t="str">
-        <v>256K&lt;Token≤1M</v>
+        <v>0&lt;Token≤256K</v>
       </c>
       <c r="F31" t="str">
-        <v>qwen3.6-plus</v>
+        <v>qwen3.6-flash</v>
       </c>
       <c r="G31" t="str">
-        <v>入 ¥8 · 出 ¥48 · 缓 ¥1.6</v>
+        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
       </c>
       <c r="H31" t="str">
-        <v>入 ¥8 · 出 ¥48 · 缓 ¥1.6</v>
+        <v>入 ¥1.2 · 出 ¥7.2 · 缓 ¥0.24</v>
       </c>
       <c r="I31" t="str">
         <v>✅ 一致</v>
@@ -9005,26 +9188,17 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="str">
-        <v>qwen3.7-max</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Qwen3.7 Max</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Tongyi</v>
-      </c>
       <c r="E32" t="str">
-        <v>0&lt;Token≤1M</v>
+        <v>256K&lt;Token≤1M</v>
       </c>
       <c r="F32" t="str">
-        <v>qwen3.7-max</v>
+        <v>qwen3.6-flash</v>
       </c>
       <c r="G32" t="str">
-        <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
+        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
       </c>
       <c r="H32" t="str">
-        <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
+        <v>入 ¥4.8 · 出 ¥28.8 · 缓 ¥0.96</v>
       </c>
       <c r="I32" t="str">
         <v>✅ 一致</v>
@@ -9041,10 +9215,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>qwen3.7-plus</v>
+        <v>qwen3.6-plus</v>
       </c>
       <c r="C33" t="str">
-        <v>Qwen3.7 Plus</v>
+        <v>Qwen3.6 Plus</v>
       </c>
       <c r="D33" t="str">
         <v>Tongyi</v>
@@ -9053,13 +9227,13 @@
         <v>0&lt;Token≤256K</v>
       </c>
       <c r="F33" t="str">
-        <v>qwen3.7-plus</v>
+        <v>qwen3.6-plus</v>
       </c>
       <c r="G33" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
       </c>
       <c r="H33" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
+        <v>入 ¥2 · 出 ¥12 · 缓 ¥0.4</v>
       </c>
       <c r="I33" t="str">
         <v>✅ 一致</v>
@@ -9079,21 +9253,117 @@
         <v>256K&lt;Token≤1M</v>
       </c>
       <c r="F34" t="str">
+        <v>qwen3.6-plus</v>
+      </c>
+      <c r="G34" t="str">
+        <v>入 ¥8 · 出 ¥48 · 缓 ¥1.6</v>
+      </c>
+      <c r="H34" t="str">
+        <v>入 ¥8 · 出 ¥48 · 缓 ¥1.6</v>
+      </c>
+      <c r="I34" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J34" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K34" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>qwen3.7-max</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Qwen3.7 Max</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="E35" t="str">
+        <v>0&lt;Token≤1M</v>
+      </c>
+      <c r="F35" t="str">
+        <v>qwen3.7-max</v>
+      </c>
+      <c r="G35" t="str">
+        <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
+      </c>
+      <c r="H35" t="str">
+        <v>入 ¥12 · 出 ¥36 · 缓 ¥2.4</v>
+      </c>
+      <c r="I35" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J35" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K35" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
         <v>qwen3.7-plus</v>
       </c>
-      <c r="G34" t="str">
+      <c r="C36" t="str">
+        <v>Qwen3.7 Plus</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Tongyi</v>
+      </c>
+      <c r="E36" t="str">
+        <v>0&lt;Token≤256K</v>
+      </c>
+      <c r="F36" t="str">
+        <v>qwen3.7-plus</v>
+      </c>
+      <c r="G36" t="str">
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
+      </c>
+      <c r="H36" t="str">
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.4</v>
+      </c>
+      <c r="I36" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J36" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K36" t="str">
+        <v>待填</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="E37" t="str">
+        <v>256K&lt;Token≤1M</v>
+      </c>
+      <c r="F37" t="str">
+        <v>qwen3.7-plus</v>
+      </c>
+      <c r="G37" t="str">
         <v>入 ¥6 · 出 ¥24 · 缓 ¥1.2</v>
       </c>
-      <c r="H34" t="str">
+      <c r="H37" t="str">
         <v>入 ¥6 · 出 ¥24 · 缓 ¥1.2</v>
       </c>
-      <c r="I34" t="str">
-        <v>✅ 一致</v>
-      </c>
-      <c r="J34" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K34" t="str">
+      <c r="I37" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="J37" t="str">
+        <v>待填</v>
+      </c>
+      <c r="K37" t="str">
         <v>待填</v>
       </c>
     </row>
@@ -9105,30 +9375,30 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="C25:C27"/>
     <mergeCell ref="D25:D27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
     <mergeCell ref="B33:B34"/>
     <mergeCell ref="C33:C34"/>
     <mergeCell ref="D33:D34"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K37"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/pricing/output/trinity-pricing-text.xlsx
+++ b/pricing/output/trinity-pricing-text.xlsx
@@ -405,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R110"/>
+  <dimension ref="A1:T110"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,45 +421,51 @@
         <v>厂商</v>
       </c>
       <c r="E1" t="str">
-        <v>档位</v>
+        <v>价格档位</v>
       </c>
       <c r="F1" t="str">
         <v>厂商官方价</v>
       </c>
       <c r="G1" t="str">
+        <v>AIGC国内</v>
+      </c>
+      <c r="H1" t="str">
         <v>AIGC国际</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>TokenHub</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>OpenRouter</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>线上刊例</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>刊例vs官方_入</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>刊例vs官方_出</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>刊例vs官方_缓</v>
       </c>
-      <c r="N1" t="str">
-        <v>AIGCvs官方</v>
-      </c>
       <c r="O1" t="str">
+        <v>AIGC国内vs官方</v>
+      </c>
+      <c r="P1" t="str">
+        <v>AIGC国际vs官方</v>
+      </c>
+      <c r="Q1" t="str">
         <v>TokenHub vs官方</v>
       </c>
-      <c r="P1" t="str">
-        <v>ORvs官方</v>
-      </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
+        <v>OpenRouter vs官方</v>
+      </c>
+      <c r="S1" t="str">
         <v>刊例结论</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>备注</v>
       </c>
     </row>
@@ -483,19 +489,19 @@
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="G2" t="str">
+        <v>—</v>
+      </c>
+      <c r="H2" t="str">
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
-      <c r="H2" t="str">
-        <v>—</v>
-      </c>
       <c r="I2" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="J2" t="str">
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="K2" t="str">
-        <v>0%</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="L2" t="str">
         <v>0%</v>
@@ -504,7 +510,7 @@
         <v>0%</v>
       </c>
       <c r="N2" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O2" t="str">
         <v>—</v>
@@ -513,9 +519,15 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q2" t="str">
+        <v>—</v>
+      </c>
+      <c r="R2" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R2" t="str">
+      <c r="S2" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T2" t="str">
         <v/>
       </c>
     </row>
@@ -539,19 +551,19 @@
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="G3" t="str">
+        <v>—</v>
+      </c>
+      <c r="H3" t="str">
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
-      <c r="H3" t="str">
-        <v>—</v>
-      </c>
       <c r="I3" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="J3" t="str">
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="K3" t="str">
-        <v>0%</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="L3" t="str">
         <v>0%</v>
@@ -560,7 +572,7 @@
         <v>0%</v>
       </c>
       <c r="N3" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O3" t="str">
         <v>—</v>
@@ -569,9 +581,15 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q3" t="str">
+        <v>—</v>
+      </c>
+      <c r="R3" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R3" t="str">
+      <c r="S3" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T3" t="str">
         <v/>
       </c>
     </row>
@@ -595,19 +613,19 @@
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="G4" t="str">
+        <v>—</v>
+      </c>
+      <c r="H4" t="str">
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
-      <c r="H4" t="str">
-        <v>—</v>
-      </c>
       <c r="I4" t="str">
-        <v>入 $5 · 出 $25 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="J4" t="str">
         <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="K4" t="str">
-        <v>0%</v>
+        <v>入 $5 · 出 $25 · 缓 $0.5</v>
       </c>
       <c r="L4" t="str">
         <v>0%</v>
@@ -616,7 +634,7 @@
         <v>0%</v>
       </c>
       <c r="N4" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O4" t="str">
         <v>—</v>
@@ -625,9 +643,15 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q4" t="str">
+        <v>—</v>
+      </c>
+      <c r="R4" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R4" t="str">
+      <c r="S4" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T4" t="str">
         <v>目录名 cd-opus-4.8</v>
       </c>
     </row>
@@ -651,19 +675,19 @@
         <v>入 $3 · 出 $15 · 缓 $0.3</v>
       </c>
       <c r="G5" t="str">
+        <v>—</v>
+      </c>
+      <c r="H5" t="str">
         <v>入 $3 · 出 $15 · 缓 $0.3</v>
       </c>
-      <c r="H5" t="str">
-        <v>—</v>
-      </c>
       <c r="I5" t="str">
-        <v>入 $3 · 出 $15 · 缓 $0.3</v>
+        <v>—</v>
       </c>
       <c r="J5" t="str">
         <v>入 $3 · 出 $15 · 缓 $0.3</v>
       </c>
       <c r="K5" t="str">
-        <v>0%</v>
+        <v>入 $3 · 出 $15 · 缓 $0.3</v>
       </c>
       <c r="L5" t="str">
         <v>0%</v>
@@ -672,7 +696,7 @@
         <v>0%</v>
       </c>
       <c r="N5" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O5" t="str">
         <v>—</v>
@@ -681,9 +705,15 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q5" t="str">
+        <v>—</v>
+      </c>
+      <c r="R5" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R5" t="str">
+      <c r="S5" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T5" t="str">
         <v/>
       </c>
     </row>
@@ -707,20 +737,20 @@
         <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
       </c>
       <c r="G6" t="str">
+        <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
+      </c>
+      <c r="H6" t="str">
         <v>入 $0.308 · 出 $0.462 · 缓 $0.062</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>入 ¥2 · 出 ¥3 · 缓 ¥0.4</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>入 $0.2288 · 出 $0.3432 · 缓 $0.02288</v>
       </c>
-      <c r="J6" t="str">
+      <c r="K6" t="str">
         <v>入 $0.307692 · 出 $0.461538 · 缓 $0.061538</v>
       </c>
-      <c r="K6" t="str">
-        <v>0%</v>
-      </c>
       <c r="L6" t="str">
         <v>0%</v>
       </c>
@@ -728,18 +758,24 @@
         <v>0%</v>
       </c>
       <c r="N6" t="str">
-        <v>入✅ 出✅ 缓⚠+0.7%</v>
+        <v>0%</v>
       </c>
       <c r="O6" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P6" t="str">
-        <v>入⚠-25.6% 出⚠-25.6% 缓⚠-62.8%</v>
+        <v>入✅ 出✅ 缓⚠+0.7%</v>
       </c>
       <c r="Q6" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R6" t="str">
+        <v>入⚠-25.6% 出⚠-25.6% 缓⚠-62.8%</v>
+      </c>
+      <c r="S6" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T6" t="str">
         <v>v3.2 价目见百炼模型定价；v4 见 DeepSeek API 文档</v>
       </c>
     </row>
@@ -763,20 +799,20 @@
         <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="G7" t="str">
+        <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
+      </c>
+      <c r="H7" t="str">
         <v>入 $0.154 · 出 $0.308 · 缓 $0.003</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>入 ¥1 · 出 ¥2 · 缓 ¥0.2</v>
       </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
         <v>入 $0.098 · 出 $0.196 · 缓 $0.02</v>
       </c>
-      <c r="J7" t="str">
+      <c r="K7" t="str">
         <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
       </c>
-      <c r="K7" t="str">
-        <v>0%</v>
-      </c>
       <c r="L7" t="str">
         <v>0%</v>
       </c>
@@ -784,18 +820,24 @@
         <v>0%</v>
       </c>
       <c r="N7" t="str">
+        <v>0%</v>
+      </c>
+      <c r="O7" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="P7" t="str">
         <v>入✅ 出✅ 缓⚠-2.5%</v>
       </c>
-      <c r="O7" t="str">
+      <c r="Q7" t="str">
         <v>入✅ 出✅ 缓⚠+900%</v>
       </c>
-      <c r="P7" t="str">
+      <c r="R7" t="str">
         <v>入⚠-36.3% 出⚠-36.3% 缓⚠+550%</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="S7" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R7" t="str">
+      <c r="T7" t="str">
         <v/>
       </c>
     </row>
@@ -819,20 +861,20 @@
         <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
       </c>
       <c r="G8" t="str">
+        <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
+      </c>
+      <c r="H8" t="str">
         <v>入 $0.462 · 出 $0.923 · 缓 $0.004</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>入 ¥12 · 出 ¥24 · 缓 ¥1</v>
       </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
         <v>入 $0.435 · 出 $0.87 · 缓 $0.003625</v>
       </c>
-      <c r="J8" t="str">
+      <c r="K8" t="str">
         <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
       </c>
-      <c r="K8" t="str">
-        <v>0%</v>
-      </c>
       <c r="L8" t="str">
         <v>0%</v>
       </c>
@@ -840,18 +882,24 @@
         <v>0%</v>
       </c>
       <c r="N8" t="str">
+        <v>0%</v>
+      </c>
+      <c r="O8" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="P8" t="str">
         <v>入✅ 出✅ 缓⚠+4%</v>
       </c>
-      <c r="O8" t="str">
+      <c r="Q8" t="str">
         <v>入⚠+300% 出⚠+300% 缓⚠+3900%</v>
       </c>
-      <c r="P8" t="str">
+      <c r="R8" t="str">
         <v>入⚠-5.8% 出⚠-5.8% 缓⚠-5.7%</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="S8" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R8" t="str">
+      <c r="T8" t="str">
         <v/>
       </c>
     </row>
@@ -875,19 +923,19 @@
         <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="G9" t="str">
+        <v>入 ¥2.25 · 出 ¥18.75 · 缓 ¥0.22</v>
+      </c>
+      <c r="H9" t="str">
         <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
-      <c r="H9" t="str">
-        <v>—</v>
-      </c>
       <c r="I9" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>—</v>
       </c>
       <c r="J9" t="str">
         <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="K9" t="str">
-        <v>0%</v>
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="L9" t="str">
         <v>0%</v>
@@ -896,18 +944,24 @@
         <v>0%</v>
       </c>
       <c r="N9" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O9" t="str">
-        <v>—</v>
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+12.8%</v>
       </c>
       <c r="P9" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q9" t="str">
+        <v>—</v>
+      </c>
+      <c r="R9" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R9" t="str">
+      <c r="S9" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T9" t="str">
         <v/>
       </c>
     </row>
@@ -919,39 +973,45 @@
         <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
       </c>
       <c r="G10" t="str">
+        <v>入 ¥7.5 · 出 ¥18.75 · 缓 ¥0.75</v>
+      </c>
+      <c r="H10" t="str">
         <v>入 $1 · 出 $2.5 · 缓 $0.1</v>
       </c>
-      <c r="H10" t="str">
-        <v>—</v>
-      </c>
       <c r="I10" t="str">
-        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+        <v>—</v>
       </c>
       <c r="J10" t="str">
         <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
       </c>
       <c r="K10" t="str">
+        <v>入 $0.3 · 出 $2.5 · 缓 $0.03</v>
+      </c>
+      <c r="L10" t="str">
         <v>-70%</v>
       </c>
-      <c r="L10" t="str">
-        <v>0%</v>
-      </c>
       <c r="M10" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N10" t="str">
         <v>-70%</v>
       </c>
-      <c r="N10" t="str">
+      <c r="O10" t="str">
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
+      </c>
+      <c r="P10" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O10" t="str">
-        <v>—</v>
-      </c>
-      <c r="P10" t="str">
+      <c r="Q10" t="str">
+        <v>—</v>
+      </c>
+      <c r="R10" t="str">
         <v>入⚠-70% 出✅ 缓⚠-70%</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="S10" t="str">
         <v>ℹ 线上音频未单独定价</v>
       </c>
-      <c r="R10" t="str">
+      <c r="T10" t="str">
         <v/>
       </c>
     </row>
@@ -975,20 +1035,20 @@
         <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="G11" t="str">
+        <v>入 ¥0.75 · 出 ¥3 · 缓 ¥0.075</v>
+      </c>
+      <c r="H11" t="str">
         <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
-      <c r="H11" t="str">
-        <v>—</v>
-      </c>
       <c r="I11" t="str">
+        <v>—</v>
+      </c>
+      <c r="J11" t="str">
         <v>入 $0.09999999999999999 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
-      <c r="J11" t="str">
+      <c r="K11" t="str">
         <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
-      <c r="K11" t="str">
-        <v>0%</v>
-      </c>
       <c r="L11" t="str">
         <v>0%</v>
       </c>
@@ -996,18 +1056,24 @@
         <v>0%</v>
       </c>
       <c r="N11" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O11" t="str">
-        <v>—</v>
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
       </c>
       <c r="P11" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q11" t="str">
+        <v>—</v>
+      </c>
+      <c r="R11" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R11" t="str">
+      <c r="S11" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T11" t="str">
         <v/>
       </c>
     </row>
@@ -1031,20 +1097,20 @@
         <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
       <c r="G12" t="str">
+        <v>入 ¥0.75 · 出 ¥3 · 缓 ¥0.075</v>
+      </c>
+      <c r="H12" t="str">
         <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
-      <c r="H12" t="str">
-        <v>—</v>
-      </c>
       <c r="I12" t="str">
+        <v>—</v>
+      </c>
+      <c r="J12" t="str">
         <v>入 $0.09999999999999999 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
-      <c r="J12" t="str">
+      <c r="K12" t="str">
         <v>入 $0.1 · 出 $0.4 · 缓 $0.01</v>
       </c>
-      <c r="K12" t="str">
-        <v>0%</v>
-      </c>
       <c r="L12" t="str">
         <v>0%</v>
       </c>
@@ -1052,18 +1118,24 @@
         <v>0%</v>
       </c>
       <c r="N12" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O12" t="str">
-        <v>—</v>
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
       </c>
       <c r="P12" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q12" t="str">
+        <v>—</v>
+      </c>
+      <c r="R12" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R12" t="str">
+      <c r="S12" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T12" t="str">
         <v>preview 别名，价目同 gemini-2.5-flash-lite</v>
       </c>
     </row>
@@ -1087,19 +1159,19 @@
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G13" t="str">
+        <v>入 ¥9.37 · 出 ¥75 · 缓 ¥0.93</v>
+      </c>
+      <c r="H13" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="H13" t="str">
-        <v>—</v>
-      </c>
       <c r="I13" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>—</v>
       </c>
       <c r="J13" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="K13" t="str">
-        <v>0%</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="L13" t="str">
         <v>0%</v>
@@ -1108,18 +1180,24 @@
         <v>0%</v>
       </c>
       <c r="N13" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O13" t="str">
-        <v>—</v>
+        <v>入⚠+15.3% 出⚠+15.4% 缓⚠+14.5%</v>
       </c>
       <c r="P13" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q13" t="str">
+        <v>—</v>
+      </c>
+      <c r="R13" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R13" t="str">
+      <c r="S13" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T13" t="str">
         <v/>
       </c>
     </row>
@@ -1131,20 +1209,20 @@
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="G14" t="str">
+        <v>入 ¥18.75 · 出 ¥112.5 · 缓 ¥1.87</v>
+      </c>
+      <c r="H14" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="H14" t="str">
-        <v>—</v>
-      </c>
       <c r="I14" t="str">
+        <v>—</v>
+      </c>
+      <c r="J14" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="J14" t="str">
+      <c r="K14" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="K14" t="str">
-        <v>0%</v>
-      </c>
       <c r="L14" t="str">
         <v>0%</v>
       </c>
@@ -1152,18 +1230,24 @@
         <v>0%</v>
       </c>
       <c r="N14" t="str">
+        <v>0%</v>
+      </c>
+      <c r="O14" t="str">
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.1%</v>
+      </c>
+      <c r="P14" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O14" t="str">
-        <v>—</v>
-      </c>
-      <c r="P14" t="str">
+      <c r="Q14" t="str">
+        <v>—</v>
+      </c>
+      <c r="R14" t="str">
         <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="S14" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R14" t="str">
+      <c r="T14" t="str">
         <v/>
       </c>
     </row>
@@ -1187,20 +1271,20 @@
         <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
       <c r="G15" t="str">
+        <v>入 ¥3.5 · 出 ¥21 · 缓 ¥0.35</v>
+      </c>
+      <c r="H15" t="str">
         <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
-      <c r="H15" t="str">
-        <v>—</v>
-      </c>
       <c r="I15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J15" t="str">
         <v>入 $0.5 · 出 $3 · 缓 $0.049999999999999996</v>
       </c>
-      <c r="J15" t="str">
+      <c r="K15" t="str">
         <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
-      <c r="K15" t="str">
-        <v>0%</v>
-      </c>
       <c r="L15" t="str">
         <v>0%</v>
       </c>
@@ -1208,18 +1292,24 @@
         <v>0%</v>
       </c>
       <c r="N15" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O15" t="str">
-        <v>—</v>
+        <v>入⚠+7.7% 出⚠+7.7% 缓⚠+7.7%</v>
       </c>
       <c r="P15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q15" t="str">
+        <v>—</v>
+      </c>
+      <c r="R15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R15" t="str">
+      <c r="S15" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T15" t="str">
         <v/>
       </c>
     </row>
@@ -1231,39 +1321,45 @@
         <v>入 $1 · 出 $3 · 缓 $0.1</v>
       </c>
       <c r="G16" t="str">
+        <v>入 ¥7 · 出 ¥21 · 缓 ¥0.7</v>
+      </c>
+      <c r="H16" t="str">
         <v>入 $1 · 出 $3 · 缓 $0.1</v>
       </c>
-      <c r="H16" t="str">
-        <v>—</v>
-      </c>
       <c r="I16" t="str">
+        <v>—</v>
+      </c>
+      <c r="J16" t="str">
         <v>入 $0.5 · 出 $3 · 缓 $0.049999999999999996</v>
       </c>
-      <c r="J16" t="str">
+      <c r="K16" t="str">
         <v>入 $0.5 · 出 $3 · 缓 $0.05</v>
       </c>
-      <c r="K16" t="str">
+      <c r="L16" t="str">
         <v>-50%</v>
       </c>
-      <c r="L16" t="str">
-        <v>0%</v>
-      </c>
       <c r="M16" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N16" t="str">
         <v>-50%</v>
       </c>
-      <c r="N16" t="str">
+      <c r="O16" t="str">
+        <v>入⚠+7.7% 出⚠+7.7% 缓⚠+7.7%</v>
+      </c>
+      <c r="P16" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O16" t="str">
-        <v>—</v>
-      </c>
-      <c r="P16" t="str">
+      <c r="Q16" t="str">
+        <v>—</v>
+      </c>
+      <c r="R16" t="str">
         <v>入⚠-50% 出✅ 缓⚠-50%</v>
       </c>
-      <c r="Q16" t="str">
+      <c r="S16" t="str">
         <v>ℹ 线上音频未单独定价</v>
       </c>
-      <c r="R16" t="str">
+      <c r="T16" t="str">
         <v/>
       </c>
     </row>
@@ -1287,20 +1383,20 @@
         <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
       <c r="G17" t="str">
+        <v>入 ¥1.87 · 出 ¥11.25 · 缓 ¥0.18</v>
+      </c>
+      <c r="H17" t="str">
         <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
-      <c r="H17" t="str">
-        <v>—</v>
-      </c>
       <c r="I17" t="str">
+        <v>—</v>
+      </c>
+      <c r="J17" t="str">
         <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
       </c>
-      <c r="J17" t="str">
+      <c r="K17" t="str">
         <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
-      <c r="K17" t="str">
-        <v>0%</v>
-      </c>
       <c r="L17" t="str">
         <v>0%</v>
       </c>
@@ -1308,18 +1404,24 @@
         <v>0%</v>
       </c>
       <c r="N17" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O17" t="str">
-        <v>—</v>
+        <v>入⚠+15.1% 出⚠+15.4% 缓⚠+10.8%</v>
       </c>
       <c r="P17" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q17" t="str">
+        <v>—</v>
+      </c>
+      <c r="R17" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R17" t="str">
+      <c r="S17" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T17" t="str">
         <v/>
       </c>
     </row>
@@ -1331,39 +1433,45 @@
         <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
       </c>
       <c r="G18" t="str">
+        <v>入 ¥3.75 · 出 ¥11.25 · 缓 ¥0.37</v>
+      </c>
+      <c r="H18" t="str">
         <v>入 $0.5 · 出 $1.5 · 缓 $0.05</v>
       </c>
-      <c r="H18" t="str">
-        <v>—</v>
-      </c>
       <c r="I18" t="str">
+        <v>—</v>
+      </c>
+      <c r="J18" t="str">
         <v>入 $0.25 · 出 $1.5 · 缓 $0.024999999999999998</v>
       </c>
-      <c r="J18" t="str">
+      <c r="K18" t="str">
         <v>入 $0.25 · 出 $1.5 · 缓 $0.025</v>
       </c>
-      <c r="K18" t="str">
+      <c r="L18" t="str">
         <v>-50%</v>
       </c>
-      <c r="L18" t="str">
-        <v>0%</v>
-      </c>
       <c r="M18" t="str">
+        <v>0%</v>
+      </c>
+      <c r="N18" t="str">
         <v>-50%</v>
       </c>
-      <c r="N18" t="str">
+      <c r="O18" t="str">
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+13.8%</v>
+      </c>
+      <c r="P18" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O18" t="str">
-        <v>—</v>
-      </c>
-      <c r="P18" t="str">
+      <c r="Q18" t="str">
+        <v>—</v>
+      </c>
+      <c r="R18" t="str">
         <v>入⚠-50% 出✅ 缓⚠-50%</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="S18" t="str">
         <v>ℹ 线上音频未单独定价</v>
       </c>
-      <c r="R18" t="str">
+      <c r="T18" t="str">
         <v/>
       </c>
     </row>
@@ -1387,20 +1495,20 @@
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
       <c r="G19" t="str">
+        <v>入 ¥15 · 出 ¥90 · 缓 ¥1.5</v>
+      </c>
+      <c r="H19" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
-      <c r="H19" t="str">
-        <v>—</v>
-      </c>
       <c r="I19" t="str">
+        <v>—</v>
+      </c>
+      <c r="J19" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.19999999999999998</v>
       </c>
-      <c r="J19" t="str">
+      <c r="K19" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
-      <c r="K19" t="str">
-        <v>0%</v>
-      </c>
       <c r="L19" t="str">
         <v>0%</v>
       </c>
@@ -1408,18 +1516,24 @@
         <v>0%</v>
       </c>
       <c r="N19" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O19" t="str">
-        <v>—</v>
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
       </c>
       <c r="P19" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q19" t="str">
+        <v>—</v>
+      </c>
+      <c r="R19" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R19" t="str">
+      <c r="S19" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T19" t="str">
         <v/>
       </c>
     </row>
@@ -1431,20 +1545,20 @@
         <v>入 $4 · 出 $18 · 缓 $0.4</v>
       </c>
       <c r="G20" t="str">
+        <v>入 ¥30 · 出 ¥135 · 缓 ¥3</v>
+      </c>
+      <c r="H20" t="str">
         <v>入 $4 · 出 $18 · 缓 $0.4</v>
       </c>
-      <c r="H20" t="str">
-        <v>—</v>
-      </c>
       <c r="I20" t="str">
+        <v>—</v>
+      </c>
+      <c r="J20" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.19999999999999998</v>
       </c>
-      <c r="J20" t="str">
+      <c r="K20" t="str">
         <v>入 $4 · 出 $18 · 缓 $0.4</v>
       </c>
-      <c r="K20" t="str">
-        <v>0%</v>
-      </c>
       <c r="L20" t="str">
         <v>0%</v>
       </c>
@@ -1452,18 +1566,24 @@
         <v>0%</v>
       </c>
       <c r="N20" t="str">
+        <v>0%</v>
+      </c>
+      <c r="O20" t="str">
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
+      </c>
+      <c r="P20" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O20" t="str">
-        <v>—</v>
-      </c>
-      <c r="P20" t="str">
+      <c r="Q20" t="str">
+        <v>—</v>
+      </c>
+      <c r="R20" t="str">
         <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
-      <c r="Q20" t="str">
+      <c r="S20" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R20" t="str">
+      <c r="T20" t="str">
         <v/>
       </c>
     </row>
@@ -1487,19 +1607,19 @@
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="G21" t="str">
+        <v>入 ¥11.25 · 出 ¥67.5 · 缓 ¥1.125</v>
+      </c>
+      <c r="H21" t="str">
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
-      <c r="H21" t="str">
-        <v>—</v>
-      </c>
       <c r="I21" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>—</v>
       </c>
       <c r="J21" t="str">
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="K21" t="str">
-        <v>0%</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="L21" t="str">
         <v>0%</v>
@@ -1508,18 +1628,24 @@
         <v>0%</v>
       </c>
       <c r="N21" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O21" t="str">
-        <v>—</v>
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
       </c>
       <c r="P21" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q21" t="str">
+        <v>—</v>
+      </c>
+      <c r="R21" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R21" t="str">
+      <c r="S21" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T21" t="str">
         <v/>
       </c>
     </row>
@@ -1531,19 +1657,19 @@
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="G22" t="str">
+        <v>入 ¥11.25 · 出 ¥67.5 · 缓 ¥1.125</v>
+      </c>
+      <c r="H22" t="str">
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
-      <c r="H22" t="str">
-        <v>—</v>
-      </c>
       <c r="I22" t="str">
-        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
+        <v>—</v>
       </c>
       <c r="J22" t="str">
         <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="K22" t="str">
-        <v>0%</v>
+        <v>入 $1.5 · 出 $9 · 缓 $0.15</v>
       </c>
       <c r="L22" t="str">
         <v>0%</v>
@@ -1552,18 +1678,24 @@
         <v>0%</v>
       </c>
       <c r="N22" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O22" t="str">
-        <v>—</v>
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
       </c>
       <c r="P22" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q22" t="str">
+        <v>—</v>
+      </c>
+      <c r="R22" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="S22" t="str">
         <v>ℹ 线上音频未单独定价</v>
       </c>
-      <c r="R22" t="str">
+      <c r="T22" t="str">
         <v/>
       </c>
     </row>
@@ -1617,9 +1749,15 @@
         <v>—</v>
       </c>
       <c r="Q23" t="str">
+        <v>—</v>
+      </c>
+      <c r="R23" t="str">
+        <v>—</v>
+      </c>
+      <c r="S23" t="str">
         <v>— 未上架</v>
       </c>
-      <c r="R23" t="str">
+      <c r="T23" t="str">
         <v>目录名 gk-4.3</v>
       </c>
     </row>
@@ -1673,9 +1811,15 @@
         <v>—</v>
       </c>
       <c r="Q24" t="str">
+        <v>—</v>
+      </c>
+      <c r="R24" t="str">
+        <v>—</v>
+      </c>
+      <c r="S24" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R24" t="str">
+      <c r="T24" t="str">
         <v>目录名 gk-4-20-non-reasoning</v>
       </c>
     </row>
@@ -1729,9 +1873,15 @@
         <v>—</v>
       </c>
       <c r="Q25" t="str">
+        <v>—</v>
+      </c>
+      <c r="R25" t="str">
+        <v>—</v>
+      </c>
+      <c r="S25" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R25" t="str">
+      <c r="T25" t="str">
         <v>目录名 gk-4-20-reasoning</v>
       </c>
     </row>
@@ -1755,19 +1905,19 @@
         <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="G26" t="str">
+        <v>入 ¥15 · 出 ¥60 · 缓 ¥3.75</v>
+      </c>
+      <c r="H26" t="str">
         <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
-      <c r="H26" t="str">
-        <v>—</v>
-      </c>
       <c r="I26" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="J26" t="str">
         <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="K26" t="str">
-        <v>0%</v>
+        <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="L26" t="str">
         <v>0%</v>
@@ -1776,18 +1926,24 @@
         <v>0%</v>
       </c>
       <c r="N26" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O26" t="str">
-        <v>—</v>
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
       </c>
       <c r="P26" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q26" t="str">
+        <v>—</v>
+      </c>
+      <c r="R26" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R26" t="str">
+      <c r="S26" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T26" t="str">
         <v/>
       </c>
     </row>
@@ -1811,20 +1967,20 @@
         <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="G27" t="str">
+        <v>入 ¥18.75 · 出 ¥75 · 缓 ¥9.37</v>
+      </c>
+      <c r="H27" t="str">
         <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
-      <c r="H27" t="str">
-        <v>—</v>
-      </c>
       <c r="I27" t="str">
+        <v>—</v>
+      </c>
+      <c r="J27" t="str">
         <v>入 $2.5 · 出 $10</v>
       </c>
-      <c r="J27" t="str">
+      <c r="K27" t="str">
         <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
-      <c r="K27" t="str">
-        <v>0%</v>
-      </c>
       <c r="L27" t="str">
         <v>0%</v>
       </c>
@@ -1832,18 +1988,24 @@
         <v>0%</v>
       </c>
       <c r="N27" t="str">
+        <v>0%</v>
+      </c>
+      <c r="O27" t="str">
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.3%</v>
+      </c>
+      <c r="P27" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O27" t="str">
-        <v>—</v>
-      </c>
-      <c r="P27" t="str">
+      <c r="Q27" t="str">
+        <v>—</v>
+      </c>
+      <c r="R27" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="Q27" t="str">
+      <c r="S27" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R27" t="str">
+      <c r="T27" t="str">
         <v/>
       </c>
     </row>
@@ -1867,19 +2029,19 @@
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G28" t="str">
+        <v>入 ¥9.37 · 出 ¥75 · 缓 ¥0.93</v>
+      </c>
+      <c r="H28" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="H28" t="str">
-        <v>—</v>
-      </c>
       <c r="I28" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>—</v>
       </c>
       <c r="J28" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="K28" t="str">
-        <v>0%</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="L28" t="str">
         <v>0%</v>
@@ -1888,18 +2050,24 @@
         <v>0%</v>
       </c>
       <c r="N28" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O28" t="str">
-        <v>—</v>
+        <v>入⚠+15.3% 出⚠+15.4% 缓⚠+14.5%</v>
       </c>
       <c r="P28" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q28" t="str">
+        <v>—</v>
+      </c>
+      <c r="R28" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R28" t="str">
+      <c r="S28" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T28" t="str">
         <v/>
       </c>
     </row>
@@ -1953,9 +2121,15 @@
         <v>—</v>
       </c>
       <c r="Q29" t="str">
+        <v>—</v>
+      </c>
+      <c r="R29" t="str">
+        <v>—</v>
+      </c>
+      <c r="S29" t="str">
         <v>— 未上架</v>
       </c>
-      <c r="R29" t="str">
+      <c r="T29" t="str">
         <v/>
       </c>
     </row>
@@ -1979,20 +2153,20 @@
         <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="G30" t="str">
+        <v>入 ¥0.37 · 出 ¥3 · 缓 ¥0.03</v>
+      </c>
+      <c r="H30" t="str">
         <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
-      <c r="H30" t="str">
-        <v>—</v>
-      </c>
       <c r="I30" t="str">
+        <v>—</v>
+      </c>
+      <c r="J30" t="str">
         <v>入 $0.049999999999999996 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
-      <c r="J30" t="str">
+      <c r="K30" t="str">
         <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
-      <c r="K30" t="str">
-        <v>0%</v>
-      </c>
       <c r="L30" t="str">
         <v>0%</v>
       </c>
@@ -2000,18 +2174,24 @@
         <v>0%</v>
       </c>
       <c r="N30" t="str">
+        <v>0%</v>
+      </c>
+      <c r="O30" t="str">
+        <v>入⚠+13.8% 出⚠+15.4% 缓⚠-7.7%</v>
+      </c>
+      <c r="P30" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O30" t="str">
-        <v>—</v>
-      </c>
-      <c r="P30" t="str">
+      <c r="Q30" t="str">
+        <v>—</v>
+      </c>
+      <c r="R30" t="str">
         <v>入✅ 出✅ 缓⚠+100%</v>
       </c>
-      <c r="Q30" t="str">
+      <c r="S30" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R30" t="str">
+      <c r="T30" t="str">
         <v/>
       </c>
     </row>
@@ -2035,20 +2215,20 @@
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G31" t="str">
+        <v>入 ¥8.75 · 出 ¥70 · 缓 ¥0.87</v>
+      </c>
+      <c r="H31" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="H31" t="str">
-        <v>—</v>
-      </c>
       <c r="I31" t="str">
+        <v>—</v>
+      </c>
+      <c r="J31" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
       </c>
-      <c r="J31" t="str">
+      <c r="K31" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="K31" t="str">
-        <v>0%</v>
-      </c>
       <c r="L31" t="str">
         <v>0%</v>
       </c>
@@ -2056,18 +2236,24 @@
         <v>0%</v>
       </c>
       <c r="N31" t="str">
+        <v>0%</v>
+      </c>
+      <c r="O31" t="str">
+        <v>入⚠+7.7% 出⚠+7.7% 缓⚠+7.1%</v>
+      </c>
+      <c r="P31" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O31" t="str">
-        <v>—</v>
-      </c>
-      <c r="P31" t="str">
+      <c r="Q31" t="str">
+        <v>—</v>
+      </c>
+      <c r="R31" t="str">
         <v>入✅ 出✅ 缓⚠+4%</v>
       </c>
-      <c r="Q31" t="str">
+      <c r="S31" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R31" t="str">
+      <c r="T31" t="str">
         <v/>
       </c>
     </row>
@@ -2091,19 +2277,19 @@
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="G32" t="str">
+        <v>入 ¥12.25 · 出 ¥98 · 缓 ¥1.22</v>
+      </c>
+      <c r="H32" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="H32" t="str">
-        <v>—</v>
-      </c>
       <c r="I32" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>—</v>
       </c>
       <c r="J32" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="K32" t="str">
-        <v>0%</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="L32" t="str">
         <v>0%</v>
@@ -2112,18 +2298,24 @@
         <v>0%</v>
       </c>
       <c r="N32" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O32" t="str">
-        <v>—</v>
+        <v>入⚠+7.7% 出⚠+7.7% 缓⚠+7.3%</v>
       </c>
       <c r="P32" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q32" t="str">
+        <v>—</v>
+      </c>
+      <c r="R32" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R32" t="str">
+      <c r="S32" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T32" t="str">
         <v/>
       </c>
     </row>
@@ -2147,20 +2339,20 @@
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="G33" t="str">
+        <v>入 ¥13.13 · 出 ¥105 · 缓 ¥1.35</v>
+      </c>
+      <c r="H33" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.18</v>
       </c>
-      <c r="H33" t="str">
-        <v>—</v>
-      </c>
       <c r="I33" t="str">
         <v>—</v>
       </c>
       <c r="J33" t="str">
+        <v>—</v>
+      </c>
+      <c r="K33" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="K33" t="str">
-        <v>0%</v>
-      </c>
       <c r="L33" t="str">
         <v>0%</v>
       </c>
@@ -2168,18 +2360,24 @@
         <v>0%</v>
       </c>
       <c r="N33" t="str">
+        <v>0%</v>
+      </c>
+      <c r="O33" t="str">
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+18.7%</v>
+      </c>
+      <c r="P33" t="str">
         <v>入✅ 出✅ 缓⚠+2.9%</v>
       </c>
-      <c r="O33" t="str">
-        <v>—</v>
-      </c>
-      <c r="P33" t="str">
-        <v>—</v>
-      </c>
       <c r="Q33" t="str">
+        <v>—</v>
+      </c>
+      <c r="R33" t="str">
+        <v>—</v>
+      </c>
+      <c r="S33" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R33" t="str">
+      <c r="T33" t="str">
         <v/>
       </c>
     </row>
@@ -2203,19 +2401,19 @@
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="G34" t="str">
+        <v>入 ¥18.75 · 出 ¥112.5 · 缓 ¥1.88</v>
+      </c>
+      <c r="H34" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="H34" t="str">
-        <v>—</v>
-      </c>
       <c r="I34" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>—</v>
       </c>
       <c r="J34" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="K34" t="str">
-        <v>0%</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="L34" t="str">
         <v>0%</v>
@@ -2224,18 +2422,24 @@
         <v>0%</v>
       </c>
       <c r="N34" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O34" t="str">
-        <v>—</v>
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.7%</v>
       </c>
       <c r="P34" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q34" t="str">
+        <v>—</v>
+      </c>
+      <c r="R34" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R34" t="str">
+      <c r="S34" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T34" t="str">
         <v/>
       </c>
     </row>
@@ -2247,20 +2451,20 @@
         <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="G35" t="str">
+        <v>入 ¥37.5 · 出 ¥168.75 · 缓 ¥3.75</v>
+      </c>
+      <c r="H35" t="str">
         <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
-      <c r="H35" t="str">
-        <v>—</v>
-      </c>
       <c r="I35" t="str">
+        <v>—</v>
+      </c>
+      <c r="J35" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="J35" t="str">
+      <c r="K35" t="str">
         <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
-      <c r="K35" t="str">
-        <v>0%</v>
-      </c>
       <c r="L35" t="str">
         <v>0%</v>
       </c>
@@ -2268,18 +2472,24 @@
         <v>0%</v>
       </c>
       <c r="N35" t="str">
+        <v>0%</v>
+      </c>
+      <c r="O35" t="str">
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
+      </c>
+      <c r="P35" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O35" t="str">
-        <v>—</v>
-      </c>
-      <c r="P35" t="str">
+      <c r="Q35" t="str">
+        <v>—</v>
+      </c>
+      <c r="R35" t="str">
         <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
-      <c r="Q35" t="str">
+      <c r="S35" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R35" t="str">
+      <c r="T35" t="str">
         <v/>
       </c>
     </row>
@@ -2303,19 +2513,19 @@
         <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="G36" t="str">
+        <v>入 ¥5.63 · 出 ¥33.75 · 缓 ¥0.56</v>
+      </c>
+      <c r="H36" t="str">
         <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
-      <c r="H36" t="str">
-        <v>—</v>
-      </c>
       <c r="I36" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>—</v>
       </c>
       <c r="J36" t="str">
         <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="K36" t="str">
-        <v>0%</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="L36" t="str">
         <v>0%</v>
@@ -2324,18 +2534,24 @@
         <v>0%</v>
       </c>
       <c r="N36" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O36" t="str">
-        <v>—</v>
+        <v>入⚠+15.5% 出⚠+15.4% 缓⚠+14.9%</v>
       </c>
       <c r="P36" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q36" t="str">
+        <v>—</v>
+      </c>
+      <c r="R36" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R36" t="str">
+      <c r="S36" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T36" t="str">
         <v/>
       </c>
     </row>
@@ -2389,9 +2605,15 @@
         <v>—</v>
       </c>
       <c r="Q37" t="str">
+        <v>—</v>
+      </c>
+      <c r="R37" t="str">
+        <v>—</v>
+      </c>
+      <c r="S37" t="str">
         <v>— 未上架</v>
       </c>
-      <c r="R37" t="str">
+      <c r="T37" t="str">
         <v/>
       </c>
     </row>
@@ -2415,39 +2637,45 @@
         <v>入 $30 · 出 $180</v>
       </c>
       <c r="G38" t="str">
+        <v>入 ¥225 · 出 ¥1350</v>
+      </c>
+      <c r="H38" t="str">
         <v>入 $30 · 出 $180</v>
       </c>
-      <c r="H38" t="str">
-        <v>—</v>
-      </c>
       <c r="I38" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>—</v>
       </c>
       <c r="J38" t="str">
         <v>入 $30 · 出 $180</v>
       </c>
       <c r="K38" t="str">
-        <v>0%</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="L38" t="str">
         <v>0%</v>
       </c>
       <c r="M38" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N38" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="O38" t="str">
-        <v>—</v>
+        <v>入⚠+15.4% 出⚠+15.4%</v>
       </c>
       <c r="P38" t="str">
         <v>入✅ 出✅</v>
       </c>
       <c r="Q38" t="str">
+        <v>—</v>
+      </c>
+      <c r="R38" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="R38" t="str">
+      <c r="S38" t="str">
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="T38" t="str">
         <v/>
       </c>
     </row>
@@ -2459,39 +2687,45 @@
         <v>入 $60 · 出 $270</v>
       </c>
       <c r="G39" t="str">
+        <v>入 ¥450 · 出 ¥2025</v>
+      </c>
+      <c r="H39" t="str">
         <v>入 $60 · 出 $270</v>
       </c>
-      <c r="H39" t="str">
-        <v>—</v>
-      </c>
       <c r="I39" t="str">
+        <v>—</v>
+      </c>
+      <c r="J39" t="str">
         <v>入 $30 · 出 $180</v>
       </c>
-      <c r="J39" t="str">
+      <c r="K39" t="str">
         <v>入 $60 · 出 $270</v>
       </c>
-      <c r="K39" t="str">
-        <v>0%</v>
-      </c>
       <c r="L39" t="str">
         <v>0%</v>
       </c>
       <c r="M39" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N39" t="str">
+        <v>—</v>
+      </c>
+      <c r="O39" t="str">
+        <v>入⚠+15.4% 出⚠+15.4%</v>
+      </c>
+      <c r="P39" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="O39" t="str">
-        <v>—</v>
-      </c>
-      <c r="P39" t="str">
+      <c r="Q39" t="str">
+        <v>—</v>
+      </c>
+      <c r="R39" t="str">
         <v>入⚠-50% 出⚠-33.3%</v>
       </c>
-      <c r="Q39" t="str">
+      <c r="S39" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="R39" t="str">
+      <c r="T39" t="str">
         <v/>
       </c>
     </row>
@@ -2515,19 +2749,19 @@
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="G40" t="str">
+        <v>入 ¥37.5 · 出 ¥225 · 缓 ¥3.75</v>
+      </c>
+      <c r="H40" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="H40" t="str">
-        <v>—</v>
-      </c>
       <c r="I40" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="J40" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="K40" t="str">
-        <v>0%</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="L40" t="str">
         <v>0%</v>
@@ -2536,18 +2770,24 @@
         <v>0%</v>
       </c>
       <c r="N40" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O40" t="str">
-        <v>—</v>
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
       </c>
       <c r="P40" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q40" t="str">
+        <v>—</v>
+      </c>
+      <c r="R40" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R40" t="str">
+      <c r="S40" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T40" t="str">
         <v/>
       </c>
     </row>
@@ -2559,20 +2799,20 @@
         <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="G41" t="str">
+        <v>入 ¥75 · 出 ¥337.5 · 缓 ¥7.5</v>
+      </c>
+      <c r="H41" t="str">
         <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
-      <c r="H41" t="str">
-        <v>—</v>
-      </c>
       <c r="I41" t="str">
+        <v>—</v>
+      </c>
+      <c r="J41" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="J41" t="str">
+      <c r="K41" t="str">
         <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
-      <c r="K41" t="str">
-        <v>0%</v>
-      </c>
       <c r="L41" t="str">
         <v>0%</v>
       </c>
@@ -2580,18 +2820,24 @@
         <v>0%</v>
       </c>
       <c r="N41" t="str">
+        <v>0%</v>
+      </c>
+      <c r="O41" t="str">
+        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
+      </c>
+      <c r="P41" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="O41" t="str">
-        <v>—</v>
-      </c>
-      <c r="P41" t="str">
+      <c r="Q41" t="str">
+        <v>—</v>
+      </c>
+      <c r="R41" t="str">
         <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
-      <c r="Q41" t="str">
+      <c r="S41" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R41" t="str">
+      <c r="T41" t="str">
         <v/>
       </c>
     </row>
@@ -2645,9 +2891,15 @@
         <v>—</v>
       </c>
       <c r="Q42" t="str">
+        <v>—</v>
+      </c>
+      <c r="R42" t="str">
+        <v>—</v>
+      </c>
+      <c r="S42" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R42" t="str">
+      <c r="T42" t="str">
         <v>对应 gpt-5.5 instant</v>
       </c>
     </row>
@@ -2689,9 +2941,15 @@
         <v>—</v>
       </c>
       <c r="Q43" t="str">
+        <v>—</v>
+      </c>
+      <c r="R43" t="str">
+        <v>—</v>
+      </c>
+      <c r="S43" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R43" t="str">
+      <c r="T43" t="str">
         <v>对应 gpt-5.5 instant</v>
       </c>
     </row>
@@ -2745,9 +3003,15 @@
         <v>—</v>
       </c>
       <c r="Q44" t="str">
+        <v>—</v>
+      </c>
+      <c r="R44" t="str">
+        <v>—</v>
+      </c>
+      <c r="S44" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R44" t="str">
+      <c r="T44" t="str">
         <v>目录名 gpt-5.2-chat</v>
       </c>
     </row>
@@ -2801,9 +3065,15 @@
         <v>—</v>
       </c>
       <c r="Q45" t="str">
+        <v>—</v>
+      </c>
+      <c r="R45" t="str">
+        <v>—</v>
+      </c>
+      <c r="S45" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R45" t="str">
+      <c r="T45" t="str">
         <v>目录名 gpt-5.3-chat</v>
       </c>
     </row>
@@ -2827,20 +3097,20 @@
         <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
       </c>
       <c r="G46" t="str">
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+      </c>
+      <c r="H46" t="str">
         <v>入 $0.616 · 出 $3.234 · 缓 $0.108</v>
       </c>
-      <c r="H46" t="str">
+      <c r="I46" t="str">
         <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
       </c>
-      <c r="I46" t="str">
+      <c r="J46" t="str">
         <v>入 $0.375 · 出 $2.025</v>
       </c>
-      <c r="J46" t="str">
+      <c r="K46" t="str">
         <v>入 $0.615385 · 出 $3.230769 · 缓 $0.107692</v>
       </c>
-      <c r="K46" t="str">
-        <v>0%</v>
-      </c>
       <c r="L46" t="str">
         <v>0%</v>
       </c>
@@ -2848,18 +3118,24 @@
         <v>0%</v>
       </c>
       <c r="N46" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O46" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P46" t="str">
-        <v>入⚠-39.1% 出⚠-37.3%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q46" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R46" t="str">
+        <v>入⚠-39.1% 出⚠-37.3%</v>
+      </c>
+      <c r="S46" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T46" t="str">
         <v/>
       </c>
     </row>
@@ -2886,17 +3162,17 @@
         <v>—</v>
       </c>
       <c r="H47" t="str">
+        <v>—</v>
+      </c>
+      <c r="I47" t="str">
         <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.1</v>
       </c>
-      <c r="I47" t="str">
+      <c r="J47" t="str">
         <v>入 $0.55 · 出 $3.1999999999999997 · 缓 $0.11</v>
       </c>
-      <c r="J47" t="str">
+      <c r="K47" t="str">
         <v>入 $1 · 出 $4.153846 · 缓 $0.169231</v>
       </c>
-      <c r="K47" t="str">
-        <v>0%</v>
-      </c>
       <c r="L47" t="str">
         <v>0%</v>
       </c>
@@ -2904,18 +3180,24 @@
         <v>0%</v>
       </c>
       <c r="N47" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O47" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P47" t="str">
-        <v>入⚠-45% 出⚠-23% 缓⚠-35%</v>
+        <v>—</v>
       </c>
       <c r="Q47" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R47" t="str">
+        <v>入⚠-45% 出⚠-23% 缓⚠-35%</v>
+      </c>
+      <c r="S47" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T47" t="str">
         <v/>
       </c>
     </row>
@@ -2942,36 +3224,42 @@
         <v>—</v>
       </c>
       <c r="H48" t="str">
+        <v>—</v>
+      </c>
+      <c r="I48" t="str">
         <v>入 ¥6.5 · 出 ¥27 · 缓 ¥1.3</v>
       </c>
-      <c r="I48" t="str">
+      <c r="J48" t="str">
         <v>入 $0.74 · 出 $3.5 · 缓 $0.15</v>
       </c>
-      <c r="J48" t="str">
+      <c r="K48" t="str">
         <v>入 $1 · 出 $4.153846</v>
       </c>
-      <c r="K48" t="str">
-        <v>0%</v>
-      </c>
       <c r="L48" t="str">
         <v>0%</v>
       </c>
       <c r="M48" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N48" t="str">
         <v>—</v>
       </c>
       <c r="O48" t="str">
+        <v>—</v>
+      </c>
+      <c r="P48" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q48" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="P48" t="str">
+      <c r="R48" t="str">
         <v>入⚠-26% 出⚠-15.7% 缓⚠-25%</v>
       </c>
-      <c r="Q48" t="str">
+      <c r="S48" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="R48" t="str">
+      <c r="T48" t="str">
         <v/>
       </c>
     </row>
@@ -2998,17 +3286,17 @@
         <v>—</v>
       </c>
       <c r="H49" t="str">
+        <v>—</v>
+      </c>
+      <c r="I49" t="str">
         <v>入 ¥13 · 出 ¥54 · 缓 ¥2.6</v>
       </c>
-      <c r="I49" t="str">
-        <v>—</v>
-      </c>
       <c r="J49" t="str">
+        <v>—</v>
+      </c>
+      <c r="K49" t="str">
         <v>入 $2 · 出 $8.307692 · 缓 $0.4</v>
       </c>
-      <c r="K49" t="str">
-        <v>0%</v>
-      </c>
       <c r="L49" t="str">
         <v>0%</v>
       </c>
@@ -3016,10 +3304,10 @@
         <v>0%</v>
       </c>
       <c r="N49" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O49" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P49" t="str">
         <v>—</v>
@@ -3028,6 +3316,12 @@
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R49" t="str">
+        <v>—</v>
+      </c>
+      <c r="S49" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T49" t="str">
         <v>K2.7 Code 高速版</v>
       </c>
     </row>
@@ -3051,20 +3345,20 @@
         <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
       </c>
       <c r="G50" t="str">
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+      </c>
+      <c r="H50" t="str">
         <v>入 $0.3 · 出 $1.2 · 缓 $0.03</v>
       </c>
-      <c r="H50" t="str">
+      <c r="I50" t="str">
         <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
       </c>
-      <c r="I50" t="str">
+      <c r="J50" t="str">
         <v>入 $0.12 · 出 $0.48</v>
       </c>
-      <c r="J50" t="str">
+      <c r="K50" t="str">
         <v>入 $0.323077 · 出 $1.292308 · 缓 $0.032308</v>
       </c>
-      <c r="K50" t="str">
-        <v>0%</v>
-      </c>
       <c r="L50" t="str">
         <v>0%</v>
       </c>
@@ -3072,18 +3366,24 @@
         <v>0%</v>
       </c>
       <c r="N50" t="str">
-        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
+        <v>0%</v>
       </c>
       <c r="O50" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P50" t="str">
-        <v>入⚠-62.9% 出⚠-62.9%</v>
+        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
       <c r="Q50" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R50" t="str">
+        <v>入⚠-62.9% 出⚠-62.9%</v>
+      </c>
+      <c r="S50" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T50" t="str">
         <v/>
       </c>
     </row>
@@ -3107,20 +3407,20 @@
         <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="G51" t="str">
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+      </c>
+      <c r="H51" t="str">
         <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
-      <c r="H51" t="str">
+      <c r="I51" t="str">
         <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
-      <c r="I51" t="str">
+      <c r="J51" t="str">
         <v>入 $0.18 · 出 $0.72</v>
       </c>
-      <c r="J51" t="str">
+      <c r="K51" t="str">
         <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
-      <c r="K51" t="str">
-        <v>0%</v>
-      </c>
       <c r="L51" t="str">
         <v>0%</v>
       </c>
@@ -3128,18 +3428,24 @@
         <v>0%</v>
       </c>
       <c r="N51" t="str">
-        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
+        <v>0%</v>
       </c>
       <c r="O51" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P51" t="str">
-        <v>入⚠-44.3% 出⚠-44.3%</v>
+        <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
       <c r="Q51" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R51" t="str">
+        <v>入⚠-44.3% 出⚠-44.3%</v>
+      </c>
+      <c r="S51" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T51" t="str">
         <v/>
       </c>
     </row>
@@ -3169,14 +3475,14 @@
         <v>—</v>
       </c>
       <c r="I52" t="str">
+        <v>—</v>
+      </c>
+      <c r="J52" t="str">
         <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
-      <c r="J52" t="str">
+      <c r="K52" t="str">
         <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
-      <c r="K52" t="str">
-        <v>0%</v>
-      </c>
       <c r="L52" t="str">
         <v>0%</v>
       </c>
@@ -3184,18 +3490,24 @@
         <v>0%</v>
       </c>
       <c r="N52" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O52" t="str">
         <v>—</v>
       </c>
       <c r="P52" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q52" t="str">
+        <v>—</v>
+      </c>
+      <c r="R52" t="str">
         <v>入⚠-7.1% 出⚠-7.1% 缓⚠-7.1%</v>
       </c>
-      <c r="Q52" t="str">
+      <c r="S52" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R52" t="str">
+      <c r="T52" t="str">
         <v>512k 以上输入档仍在内测开放中</v>
       </c>
     </row>
@@ -3210,17 +3522,17 @@
         <v>—</v>
       </c>
       <c r="H53" t="str">
+        <v>—</v>
+      </c>
+      <c r="I53" t="str">
         <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
-      <c r="I53" t="str">
+      <c r="J53" t="str">
         <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
-      <c r="J53" t="str">
+      <c r="K53" t="str">
         <v>入 $0.646154 · 出 $2.584615 · 缓 $0.129231</v>
       </c>
-      <c r="K53" t="str">
-        <v>0%</v>
-      </c>
       <c r="L53" t="str">
         <v>0%</v>
       </c>
@@ -3228,18 +3540,24 @@
         <v>0%</v>
       </c>
       <c r="N53" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O53" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P53" t="str">
-        <v>入⚠-53.6% 出⚠-53.6% 缓⚠-53.6%</v>
+        <v>—</v>
       </c>
       <c r="Q53" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R53" t="str">
+        <v>入⚠-53.6% 出⚠-53.6% 缓⚠-53.6%</v>
+      </c>
+      <c r="S53" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T53" t="str">
         <v>512k 以上输入档仍在内测开放中</v>
       </c>
     </row>
@@ -3293,9 +3611,15 @@
         <v>—</v>
       </c>
       <c r="Q54" t="str">
+        <v>—</v>
+      </c>
+      <c r="R54" t="str">
+        <v>—</v>
+      </c>
+      <c r="S54" t="str">
         <v>— 未上架</v>
       </c>
-      <c r="R54" t="str">
+      <c r="T54" t="str">
         <v>Trinity ID glm-4-7-251222</v>
       </c>
     </row>
@@ -3337,9 +3661,15 @@
         <v>—</v>
       </c>
       <c r="Q55" t="str">
+        <v>—</v>
+      </c>
+      <c r="R55" t="str">
+        <v>—</v>
+      </c>
+      <c r="S55" t="str">
         <v>— 未上架</v>
       </c>
-      <c r="R55" t="str">
+      <c r="T55" t="str">
         <v>Trinity ID glm-4-7-251222</v>
       </c>
     </row>
@@ -3381,9 +3711,15 @@
         <v>—</v>
       </c>
       <c r="Q56" t="str">
+        <v>—</v>
+      </c>
+      <c r="R56" t="str">
+        <v>—</v>
+      </c>
+      <c r="S56" t="str">
         <v>— 未上架</v>
       </c>
-      <c r="R56" t="str">
+      <c r="T56" t="str">
         <v>Trinity ID glm-4-7-251222</v>
       </c>
     </row>
@@ -3407,20 +3743,20 @@
         <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
       <c r="G57" t="str">
+        <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
+      </c>
+      <c r="H57" t="str">
         <v>入 $0.616 · 出 $2.772 · 缓 $0.154</v>
       </c>
-      <c r="H57" t="str">
+      <c r="I57" t="str">
         <v>入 ¥4 · 出 ¥18 · 缓 ¥1</v>
       </c>
-      <c r="I57" t="str">
+      <c r="J57" t="str">
         <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
       </c>
-      <c r="J57" t="str">
+      <c r="K57" t="str">
         <v>入 $0.615385 · 出 $2.769231 · 缓 $0.153846</v>
       </c>
-      <c r="K57" t="str">
-        <v>0%</v>
-      </c>
       <c r="L57" t="str">
         <v>0%</v>
       </c>
@@ -3428,18 +3764,24 @@
         <v>0%</v>
       </c>
       <c r="N57" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O57" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P57" t="str">
-        <v>入⚠-2.5% 出⚠-30.7% 缓⚠-22%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q57" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R57" t="str">
+        <v>入⚠-2.5% 出⚠-30.7% 缓⚠-22%</v>
+      </c>
+      <c r="S57" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T57" t="str">
         <v/>
       </c>
     </row>
@@ -3451,20 +3793,20 @@
         <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
       <c r="G58" t="str">
+        <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
+      </c>
+      <c r="H58" t="str">
         <v>入 $0.924 · 出 $3.388 · 缓 $0.231</v>
       </c>
-      <c r="H58" t="str">
+      <c r="I58" t="str">
         <v>入 ¥6 · 出 ¥22 · 缓 ¥1.5</v>
       </c>
-      <c r="I58" t="str">
+      <c r="J58" t="str">
         <v>入 $0.6 · 出 $1.92 · 缓 $0.12</v>
       </c>
-      <c r="J58" t="str">
+      <c r="K58" t="str">
         <v>入 $0.923077 · 出 $3.384615 · 缓 $0.230769</v>
       </c>
-      <c r="K58" t="str">
-        <v>0%</v>
-      </c>
       <c r="L58" t="str">
         <v>0%</v>
       </c>
@@ -3472,18 +3814,24 @@
         <v>0%</v>
       </c>
       <c r="N58" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O58" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P58" t="str">
-        <v>入⚠-35% 出⚠-43.3% 缓⚠-48%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q58" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R58" t="str">
+        <v>入⚠-35% 出⚠-43.3% 缓⚠-48%</v>
+      </c>
+      <c r="S58" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T58" t="str">
         <v/>
       </c>
     </row>
@@ -3507,20 +3855,20 @@
         <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
       <c r="G59" t="str">
+        <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
+      </c>
+      <c r="H59" t="str">
         <v>入 $0.77 · 出 $3.388 · 缓 $0.185</v>
       </c>
-      <c r="H59" t="str">
+      <c r="I59" t="str">
         <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
-      <c r="I59" t="str">
+      <c r="J59" t="str">
         <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
-      <c r="J59" t="str">
+      <c r="K59" t="str">
         <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
       </c>
-      <c r="K59" t="str">
-        <v>0%</v>
-      </c>
       <c r="L59" t="str">
         <v>0%</v>
       </c>
@@ -3528,18 +3876,24 @@
         <v>0%</v>
       </c>
       <c r="N59" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O59" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P59" t="str">
-        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q59" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R59" t="str">
+        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
+      </c>
+      <c r="S59" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T59" t="str">
         <v/>
       </c>
     </row>
@@ -3551,20 +3905,20 @@
         <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
       <c r="G60" t="str">
+        <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
+      </c>
+      <c r="H60" t="str">
         <v>入 $1.078 · 出 $4.004 · 缓 $0.277</v>
       </c>
-      <c r="H60" t="str">
+      <c r="I60" t="str">
         <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
-      <c r="I60" t="str">
+      <c r="J60" t="str">
         <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
-      <c r="J60" t="str">
+      <c r="K60" t="str">
         <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
       </c>
-      <c r="K60" t="str">
-        <v>0%</v>
-      </c>
       <c r="L60" t="str">
         <v>0%</v>
       </c>
@@ -3572,18 +3926,24 @@
         <v>0%</v>
       </c>
       <c r="N60" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O60" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P60" t="str">
-        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q60" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R60" t="str">
+        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
+      </c>
+      <c r="S60" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T60" t="str">
         <v/>
       </c>
     </row>
@@ -3607,20 +3967,20 @@
         <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
       <c r="G61" t="str">
+        <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
+      </c>
+      <c r="H61" t="str">
         <v>入 $0.924 · 出 $3.696 · 缓 $0.2</v>
       </c>
-      <c r="H61" t="str">
+      <c r="I61" t="str">
         <v>入 ¥6 · 出 ¥24 · 缓 ¥1.3</v>
       </c>
-      <c r="I61" t="str">
+      <c r="J61" t="str">
         <v>入 $0.975 · 出 $4.300000000000001</v>
       </c>
-      <c r="J61" t="str">
+      <c r="K61" t="str">
         <v>入 $0.923077 · 出 $3.692308 · 缓 $0.2</v>
       </c>
-      <c r="K61" t="str">
-        <v>0%</v>
-      </c>
       <c r="L61" t="str">
         <v>0%</v>
       </c>
@@ -3628,18 +3988,24 @@
         <v>0%</v>
       </c>
       <c r="N61" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O61" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P61" t="str">
-        <v>入⚠+5.6% 出⚠+16.5%</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q61" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R61" t="str">
+        <v>入⚠+5.6% 出⚠+16.5%</v>
+      </c>
+      <c r="S61" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T61" t="str">
         <v/>
       </c>
     </row>
@@ -3651,20 +4017,20 @@
         <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
       <c r="G62" t="str">
+        <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
+      </c>
+      <c r="H62" t="str">
         <v>入 $1.232 · 出 $4.312 · 缓 $0.308</v>
       </c>
-      <c r="H62" t="str">
+      <c r="I62" t="str">
         <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
-      <c r="I62" t="str">
+      <c r="J62" t="str">
         <v>入 $0.975 · 出 $4.300000000000001</v>
       </c>
-      <c r="J62" t="str">
+      <c r="K62" t="str">
         <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
       </c>
-      <c r="K62" t="str">
-        <v>0%</v>
-      </c>
       <c r="L62" t="str">
         <v>0%</v>
       </c>
@@ -3672,18 +4038,24 @@
         <v>0%</v>
       </c>
       <c r="N62" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>0%</v>
       </c>
       <c r="O62" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P62" t="str">
-        <v>入⚠-20.8% 出✅</v>
+        <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="Q62" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R62" t="str">
+        <v>入⚠-20.8% 出✅</v>
+      </c>
+      <c r="S62" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T62" t="str">
         <v/>
       </c>
     </row>
@@ -3710,17 +4082,17 @@
         <v>—</v>
       </c>
       <c r="H63" t="str">
+        <v>—</v>
+      </c>
+      <c r="I63" t="str">
         <v>入 ¥8 · 出 ¥28 · 缓 ¥2</v>
       </c>
-      <c r="I63" t="str">
+      <c r="J63" t="str">
         <v>入 $0.9299999999999999 · 出 $3 · 缓 $0.18</v>
       </c>
-      <c r="J63" t="str">
+      <c r="K63" t="str">
         <v>入 $1.230769 · 出 $4.307692 · 缓 $0.307692</v>
       </c>
-      <c r="K63" t="str">
-        <v>0%</v>
-      </c>
       <c r="L63" t="str">
         <v>0%</v>
       </c>
@@ -3728,18 +4100,24 @@
         <v>0%</v>
       </c>
       <c r="N63" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O63" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P63" t="str">
-        <v>入⚠-24.4% 出⚠-30.4% 缓⚠-41.5%</v>
+        <v>—</v>
       </c>
       <c r="Q63" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R63" t="str">
+        <v>入⚠-24.4% 出⚠-30.4% 缓⚠-41.5%</v>
+      </c>
+      <c r="S63" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T63" t="str">
         <v/>
       </c>
     </row>
@@ -3766,17 +4144,17 @@
         <v>—</v>
       </c>
       <c r="H64" t="str">
+        <v>—</v>
+      </c>
+      <c r="I64" t="str">
         <v>入 ¥5 · 出 ¥22 · 缓 ¥1.2</v>
       </c>
-      <c r="I64" t="str">
+      <c r="J64" t="str">
         <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
-      <c r="J64" t="str">
+      <c r="K64" t="str">
         <v>入 $0.769231 · 出 $3.384615 · 缓 $0.184615</v>
       </c>
-      <c r="K64" t="str">
-        <v>0%</v>
-      </c>
       <c r="L64" t="str">
         <v>0%</v>
       </c>
@@ -3784,18 +4162,24 @@
         <v>0%</v>
       </c>
       <c r="N64" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O64" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P64" t="str">
-        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
+        <v>—</v>
       </c>
       <c r="Q64" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R64" t="str">
+        <v>入⚠+56% 出⚠+18.2% 缓⚠+30%</v>
+      </c>
+      <c r="S64" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T64" t="str">
         <v>多模态 Coding 基座</v>
       </c>
     </row>
@@ -3810,17 +4194,17 @@
         <v>—</v>
       </c>
       <c r="H65" t="str">
+        <v>—</v>
+      </c>
+      <c r="I65" t="str">
         <v>入 ¥7 · 出 ¥26 · 缓 ¥1.8</v>
       </c>
-      <c r="I65" t="str">
+      <c r="J65" t="str">
         <v>入 $1.2 · 出 $4 · 缓 $0.24</v>
       </c>
-      <c r="J65" t="str">
+      <c r="K65" t="str">
         <v>入 $1.076923 · 出 $4 · 缓 $0.276923</v>
       </c>
-      <c r="K65" t="str">
-        <v>0%</v>
-      </c>
       <c r="L65" t="str">
         <v>0%</v>
       </c>
@@ -3828,18 +4212,24 @@
         <v>0%</v>
       </c>
       <c r="N65" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O65" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P65" t="str">
-        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
+        <v>—</v>
       </c>
       <c r="Q65" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R65" t="str">
+        <v>入⚠+11.4% 出✅ 缓⚠-13.3%</v>
+      </c>
+      <c r="S65" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T65" t="str">
         <v>多模态 Coding 基座</v>
       </c>
     </row>
@@ -3866,28 +4256,28 @@
         <v>—</v>
       </c>
       <c r="H66" t="str">
+        <v>—</v>
+      </c>
+      <c r="I66" t="str">
         <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
-      <c r="I66" t="str">
-        <v>—</v>
-      </c>
       <c r="J66" t="str">
+        <v>—</v>
+      </c>
+      <c r="K66" t="str">
         <v>入 $0.369231 · 出 $1.476923</v>
       </c>
-      <c r="K66" t="str">
-        <v>0%</v>
-      </c>
       <c r="L66" t="str">
         <v>0%</v>
       </c>
       <c r="M66" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N66" t="str">
         <v>—</v>
       </c>
       <c r="O66" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="P66" t="str">
         <v>—</v>
@@ -3896,6 +4286,12 @@
         <v>入✅ 出✅</v>
       </c>
       <c r="R66" t="str">
+        <v>—</v>
+      </c>
+      <c r="S66" t="str">
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="T66" t="str">
         <v>Hy-Role-Latest</v>
       </c>
     </row>
@@ -3922,28 +4318,28 @@
         <v>—</v>
       </c>
       <c r="H67" t="str">
+        <v>—</v>
+      </c>
+      <c r="I67" t="str">
         <v>入 ¥0.3 · 出 ¥1.2</v>
       </c>
-      <c r="I67" t="str">
-        <v>—</v>
-      </c>
       <c r="J67" t="str">
+        <v>—</v>
+      </c>
+      <c r="K67" t="str">
         <v>入 $0.046154 · 出 $0.184615</v>
       </c>
-      <c r="K67" t="str">
-        <v>0%</v>
-      </c>
       <c r="L67" t="str">
         <v>0%</v>
       </c>
       <c r="M67" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N67" t="str">
         <v>—</v>
       </c>
       <c r="O67" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="P67" t="str">
         <v>—</v>
@@ -3952,6 +4348,12 @@
         <v>入✅ 出✅</v>
       </c>
       <c r="R67" t="str">
+        <v>—</v>
+      </c>
+      <c r="S67" t="str">
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="T67" t="str">
         <v/>
       </c>
     </row>
@@ -3978,28 +4380,28 @@
         <v>—</v>
       </c>
       <c r="H68" t="str">
+        <v>—</v>
+      </c>
+      <c r="I68" t="str">
         <v>入 ¥0.5 · 出 ¥2</v>
       </c>
-      <c r="I68" t="str">
-        <v>—</v>
-      </c>
       <c r="J68" t="str">
+        <v>—</v>
+      </c>
+      <c r="K68" t="str">
         <v>入 $0.076923 · 出 $0.307692</v>
       </c>
-      <c r="K68" t="str">
-        <v>0%</v>
-      </c>
       <c r="L68" t="str">
         <v>0%</v>
       </c>
       <c r="M68" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N68" t="str">
         <v>—</v>
       </c>
       <c r="O68" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="P68" t="str">
         <v>—</v>
@@ -4008,6 +4410,12 @@
         <v>入✅ 出✅</v>
       </c>
       <c r="R68" t="str">
+        <v>—</v>
+      </c>
+      <c r="S68" t="str">
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="T68" t="str">
         <v/>
       </c>
     </row>
@@ -4034,28 +4442,28 @@
         <v>—</v>
       </c>
       <c r="H69" t="str">
+        <v>—</v>
+      </c>
+      <c r="I69" t="str">
         <v>入 ¥0.5 · 出 ¥2</v>
       </c>
-      <c r="I69" t="str">
-        <v>—</v>
-      </c>
       <c r="J69" t="str">
+        <v>—</v>
+      </c>
+      <c r="K69" t="str">
         <v>入 $0.076923 · 出 $0.307692</v>
       </c>
-      <c r="K69" t="str">
-        <v>0%</v>
-      </c>
       <c r="L69" t="str">
         <v>0%</v>
       </c>
       <c r="M69" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N69" t="str">
         <v>—</v>
       </c>
       <c r="O69" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="P69" t="str">
         <v>—</v>
@@ -4064,6 +4472,12 @@
         <v>入✅ 出✅</v>
       </c>
       <c r="R69" t="str">
+        <v>—</v>
+      </c>
+      <c r="S69" t="str">
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="T69" t="str">
         <v/>
       </c>
     </row>
@@ -4090,28 +4504,28 @@
         <v>—</v>
       </c>
       <c r="H70" t="str">
+        <v>—</v>
+      </c>
+      <c r="I70" t="str">
         <v>入 ¥2.4 · 出 ¥9.6</v>
       </c>
-      <c r="I70" t="str">
-        <v>—</v>
-      </c>
       <c r="J70" t="str">
+        <v>—</v>
+      </c>
+      <c r="K70" t="str">
         <v>入 $0.369231 · 出 $1.476923</v>
       </c>
-      <c r="K70" t="str">
-        <v>0%</v>
-      </c>
       <c r="L70" t="str">
         <v>0%</v>
       </c>
       <c r="M70" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N70" t="str">
         <v>—</v>
       </c>
       <c r="O70" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="P70" t="str">
         <v>—</v>
@@ -4120,6 +4534,12 @@
         <v>入✅ 出✅</v>
       </c>
       <c r="R70" t="str">
+        <v>—</v>
+      </c>
+      <c r="S70" t="str">
+        <v>入✅ 出✅</v>
+      </c>
+      <c r="T70" t="str">
         <v/>
       </c>
     </row>
@@ -4152,16 +4572,16 @@
         <v>—</v>
       </c>
       <c r="J71" t="str">
+        <v>—</v>
+      </c>
+      <c r="K71" t="str">
         <v>入 $1.153846 · 出 $2.692308</v>
       </c>
-      <c r="K71" t="str">
-        <v>0%</v>
-      </c>
       <c r="L71" t="str">
         <v>0%</v>
       </c>
       <c r="M71" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N71" t="str">
         <v>—</v>
@@ -4173,9 +4593,15 @@
         <v>—</v>
       </c>
       <c r="Q71" t="str">
+        <v>—</v>
+      </c>
+      <c r="R71" t="str">
+        <v>—</v>
+      </c>
+      <c r="S71" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="R71" t="str">
+      <c r="T71" t="str">
         <v>多模态视觉理解 · 按 token 计费</v>
       </c>
     </row>
@@ -4199,20 +4625,20 @@
         <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
       </c>
       <c r="G72" t="str">
-        <v>—</v>
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
       </c>
       <c r="H72" t="str">
+        <v>—</v>
+      </c>
+      <c r="I72" t="str">
         <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
       </c>
-      <c r="I72" t="str">
+      <c r="J72" t="str">
         <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
-      <c r="J72" t="str">
+      <c r="K72" t="str">
         <v>入 $0.184615 · 出 $0.615385 · 缓 $0.061538</v>
       </c>
-      <c r="K72" t="str">
-        <v>0%</v>
-      </c>
       <c r="L72" t="str">
         <v>0%</v>
       </c>
@@ -4220,18 +4646,24 @@
         <v>0%</v>
       </c>
       <c r="N72" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O72" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P72" t="str">
-        <v>入⚠-65.9% 出⚠-65.9% 缓⚠-65.9%</v>
+        <v>—</v>
       </c>
       <c r="Q72" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R72" t="str">
+        <v>入⚠-65.9% 出⚠-65.9% 缓⚠-65.9%</v>
+      </c>
+      <c r="S72" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T72" t="str">
         <v/>
       </c>
     </row>
@@ -4243,20 +4675,20 @@
         <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
       <c r="G73" t="str">
-        <v>—</v>
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
       <c r="H73" t="str">
+        <v>—</v>
+      </c>
+      <c r="I73" t="str">
         <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
       </c>
-      <c r="I73" t="str">
+      <c r="J73" t="str">
         <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
-      <c r="J73" t="str">
+      <c r="K73" t="str">
         <v>入 $0.246154 · 出 $0.984615 · 缓 $0.092308</v>
       </c>
-      <c r="K73" t="str">
-        <v>0%</v>
-      </c>
       <c r="L73" t="str">
         <v>0%</v>
       </c>
@@ -4264,18 +4696,24 @@
         <v>0%</v>
       </c>
       <c r="N73" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O73" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P73" t="str">
-        <v>入⚠-74.4% 出⚠-78.7% 缓⚠-77.2%</v>
+        <v>—</v>
       </c>
       <c r="Q73" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R73" t="str">
+        <v>入⚠-74.4% 出⚠-78.7% 缓⚠-77.2%</v>
+      </c>
+      <c r="S73" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T73" t="str">
         <v/>
       </c>
     </row>
@@ -4287,20 +4725,20 @@
         <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="G74" t="str">
-        <v>—</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="H74" t="str">
+        <v>—</v>
+      </c>
+      <c r="I74" t="str">
         <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
-      <c r="I74" t="str">
+      <c r="J74" t="str">
         <v>入 $0.063 · 出 $0.21 · 缓 $0.020999999999999998</v>
       </c>
-      <c r="J74" t="str">
+      <c r="K74" t="str">
         <v>入 $0.307692 · 出 $1.230769 · 缓 $0.123077</v>
       </c>
-      <c r="K74" t="str">
-        <v>0%</v>
-      </c>
       <c r="L74" t="str">
         <v>0%</v>
       </c>
@@ -4308,18 +4746,24 @@
         <v>0%</v>
       </c>
       <c r="N74" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O74" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="P74" t="str">
-        <v>入⚠-79.5% 出⚠-82.9% 缓⚠-82.9%</v>
+        <v>—</v>
       </c>
       <c r="Q74" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R74" t="str">
+        <v>入⚠-79.5% 出⚠-82.9% 缓⚠-82.9%</v>
+      </c>
+      <c r="S74" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T74" t="str">
         <v/>
       </c>
     </row>
@@ -4352,11 +4796,11 @@
         <v>—</v>
       </c>
       <c r="J75" t="str">
+        <v>—</v>
+      </c>
+      <c r="K75" t="str">
         <v>入 $0.023077 · 出 $0.230769 · 缓 $0.004615</v>
       </c>
-      <c r="K75" t="str">
-        <v>0%</v>
-      </c>
       <c r="L75" t="str">
         <v>0%</v>
       </c>
@@ -4364,7 +4808,7 @@
         <v>0%</v>
       </c>
       <c r="N75" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O75" t="str">
         <v>—</v>
@@ -4373,9 +4817,15 @@
         <v>—</v>
       </c>
       <c r="Q75" t="str">
+        <v>—</v>
+      </c>
+      <c r="R75" t="str">
+        <v>—</v>
+      </c>
+      <c r="S75" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R75" t="str">
+      <c r="T75" t="str">
         <v/>
       </c>
     </row>
@@ -4417,9 +4867,15 @@
         <v>—</v>
       </c>
       <c r="Q76" t="str">
+        <v>—</v>
+      </c>
+      <c r="R76" t="str">
+        <v>—</v>
+      </c>
+      <c r="S76" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="R76" t="str">
+      <c r="T76" t="str">
         <v/>
       </c>
     </row>
@@ -4461,9 +4917,15 @@
         <v>—</v>
       </c>
       <c r="Q77" t="str">
+        <v>—</v>
+      </c>
+      <c r="R77" t="str">
+        <v>—</v>
+      </c>
+      <c r="S77" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="R77" t="str">
+      <c r="T77" t="str">
         <v/>
       </c>
     </row>
@@ -4496,16 +4958,16 @@
         <v>—</v>
       </c>
       <c r="J78" t="str">
+        <v>—</v>
+      </c>
+      <c r="K78" t="str">
         <v>入 $0.369231 · 出 $1.476923 · 缓 $0.082759</v>
       </c>
-      <c r="K78" t="str">
-        <v>0%</v>
-      </c>
       <c r="L78" t="str">
         <v>0%</v>
       </c>
       <c r="M78" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N78" t="str">
         <v>—</v>
@@ -4517,9 +4979,15 @@
         <v>—</v>
       </c>
       <c r="Q78" t="str">
+        <v>—</v>
+      </c>
+      <c r="R78" t="str">
+        <v>—</v>
+      </c>
+      <c r="S78" t="str">
         <v>入✅ 出✅ 缓—</v>
       </c>
-      <c r="R78" t="str">
+      <c r="T78" t="str">
         <v/>
       </c>
     </row>
@@ -4549,14 +5017,14 @@
         <v>—</v>
       </c>
       <c r="I79" t="str">
+        <v>—</v>
+      </c>
+      <c r="J79" t="str">
         <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
       </c>
-      <c r="J79" t="str">
+      <c r="K79" t="str">
         <v>入 $0.123077 · 出 $0.307692 · 缓 $0.024615</v>
       </c>
-      <c r="K79" t="str">
-        <v>0%</v>
-      </c>
       <c r="L79" t="str">
         <v>0%</v>
       </c>
@@ -4564,18 +5032,24 @@
         <v>0%</v>
       </c>
       <c r="N79" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O79" t="str">
         <v>—</v>
       </c>
       <c r="P79" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q79" t="str">
+        <v>—</v>
+      </c>
+      <c r="R79" t="str">
         <v>入⚠+111.3% 出⚠+153.5% 缓⚠+111.3%</v>
       </c>
-      <c r="Q79" t="str">
+      <c r="S79" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R79" t="str">
+      <c r="T79" t="str">
         <v/>
       </c>
     </row>
@@ -4593,11 +5067,11 @@
         <v>—</v>
       </c>
       <c r="I80" t="str">
+        <v>—</v>
+      </c>
+      <c r="J80" t="str">
         <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
       </c>
-      <c r="J80" t="str">
-        <v>—</v>
-      </c>
       <c r="K80" t="str">
         <v>—</v>
       </c>
@@ -4614,12 +5088,18 @@
         <v>—</v>
       </c>
       <c r="P80" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q80" t="str">
+        <v>—</v>
+      </c>
+      <c r="R80" t="str">
         <v>入⚠-29.6% 出⚠-74.6% 缓⚠-29.6%</v>
       </c>
-      <c r="Q80" t="str">
+      <c r="S80" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="R80" t="str">
+      <c r="T80" t="str">
         <v/>
       </c>
     </row>
@@ -4637,11 +5117,11 @@
         <v>—</v>
       </c>
       <c r="I81" t="str">
+        <v>—</v>
+      </c>
+      <c r="J81" t="str">
         <v>入 $0.26 · 出 $0.78 · 缓 $0.052000000000000005</v>
       </c>
-      <c r="J81" t="str">
-        <v>—</v>
-      </c>
       <c r="K81" t="str">
         <v>—</v>
       </c>
@@ -4658,12 +5138,18 @@
         <v>—</v>
       </c>
       <c r="P81" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q81" t="str">
+        <v>—</v>
+      </c>
+      <c r="R81" t="str">
         <v>入⚠-64.8% 出⚠-89.4% 缓⚠-64.8%</v>
       </c>
-      <c r="Q81" t="str">
+      <c r="S81" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="R81" t="str">
+      <c r="T81" t="str">
         <v/>
       </c>
     </row>
@@ -4696,16 +5182,16 @@
         <v>—</v>
       </c>
       <c r="J82" t="str">
+        <v>—</v>
+      </c>
+      <c r="K82" t="str">
         <v>入 $0.046154 · 出 $0.092308 · 缓 $0.010345</v>
       </c>
-      <c r="K82" t="str">
-        <v>0%</v>
-      </c>
       <c r="L82" t="str">
         <v>0%</v>
       </c>
       <c r="M82" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="N82" t="str">
         <v>—</v>
@@ -4717,9 +5203,15 @@
         <v>—</v>
       </c>
       <c r="Q82" t="str">
+        <v>—</v>
+      </c>
+      <c r="R82" t="str">
+        <v>—</v>
+      </c>
+      <c r="S82" t="str">
         <v>入✅ 出✅ 缓—</v>
       </c>
-      <c r="R82" t="str">
+      <c r="T82" t="str">
         <v/>
       </c>
     </row>
@@ -4746,17 +5238,17 @@
         <v>—</v>
       </c>
       <c r="H83" t="str">
+        <v>—</v>
+      </c>
+      <c r="I83" t="str">
         <v>入 ¥0.2 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
-      <c r="I83" t="str">
+      <c r="J83" t="str">
         <v>入 $0.065 · 出 $0.26</v>
       </c>
-      <c r="J83" t="str">
+      <c r="K83" t="str">
         <v>入 $0.030769 · 出 $0.307692 · 缓 $0.003077</v>
       </c>
-      <c r="K83" t="str">
-        <v>0%</v>
-      </c>
       <c r="L83" t="str">
         <v>0%</v>
       </c>
@@ -4764,18 +5256,24 @@
         <v>0%</v>
       </c>
       <c r="N83" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O83" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P83" t="str">
-        <v>入⚠+111.3% 出⚠-15.5%</v>
+        <v>—</v>
       </c>
       <c r="Q83" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R83" t="str">
+        <v>入⚠+111.3% 出⚠-15.5%</v>
+      </c>
+      <c r="S83" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T83" t="str">
         <v/>
       </c>
     </row>
@@ -4790,14 +5288,14 @@
         <v>—</v>
       </c>
       <c r="H84" t="str">
+        <v>—</v>
+      </c>
+      <c r="I84" t="str">
         <v>入 ¥0.8 · 出 ¥8 · 缓 ¥0.08</v>
       </c>
-      <c r="I84" t="str">
+      <c r="J84" t="str">
         <v>入 $0.065 · 出 $0.26</v>
       </c>
-      <c r="J84" t="str">
-        <v>—</v>
-      </c>
       <c r="K84" t="str">
         <v>—</v>
       </c>
@@ -4811,15 +5309,21 @@
         <v>—</v>
       </c>
       <c r="O84" t="str">
+        <v>—</v>
+      </c>
+      <c r="P84" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q84" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="P84" t="str">
+      <c r="R84" t="str">
         <v>入⚠-47.2% 出⚠-78.9%</v>
       </c>
-      <c r="Q84" t="str">
+      <c r="S84" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="R84" t="str">
+      <c r="T84" t="str">
         <v/>
       </c>
     </row>
@@ -4834,14 +5338,14 @@
         <v>—</v>
       </c>
       <c r="H85" t="str">
+        <v>—</v>
+      </c>
+      <c r="I85" t="str">
         <v>入 ¥1.2 · 出 ¥12 · 缓 ¥0.12</v>
       </c>
-      <c r="I85" t="str">
+      <c r="J85" t="str">
         <v>入 $0.065 · 出 $0.26</v>
       </c>
-      <c r="J85" t="str">
-        <v>—</v>
-      </c>
       <c r="K85" t="str">
         <v>—</v>
       </c>
@@ -4855,15 +5359,21 @@
         <v>—</v>
       </c>
       <c r="O85" t="str">
+        <v>—</v>
+      </c>
+      <c r="P85" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q85" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="P85" t="str">
+      <c r="R85" t="str">
         <v>入⚠-64.8% 出⚠-85.9%</v>
       </c>
-      <c r="Q85" t="str">
+      <c r="S85" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="R85" t="str">
+      <c r="T85" t="str">
         <v/>
       </c>
     </row>
@@ -4890,17 +5400,17 @@
         <v>—</v>
       </c>
       <c r="H86" t="str">
+        <v>—</v>
+      </c>
+      <c r="I86" t="str">
         <v>入 ¥0.8 · 出 ¥4.8 · 缓 ¥0.08</v>
       </c>
-      <c r="I86" t="str">
+      <c r="J86" t="str">
         <v>入 $0.3 · 出 $1.7999999999999998</v>
       </c>
-      <c r="J86" t="str">
+      <c r="K86" t="str">
         <v>入 $0.123077 · 出 $0.738462 · 缓 $0.012308</v>
       </c>
-      <c r="K86" t="str">
-        <v>0%</v>
-      </c>
       <c r="L86" t="str">
         <v>0%</v>
       </c>
@@ -4908,18 +5418,24 @@
         <v>0%</v>
       </c>
       <c r="N86" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O86" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="P86" t="str">
-        <v>入⚠+143.7% 出⚠+143.7%</v>
+        <v>—</v>
       </c>
       <c r="Q86" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
       <c r="R86" t="str">
+        <v>入⚠+143.7% 出⚠+143.7%</v>
+      </c>
+      <c r="S86" t="str">
+        <v>入✅ 出✅ 缓✅</v>
+      </c>
+      <c r="T86" t="str">
         <v/>
       </c>
     </row>
@@ -4934,14 +5450,14 @@
         <v>—</v>
       </c>
       <c r="H87" t="str">
+        <v>—</v>
+      </c>
+      <c r="I87" t="str">
         <v>入 ¥2 · 出 ¥12 · 缓 ¥0.2</v>
       </c>
-      <c r="I87" t="str">
+      <c r="J87" t="str">
         <v>入 $0.3 · 出 $1.7999999999999998</v>
       </c>
-      <c r="J87" t="str">
-        <v>—</v>
-      </c>
       <c r="K87" t="str">
         <v>—</v>
       </c>
@@ -4955,15 +5471,21 @@
         <v>—</v>
       </c>
       <c r="O87" t="str">
+        <v>—</v>
+      </c>
+      <c r="P87" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q87" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="P87" t="str">
+      <c r="R87" t="str">
         <v>入⚠-2.5% 出⚠-2.5%</v>
       </c>
-      <c r="Q87" t="str">
+      <c r="S87" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="R87" t="str">
+      <c r="T87" t="str">
         <v/>
       </c>
     </row>
@@ -4978,14 +5500,14 @@
         <v>—</v>
       </c>
       <c r="H88" t="str">
+        <v>—</v>
+      </c>
+      <c r="I88" t="str">
         <v>入 ¥4 · 出 ¥24 · 缓 ¥0.4</v>
       </c>
-      <c r="I88" t="str">
+      <c r="J88" t="str">
         <v>入 $0.3 · 出 $1.7999999999999998</v>
       </c>
-      <c r="J88" t="str">
-        <v>—</v>
-      </c>
       <c r="K88" t="str">
         <v>—</v>
       </c>
@@ -4999,15 +5521,21 @@
         <v>—</v>
       </c>
       <c r="O88" t="str">
+        <v>—</v>
+      </c>
+      <c r="P88" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q88" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="P88" t="str">
+      <c r="R88" t="str">
         <v>入⚠-51.3% 出⚠-51.3%</v>
       </c>
-      <c r="Q88" t="str">
+      <c r="S88" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="R88" t="str">
+      <c r="T88" t="str">
         <v/>
       </c>
     </row>
@@ -5037,14 +5565,14 @@
         <v>—</v>
       </c>
       <c r="I89" t="str">
+        <v>—</v>
+      </c>
+      <c r="J89" t="str">
         <v>入 $0.1875 · 出 $1.125</v>
       </c>
-      <c r="J89" t="str">
+      <c r="K89" t="str">
         <v>入 $0.184615 · 出 $1.107692 · 缓 $0.036923</v>
       </c>
-      <c r="K89" t="str">
-        <v>0%</v>
-      </c>
       <c r="L89" t="str">
         <v>0%</v>
       </c>
@@ -5052,18 +5580,24 @@
         <v>0%</v>
       </c>
       <c r="N89" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O89" t="str">
         <v>—</v>
       </c>
       <c r="P89" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q89" t="str">
+        <v>—</v>
+      </c>
+      <c r="R89" t="str">
         <v>入⚠+1.6% 出⚠+1.6%</v>
       </c>
-      <c r="Q89" t="str">
+      <c r="S89" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R89" t="str">
+      <c r="T89" t="str">
         <v/>
       </c>
     </row>
@@ -5081,11 +5615,11 @@
         <v>—</v>
       </c>
       <c r="I90" t="str">
+        <v>—</v>
+      </c>
+      <c r="J90" t="str">
         <v>入 $0.1875 · 出 $1.125</v>
       </c>
-      <c r="J90" t="str">
-        <v>—</v>
-      </c>
       <c r="K90" t="str">
         <v>—</v>
       </c>
@@ -5102,12 +5636,18 @@
         <v>—</v>
       </c>
       <c r="P90" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q90" t="str">
+        <v>—</v>
+      </c>
+      <c r="R90" t="str">
         <v>入⚠-74.6% 出⚠-74.6%</v>
       </c>
-      <c r="Q90" t="str">
+      <c r="S90" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="R90" t="str">
+      <c r="T90" t="str">
         <v/>
       </c>
     </row>
@@ -5137,14 +5677,14 @@
         <v>—</v>
       </c>
       <c r="I91" t="str">
+        <v>—</v>
+      </c>
+      <c r="J91" t="str">
         <v>入 $0.325 · 出 $1.95</v>
       </c>
-      <c r="J91" t="str">
+      <c r="K91" t="str">
         <v>入 $0.307692 · 出 $1.846154 · 缓 $0.061538</v>
       </c>
-      <c r="K91" t="str">
-        <v>0%</v>
-      </c>
       <c r="L91" t="str">
         <v>0%</v>
       </c>
@@ -5152,18 +5692,24 @@
         <v>0%</v>
       </c>
       <c r="N91" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O91" t="str">
         <v>—</v>
       </c>
       <c r="P91" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q91" t="str">
+        <v>—</v>
+      </c>
+      <c r="R91" t="str">
         <v>入⚠+5.6% 出⚠+5.6%</v>
       </c>
-      <c r="Q91" t="str">
+      <c r="S91" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R91" t="str">
+      <c r="T91" t="str">
         <v/>
       </c>
     </row>
@@ -5181,11 +5727,11 @@
         <v>—</v>
       </c>
       <c r="I92" t="str">
+        <v>—</v>
+      </c>
+      <c r="J92" t="str">
         <v>入 $0.325 · 出 $1.95</v>
       </c>
-      <c r="J92" t="str">
-        <v>—</v>
-      </c>
       <c r="K92" t="str">
         <v>—</v>
       </c>
@@ -5202,12 +5748,18 @@
         <v>—</v>
       </c>
       <c r="P92" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q92" t="str">
+        <v>—</v>
+      </c>
+      <c r="R92" t="str">
         <v>入⚠-73.6% 出⚠-73.6%</v>
       </c>
-      <c r="Q92" t="str">
+      <c r="S92" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="R92" t="str">
+      <c r="T92" t="str">
         <v/>
       </c>
     </row>
@@ -5237,14 +5789,14 @@
         <v>—</v>
       </c>
       <c r="I93" t="str">
+        <v>—</v>
+      </c>
+      <c r="J93" t="str">
         <v>入 $1.25 · 出 $3.75 · 缓 $0.25</v>
       </c>
-      <c r="J93" t="str">
+      <c r="K93" t="str">
         <v>入 $1.846154 · 出 $5.538462 · 缓 $0.369231</v>
       </c>
-      <c r="K93" t="str">
-        <v>0%</v>
-      </c>
       <c r="L93" t="str">
         <v>0%</v>
       </c>
@@ -5252,18 +5804,24 @@
         <v>0%</v>
       </c>
       <c r="N93" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O93" t="str">
         <v>—</v>
       </c>
       <c r="P93" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q93" t="str">
+        <v>—</v>
+      </c>
+      <c r="R93" t="str">
         <v>入⚠-32.3% 出⚠-32.3% 缓⚠-32.3%</v>
       </c>
-      <c r="Q93" t="str">
+      <c r="S93" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R93" t="str">
+      <c r="T93" t="str">
         <v/>
       </c>
     </row>
@@ -5293,14 +5851,14 @@
         <v>—</v>
       </c>
       <c r="I94" t="str">
+        <v>—</v>
+      </c>
+      <c r="J94" t="str">
         <v>入 $0.32 · 出 $1.28 · 缓 $0.064</v>
       </c>
-      <c r="J94" t="str">
+      <c r="K94" t="str">
         <v>入 $0.307692 · 出 $1.230769 · 缓 $0.061538</v>
       </c>
-      <c r="K94" t="str">
-        <v>0%</v>
-      </c>
       <c r="L94" t="str">
         <v>0%</v>
       </c>
@@ -5308,18 +5866,24 @@
         <v>0%</v>
       </c>
       <c r="N94" t="str">
-        <v>—</v>
+        <v>0%</v>
       </c>
       <c r="O94" t="str">
         <v>—</v>
       </c>
       <c r="P94" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q94" t="str">
+        <v>—</v>
+      </c>
+      <c r="R94" t="str">
         <v>入⚠+4% 出⚠+4% 缓⚠+4%</v>
       </c>
-      <c r="Q94" t="str">
+      <c r="S94" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="R94" t="str">
+      <c r="T94" t="str">
         <v/>
       </c>
     </row>
@@ -5337,11 +5901,11 @@
         <v>—</v>
       </c>
       <c r="I95" t="str">
+        <v>—</v>
+      </c>
+      <c r="J95" t="str">
         <v>入 $0.32 · 出 $1.28 · 缓 $0.064</v>
       </c>
-      <c r="J95" t="str">
-        <v>—</v>
-      </c>
       <c r="K95" t="str">
         <v>—</v>
       </c>
@@ -5358,12 +5922,18 @@
         <v>—</v>
       </c>
       <c r="P95" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q95" t="str">
+        <v>—</v>
+      </c>
+      <c r="R95" t="str">
         <v>入⚠-65.3% 出⚠-65.3% 缓⚠-65.3%</v>
       </c>
-      <c r="Q95" t="str">
+      <c r="S95" t="str">
         <v>ℹ 线上无同档</v>
       </c>
-      <c r="R95" t="str">
+      <c r="T95" t="str">
         <v/>
       </c>
     </row>
@@ -5417,9 +5987,15 @@
         <v>—</v>
       </c>
       <c r="Q96" t="str">
+        <v>—</v>
+      </c>
+      <c r="R96" t="str">
+        <v>—</v>
+      </c>
+      <c r="S96" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R96" t="str">
+      <c r="T96" t="str">
         <v/>
       </c>
     </row>
@@ -5473,9 +6049,15 @@
         <v>—</v>
       </c>
       <c r="Q97" t="str">
+        <v>—</v>
+      </c>
+      <c r="R97" t="str">
+        <v>—</v>
+      </c>
+      <c r="S97" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R97" t="str">
+      <c r="T97" t="str">
         <v/>
       </c>
     </row>
@@ -5529,9 +6111,15 @@
         <v>—</v>
       </c>
       <c r="Q98" t="str">
+        <v>—</v>
+      </c>
+      <c r="R98" t="str">
+        <v>—</v>
+      </c>
+      <c r="S98" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R98" t="str">
+      <c r="T98" t="str">
         <v/>
       </c>
     </row>
@@ -5573,9 +6161,15 @@
         <v>—</v>
       </c>
       <c r="Q99" t="str">
+        <v>—</v>
+      </c>
+      <c r="R99" t="str">
+        <v>—</v>
+      </c>
+      <c r="S99" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R99" t="str">
+      <c r="T99" t="str">
         <v/>
       </c>
     </row>
@@ -5629,9 +6223,15 @@
         <v>—</v>
       </c>
       <c r="Q100" t="str">
+        <v>—</v>
+      </c>
+      <c r="R100" t="str">
+        <v>—</v>
+      </c>
+      <c r="S100" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R100" t="str">
+      <c r="T100" t="str">
         <v/>
       </c>
     </row>
@@ -5673,9 +6273,15 @@
         <v>—</v>
       </c>
       <c r="Q101" t="str">
+        <v>—</v>
+      </c>
+      <c r="R101" t="str">
+        <v>—</v>
+      </c>
+      <c r="S101" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R101" t="str">
+      <c r="T101" t="str">
         <v/>
       </c>
     </row>
@@ -5729,9 +6335,15 @@
         <v>—</v>
       </c>
       <c r="Q102" t="str">
+        <v>—</v>
+      </c>
+      <c r="R102" t="str">
+        <v>—</v>
+      </c>
+      <c r="S102" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R102" t="str">
+      <c r="T102" t="str">
         <v/>
       </c>
     </row>
@@ -5773,9 +6385,15 @@
         <v>—</v>
       </c>
       <c r="Q103" t="str">
+        <v>—</v>
+      </c>
+      <c r="R103" t="str">
+        <v>—</v>
+      </c>
+      <c r="S103" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R103" t="str">
+      <c r="T103" t="str">
         <v/>
       </c>
     </row>
@@ -5829,9 +6447,15 @@
         <v>—</v>
       </c>
       <c r="Q104" t="str">
+        <v>—</v>
+      </c>
+      <c r="R104" t="str">
+        <v>—</v>
+      </c>
+      <c r="S104" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R104" t="str">
+      <c r="T104" t="str">
         <v/>
       </c>
     </row>
@@ -5873,9 +6497,15 @@
         <v>—</v>
       </c>
       <c r="Q105" t="str">
+        <v>—</v>
+      </c>
+      <c r="R105" t="str">
+        <v>—</v>
+      </c>
+      <c r="S105" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R105" t="str">
+      <c r="T105" t="str">
         <v/>
       </c>
     </row>
@@ -5929,9 +6559,15 @@
         <v>—</v>
       </c>
       <c r="Q106" t="str">
+        <v>—</v>
+      </c>
+      <c r="R106" t="str">
+        <v>—</v>
+      </c>
+      <c r="S106" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R106" t="str">
+      <c r="T106" t="str">
         <v/>
       </c>
     </row>
@@ -5973,9 +6609,15 @@
         <v>—</v>
       </c>
       <c r="Q107" t="str">
+        <v>—</v>
+      </c>
+      <c r="R107" t="str">
+        <v>—</v>
+      </c>
+      <c r="S107" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R107" t="str">
+      <c r="T107" t="str">
         <v/>
       </c>
     </row>
@@ -6017,9 +6659,15 @@
         <v>—</v>
       </c>
       <c r="Q108" t="str">
+        <v>—</v>
+      </c>
+      <c r="R108" t="str">
+        <v>—</v>
+      </c>
+      <c r="S108" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R108" t="str">
+      <c r="T108" t="str">
         <v/>
       </c>
     </row>
@@ -6073,9 +6721,15 @@
         <v>—</v>
       </c>
       <c r="Q109" t="str">
+        <v>—</v>
+      </c>
+      <c r="R109" t="str">
+        <v>—</v>
+      </c>
+      <c r="S109" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R109" t="str">
+      <c r="T109" t="str">
         <v/>
       </c>
     </row>
@@ -6129,9 +6783,15 @@
         <v>—</v>
       </c>
       <c r="Q110" t="str">
+        <v>—</v>
+      </c>
+      <c r="R110" t="str">
+        <v>—</v>
+      </c>
+      <c r="S110" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="R110" t="str">
+      <c r="T110" t="str">
         <v/>
       </c>
     </row>
@@ -6255,7 +6915,7 @@
     <mergeCell ref="D106:D108"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R110"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T110"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7036,7 +7696,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>生成时间：2026-07-06T10:02:50Z</v>
+        <v>生成时间：2026-07-08T06:32:44Z</v>
       </c>
     </row>
     <row r="39">
@@ -7053,7 +7713,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:I34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7083,12 +7743,6 @@
       <c r="I1" t="str">
         <v>供应商vs官方</v>
       </c>
-      <c r="J1" t="str">
-        <v>折扣</v>
-      </c>
-      <c r="K1" t="str">
-        <v>成本(元/百万tokens)</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -7118,12 +7772,6 @@
       <c r="I2" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J2" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K2" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -7153,12 +7801,6 @@
       <c r="I3" t="str">
         <v>⚠ 缓+900%</v>
       </c>
-      <c r="J3" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K3" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -7188,12 +7830,6 @@
       <c r="I4" t="str">
         <v>⚠ 入+300% 出+300% 缓+3900%</v>
       </c>
-      <c r="J4" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K4" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -7223,12 +7859,6 @@
       <c r="I5" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J5" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K5" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -7249,12 +7879,6 @@
       <c r="I6" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J6" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K6" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -7284,12 +7908,6 @@
       <c r="I7" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J7" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K7" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -7310,12 +7928,6 @@
       <c r="I8" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J8" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K8" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -7345,12 +7957,6 @@
       <c r="I9" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J9" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K9" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -7371,12 +7977,6 @@
       <c r="I10" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J10" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K10" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -7406,12 +8006,6 @@
       <c r="I11" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J11" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K11" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -7441,12 +8035,6 @@
       <c r="I12" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J12" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K12" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -7467,12 +8055,6 @@
       <c r="I13" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J13" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K13" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -7502,12 +8084,6 @@
       <c r="I14" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J14" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K14" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -7537,12 +8113,6 @@
       <c r="I15" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J15" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K15" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -7572,12 +8142,6 @@
       <c r="I16" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J16" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K16" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -7607,12 +8171,6 @@
       <c r="I17" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J17" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K17" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -7642,12 +8200,6 @@
       <c r="I18" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J18" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K18" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -7677,12 +8229,6 @@
       <c r="I19" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J19" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K19" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -7703,12 +8249,6 @@
       <c r="I20" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J20" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K20" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -7729,12 +8269,6 @@
       <c r="I21" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J21" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K21" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -7764,12 +8298,6 @@
       <c r="I22" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J22" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K22" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -7799,12 +8327,6 @@
       <c r="I23" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J23" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K23" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -7834,12 +8356,6 @@
       <c r="I24" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J24" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K24" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -7869,12 +8385,6 @@
       <c r="I25" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J25" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K25" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -7904,12 +8414,6 @@
       <c r="I26" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J26" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K26" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -7939,12 +8443,6 @@
       <c r="I27" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J27" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K27" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -7974,12 +8472,6 @@
       <c r="I28" t="str">
         <v>⚠ 入+100% 出+100% 缓+100%</v>
       </c>
-      <c r="J28" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K28" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -8009,12 +8501,6 @@
       <c r="I29" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J29" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K29" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -8035,12 +8521,6 @@
       <c r="I30" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J30" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K30" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -8061,12 +8541,6 @@
       <c r="I31" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J31" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K31" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -8096,12 +8570,6 @@
       <c r="I32" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J32" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K32" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -8122,12 +8590,6 @@
       <c r="I33" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J33" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K33" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -8147,12 +8609,6 @@
       </c>
       <c r="I34" t="str">
         <v>✅ 一致</v>
-      </c>
-      <c r="J34" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K34" t="str">
-        <v>待填</v>
       </c>
     </row>
   </sheetData>
@@ -8180,14 +8636,14 @@
     <mergeCell ref="D32:D34"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I34"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:I37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8217,12 +8673,6 @@
       <c r="I1" t="str">
         <v>供应商vs官方</v>
       </c>
-      <c r="J1" t="str">
-        <v>折扣</v>
-      </c>
-      <c r="K1" t="str">
-        <v>成本(元/百万tokens)</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -8252,12 +8702,6 @@
       <c r="I2" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J2" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K2" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -8287,12 +8731,6 @@
       <c r="I3" t="str">
         <v>⚠ 缓+900%</v>
       </c>
-      <c r="J3" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K3" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -8322,12 +8760,6 @@
       <c r="I4" t="str">
         <v>⚠ 入+300% 出+300%</v>
       </c>
-      <c r="J4" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K4" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -8357,12 +8789,6 @@
       <c r="I5" t="str">
         <v>⚠ 缓-20%</v>
       </c>
-      <c r="J5" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K5" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -8383,12 +8809,6 @@
       <c r="I6" t="str">
         <v>⚠ 缓-20%</v>
       </c>
-      <c r="J6" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K6" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -8418,12 +8838,6 @@
       <c r="I7" t="str">
         <v>⚠ 缓-7.7%</v>
       </c>
-      <c r="J7" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K7" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -8444,12 +8858,6 @@
       <c r="I8" t="str">
         <v>⚠ 缓-20%</v>
       </c>
-      <c r="J8" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K8" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -8479,12 +8887,6 @@
       <c r="I9" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J9" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K9" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -8514,12 +8916,6 @@
       <c r="I10" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J10" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K10" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -8549,12 +8945,6 @@
       <c r="I11" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J11" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K11" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -8584,12 +8974,6 @@
       <c r="I12" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J12" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K12" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -8619,12 +9003,6 @@
       <c r="I13" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J13" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K13" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -8654,12 +9032,6 @@
       <c r="I14" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J14" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K14" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -8689,12 +9061,6 @@
       <c r="I15" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J15" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K15" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -8724,12 +9090,6 @@
       <c r="I16" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J16" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K16" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -8759,12 +9119,6 @@
       <c r="I17" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J17" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K17" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -8785,12 +9139,6 @@
       <c r="I18" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J18" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K18" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -8811,12 +9159,6 @@
       <c r="I19" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J19" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K19" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -8846,12 +9188,6 @@
       <c r="I20" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J20" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K20" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -8881,12 +9217,6 @@
       <c r="I21" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J21" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K21" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -8907,12 +9237,6 @@
       <c r="I22" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J22" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K22" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -8933,12 +9257,6 @@
       <c r="I23" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J23" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K23" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -8968,12 +9286,6 @@
       <c r="I24" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J24" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K24" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -9003,12 +9315,6 @@
       <c r="I25" t="str">
         <v>⚠ 缓+100%</v>
       </c>
-      <c r="J25" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K25" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -9029,12 +9335,6 @@
       <c r="I26" t="str">
         <v>⚠ 缓+100%</v>
       </c>
-      <c r="J26" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K26" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -9055,12 +9355,6 @@
       <c r="I27" t="str">
         <v>⚠ 缓+100%</v>
       </c>
-      <c r="J27" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K27" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -9090,12 +9384,6 @@
       <c r="I28" t="str">
         <v>⚠ 缓+100%</v>
       </c>
-      <c r="J28" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K28" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -9116,12 +9404,6 @@
       <c r="I29" t="str">
         <v>⚠ 缓+100%</v>
       </c>
-      <c r="J29" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K29" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -9142,12 +9424,6 @@
       <c r="I30" t="str">
         <v>⚠ 缓+100%</v>
       </c>
-      <c r="J30" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K30" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -9177,12 +9453,6 @@
       <c r="I31" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J31" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K31" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -9203,12 +9473,6 @@
       <c r="I32" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J32" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K32" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -9238,12 +9502,6 @@
       <c r="I33" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J33" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K33" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -9264,12 +9522,6 @@
       <c r="I34" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J34" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K34" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -9299,12 +9551,6 @@
       <c r="I35" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J35" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K35" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -9334,12 +9580,6 @@
       <c r="I36" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J36" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K36" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -9359,12 +9599,6 @@
       </c>
       <c r="I37" t="str">
         <v>✅ 一致</v>
-      </c>
-      <c r="J37" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K37" t="str">
-        <v>待填</v>
       </c>
     </row>
   </sheetData>
@@ -9398,14 +9632,14 @@
     <mergeCell ref="D36:D37"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I37"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:I47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9435,12 +9669,6 @@
       <c r="I1" t="str">
         <v>供应商vs官方</v>
       </c>
-      <c r="J1" t="str">
-        <v>折扣</v>
-      </c>
-      <c r="K1" t="str">
-        <v>成本(元/百万tokens)</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -9470,12 +9698,6 @@
       <c r="I2" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J2" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K2" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -9505,12 +9727,6 @@
       <c r="I3" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J3" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K3" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -9540,12 +9756,6 @@
       <c r="I4" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J4" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K4" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -9575,12 +9785,6 @@
       <c r="I5" t="str">
         <v>⚠ 缓-2.2%</v>
       </c>
-      <c r="J5" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K5" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -9601,12 +9805,6 @@
       <c r="I6" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J6" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K6" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -9636,12 +9834,6 @@
       <c r="I7" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J7" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K7" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -9671,12 +9863,6 @@
       <c r="I8" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J8" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K8" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -9706,12 +9892,6 @@
       <c r="I9" t="str">
         <v>⚠ 缓-0.7%</v>
       </c>
-      <c r="J9" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K9" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -9732,12 +9912,6 @@
       <c r="I10" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J10" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K10" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -9767,12 +9941,6 @@
       <c r="I11" t="str">
         <v>✅ 一致(÷隐含)</v>
       </c>
-      <c r="J11" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K11" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -9793,12 +9961,6 @@
       <c r="I12" t="str">
         <v>✅ 一致(÷隐含)</v>
       </c>
-      <c r="J12" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K12" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -9828,12 +9990,6 @@
       <c r="I13" t="str">
         <v>⚠ 入+3.2% 出+3.4% 缓-0.7%</v>
       </c>
-      <c r="J13" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K13" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -9854,12 +10010,6 @@
       <c r="I14" t="str">
         <v>⚠ 缓-1.3%</v>
       </c>
-      <c r="J14" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K14" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -9889,12 +10039,6 @@
       <c r="I15" t="str">
         <v>⚠ 入+3.2% 出+3.4% 缓-0.7%</v>
       </c>
-      <c r="J15" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K15" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -9915,12 +10059,6 @@
       <c r="I16" t="str">
         <v>⚠ 缓-1.3%</v>
       </c>
-      <c r="J16" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K16" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -9950,12 +10088,6 @@
       <c r="I17" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J17" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K17" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -9976,12 +10108,6 @@
       <c r="I18" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J18" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K18" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -10011,12 +10137,6 @@
       <c r="I19" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J19" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K19" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -10037,12 +10157,6 @@
       <c r="I20" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J20" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K20" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -10072,12 +10186,6 @@
       <c r="I21" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J21" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K21" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -10098,12 +10206,6 @@
       <c r="I22" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J22" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K22" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -10133,12 +10235,6 @@
       <c r="I23" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J23" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K23" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -10159,12 +10255,6 @@
       <c r="I24" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J24" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K24" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -10194,12 +10284,6 @@
       <c r="I25" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J25" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K25" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -10220,12 +10304,6 @@
       <c r="I26" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J26" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K26" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -10255,12 +10333,6 @@
       <c r="I27" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J27" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K27" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -10290,12 +10362,6 @@
       <c r="I28" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J28" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K28" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -10325,12 +10391,6 @@
       <c r="I29" t="str">
         <v>⚠ 缓-0.7%</v>
       </c>
-      <c r="J29" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K29" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -10360,12 +10420,6 @@
       <c r="I30" t="str">
         <v>⚠ 入+13.8% 出+15.4% 缓-7.7%</v>
       </c>
-      <c r="J30" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K30" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -10395,12 +10449,6 @@
       <c r="I31" t="str">
         <v>⚠ 缓-0.6%</v>
       </c>
-      <c r="J31" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K31" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -10430,12 +10478,6 @@
       <c r="I32" t="str">
         <v>⚠ 缓-0.7%</v>
       </c>
-      <c r="J32" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K32" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -10465,12 +10507,6 @@
       <c r="I33" t="str">
         <v>✅ 一致(÷隐含)</v>
       </c>
-      <c r="J33" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K33" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -10500,12 +10536,6 @@
       <c r="I34" t="str">
         <v>⚠ 缓+2.8%</v>
       </c>
-      <c r="J34" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K34" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -10535,12 +10565,6 @@
       <c r="I35" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J35" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K35" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -10561,12 +10585,6 @@
       <c r="I36" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J36" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K36" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -10596,12 +10614,6 @@
       <c r="I37" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J37" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K37" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -10631,12 +10643,6 @@
       <c r="I38" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J38" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K38" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -10657,12 +10663,6 @@
       <c r="I39" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J39" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K39" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -10692,12 +10692,6 @@
       <c r="I40" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J40" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K40" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -10718,12 +10712,6 @@
       <c r="I41" t="str">
         <v>✅ 一致(÷7.5)</v>
       </c>
-      <c r="J41" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K41" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -10753,12 +10741,6 @@
       <c r="I42" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J42" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K42" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -10779,12 +10761,6 @@
       <c r="I43" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J43" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K43" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -10805,12 +10781,6 @@
       <c r="I44" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J44" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K44" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -10840,12 +10810,6 @@
       <c r="I45" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J45" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K45" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -10875,12 +10839,6 @@
       <c r="I46" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J46" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K46" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -10909,12 +10867,6 @@
       </c>
       <c r="I47" t="str">
         <v>✅ 一致</v>
-      </c>
-      <c r="J47" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K47" t="str">
-        <v>待填</v>
       </c>
     </row>
   </sheetData>
@@ -10963,14 +10915,14 @@
     <mergeCell ref="D42:D44"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I47"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:I48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11000,12 +10952,6 @@
       <c r="I1" t="str">
         <v>供应商vs官方</v>
       </c>
-      <c r="J1" t="str">
-        <v>折扣</v>
-      </c>
-      <c r="K1" t="str">
-        <v>成本(USD/百万tokens)</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -11035,12 +10981,6 @@
       <c r="I2" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J2" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K2" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -11070,12 +11010,6 @@
       <c r="I3" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J3" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K3" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -11105,12 +11039,6 @@
       <c r="I4" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J4" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K4" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -11140,12 +11068,6 @@
       <c r="I5" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J5" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K5" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -11175,12 +11097,6 @@
       <c r="I6" t="str">
         <v>⚠ 缓+0.7%</v>
       </c>
-      <c r="J6" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K6" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -11210,12 +11126,6 @@
       <c r="I7" t="str">
         <v>⚠ 缓-2.5%</v>
       </c>
-      <c r="J7" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K7" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -11245,12 +11155,6 @@
       <c r="I8" t="str">
         <v>⚠ 缓+4%</v>
       </c>
-      <c r="J8" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K8" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -11280,12 +11184,6 @@
       <c r="I9" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J9" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K9" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -11306,12 +11204,6 @@
       <c r="I10" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J10" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K10" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -11341,12 +11233,6 @@
       <c r="I11" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J11" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K11" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -11376,12 +11262,6 @@
       <c r="I12" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J12" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K12" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -11411,12 +11291,6 @@
       <c r="I13" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J13" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K13" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -11437,12 +11311,6 @@
       <c r="I14" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J14" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K14" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -11472,12 +11340,6 @@
       <c r="I15" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J15" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K15" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -11498,12 +11360,6 @@
       <c r="I16" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J16" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K16" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -11533,12 +11389,6 @@
       <c r="I17" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J17" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K17" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -11559,12 +11409,6 @@
       <c r="I18" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J18" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K18" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -11594,12 +11438,6 @@
       <c r="I19" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J19" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K19" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -11620,12 +11458,6 @@
       <c r="I20" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J20" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K20" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -11655,12 +11487,6 @@
       <c r="I21" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J21" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K21" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -11681,12 +11507,6 @@
       <c r="I22" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J22" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K22" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -11716,12 +11536,6 @@
       <c r="I23" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J23" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K23" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -11742,12 +11556,6 @@
       <c r="I24" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J24" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K24" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -11777,12 +11585,6 @@
       <c r="I25" t="str">
         <v>✅ 一致(÷6.5)</v>
       </c>
-      <c r="J25" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K25" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -11803,12 +11605,6 @@
       <c r="I26" t="str">
         <v>✅ 一致(÷6.5)</v>
       </c>
-      <c r="J26" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K26" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -11838,12 +11634,6 @@
       <c r="I27" t="str">
         <v>✅ 一致(÷6.5)</v>
       </c>
-      <c r="J27" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K27" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -11864,12 +11654,6 @@
       <c r="I28" t="str">
         <v>✅ 一致(÷6.5)</v>
       </c>
-      <c r="J28" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K28" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -11899,12 +11683,6 @@
       <c r="I29" t="str">
         <v>✅ 一致(÷6.5)</v>
       </c>
-      <c r="J29" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K29" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -11925,12 +11703,6 @@
       <c r="I30" t="str">
         <v>✅ 一致(÷6.5)</v>
       </c>
-      <c r="J30" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K30" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -11960,12 +11732,6 @@
       <c r="I31" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J31" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K31" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -11995,12 +11761,6 @@
       <c r="I32" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J32" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K32" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -12030,12 +11790,6 @@
       <c r="I33" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J33" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K33" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -12065,12 +11819,6 @@
       <c r="I34" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J34" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K34" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -12100,12 +11848,6 @@
       <c r="I35" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J35" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K35" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -12135,12 +11877,6 @@
       <c r="I36" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J36" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K36" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -12170,12 +11906,6 @@
       <c r="I37" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J37" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K37" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -12205,12 +11935,6 @@
       <c r="I38" t="str">
         <v>⚠ 缓+2.9%</v>
       </c>
-      <c r="J38" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K38" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -12240,12 +11964,6 @@
       <c r="I39" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J39" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K39" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -12266,12 +11984,6 @@
       <c r="I40" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J40" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K40" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -12301,12 +12013,6 @@
       <c r="I41" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J41" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K41" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -12336,12 +12042,6 @@
       <c r="I42" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J42" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K42" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -12362,12 +12062,6 @@
       <c r="I43" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J43" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K43" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -12397,12 +12091,6 @@
       <c r="I44" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J44" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K44" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -12423,12 +12111,6 @@
       <c r="I45" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J45" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K45" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -12458,12 +12140,6 @@
       <c r="I46" t="str">
         <v>✅ 一致(÷6.5)</v>
       </c>
-      <c r="J46" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K46" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -12493,12 +12169,6 @@
       <c r="I47" t="str">
         <v>⚠ 入-7.1% 出-7.1% 缓-7.1%</v>
       </c>
-      <c r="J47" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K47" t="str">
-        <v>待填</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -12527,12 +12197,6 @@
       </c>
       <c r="I48" t="str">
         <v>⚠ 入-7.1% 出-7.1% 缓-7.1%</v>
-      </c>
-      <c r="J48" t="str">
-        <v>待填</v>
-      </c>
-      <c r="K48" t="str">
-        <v>待填</v>
       </c>
     </row>
   </sheetData>
@@ -12578,14 +12242,14 @@
     <mergeCell ref="D44:D45"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I48"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:I54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -12615,12 +12279,6 @@
       <c r="I1" t="str">
         <v>供应商vs官方</v>
       </c>
-      <c r="J1" t="str">
-        <v>折扣</v>
-      </c>
-      <c r="K1" t="str">
-        <v>成本(元/百万tokens)</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -12650,12 +12308,6 @@
       <c r="I2" t="str">
         <v>—</v>
       </c>
-      <c r="J2" t="str">
-        <v>—</v>
-      </c>
-      <c r="K2" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -12676,12 +12328,6 @@
       <c r="I3" t="str">
         <v>—</v>
       </c>
-      <c r="J3" t="str">
-        <v>—</v>
-      </c>
-      <c r="K3" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -12702,12 +12348,6 @@
       <c r="I4" t="str">
         <v>—</v>
       </c>
-      <c r="J4" t="str">
-        <v>—</v>
-      </c>
-      <c r="K4" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -12728,12 +12368,6 @@
       <c r="I5" t="str">
         <v>—</v>
       </c>
-      <c r="J5" t="str">
-        <v>—</v>
-      </c>
-      <c r="K5" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -12754,12 +12388,6 @@
       <c r="I6" t="str">
         <v>—</v>
       </c>
-      <c r="J6" t="str">
-        <v>—</v>
-      </c>
-      <c r="K6" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -12780,12 +12408,6 @@
       <c r="I7" t="str">
         <v>—</v>
       </c>
-      <c r="J7" t="str">
-        <v>—</v>
-      </c>
-      <c r="K7" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -12806,12 +12428,6 @@
       <c r="I8" t="str">
         <v>—</v>
       </c>
-      <c r="J8" t="str">
-        <v>—</v>
-      </c>
-      <c r="K8" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -12832,12 +12448,6 @@
       <c r="I9" t="str">
         <v>—</v>
       </c>
-      <c r="J9" t="str">
-        <v>—</v>
-      </c>
-      <c r="K9" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -12858,12 +12468,6 @@
       <c r="I10" t="str">
         <v>—</v>
       </c>
-      <c r="J10" t="str">
-        <v>—</v>
-      </c>
-      <c r="K10" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -12884,12 +12488,6 @@
       <c r="I11" t="str">
         <v>—</v>
       </c>
-      <c r="J11" t="str">
-        <v>—</v>
-      </c>
-      <c r="K11" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -12910,12 +12508,6 @@
       <c r="I12" t="str">
         <v>—</v>
       </c>
-      <c r="J12" t="str">
-        <v>—</v>
-      </c>
-      <c r="K12" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -12936,12 +12528,6 @@
       <c r="I13" t="str">
         <v>—</v>
       </c>
-      <c r="J13" t="str">
-        <v>—</v>
-      </c>
-      <c r="K13" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -12962,12 +12548,6 @@
       <c r="I14" t="str">
         <v>—</v>
       </c>
-      <c r="J14" t="str">
-        <v>—</v>
-      </c>
-      <c r="K14" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -12988,12 +12568,6 @@
       <c r="I15" t="str">
         <v>—</v>
       </c>
-      <c r="J15" t="str">
-        <v>—</v>
-      </c>
-      <c r="K15" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -13014,12 +12588,6 @@
       <c r="I16" t="str">
         <v>—</v>
       </c>
-      <c r="J16" t="str">
-        <v>—</v>
-      </c>
-      <c r="K16" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -13040,12 +12608,6 @@
       <c r="I17" t="str">
         <v>—</v>
       </c>
-      <c r="J17" t="str">
-        <v>—</v>
-      </c>
-      <c r="K17" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -13066,12 +12628,6 @@
       <c r="I18" t="str">
         <v>—</v>
       </c>
-      <c r="J18" t="str">
-        <v>—</v>
-      </c>
-      <c r="K18" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -13092,12 +12648,6 @@
       <c r="I19" t="str">
         <v>—</v>
       </c>
-      <c r="J19" t="str">
-        <v>—</v>
-      </c>
-      <c r="K19" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -13118,12 +12668,6 @@
       <c r="I20" t="str">
         <v>—</v>
       </c>
-      <c r="J20" t="str">
-        <v>—</v>
-      </c>
-      <c r="K20" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -13144,12 +12688,6 @@
       <c r="I21" t="str">
         <v>—</v>
       </c>
-      <c r="J21" t="str">
-        <v>—</v>
-      </c>
-      <c r="K21" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -13170,12 +12708,6 @@
       <c r="I22" t="str">
         <v>—</v>
       </c>
-      <c r="J22" t="str">
-        <v>—</v>
-      </c>
-      <c r="K22" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -13196,12 +12728,6 @@
       <c r="I23" t="str">
         <v>—</v>
       </c>
-      <c r="J23" t="str">
-        <v>—</v>
-      </c>
-      <c r="K23" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -13222,12 +12748,6 @@
       <c r="I24" t="str">
         <v>—</v>
       </c>
-      <c r="J24" t="str">
-        <v>—</v>
-      </c>
-      <c r="K24" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -13248,12 +12768,6 @@
       <c r="I25" t="str">
         <v>—</v>
       </c>
-      <c r="J25" t="str">
-        <v>—</v>
-      </c>
-      <c r="K25" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -13274,12 +12788,6 @@
       <c r="I26" t="str">
         <v>—</v>
       </c>
-      <c r="J26" t="str">
-        <v>—</v>
-      </c>
-      <c r="K26" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -13300,12 +12808,6 @@
       <c r="I27" t="str">
         <v>—</v>
       </c>
-      <c r="J27" t="str">
-        <v>—</v>
-      </c>
-      <c r="K27" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -13326,12 +12828,6 @@
       <c r="I28" t="str">
         <v>—</v>
       </c>
-      <c r="J28" t="str">
-        <v>—</v>
-      </c>
-      <c r="K28" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -13352,12 +12848,6 @@
       <c r="I29" t="str">
         <v>—</v>
       </c>
-      <c r="J29" t="str">
-        <v>—</v>
-      </c>
-      <c r="K29" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -13378,12 +12868,6 @@
       <c r="I30" t="str">
         <v>—</v>
       </c>
-      <c r="J30" t="str">
-        <v>—</v>
-      </c>
-      <c r="K30" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -13404,12 +12888,6 @@
       <c r="I31" t="str">
         <v>—</v>
       </c>
-      <c r="J31" t="str">
-        <v>—</v>
-      </c>
-      <c r="K31" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -13430,12 +12908,6 @@
       <c r="I32" t="str">
         <v>—</v>
       </c>
-      <c r="J32" t="str">
-        <v>—</v>
-      </c>
-      <c r="K32" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -13456,12 +12928,6 @@
       <c r="I33" t="str">
         <v>—</v>
       </c>
-      <c r="J33" t="str">
-        <v>—</v>
-      </c>
-      <c r="K33" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -13482,12 +12948,6 @@
       <c r="I34" t="str">
         <v>—</v>
       </c>
-      <c r="J34" t="str">
-        <v>—</v>
-      </c>
-      <c r="K34" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -13508,12 +12968,6 @@
       <c r="I35" t="str">
         <v>—</v>
       </c>
-      <c r="J35" t="str">
-        <v>—</v>
-      </c>
-      <c r="K35" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -13534,12 +12988,6 @@
       <c r="I36" t="str">
         <v>—</v>
       </c>
-      <c r="J36" t="str">
-        <v>—</v>
-      </c>
-      <c r="K36" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -13560,12 +13008,6 @@
       <c r="I37" t="str">
         <v>—</v>
       </c>
-      <c r="J37" t="str">
-        <v>—</v>
-      </c>
-      <c r="K37" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -13586,12 +13028,6 @@
       <c r="I38" t="str">
         <v>—</v>
       </c>
-      <c r="J38" t="str">
-        <v>—</v>
-      </c>
-      <c r="K38" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -13612,12 +13048,6 @@
       <c r="I39" t="str">
         <v>—</v>
       </c>
-      <c r="J39" t="str">
-        <v>—</v>
-      </c>
-      <c r="K39" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -13638,12 +13068,6 @@
       <c r="I40" t="str">
         <v>—</v>
       </c>
-      <c r="J40" t="str">
-        <v>—</v>
-      </c>
-      <c r="K40" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -13664,12 +13088,6 @@
       <c r="I41" t="str">
         <v>—</v>
       </c>
-      <c r="J41" t="str">
-        <v>—</v>
-      </c>
-      <c r="K41" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -13690,12 +13108,6 @@
       <c r="I42" t="str">
         <v>—</v>
       </c>
-      <c r="J42" t="str">
-        <v>—</v>
-      </c>
-      <c r="K42" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -13716,12 +13128,6 @@
       <c r="I43" t="str">
         <v>—</v>
       </c>
-      <c r="J43" t="str">
-        <v>—</v>
-      </c>
-      <c r="K43" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -13751,12 +13157,6 @@
       <c r="I44" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J44" t="str">
-        <v>—</v>
-      </c>
-      <c r="K44" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -13786,12 +13186,6 @@
       <c r="I45" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J45" t="str">
-        <v>—</v>
-      </c>
-      <c r="K45" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -13812,12 +13206,6 @@
       <c r="I46" t="str">
         <v>⚠ 入+50% 出+75% 缓+50%</v>
       </c>
-      <c r="J46" t="str">
-        <v>—</v>
-      </c>
-      <c r="K46" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -13838,12 +13226,6 @@
       <c r="I47" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J47" t="str">
-        <v>—</v>
-      </c>
-      <c r="K47" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -13873,12 +13255,6 @@
       <c r="I48" t="str">
         <v>⚠ 入+300% 出+300% 缓+3900%</v>
       </c>
-      <c r="J48" t="str">
-        <v>—</v>
-      </c>
-      <c r="K48" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -13908,12 +13284,6 @@
       <c r="I49" t="str">
         <v>⚠ 缓+900%</v>
       </c>
-      <c r="J49" t="str">
-        <v>—</v>
-      </c>
-      <c r="K49" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -13943,12 +13313,6 @@
       <c r="I50" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J50" t="str">
-        <v>—</v>
-      </c>
-      <c r="K50" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -13969,12 +13333,6 @@
       <c r="I51" t="str">
         <v>⚠ 入+100% 出+100%</v>
       </c>
-      <c r="J51" t="str">
-        <v>—</v>
-      </c>
-      <c r="K51" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -13995,12 +13353,6 @@
       <c r="I52" t="str">
         <v>—</v>
       </c>
-      <c r="J52" t="str">
-        <v>—</v>
-      </c>
-      <c r="K52" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -14021,12 +13373,6 @@
       <c r="I53" t="str">
         <v>—</v>
       </c>
-      <c r="J53" t="str">
-        <v>—</v>
-      </c>
-      <c r="K53" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -14045,12 +13391,6 @@
         <v>入 ¥4 · 出 ¥16 · 缓 ¥0.8</v>
       </c>
       <c r="I54" t="str">
-        <v>—</v>
-      </c>
-      <c r="J54" t="str">
-        <v>—</v>
-      </c>
-      <c r="K54" t="str">
         <v>—</v>
       </c>
     </row>
@@ -14067,14 +13407,14 @@
     <mergeCell ref="D50:D54"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I54"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:I40"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14104,12 +13444,6 @@
       <c r="I1" t="str">
         <v>供应商vs官方</v>
       </c>
-      <c r="J1" t="str">
-        <v>折扣</v>
-      </c>
-      <c r="K1" t="str">
-        <v>成本(USD/百万tokens)</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -14139,12 +13473,6 @@
       <c r="I2" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J2" t="str">
-        <v>—</v>
-      </c>
-      <c r="K2" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -14165,12 +13493,6 @@
       <c r="I3" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J3" t="str">
-        <v>—</v>
-      </c>
-      <c r="K3" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -14200,12 +13522,6 @@
       <c r="I4" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J4" t="str">
-        <v>—</v>
-      </c>
-      <c r="K4" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -14235,12 +13551,6 @@
       <c r="I5" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J5" t="str">
-        <v>—</v>
-      </c>
-      <c r="K5" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -14270,12 +13580,6 @@
       <c r="I6" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J6" t="str">
-        <v>—</v>
-      </c>
-      <c r="K6" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -14296,12 +13600,6 @@
       <c r="I7" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J7" t="str">
-        <v>—</v>
-      </c>
-      <c r="K7" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -14331,12 +13629,6 @@
       <c r="I8" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J8" t="str">
-        <v>—</v>
-      </c>
-      <c r="K8" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -14357,12 +13649,6 @@
       <c r="I9" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J9" t="str">
-        <v>—</v>
-      </c>
-      <c r="K9" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -14383,12 +13669,6 @@
       <c r="I10" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J10" t="str">
-        <v>—</v>
-      </c>
-      <c r="K10" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -14418,12 +13698,6 @@
       <c r="I11" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J11" t="str">
-        <v>—</v>
-      </c>
-      <c r="K11" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -14444,12 +13718,6 @@
       <c r="I12" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J12" t="str">
-        <v>—</v>
-      </c>
-      <c r="K12" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -14470,12 +13738,6 @@
       <c r="I13" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J13" t="str">
-        <v>—</v>
-      </c>
-      <c r="K13" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -14496,12 +13758,6 @@
       <c r="I14" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J14" t="str">
-        <v>—</v>
-      </c>
-      <c r="K14" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -14531,12 +13787,6 @@
       <c r="I15" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J15" t="str">
-        <v>—</v>
-      </c>
-      <c r="K15" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -14557,12 +13807,6 @@
       <c r="I16" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J16" t="str">
-        <v>—</v>
-      </c>
-      <c r="K16" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -14592,12 +13836,6 @@
       <c r="I17" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J17" t="str">
-        <v>—</v>
-      </c>
-      <c r="K17" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -14618,12 +13856,6 @@
       <c r="I18" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J18" t="str">
-        <v>—</v>
-      </c>
-      <c r="K18" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -14644,12 +13876,6 @@
       <c r="I19" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J19" t="str">
-        <v>—</v>
-      </c>
-      <c r="K19" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -14670,12 +13896,6 @@
       <c r="I20" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J20" t="str">
-        <v>—</v>
-      </c>
-      <c r="K20" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -14705,12 +13925,6 @@
       <c r="I21" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J21" t="str">
-        <v>—</v>
-      </c>
-      <c r="K21" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -14740,12 +13954,6 @@
       <c r="I22" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J22" t="str">
-        <v>—</v>
-      </c>
-      <c r="K22" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -14775,12 +13983,6 @@
       <c r="I23" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J23" t="str">
-        <v>—</v>
-      </c>
-      <c r="K23" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -14801,12 +14003,6 @@
       <c r="I24" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J24" t="str">
-        <v>—</v>
-      </c>
-      <c r="K24" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -14836,12 +14032,6 @@
       <c r="I25" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J25" t="str">
-        <v>—</v>
-      </c>
-      <c r="K25" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -14871,12 +14061,6 @@
       <c r="I26" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J26" t="str">
-        <v>—</v>
-      </c>
-      <c r="K26" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -14906,12 +14090,6 @@
       <c r="I27" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J27" t="str">
-        <v>—</v>
-      </c>
-      <c r="K27" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -14941,12 +14119,6 @@
       <c r="I28" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J28" t="str">
-        <v>—</v>
-      </c>
-      <c r="K28" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -14976,12 +14148,6 @@
       <c r="I29" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J29" t="str">
-        <v>—</v>
-      </c>
-      <c r="K29" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -15002,12 +14168,6 @@
       <c r="I30" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J30" t="str">
-        <v>—</v>
-      </c>
-      <c r="K30" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -15028,12 +14188,6 @@
       <c r="I31" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J31" t="str">
-        <v>—</v>
-      </c>
-      <c r="K31" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -15063,12 +14217,6 @@
       <c r="I32" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J32" t="str">
-        <v>—</v>
-      </c>
-      <c r="K32" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -15098,12 +14246,6 @@
       <c r="I33" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J33" t="str">
-        <v>—</v>
-      </c>
-      <c r="K33" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -15124,12 +14266,6 @@
       <c r="I34" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J34" t="str">
-        <v>—</v>
-      </c>
-      <c r="K34" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -15159,12 +14295,6 @@
       <c r="I35" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J35" t="str">
-        <v>—</v>
-      </c>
-      <c r="K35" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -15194,12 +14324,6 @@
       <c r="I36" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J36" t="str">
-        <v>—</v>
-      </c>
-      <c r="K36" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -15229,12 +14353,6 @@
       <c r="I37" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J37" t="str">
-        <v>—</v>
-      </c>
-      <c r="K37" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -15255,12 +14373,6 @@
       <c r="I38" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J38" t="str">
-        <v>—</v>
-      </c>
-      <c r="K38" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -15290,12 +14402,6 @@
       <c r="I39" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J39" t="str">
-        <v>—</v>
-      </c>
-      <c r="K39" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -15315,12 +14421,6 @@
       </c>
       <c r="I40" t="str">
         <v>✅ 一致</v>
-      </c>
-      <c r="J40" t="str">
-        <v>—</v>
-      </c>
-      <c r="K40" t="str">
-        <v>—</v>
       </c>
     </row>
   </sheetData>
@@ -15360,14 +14460,14 @@
     <mergeCell ref="D39:D40"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I40"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:I117"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15397,12 +14497,6 @@
       <c r="I1" t="str">
         <v>供应商vs官方</v>
       </c>
-      <c r="J1" t="str">
-        <v>折扣</v>
-      </c>
-      <c r="K1" t="str">
-        <v>成本(元或USD/百万tokens)</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -15432,12 +14526,6 @@
       <c r="I2" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J2" t="str">
-        <v>—</v>
-      </c>
-      <c r="K2" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -15467,12 +14555,6 @@
       <c r="I3" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J3" t="str">
-        <v>—</v>
-      </c>
-      <c r="K3" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -15502,12 +14584,6 @@
       <c r="I4" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J4" t="str">
-        <v>—</v>
-      </c>
-      <c r="K4" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -15537,12 +14613,6 @@
       <c r="I5" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J5" t="str">
-        <v>—</v>
-      </c>
-      <c r="K5" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -15572,12 +14642,6 @@
       <c r="I6" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J6" t="str">
-        <v>—</v>
-      </c>
-      <c r="K6" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -15598,12 +14662,6 @@
       <c r="I7" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J7" t="str">
-        <v>—</v>
-      </c>
-      <c r="K7" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -15624,12 +14682,6 @@
       <c r="I8" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J8" t="str">
-        <v>—</v>
-      </c>
-      <c r="K8" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -15659,12 +14711,6 @@
       <c r="I9" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J9" t="str">
-        <v>—</v>
-      </c>
-      <c r="K9" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -15694,12 +14740,6 @@
       <c r="I10" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J10" t="str">
-        <v>—</v>
-      </c>
-      <c r="K10" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -15720,12 +14760,6 @@
       <c r="I11" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J11" t="str">
-        <v>—</v>
-      </c>
-      <c r="K11" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -15746,12 +14780,6 @@
       <c r="I12" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J12" t="str">
-        <v>—</v>
-      </c>
-      <c r="K12" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -15781,12 +14809,6 @@
       <c r="I13" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J13" t="str">
-        <v>—</v>
-      </c>
-      <c r="K13" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -15816,12 +14838,6 @@
       <c r="I14" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J14" t="str">
-        <v>—</v>
-      </c>
-      <c r="K14" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -15842,12 +14858,6 @@
       <c r="I15" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J15" t="str">
-        <v>—</v>
-      </c>
-      <c r="K15" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -15868,12 +14878,6 @@
       <c r="I16" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J16" t="str">
-        <v>—</v>
-      </c>
-      <c r="K16" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -15903,12 +14907,6 @@
       <c r="I17" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J17" t="str">
-        <v>—</v>
-      </c>
-      <c r="K17" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -15929,12 +14927,6 @@
       <c r="I18" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J18" t="str">
-        <v>—</v>
-      </c>
-      <c r="K18" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -15955,12 +14947,6 @@
       <c r="I19" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J19" t="str">
-        <v>—</v>
-      </c>
-      <c r="K19" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -15990,12 +14976,6 @@
       <c r="I20" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J20" t="str">
-        <v>—</v>
-      </c>
-      <c r="K20" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -16016,12 +14996,6 @@
       <c r="I21" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J21" t="str">
-        <v>—</v>
-      </c>
-      <c r="K21" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -16051,12 +15025,6 @@
       <c r="I22" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J22" t="str">
-        <v>—</v>
-      </c>
-      <c r="K22" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -16077,12 +15045,6 @@
       <c r="I23" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J23" t="str">
-        <v>—</v>
-      </c>
-      <c r="K23" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -16112,12 +15074,6 @@
       <c r="I24" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J24" t="str">
-        <v>—</v>
-      </c>
-      <c r="K24" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -16147,12 +15103,6 @@
       <c r="I25" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J25" t="str">
-        <v>—</v>
-      </c>
-      <c r="K25" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -16173,12 +15123,6 @@
       <c r="I26" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J26" t="str">
-        <v>—</v>
-      </c>
-      <c r="K26" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -16208,12 +15152,6 @@
       <c r="I27" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J27" t="str">
-        <v>—</v>
-      </c>
-      <c r="K27" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -16243,12 +15181,6 @@
       <c r="I28" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J28" t="str">
-        <v>—</v>
-      </c>
-      <c r="K28" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -16278,12 +15210,6 @@
       <c r="I29" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J29" t="str">
-        <v>—</v>
-      </c>
-      <c r="K29" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -16313,12 +15239,6 @@
       <c r="I30" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J30" t="str">
-        <v>—</v>
-      </c>
-      <c r="K30" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -16339,12 +15259,6 @@
       <c r="I31" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J31" t="str">
-        <v>—</v>
-      </c>
-      <c r="K31" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -16374,12 +15288,6 @@
       <c r="I32" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J32" t="str">
-        <v>—</v>
-      </c>
-      <c r="K32" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -16409,12 +15317,6 @@
       <c r="I33" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J33" t="str">
-        <v>—</v>
-      </c>
-      <c r="K33" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -16444,12 +15346,6 @@
       <c r="I34" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J34" t="str">
-        <v>—</v>
-      </c>
-      <c r="K34" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -16470,12 +15366,6 @@
       <c r="I35" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J35" t="str">
-        <v>—</v>
-      </c>
-      <c r="K35" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -16505,12 +15395,6 @@
       <c r="I36" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J36" t="str">
-        <v>—</v>
-      </c>
-      <c r="K36" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -16531,12 +15415,6 @@
       <c r="I37" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J37" t="str">
-        <v>—</v>
-      </c>
-      <c r="K37" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -16557,12 +15435,6 @@
       <c r="I38" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J38" t="str">
-        <v>—</v>
-      </c>
-      <c r="K38" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -16592,12 +15464,6 @@
       <c r="I39" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J39" t="str">
-        <v>—</v>
-      </c>
-      <c r="K39" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -16618,12 +15484,6 @@
       <c r="I40" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J40" t="str">
-        <v>—</v>
-      </c>
-      <c r="K40" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -16644,12 +15504,6 @@
       <c r="I41" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J41" t="str">
-        <v>—</v>
-      </c>
-      <c r="K41" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -16670,12 +15524,6 @@
       <c r="I42" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J42" t="str">
-        <v>—</v>
-      </c>
-      <c r="K42" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -16705,12 +15553,6 @@
       <c r="I43" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J43" t="str">
-        <v>—</v>
-      </c>
-      <c r="K43" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -16731,12 +15573,6 @@
       <c r="I44" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J44" t="str">
-        <v>—</v>
-      </c>
-      <c r="K44" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -16766,12 +15602,6 @@
       <c r="I45" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J45" t="str">
-        <v>—</v>
-      </c>
-      <c r="K45" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -16792,12 +15622,6 @@
       <c r="I46" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J46" t="str">
-        <v>—</v>
-      </c>
-      <c r="K46" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -16827,12 +15651,6 @@
       <c r="I47" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J47" t="str">
-        <v>—</v>
-      </c>
-      <c r="K47" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -16862,12 +15680,6 @@
       <c r="I48" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J48" t="str">
-        <v>—</v>
-      </c>
-      <c r="K48" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -16897,12 +15709,6 @@
       <c r="I49" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J49" t="str">
-        <v>—</v>
-      </c>
-      <c r="K49" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -16932,12 +15738,6 @@
       <c r="I50" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J50" t="str">
-        <v>—</v>
-      </c>
-      <c r="K50" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -16967,12 +15767,6 @@
       <c r="I51" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J51" t="str">
-        <v>—</v>
-      </c>
-      <c r="K51" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -17002,12 +15796,6 @@
       <c r="I52" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J52" t="str">
-        <v>—</v>
-      </c>
-      <c r="K52" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -17037,12 +15825,6 @@
       <c r="I53" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J53" t="str">
-        <v>—</v>
-      </c>
-      <c r="K53" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -17063,12 +15845,6 @@
       <c r="I54" t="str">
         <v>⚠ 入+100% 出+100% 缓+100%</v>
       </c>
-      <c r="J54" t="str">
-        <v>—</v>
-      </c>
-      <c r="K54" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -17089,12 +15865,6 @@
       <c r="I55" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J55" t="str">
-        <v>—</v>
-      </c>
-      <c r="K55" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -17115,12 +15885,6 @@
       <c r="I56" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J56" t="str">
-        <v>—</v>
-      </c>
-      <c r="K56" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -17150,12 +15914,6 @@
       <c r="I57" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J57" t="str">
-        <v>—</v>
-      </c>
-      <c r="K57" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -17185,12 +15943,6 @@
       <c r="I58" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J58" t="str">
-        <v>—</v>
-      </c>
-      <c r="K58" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -17220,12 +15972,6 @@
       <c r="I59" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J59" t="str">
-        <v>—</v>
-      </c>
-      <c r="K59" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -17246,12 +15992,6 @@
       <c r="I60" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J60" t="str">
-        <v>—</v>
-      </c>
-      <c r="K60" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -17281,12 +16021,6 @@
       <c r="I61" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J61" t="str">
-        <v>—</v>
-      </c>
-      <c r="K61" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -17316,12 +16050,6 @@
       <c r="I62" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J62" t="str">
-        <v>—</v>
-      </c>
-      <c r="K62" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -17351,12 +16079,6 @@
       <c r="I63" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J63" t="str">
-        <v>—</v>
-      </c>
-      <c r="K63" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -17386,12 +16108,6 @@
       <c r="I64" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J64" t="str">
-        <v>—</v>
-      </c>
-      <c r="K64" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -17421,12 +16137,6 @@
       <c r="I65" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J65" t="str">
-        <v>—</v>
-      </c>
-      <c r="K65" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -17447,12 +16157,6 @@
       <c r="I66" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J66" t="str">
-        <v>—</v>
-      </c>
-      <c r="K66" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -17473,12 +16177,6 @@
       <c r="I67" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J67" t="str">
-        <v>—</v>
-      </c>
-      <c r="K67" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -17508,12 +16206,6 @@
       <c r="I68" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J68" t="str">
-        <v>—</v>
-      </c>
-      <c r="K68" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -17543,12 +16235,6 @@
       <c r="I69" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J69" t="str">
-        <v>—</v>
-      </c>
-      <c r="K69" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -17569,12 +16255,6 @@
       <c r="I70" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J70" t="str">
-        <v>—</v>
-      </c>
-      <c r="K70" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -17604,12 +16284,6 @@
       <c r="I71" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J71" t="str">
-        <v>—</v>
-      </c>
-      <c r="K71" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -17639,12 +16313,6 @@
       <c r="I72" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J72" t="str">
-        <v>—</v>
-      </c>
-      <c r="K72" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -17674,12 +16342,6 @@
       <c r="I73" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J73" t="str">
-        <v>—</v>
-      </c>
-      <c r="K73" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -17700,12 +16362,6 @@
       <c r="I74" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J74" t="str">
-        <v>—</v>
-      </c>
-      <c r="K74" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -17735,12 +16391,6 @@
       <c r="I75" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J75" t="str">
-        <v>—</v>
-      </c>
-      <c r="K75" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -17761,12 +16411,6 @@
       <c r="I76" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J76" t="str">
-        <v>—</v>
-      </c>
-      <c r="K76" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -17796,12 +16440,6 @@
       <c r="I77" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J77" t="str">
-        <v>—</v>
-      </c>
-      <c r="K77" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -17831,12 +16469,6 @@
       <c r="I78" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J78" t="str">
-        <v>—</v>
-      </c>
-      <c r="K78" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -17866,12 +16498,6 @@
       <c r="I79" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J79" t="str">
-        <v>—</v>
-      </c>
-      <c r="K79" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -17901,12 +16527,6 @@
       <c r="I80" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J80" t="str">
-        <v>—</v>
-      </c>
-      <c r="K80" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -17936,12 +16556,6 @@
       <c r="I81" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J81" t="str">
-        <v>—</v>
-      </c>
-      <c r="K81" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -17971,12 +16585,6 @@
       <c r="I82" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J82" t="str">
-        <v>—</v>
-      </c>
-      <c r="K82" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -18006,12 +16614,6 @@
       <c r="I83" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J83" t="str">
-        <v>—</v>
-      </c>
-      <c r="K83" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -18032,12 +16634,6 @@
       <c r="I84" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J84" t="str">
-        <v>—</v>
-      </c>
-      <c r="K84" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -18058,12 +16654,6 @@
       <c r="I85" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J85" t="str">
-        <v>—</v>
-      </c>
-      <c r="K85" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -18084,12 +16674,6 @@
       <c r="I86" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J86" t="str">
-        <v>—</v>
-      </c>
-      <c r="K86" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -18110,12 +16694,6 @@
       <c r="I87" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J87" t="str">
-        <v>—</v>
-      </c>
-      <c r="K87" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -18136,12 +16714,6 @@
       <c r="I88" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J88" t="str">
-        <v>—</v>
-      </c>
-      <c r="K88" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -18162,12 +16734,6 @@
       <c r="I89" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J89" t="str">
-        <v>—</v>
-      </c>
-      <c r="K89" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -18188,12 +16754,6 @@
       <c r="I90" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J90" t="str">
-        <v>—</v>
-      </c>
-      <c r="K90" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -18214,12 +16774,6 @@
       <c r="I91" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J91" t="str">
-        <v>—</v>
-      </c>
-      <c r="K91" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -18240,12 +16794,6 @@
       <c r="I92" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J92" t="str">
-        <v>—</v>
-      </c>
-      <c r="K92" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -18266,12 +16814,6 @@
       <c r="I93" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J93" t="str">
-        <v>—</v>
-      </c>
-      <c r="K93" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -18292,12 +16834,6 @@
       <c r="I94" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J94" t="str">
-        <v>—</v>
-      </c>
-      <c r="K94" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -18318,12 +16854,6 @@
       <c r="I95" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J95" t="str">
-        <v>—</v>
-      </c>
-      <c r="K95" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -18344,12 +16874,6 @@
       <c r="I96" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J96" t="str">
-        <v>—</v>
-      </c>
-      <c r="K96" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -18370,12 +16894,6 @@
       <c r="I97" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J97" t="str">
-        <v>—</v>
-      </c>
-      <c r="K97" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -18396,12 +16914,6 @@
       <c r="I98" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J98" t="str">
-        <v>—</v>
-      </c>
-      <c r="K98" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -18422,12 +16934,6 @@
       <c r="I99" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J99" t="str">
-        <v>—</v>
-      </c>
-      <c r="K99" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -18448,12 +16954,6 @@
       <c r="I100" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J100" t="str">
-        <v>—</v>
-      </c>
-      <c r="K100" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -18474,12 +16974,6 @@
       <c r="I101" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J101" t="str">
-        <v>—</v>
-      </c>
-      <c r="K101" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -18500,12 +16994,6 @@
       <c r="I102" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J102" t="str">
-        <v>—</v>
-      </c>
-      <c r="K102" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -18526,12 +17014,6 @@
       <c r="I103" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J103" t="str">
-        <v>—</v>
-      </c>
-      <c r="K103" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -18552,12 +17034,6 @@
       <c r="I104" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J104" t="str">
-        <v>—</v>
-      </c>
-      <c r="K104" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -18587,12 +17063,6 @@
       <c r="I105" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J105" t="str">
-        <v>—</v>
-      </c>
-      <c r="K105" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -18622,12 +17092,6 @@
       <c r="I106" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J106" t="str">
-        <v>—</v>
-      </c>
-      <c r="K106" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -18648,12 +17112,6 @@
       <c r="I107" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J107" t="str">
-        <v>—</v>
-      </c>
-      <c r="K107" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -18674,12 +17132,6 @@
       <c r="I108" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J108" t="str">
-        <v>—</v>
-      </c>
-      <c r="K108" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -18709,12 +17161,6 @@
       <c r="I109" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J109" t="str">
-        <v>—</v>
-      </c>
-      <c r="K109" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -18735,12 +17181,6 @@
       <c r="I110" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J110" t="str">
-        <v>—</v>
-      </c>
-      <c r="K110" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -18770,12 +17210,6 @@
       <c r="I111" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J111" t="str">
-        <v>—</v>
-      </c>
-      <c r="K111" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -18796,12 +17230,6 @@
       <c r="I112" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J112" t="str">
-        <v>—</v>
-      </c>
-      <c r="K112" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -18831,12 +17259,6 @@
       <c r="I113" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J113" t="str">
-        <v>—</v>
-      </c>
-      <c r="K113" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -18857,12 +17279,6 @@
       <c r="I114" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J114" t="str">
-        <v>—</v>
-      </c>
-      <c r="K114" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -18892,12 +17308,6 @@
       <c r="I115" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J115" t="str">
-        <v>—</v>
-      </c>
-      <c r="K115" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -18927,12 +17337,6 @@
       <c r="I116" t="str">
         <v>✅ 一致</v>
       </c>
-      <c r="J116" t="str">
-        <v>—</v>
-      </c>
-      <c r="K116" t="str">
-        <v>—</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -18952,12 +17356,6 @@
       </c>
       <c r="I117" t="str">
         <v>✅ 一致</v>
-      </c>
-      <c r="J117" t="str">
-        <v>—</v>
-      </c>
-      <c r="K117" t="str">
-        <v>—</v>
       </c>
     </row>
   </sheetData>
@@ -19039,7 +17437,7 @@
     <mergeCell ref="D116:D117"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K117"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I117"/>
   </ignoredErrors>
 </worksheet>
 </file>